--- a/Data/National Accounts/PSA-03DEQ_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-03DEQ_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E4C44D-6F22-4B48-975F-BFE0007539CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DD0AE7-E191-47DD-92BC-2761FD9611B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEQ" sheetId="3" r:id="rId1"/>
@@ -270,13 +270,13 @@
     <t>2024 - 2025</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
     <t>Q1 2001 to Q4 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -441,12 +441,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -455,6 +449,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -466,14 +466,7 @@
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{008F8423-7867-4CB4-A558-4D234F15232D}"/>
     <cellStyle name="Normal 3" xfId="6" xr:uid="{8C6D19FF-306C-41BE-9C1F-A9A8F7C52269}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -834,7 +827,7 @@
     </row>
     <row r="3" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.2">
@@ -844,7 +837,7 @@
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.2">
@@ -854,132 +847,132 @@
     </row>
     <row r="9" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="41">
+      <c r="B9" s="45">
         <v>2000</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41">
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45">
         <v>2001</v>
       </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41">
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45">
         <v>2002</v>
       </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41">
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45">
         <v>2003</v>
       </c>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41">
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45">
         <v>2004</v>
       </c>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41">
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="45">
         <v>2005</v>
       </c>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41">
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45">
         <v>2006</v>
       </c>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="41">
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45">
         <v>2007</v>
       </c>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="41"/>
-      <c r="AH9" s="41">
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45">
         <v>2008</v>
       </c>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41">
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45">
         <v>2009</v>
       </c>
-      <c r="AM9" s="41"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="41">
+      <c r="AM9" s="45"/>
+      <c r="AN9" s="45"/>
+      <c r="AO9" s="45"/>
+      <c r="AP9" s="45">
         <v>2010</v>
       </c>
-      <c r="AQ9" s="41"/>
-      <c r="AR9" s="41"/>
-      <c r="AS9" s="41"/>
-      <c r="AT9" s="41">
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="45"/>
+      <c r="AS9" s="45"/>
+      <c r="AT9" s="45">
         <v>2011</v>
       </c>
-      <c r="AU9" s="41"/>
-      <c r="AV9" s="41"/>
-      <c r="AW9" s="41"/>
-      <c r="AX9" s="41">
+      <c r="AU9" s="45"/>
+      <c r="AV9" s="45"/>
+      <c r="AW9" s="45"/>
+      <c r="AX9" s="45">
         <v>2012</v>
       </c>
-      <c r="AY9" s="41"/>
-      <c r="AZ9" s="41"/>
-      <c r="BA9" s="41"/>
-      <c r="BB9" s="41">
+      <c r="AY9" s="45"/>
+      <c r="AZ9" s="45"/>
+      <c r="BA9" s="45"/>
+      <c r="BB9" s="45">
         <v>2013</v>
       </c>
-      <c r="BC9" s="41"/>
-      <c r="BD9" s="41"/>
-      <c r="BE9" s="41"/>
-      <c r="BF9" s="41">
+      <c r="BC9" s="45"/>
+      <c r="BD9" s="45"/>
+      <c r="BE9" s="45"/>
+      <c r="BF9" s="45">
         <v>2014</v>
       </c>
-      <c r="BG9" s="41"/>
-      <c r="BH9" s="41"/>
-      <c r="BI9" s="41"/>
-      <c r="BJ9" s="41">
+      <c r="BG9" s="45"/>
+      <c r="BH9" s="45"/>
+      <c r="BI9" s="45"/>
+      <c r="BJ9" s="45">
         <v>2015</v>
       </c>
-      <c r="BK9" s="41"/>
-      <c r="BL9" s="41"/>
-      <c r="BM9" s="41"/>
-      <c r="BN9" s="41">
+      <c r="BK9" s="45"/>
+      <c r="BL9" s="45"/>
+      <c r="BM9" s="45"/>
+      <c r="BN9" s="45">
         <v>2016</v>
       </c>
-      <c r="BO9" s="41"/>
-      <c r="BP9" s="41"/>
-      <c r="BQ9" s="41"/>
-      <c r="BR9" s="41">
+      <c r="BO9" s="45"/>
+      <c r="BP9" s="45"/>
+      <c r="BQ9" s="45"/>
+      <c r="BR9" s="45">
         <v>2017</v>
       </c>
-      <c r="BS9" s="41"/>
-      <c r="BT9" s="41"/>
-      <c r="BU9" s="41"/>
-      <c r="BV9" s="41">
+      <c r="BS9" s="45"/>
+      <c r="BT9" s="45"/>
+      <c r="BU9" s="45"/>
+      <c r="BV9" s="45">
         <v>2018</v>
       </c>
-      <c r="BW9" s="41"/>
-      <c r="BX9" s="41"/>
-      <c r="BY9" s="41"/>
-      <c r="BZ9" s="41">
+      <c r="BW9" s="45"/>
+      <c r="BX9" s="45"/>
+      <c r="BY9" s="45"/>
+      <c r="BZ9" s="45">
         <v>2019</v>
       </c>
-      <c r="CA9" s="41"/>
-      <c r="CB9" s="41"/>
-      <c r="CC9" s="41"/>
-      <c r="CD9" s="41">
+      <c r="CA9" s="45"/>
+      <c r="CB9" s="45"/>
+      <c r="CC9" s="45"/>
+      <c r="CD9" s="45">
         <v>2020</v>
       </c>
-      <c r="CE9" s="41"/>
-      <c r="CF9" s="41"/>
-      <c r="CG9" s="41"/>
+      <c r="CE9" s="45"/>
+      <c r="CF9" s="45"/>
+      <c r="CG9" s="45"/>
       <c r="CH9" s="26">
         <v>2021</v>
       </c>
@@ -1624,28 +1617,28 @@
         <v>56544.779725205124</v>
       </c>
       <c r="CT12" s="29">
-        <v>58029.821449489667</v>
+        <v>58049.005790302566</v>
       </c>
       <c r="CU12" s="29">
-        <v>53435.473488046759</v>
+        <v>53440.937971683328</v>
       </c>
       <c r="CV12" s="29">
-        <v>42464.715503666666</v>
+        <v>42452.253441930341</v>
       </c>
       <c r="CW12" s="29">
-        <v>62024.546587876568</v>
+        <v>62464.989238267895</v>
       </c>
       <c r="CX12" s="29">
-        <v>70558.174267277282</v>
+        <v>70424.78232489989</v>
       </c>
       <c r="CY12" s="29">
-        <v>58623.731089966757</v>
+        <v>59110.162465432157</v>
       </c>
       <c r="CZ12" s="29">
-        <v>45407.323865792918</v>
+        <v>45793.083665890699</v>
       </c>
       <c r="DA12" s="29">
-        <v>56070.712074131159</v>
+        <v>57081.223119989634</v>
       </c>
       <c r="DB12" s="9"/>
       <c r="DC12" s="9"/>
@@ -1988,28 +1981,28 @@
         <v>4857.2091199101742</v>
       </c>
       <c r="CT13" s="30">
-        <v>3733.9896943082736</v>
+        <v>3733.9896941721013</v>
       </c>
       <c r="CU13" s="30">
-        <v>3722.6681072217789</v>
+        <v>3722.1394763878429</v>
       </c>
       <c r="CV13" s="30">
-        <v>3191.1799049429842</v>
+        <v>3191.0888096922695</v>
       </c>
       <c r="CW13" s="30">
-        <v>3557.8903701265394</v>
+        <v>3564.6278885363595</v>
       </c>
       <c r="CX13" s="30">
-        <v>5891.8534750224071</v>
+        <v>5896.7394849249977</v>
       </c>
       <c r="CY13" s="30">
-        <v>4895.2311351055541</v>
+        <v>4895.3971928936207</v>
       </c>
       <c r="CZ13" s="30">
-        <v>3590.7695906323429</v>
+        <v>3598.1683873852271</v>
       </c>
       <c r="DA13" s="30">
-        <v>3391.8995893488923</v>
+        <v>3474.2554059409449</v>
       </c>
       <c r="DB13" s="9"/>
       <c r="DC13" s="9"/>
@@ -2352,28 +2345,28 @@
         <v>8755.0239397229398</v>
       </c>
       <c r="CT14" s="30">
-        <v>8893.4074400569334</v>
+        <v>8911.3905472873557</v>
       </c>
       <c r="CU14" s="30">
-        <v>12294.288123809083</v>
+        <v>12319.255176090144</v>
       </c>
       <c r="CV14" s="30">
         <v>9038.3904989706243</v>
       </c>
       <c r="CW14" s="30">
-        <v>11100.764852463642</v>
+        <v>11144.734856138282</v>
       </c>
       <c r="CX14" s="30">
-        <v>10757.071103502012</v>
+        <v>10768.580076542281</v>
       </c>
       <c r="CY14" s="30">
-        <v>12396.198323386661</v>
+        <v>12409.826784337911</v>
       </c>
       <c r="CZ14" s="30">
-        <v>8152.2974854453059</v>
+        <v>8194.0291958510388</v>
       </c>
       <c r="DA14" s="30">
-        <v>11307.132833706328</v>
+        <v>11614.15543271483</v>
       </c>
       <c r="DB14" s="9"/>
       <c r="DC14" s="9"/>
@@ -2716,28 +2709,28 @@
         <v>1083.7667151899973</v>
       </c>
       <c r="CT15" s="30">
-        <v>542.44328475173847</v>
+        <v>542.443284740433</v>
       </c>
       <c r="CU15" s="30">
-        <v>857.09554723924066</v>
+        <v>857.09554723924089</v>
       </c>
       <c r="CV15" s="30">
         <v>839.30891889837199</v>
       </c>
       <c r="CW15" s="30">
-        <v>1248.0166913013697</v>
+        <v>1293.8745302513098</v>
       </c>
       <c r="CX15" s="30">
-        <v>809.87853600496396</v>
+        <v>823.51032233060937</v>
       </c>
       <c r="CY15" s="30">
-        <v>1413.2402650947524</v>
+        <v>1412.939139569625</v>
       </c>
       <c r="CZ15" s="30">
-        <v>763.11368547087409</v>
+        <v>817.9616276975712</v>
       </c>
       <c r="DA15" s="30">
-        <v>1486.632860498539</v>
+        <v>1520.1872451638005</v>
       </c>
       <c r="DB15" s="9"/>
       <c r="DC15" s="9"/>
@@ -3080,28 +3073,28 @@
         <v>554.58749689413605</v>
       </c>
       <c r="CT16" s="30">
-        <v>842.18138199540908</v>
+        <v>842.18138196287225</v>
       </c>
       <c r="CU16" s="30">
-        <v>780.75605351935076</v>
+        <v>781.43742379790797</v>
       </c>
       <c r="CV16" s="30">
-        <v>683.65029957453805</v>
+        <v>683.7342339283166</v>
       </c>
       <c r="CW16" s="30">
-        <v>781.93643755238907</v>
+        <v>794.98079638972342</v>
       </c>
       <c r="CX16" s="30">
-        <v>907.59554004524887</v>
+        <v>907.88762466204025</v>
       </c>
       <c r="CY16" s="30">
-        <v>1036.9581615200432</v>
+        <v>1037.0333297631603</v>
       </c>
       <c r="CZ16" s="30">
-        <v>672.29524982253929</v>
+        <v>679.6518715490256</v>
       </c>
       <c r="DA16" s="30">
-        <v>707.38856787539578</v>
+        <v>718.58424833780975</v>
       </c>
       <c r="DB16" s="9"/>
       <c r="DC16" s="9"/>
@@ -3444,28 +3437,28 @@
         <v>2902.5505163276421</v>
       </c>
       <c r="CT17" s="30">
-        <v>2493.3260484663138</v>
+        <v>2493.3260483687623</v>
       </c>
       <c r="CU17" s="30">
-        <v>2523.2901883012782</v>
+        <v>2523.2901883012778</v>
       </c>
       <c r="CV17" s="30">
         <v>2798.7658897177785</v>
       </c>
       <c r="CW17" s="30">
-        <v>2732.0393672032847</v>
+        <v>2764.6848542593038</v>
       </c>
       <c r="CX17" s="30">
-        <v>3620.5917793586473</v>
+        <v>3627.5468981291042</v>
       </c>
       <c r="CY17" s="30">
-        <v>3271.9651952183021</v>
+        <v>3274.671784682595</v>
       </c>
       <c r="CZ17" s="30">
-        <v>3384.0901362688655</v>
+        <v>3376.3916605129466</v>
       </c>
       <c r="DA17" s="30">
-        <v>2652.9279056460746</v>
+        <v>2742.2980133333554</v>
       </c>
       <c r="DB17" s="9"/>
       <c r="DC17" s="9"/>
@@ -3808,28 +3801,28 @@
         <v>28066.626880688695</v>
       </c>
       <c r="CT18" s="30">
-        <v>32462.033647573473</v>
+        <v>32463.234881659897</v>
       </c>
       <c r="CU18" s="30">
-        <v>25280.244950273111</v>
+        <v>25262.364341391814</v>
       </c>
       <c r="CV18" s="30">
-        <v>16541.894331969947</v>
+        <v>16531.953510954405</v>
       </c>
       <c r="CW18" s="30">
-        <v>29728.154466901418</v>
+        <v>29714.797626452411</v>
       </c>
       <c r="CX18" s="30">
-        <v>35707.936445939442</v>
+        <v>35553.102926642343</v>
       </c>
       <c r="CY18" s="30">
-        <v>26128.489262519251</v>
+        <v>26305.237263315365</v>
       </c>
       <c r="CZ18" s="30">
-        <v>16595.703562261733</v>
+        <v>16590.619880211791</v>
       </c>
       <c r="DA18" s="30">
-        <v>24816.36874155244</v>
+        <v>24882.403139781571</v>
       </c>
       <c r="DB18" s="9"/>
       <c r="DC18" s="9"/>
@@ -4172,28 +4165,28 @@
         <v>1045.3296678720405</v>
       </c>
       <c r="CT19" s="30">
-        <v>919.46664078367519</v>
+        <v>919.46664075136346</v>
       </c>
       <c r="CU19" s="30">
         <v>1387.9349120094303</v>
       </c>
       <c r="CV19" s="30">
-        <v>758.27625342501221</v>
+        <v>758.18680275675297</v>
       </c>
       <c r="CW19" s="30">
-        <v>1996.3428454831649</v>
+        <v>2003.9908843853666</v>
       </c>
       <c r="CX19" s="30">
-        <v>1380.176796064037</v>
+        <v>1380.4169727623355</v>
       </c>
       <c r="CY19" s="30">
-        <v>2018.8323086660901</v>
+        <v>2020.6555163900566</v>
       </c>
       <c r="CZ19" s="30">
-        <v>1134.7129486434612</v>
+        <v>1141.9349938212163</v>
       </c>
       <c r="DA19" s="30">
-        <v>1669.4136487044705</v>
+        <v>1685.725358115104</v>
       </c>
       <c r="DB19" s="9"/>
       <c r="DC19" s="9"/>
@@ -4536,28 +4529,28 @@
         <v>9279.6853885994969</v>
       </c>
       <c r="CT20" s="30">
-        <v>8142.9733115538438</v>
+        <v>8142.973311359774</v>
       </c>
       <c r="CU20" s="30">
-        <v>6589.1956056734944</v>
+        <v>6587.4209064656707</v>
       </c>
       <c r="CV20" s="30">
-        <v>8613.2494061674115</v>
+        <v>8610.8247770118141</v>
       </c>
       <c r="CW20" s="30">
-        <v>10879.401556844758</v>
+        <v>11183.29780185514</v>
       </c>
       <c r="CX20" s="30">
-        <v>11483.070591340525</v>
+        <v>11466.99801890617</v>
       </c>
       <c r="CY20" s="30">
-        <v>7462.8164384561023</v>
+        <v>7754.4014544798292</v>
       </c>
       <c r="CZ20" s="30">
-        <v>11114.341207247795</v>
+        <v>11394.326048861885</v>
       </c>
       <c r="DA20" s="30">
-        <v>10038.947926799023</v>
+        <v>10443.614276602226</v>
       </c>
       <c r="DB20" s="9"/>
       <c r="DC20" s="9"/>
@@ -4900,28 +4893,28 @@
         <v>65035.33789007867</v>
       </c>
       <c r="CT21" s="29">
-        <v>68073.432571034122</v>
+        <v>68083.39495242227</v>
       </c>
       <c r="CU21" s="29">
-        <v>68989.701348243325</v>
+        <v>69134.086797052485</v>
       </c>
       <c r="CV21" s="29">
-        <v>57970.687087213722</v>
+        <v>57937.870600289709</v>
       </c>
       <c r="CW21" s="29">
-        <v>68488.952942704695</v>
+        <v>68425.233306382986</v>
       </c>
       <c r="CX21" s="29">
-        <v>68579.520305234721</v>
+        <v>69058.052854228168</v>
       </c>
       <c r="CY21" s="29">
-        <v>63506.619531940596</v>
+        <v>63902.963558962438</v>
       </c>
       <c r="CZ21" s="29">
-        <v>68585.526876661912</v>
+        <v>68539.581745968113</v>
       </c>
       <c r="DA21" s="29">
-        <v>74995.075033693545</v>
+        <v>76157.402638788422</v>
       </c>
       <c r="DB21" s="9"/>
       <c r="DC21" s="9"/>
@@ -5264,28 +5257,28 @@
         <v>12858.74663508535</v>
       </c>
       <c r="CT22" s="30">
-        <v>11952.144333330501</v>
+        <v>11953.437482204819</v>
       </c>
       <c r="CU22" s="30">
-        <v>13384.542201674805</v>
+        <v>13381.907557390776</v>
       </c>
       <c r="CV22" s="30">
-        <v>10892.264860194824</v>
+        <v>10890.879880200115</v>
       </c>
       <c r="CW22" s="30">
-        <v>14843.822370495709</v>
+        <v>14846.258729873674</v>
       </c>
       <c r="CX22" s="30">
-        <v>13570.080506438848</v>
+        <v>13579.149095252953</v>
       </c>
       <c r="CY22" s="30">
-        <v>13068.782620425669</v>
+        <v>13070.860668354318</v>
       </c>
       <c r="CZ22" s="30">
-        <v>8767.8170510181299</v>
+        <v>8767.9930672227565</v>
       </c>
       <c r="DA22" s="30">
-        <v>12491.68532209743</v>
+        <v>12758.064668105701</v>
       </c>
       <c r="DB22" s="9"/>
       <c r="DC22" s="9"/>
@@ -5628,28 +5621,28 @@
         <v>7068.7299972728142</v>
       </c>
       <c r="CT23" s="30">
-        <v>6679.2874950578289</v>
+        <v>6680.316132725141</v>
       </c>
       <c r="CU23" s="30">
-        <v>7438.1395803251053</v>
+        <v>7430.5333210265071</v>
       </c>
       <c r="CV23" s="30">
-        <v>7037.8245872726229</v>
+        <v>7042.1770112976219</v>
       </c>
       <c r="CW23" s="30">
-        <v>7872.5422141549334</v>
+        <v>7852.7295733254059</v>
       </c>
       <c r="CX23" s="30">
-        <v>8050.7398145465659</v>
+        <v>8064.3985661492952</v>
       </c>
       <c r="CY23" s="30">
-        <v>7901.1343706197822</v>
+        <v>7909.1063546295045</v>
       </c>
       <c r="CZ23" s="30">
-        <v>6833.9872664616723</v>
+        <v>6836.7530636653682</v>
       </c>
       <c r="DA23" s="30">
-        <v>8555.7586261891265</v>
+        <v>8760.7955594391788</v>
       </c>
       <c r="DB23" s="9"/>
       <c r="DC23" s="9"/>
@@ -5992,28 +5985,28 @@
         <v>23869.110796515517</v>
       </c>
       <c r="CT24" s="30">
-        <v>26133.70314868851</v>
+        <v>26134.053921299223</v>
       </c>
       <c r="CU24" s="30">
-        <v>26938.150363074692</v>
+        <v>27046.85847767106</v>
       </c>
       <c r="CV24" s="30">
-        <v>21376.44952211378</v>
+        <v>21337.549143043718</v>
       </c>
       <c r="CW24" s="30">
-        <v>20599.758768111846</v>
+        <v>20550.918082383432</v>
       </c>
       <c r="CX24" s="30">
-        <v>18063.921034013765</v>
+        <v>18357.064259609651</v>
       </c>
       <c r="CY24" s="30">
-        <v>21325.222509351912</v>
+        <v>21588.096968003705</v>
       </c>
       <c r="CZ24" s="30">
-        <v>31886.072401716599</v>
+        <v>31837.825995757092</v>
       </c>
       <c r="DA24" s="30">
-        <v>25310.809530005761</v>
+        <v>25260.186450065692</v>
       </c>
       <c r="DB24" s="9"/>
       <c r="DC24" s="9"/>
@@ -6356,28 +6349,28 @@
         <v>21238.750461204989</v>
       </c>
       <c r="CT25" s="30">
-        <v>23308.297593957275</v>
+        <v>23315.587416193077</v>
       </c>
       <c r="CU25" s="30">
-        <v>21228.869203168728</v>
+        <v>21274.787440964137</v>
       </c>
       <c r="CV25" s="30">
-        <v>18664.148117632492</v>
+        <v>18667.264565748254</v>
       </c>
       <c r="CW25" s="30">
-        <v>25172.829589942205</v>
+        <v>25175.326920800475</v>
       </c>
       <c r="CX25" s="30">
-        <v>28894.778950235544</v>
+        <v>29057.440933216269</v>
       </c>
       <c r="CY25" s="30">
-        <v>21211.48003154324</v>
+        <v>21334.899567974906</v>
       </c>
       <c r="CZ25" s="30">
-        <v>21097.650157465516</v>
+        <v>21097.009619322893</v>
       </c>
       <c r="DA25" s="30">
-        <v>28636.821555401228</v>
+        <v>29378.355961177844</v>
       </c>
       <c r="DB25" s="9"/>
       <c r="DC25" s="9"/>
@@ -6720,28 +6713,28 @@
         <v>208001.08709493181</v>
       </c>
       <c r="CT26" s="29">
-        <v>183598.4559540656</v>
+        <v>183778.72136547722</v>
       </c>
       <c r="CU26" s="29">
-        <v>172273.95576534854</v>
+        <v>172462.35464713338</v>
       </c>
       <c r="CV26" s="29">
-        <v>205114.88445233618</v>
+        <v>205178.13309710118</v>
       </c>
       <c r="CW26" s="29">
-        <v>211725.95654095121</v>
+        <v>211935.11331482232</v>
       </c>
       <c r="CX26" s="29">
-        <v>208380.08038148255</v>
+        <v>208576.12993565467</v>
       </c>
       <c r="CY26" s="29">
-        <v>210377.38141189731</v>
+        <v>210571.05190088012</v>
       </c>
       <c r="CZ26" s="29">
-        <v>191371.26664538163</v>
+        <v>192754.70482531891</v>
       </c>
       <c r="DA26" s="29">
-        <v>210101.51649888422</v>
+        <v>210572.16905781714</v>
       </c>
       <c r="DB26" s="9"/>
       <c r="DC26" s="9"/>
@@ -7084,28 +7077,28 @@
         <v>170565.88071203989</v>
       </c>
       <c r="CT27" s="30">
-        <v>161845.66787694581</v>
+        <v>162009.8741835946</v>
       </c>
       <c r="CU27" s="30">
-        <v>162000.87630867169</v>
+        <v>162176.86053104</v>
       </c>
       <c r="CV27" s="30">
-        <v>165572.53739256394</v>
+        <v>165635.78603732894</v>
       </c>
       <c r="CW27" s="30">
-        <v>182706.44375868799</v>
+        <v>182909.78823537967</v>
       </c>
       <c r="CX27" s="30">
-        <v>192390.63615844247</v>
+        <v>192580.12934447842</v>
       </c>
       <c r="CY27" s="30">
-        <v>189928.20408878924</v>
+        <v>190122.3956709078</v>
       </c>
       <c r="CZ27" s="30">
-        <v>173561.67864521212</v>
+        <v>174945.11682514939</v>
       </c>
       <c r="DA27" s="30">
-        <v>178345.29955564981</v>
+        <v>178731.21117082197</v>
       </c>
       <c r="DB27" s="9"/>
       <c r="DC27" s="9"/>
@@ -7448,10 +7441,10 @@
         <v>1198.652595735346</v>
       </c>
       <c r="CT28" s="30">
-        <v>3098.2056876864458</v>
+        <v>3098.2056875968146</v>
       </c>
       <c r="CU28" s="30">
-        <v>1302.4892972366001</v>
+        <v>1302.4892972293794</v>
       </c>
       <c r="CV28" s="30">
         <v>3249.3236452471542</v>
@@ -7460,16 +7453,16 @@
         <v>3749.4413508902271</v>
       </c>
       <c r="CX28" s="30">
-        <v>342.27665236936201</v>
+        <v>342.27665234229983</v>
       </c>
       <c r="CY28" s="30">
-        <v>48.506231028192992</v>
+        <v>48.506231027924109</v>
       </c>
       <c r="CZ28" s="30">
-        <v>402.50723776195753</v>
+        <v>402.50723776195758</v>
       </c>
       <c r="DA28" s="30">
-        <v>174.19804077040121</v>
+        <v>174.76223405781082</v>
       </c>
       <c r="DB28" s="9"/>
       <c r="DC28" s="9"/>
@@ -7812,28 +7805,28 @@
         <v>27158.336015482608</v>
       </c>
       <c r="CT29" s="30">
-        <v>13757.951761906634</v>
+        <v>13757.951761828066</v>
       </c>
       <c r="CU29" s="30">
-        <v>7540.2208581103041</v>
+        <v>7539.8470322519934</v>
       </c>
       <c r="CV29" s="30">
         <v>33870.509299189471</v>
       </c>
       <c r="CW29" s="30">
-        <v>22957.971791476273</v>
+        <v>22957.929406709503</v>
       </c>
       <c r="CX29" s="30">
-        <v>11598.816569465142</v>
+        <v>11598.830275374678</v>
       </c>
       <c r="CY29" s="30">
-        <v>2546.3574101496251</v>
+        <v>2558.4746096249055</v>
       </c>
       <c r="CZ29" s="30">
-        <v>9786.6295670266627</v>
+        <v>9786.6295670266645</v>
       </c>
       <c r="DA29" s="30">
-        <v>30258.796678086313</v>
+        <v>30281.221356471702</v>
       </c>
       <c r="DB29" s="9"/>
       <c r="DC29" s="9"/>
@@ -8176,28 +8169,28 @@
         <v>9078.2177716739479</v>
       </c>
       <c r="CT30" s="30">
-        <v>4896.6306275266898</v>
+        <v>4912.6897324577358</v>
       </c>
       <c r="CU30" s="30">
-        <v>1430.3693013299187</v>
+        <v>1443.1577866119835</v>
       </c>
       <c r="CV30" s="30">
         <v>2422.5141153356149</v>
       </c>
       <c r="CW30" s="30">
-        <v>2312.0996398967095</v>
+        <v>2317.9543218428971</v>
       </c>
       <c r="CX30" s="30">
-        <v>4048.3510012055617</v>
+        <v>4054.8936634592701</v>
       </c>
       <c r="CY30" s="30">
-        <v>17854.313681930267</v>
+        <v>17841.675389319498</v>
       </c>
       <c r="CZ30" s="30">
         <v>7620.4511953809088</v>
       </c>
       <c r="DA30" s="30">
-        <v>1323.2222243777151</v>
+        <v>1384.9742964656382</v>
       </c>
       <c r="DB30" s="9"/>
       <c r="DC30" s="9"/>
@@ -8540,28 +8533,28 @@
         <v>69192.793804194211</v>
       </c>
       <c r="CT31" s="29">
-        <v>71582.67036691973</v>
+        <v>71589.666157069631</v>
       </c>
       <c r="CU31" s="29">
-        <v>67194.675251149572</v>
+        <v>67142.469469425894</v>
       </c>
       <c r="CV31" s="29">
-        <v>58967.948936150322</v>
+        <v>58979.014471155002</v>
       </c>
       <c r="CW31" s="29">
-        <v>74620.587225092881</v>
+        <v>74514.647278517397</v>
       </c>
       <c r="CX31" s="29">
-        <v>83131.985071862451</v>
+        <v>83293.071178498765</v>
       </c>
       <c r="CY31" s="29">
-        <v>73550.846617426025</v>
+        <v>73200.197015659098</v>
       </c>
       <c r="CZ31" s="29">
-        <v>69201.594827858149</v>
+        <v>68545.985153692469</v>
       </c>
       <c r="DA31" s="29">
-        <v>77108.100429274462</v>
+        <v>78551.955605121591</v>
       </c>
       <c r="DB31" s="9"/>
       <c r="DC31" s="9"/>
@@ -8904,28 +8897,28 @@
         <v>7532.1893619104512</v>
       </c>
       <c r="CT32" s="30">
-        <v>4857.3776528322423</v>
+        <v>4858.57596902978</v>
       </c>
       <c r="CU32" s="30">
-        <v>6348.4076284285547</v>
+        <v>6344.2552605212604</v>
       </c>
       <c r="CV32" s="30">
-        <v>5278.5067907721477</v>
+        <v>5264.8142324195214</v>
       </c>
       <c r="CW32" s="30">
-        <v>7515.1567997028533</v>
+        <v>7505.0052896567367</v>
       </c>
       <c r="CX32" s="30">
-        <v>5743.5645272003057</v>
+        <v>5748.80662280656</v>
       </c>
       <c r="CY32" s="30">
-        <v>6717.5514794399423</v>
+        <v>6722.7054170694819</v>
       </c>
       <c r="CZ32" s="30">
-        <v>9218.7728526344472</v>
+        <v>9190.7335410478208</v>
       </c>
       <c r="DA32" s="30">
-        <v>10446.417355855918</v>
+        <v>10645.191730097835</v>
       </c>
       <c r="DB32" s="9"/>
       <c r="DC32" s="9"/>
@@ -9268,28 +9261,28 @@
         <v>12204.305295259688</v>
       </c>
       <c r="CT33" s="30">
-        <v>15175.088469188246</v>
+        <v>15173.148546523968</v>
       </c>
       <c r="CU33" s="30">
-        <v>13144.804364077856</v>
+        <v>13140.5397577943</v>
       </c>
       <c r="CV33" s="30">
-        <v>11326.969124651314</v>
+        <v>11337.116504098922</v>
       </c>
       <c r="CW33" s="30">
-        <v>13877.242911778763</v>
+        <v>13920.879299877624</v>
       </c>
       <c r="CX33" s="30">
-        <v>15120.701022661475</v>
+        <v>15047.467052894728</v>
       </c>
       <c r="CY33" s="30">
-        <v>11155.981158698574</v>
+        <v>11069.068096478008</v>
       </c>
       <c r="CZ33" s="30">
-        <v>9653.4878100572496</v>
+        <v>9626.7644651620576</v>
       </c>
       <c r="DA33" s="30">
-        <v>11394.753236325349</v>
+        <v>11813.930132493941</v>
       </c>
       <c r="DB33" s="9"/>
       <c r="DC33" s="9"/>
@@ -9632,28 +9625,28 @@
         <v>37465.517903545478</v>
       </c>
       <c r="CT34" s="30">
-        <v>34092.318173098749</v>
+        <v>34100.111286516381</v>
       </c>
       <c r="CU34" s="30">
-        <v>31033.469727595137</v>
+        <v>30995.166937362235</v>
       </c>
       <c r="CV34" s="30">
-        <v>32181.16900307178</v>
+        <v>32197.773407489363</v>
       </c>
       <c r="CW34" s="30">
-        <v>39466.072293342855</v>
+        <v>39325.778865586741</v>
       </c>
       <c r="CX34" s="30">
-        <v>41931.762008525708</v>
+        <v>42021.12980338397</v>
       </c>
       <c r="CY34" s="30">
-        <v>37913.574538197492</v>
+        <v>38022.025041977628</v>
       </c>
       <c r="CZ34" s="30">
-        <v>39176.315636961212</v>
+        <v>39192.684326714494</v>
       </c>
       <c r="DA34" s="30">
-        <v>42715.769033122371</v>
+        <v>43452.700015068054</v>
       </c>
       <c r="DB34" s="9"/>
       <c r="DC34" s="9"/>
@@ -9996,28 +9989,28 @@
         <v>11990.781243478588</v>
       </c>
       <c r="CT35" s="30">
-        <v>17457.886071800498</v>
+        <v>17457.8303549995</v>
       </c>
       <c r="CU35" s="30">
-        <v>16667.993531048025</v>
+        <v>16662.507513748093</v>
       </c>
       <c r="CV35" s="30">
-        <v>10181.304017655075</v>
+        <v>10179.310327147201</v>
       </c>
       <c r="CW35" s="30">
-        <v>13762.115220268413</v>
+        <v>13762.983823396296</v>
       </c>
       <c r="CX35" s="30">
-        <v>20335.957513474961</v>
+        <v>20475.667699413505</v>
       </c>
       <c r="CY35" s="30">
-        <v>17763.739441090009</v>
+        <v>17386.398460133976</v>
       </c>
       <c r="CZ35" s="30">
-        <v>11153.018528205235</v>
+        <v>10535.802820768104</v>
       </c>
       <c r="DA35" s="30">
-        <v>12551.160803970819</v>
+        <v>12640.133727461765</v>
       </c>
       <c r="DB35" s="9"/>
       <c r="DC35" s="9"/>
@@ -10513,28 +10506,28 @@
         <v>398773.99851440976</v>
       </c>
       <c r="CT37" s="32">
-        <v>381284.38034150912</v>
+        <v>381500.78826527169</v>
       </c>
       <c r="CU37" s="32">
-        <v>361893.80585278821</v>
+        <v>362179.8488852951</v>
       </c>
       <c r="CV37" s="32">
-        <v>364518.23597936693</v>
+        <v>364547.27161047625</v>
       </c>
       <c r="CW37" s="32">
-        <v>416860.04329662531</v>
+        <v>417339.98313799058</v>
       </c>
       <c r="CX37" s="32">
-        <v>430649.76002585702</v>
+        <v>431352.03629328148</v>
       </c>
       <c r="CY37" s="32">
-        <v>406058.57865123067</v>
+        <v>406784.37494093378</v>
       </c>
       <c r="CZ37" s="32">
-        <v>374565.7122156946</v>
+        <v>375633.35539087019</v>
       </c>
       <c r="DA37" s="32">
-        <v>418275.40403598337</v>
+        <v>422362.75042171683</v>
       </c>
       <c r="DB37" s="9"/>
       <c r="DC37" s="9"/>
@@ -11034,7 +11027,7 @@
     </row>
     <row r="44" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:152" x14ac:dyDescent="0.2">
@@ -11044,7 +11037,7 @@
     </row>
     <row r="47" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:152" x14ac:dyDescent="0.2">
@@ -11054,132 +11047,132 @@
     </row>
     <row r="50" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
-      <c r="B50" s="42">
+      <c r="B50" s="44">
         <v>2000</v>
       </c>
-      <c r="C50" s="42"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42">
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44">
         <v>2001</v>
       </c>
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42">
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44">
         <v>2002</v>
       </c>
-      <c r="K50" s="42"/>
-      <c r="L50" s="42"/>
-      <c r="M50" s="42"/>
-      <c r="N50" s="42">
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44">
         <v>2003</v>
       </c>
-      <c r="O50" s="42"/>
-      <c r="P50" s="42"/>
-      <c r="Q50" s="42"/>
-      <c r="R50" s="42">
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44">
         <v>2004</v>
       </c>
-      <c r="S50" s="42"/>
-      <c r="T50" s="42"/>
-      <c r="U50" s="42"/>
-      <c r="V50" s="42">
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44">
         <v>2005</v>
       </c>
-      <c r="W50" s="42"/>
-      <c r="X50" s="42"/>
-      <c r="Y50" s="42"/>
-      <c r="Z50" s="42">
+      <c r="W50" s="44"/>
+      <c r="X50" s="44"/>
+      <c r="Y50" s="44"/>
+      <c r="Z50" s="44">
         <v>2006</v>
       </c>
-      <c r="AA50" s="42"/>
-      <c r="AB50" s="42"/>
-      <c r="AC50" s="42"/>
-      <c r="AD50" s="42">
+      <c r="AA50" s="44"/>
+      <c r="AB50" s="44"/>
+      <c r="AC50" s="44"/>
+      <c r="AD50" s="44">
         <v>2007</v>
       </c>
-      <c r="AE50" s="42"/>
-      <c r="AF50" s="42"/>
-      <c r="AG50" s="42"/>
-      <c r="AH50" s="42">
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="44"/>
+      <c r="AG50" s="44"/>
+      <c r="AH50" s="44">
         <v>2008</v>
       </c>
-      <c r="AI50" s="42"/>
-      <c r="AJ50" s="42"/>
-      <c r="AK50" s="42"/>
-      <c r="AL50" s="42">
+      <c r="AI50" s="44"/>
+      <c r="AJ50" s="44"/>
+      <c r="AK50" s="44"/>
+      <c r="AL50" s="44">
         <v>2009</v>
       </c>
-      <c r="AM50" s="42"/>
-      <c r="AN50" s="42"/>
-      <c r="AO50" s="42"/>
-      <c r="AP50" s="42">
+      <c r="AM50" s="44"/>
+      <c r="AN50" s="44"/>
+      <c r="AO50" s="44"/>
+      <c r="AP50" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ50" s="42"/>
-      <c r="AR50" s="42"/>
-      <c r="AS50" s="42"/>
-      <c r="AT50" s="42">
+      <c r="AQ50" s="44"/>
+      <c r="AR50" s="44"/>
+      <c r="AS50" s="44"/>
+      <c r="AT50" s="44">
         <v>2011</v>
       </c>
-      <c r="AU50" s="42"/>
-      <c r="AV50" s="42"/>
-      <c r="AW50" s="42"/>
-      <c r="AX50" s="42">
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="44">
         <v>2012</v>
       </c>
-      <c r="AY50" s="42"/>
-      <c r="AZ50" s="42"/>
-      <c r="BA50" s="42"/>
-      <c r="BB50" s="42">
+      <c r="AY50" s="44"/>
+      <c r="AZ50" s="44"/>
+      <c r="BA50" s="44"/>
+      <c r="BB50" s="44">
         <v>2013</v>
       </c>
-      <c r="BC50" s="42"/>
-      <c r="BD50" s="42"/>
-      <c r="BE50" s="42"/>
-      <c r="BF50" s="42">
+      <c r="BC50" s="44"/>
+      <c r="BD50" s="44"/>
+      <c r="BE50" s="44"/>
+      <c r="BF50" s="44">
         <v>2014</v>
       </c>
-      <c r="BG50" s="42"/>
-      <c r="BH50" s="42"/>
-      <c r="BI50" s="42"/>
-      <c r="BJ50" s="42">
+      <c r="BG50" s="44"/>
+      <c r="BH50" s="44"/>
+      <c r="BI50" s="44"/>
+      <c r="BJ50" s="44">
         <v>2015</v>
       </c>
-      <c r="BK50" s="42"/>
-      <c r="BL50" s="42"/>
-      <c r="BM50" s="42"/>
-      <c r="BN50" s="42">
+      <c r="BK50" s="44"/>
+      <c r="BL50" s="44"/>
+      <c r="BM50" s="44"/>
+      <c r="BN50" s="44">
         <v>2016</v>
       </c>
-      <c r="BO50" s="42"/>
-      <c r="BP50" s="42"/>
-      <c r="BQ50" s="42"/>
-      <c r="BR50" s="42">
+      <c r="BO50" s="44"/>
+      <c r="BP50" s="44"/>
+      <c r="BQ50" s="44"/>
+      <c r="BR50" s="44">
         <v>2017</v>
       </c>
-      <c r="BS50" s="42"/>
-      <c r="BT50" s="42"/>
-      <c r="BU50" s="42"/>
-      <c r="BV50" s="42">
+      <c r="BS50" s="44"/>
+      <c r="BT50" s="44"/>
+      <c r="BU50" s="44"/>
+      <c r="BV50" s="44">
         <v>2018</v>
       </c>
-      <c r="BW50" s="42"/>
-      <c r="BX50" s="42"/>
-      <c r="BY50" s="42"/>
-      <c r="BZ50" s="42">
+      <c r="BW50" s="44"/>
+      <c r="BX50" s="44"/>
+      <c r="BY50" s="44"/>
+      <c r="BZ50" s="44">
         <v>2019</v>
       </c>
-      <c r="CA50" s="42"/>
-      <c r="CB50" s="42"/>
-      <c r="CC50" s="42"/>
-      <c r="CD50" s="41">
+      <c r="CA50" s="44"/>
+      <c r="CB50" s="44"/>
+      <c r="CC50" s="44"/>
+      <c r="CD50" s="45">
         <v>2020</v>
       </c>
-      <c r="CE50" s="41"/>
-      <c r="CF50" s="41"/>
-      <c r="CG50" s="41"/>
+      <c r="CE50" s="45"/>
+      <c r="CF50" s="45"/>
+      <c r="CG50" s="45"/>
       <c r="CH50" s="26">
         <v>2021</v>
       </c>
@@ -11824,28 +11817,28 @@
         <v>57728.765783469571</v>
       </c>
       <c r="CT53" s="29">
-        <v>48037.05807411328</v>
+        <v>48052.034528874108</v>
       </c>
       <c r="CU53" s="29">
-        <v>32595.146973219784</v>
+        <v>32592.530453646483</v>
       </c>
       <c r="CV53" s="29">
-        <v>41310.86796502403</v>
+        <v>41299.175762411105</v>
       </c>
       <c r="CW53" s="29">
-        <v>60653.356869799623</v>
+        <v>61112.320740761876</v>
       </c>
       <c r="CX53" s="29">
-        <v>56700.410601159121</v>
+        <v>56548.377464715129</v>
       </c>
       <c r="CY53" s="29">
-        <v>34388.405371942317</v>
+        <v>34457.67076257593</v>
       </c>
       <c r="CZ53" s="29">
-        <v>43968.007811422794</v>
+        <v>44424.709538747382</v>
       </c>
       <c r="DA53" s="29">
-        <v>54445.28763259056</v>
+        <v>55485.425004640681</v>
       </c>
       <c r="DB53" s="9"/>
       <c r="DC53" s="9"/>
@@ -12188,28 +12181,28 @@
         <v>5814.1615397180176</v>
       </c>
       <c r="CT54" s="30">
-        <v>3014.79477610719</v>
+        <v>3014.7947759976946</v>
       </c>
       <c r="CU54" s="30">
-        <v>998.35786607270268</v>
+        <v>998.21787573493987</v>
       </c>
       <c r="CV54" s="30">
-        <v>3074.6292661069892</v>
+        <v>3074.5417285398848</v>
       </c>
       <c r="CW54" s="30">
-        <v>4018.0968774796488</v>
+        <v>4025.0398142706499</v>
       </c>
       <c r="CX54" s="30">
-        <v>4521.5480414993272</v>
+        <v>4525.1362146639376</v>
       </c>
       <c r="CY54" s="30">
-        <v>1296.6909448372442</v>
+        <v>1296.7054627853495</v>
       </c>
       <c r="CZ54" s="30">
-        <v>3471.7694930102884</v>
+        <v>3479.7352388320528</v>
       </c>
       <c r="DA54" s="30">
-        <v>3653.9682441850614</v>
+        <v>3742.5695592526358</v>
       </c>
       <c r="DB54" s="9"/>
       <c r="DC54" s="9"/>
@@ -12552,28 +12545,28 @@
         <v>10564.770999125005</v>
       </c>
       <c r="CT55" s="30">
-        <v>7075.5339596075801</v>
+        <v>7089.7070647065229</v>
       </c>
       <c r="CU55" s="30">
-        <v>3394.3164174232866</v>
+        <v>3401.0086906617862</v>
       </c>
       <c r="CV55" s="30">
         <v>8776.2430520431972</v>
       </c>
       <c r="CW55" s="30">
-        <v>12659.121259086265</v>
+        <v>12706.425888217011</v>
       </c>
       <c r="CX55" s="30">
-        <v>8154.1365774332544</v>
+        <v>8161.9830625809336</v>
       </c>
       <c r="CY55" s="30">
-        <v>3399.557225540279</v>
+        <v>3402.9423407781651</v>
       </c>
       <c r="CZ55" s="30">
-        <v>7944.1060436031885</v>
+        <v>7988.5476759040939</v>
       </c>
       <c r="DA55" s="30">
-        <v>12307.820836874051</v>
+        <v>12641.471973945498</v>
       </c>
       <c r="DB55" s="9"/>
       <c r="DC55" s="9"/>
@@ -12916,28 +12909,28 @@
         <v>1203.5365334754647</v>
       </c>
       <c r="CT56" s="30">
-        <v>503.2078142339019</v>
+        <v>503.20781422531013</v>
       </c>
       <c r="CU56" s="30">
-        <v>330.80965707522319</v>
+        <v>330.80965707522324</v>
       </c>
       <c r="CV56" s="30">
         <v>852.43784353068236</v>
       </c>
       <c r="CW56" s="30">
-        <v>1325.0339149849692</v>
+        <v>1372.4983820719387</v>
       </c>
       <c r="CX56" s="30">
-        <v>712.93592724480902</v>
+        <v>721.73734911701922</v>
       </c>
       <c r="CY56" s="30">
-        <v>486.2326567784902</v>
+        <v>485.90548276839115</v>
       </c>
       <c r="CZ56" s="30">
-        <v>766.5379059731448</v>
+        <v>825.61023836910203</v>
       </c>
       <c r="DA56" s="30">
-        <v>1544.7107963883598</v>
+        <v>1579.4531969245238</v>
       </c>
       <c r="DB56" s="9"/>
       <c r="DC56" s="9"/>
@@ -13280,28 +13273,28 @@
         <v>630.19612524825152</v>
       </c>
       <c r="CT57" s="30">
-        <v>558.90895245012564</v>
+        <v>558.90895242936369</v>
       </c>
       <c r="CU57" s="30">
-        <v>228.57633377994429</v>
+        <v>228.75543695697087</v>
       </c>
       <c r="CV57" s="30">
-        <v>658.30225131676718</v>
+        <v>658.38201395940951</v>
       </c>
       <c r="CW57" s="30">
-        <v>847.43502717228228</v>
+        <v>860.92169855718669</v>
       </c>
       <c r="CX57" s="30">
-        <v>579.24846398560146</v>
+        <v>579.19063118044915</v>
       </c>
       <c r="CY57" s="30">
-        <v>296.19481333686929</v>
+        <v>296.16036038651953</v>
       </c>
       <c r="CZ57" s="30">
-        <v>648.12544748204004</v>
+        <v>656.03842067564335</v>
       </c>
       <c r="DA57" s="30">
-        <v>739.40188929536509</v>
+        <v>751.02438727416393</v>
       </c>
       <c r="DB57" s="9"/>
       <c r="DC57" s="9"/>
@@ -13644,28 +13637,28 @@
         <v>3409.0795214123777</v>
       </c>
       <c r="CT58" s="30">
-        <v>1917.3522174104112</v>
+        <v>1917.3522173363572</v>
       </c>
       <c r="CU58" s="30">
-        <v>723.69902417665082</v>
+        <v>723.69902417665071</v>
       </c>
       <c r="CV58" s="30">
         <v>2637.3105431223571</v>
       </c>
       <c r="CW58" s="30">
-        <v>3030.1597011960671</v>
+        <v>3065.0665810908908</v>
       </c>
       <c r="CX58" s="30">
-        <v>2650.2757765662063</v>
+        <v>2654.9877113982702</v>
       </c>
       <c r="CY58" s="30">
-        <v>919.21930414664871</v>
+        <v>919.77583201624009</v>
       </c>
       <c r="CZ58" s="30">
-        <v>3189.2414175598915</v>
+        <v>3185.1838802306065</v>
       </c>
       <c r="DA58" s="30">
-        <v>2818.2849616363897</v>
+        <v>2913.0534341657817</v>
       </c>
       <c r="DB58" s="9"/>
       <c r="DC58" s="9"/>
@@ -14008,28 +14001,28 @@
         <v>24394.929982672395</v>
       </c>
       <c r="CT59" s="30">
-        <v>27489.381504158875</v>
+        <v>27490.184854203522</v>
       </c>
       <c r="CU59" s="30">
-        <v>23925.109547793545</v>
+        <v>23916.234856404524</v>
       </c>
       <c r="CV59" s="30">
-        <v>15746.244062234367</v>
+        <v>15736.943799349585</v>
       </c>
       <c r="CW59" s="30">
-        <v>24787.505401119037</v>
+        <v>24774.215441638429</v>
       </c>
       <c r="CX59" s="30">
-        <v>29957.30236963943</v>
+        <v>29799.527951911448</v>
       </c>
       <c r="CY59" s="30">
-        <v>24501.965753533677</v>
+        <v>24492.227969502601</v>
       </c>
       <c r="CZ59" s="30">
-        <v>15735.320466904672</v>
+        <v>15730.543268241938</v>
       </c>
       <c r="DA59" s="30">
-        <v>21055.325737911859</v>
+        <v>21093.154943835943</v>
       </c>
       <c r="DB59" s="9"/>
       <c r="DC59" s="9"/>
@@ -14372,28 +14365,28 @@
         <v>1281.1559321405966</v>
       </c>
       <c r="CT60" s="30">
-        <v>756.45365228330832</v>
+        <v>756.45365225722583</v>
       </c>
       <c r="CU60" s="30">
         <v>396.01455919410614</v>
       </c>
       <c r="CV60" s="30">
-        <v>749.21499391875034</v>
+        <v>749.12740896435764</v>
       </c>
       <c r="CW60" s="30">
-        <v>2323.7247698150277</v>
+        <v>2331.6216420724722</v>
       </c>
       <c r="CX60" s="30">
-        <v>1079.7097760065233</v>
+        <v>1079.725168656126</v>
       </c>
       <c r="CY60" s="30">
-        <v>563.46887307115196</v>
+        <v>563.90715862365914</v>
       </c>
       <c r="CZ60" s="30">
-        <v>1120.806792644277</v>
+        <v>1128.5812804132149</v>
       </c>
       <c r="DA60" s="30">
-        <v>1857.3236429261622</v>
+        <v>1875.1515277699841</v>
       </c>
       <c r="DB60" s="9"/>
       <c r="DC60" s="9"/>
@@ -14736,28 +14729,28 @@
         <v>10430.935149677465</v>
       </c>
       <c r="CT61" s="30">
-        <v>6721.4251978618913</v>
+        <v>6721.4251977181193</v>
       </c>
       <c r="CU61" s="30">
-        <v>2598.2635677043213</v>
+        <v>2597.7903534422799</v>
       </c>
       <c r="CV61" s="30">
-        <v>8816.4859527509179</v>
+        <v>8814.1893729016301</v>
       </c>
       <c r="CW61" s="30">
-        <v>11662.279918946326</v>
+        <v>11976.53129284329</v>
       </c>
       <c r="CX61" s="30">
-        <v>9045.2536687839784</v>
+        <v>9026.0893752069423</v>
       </c>
       <c r="CY61" s="30">
-        <v>2925.0758006979549</v>
+        <v>3000.046155715007</v>
       </c>
       <c r="CZ61" s="30">
-        <v>11092.100244245299</v>
+        <v>11430.469536080729</v>
       </c>
       <c r="DA61" s="30">
-        <v>10468.451523373318</v>
+        <v>10889.545981472149</v>
       </c>
       <c r="DB61" s="9"/>
       <c r="DC61" s="9"/>
@@ -15100,28 +15093,28 @@
         <v>57992.824554552717</v>
       </c>
       <c r="CT62" s="29">
-        <v>57920.414434156322</v>
+        <v>57928.116979009268</v>
       </c>
       <c r="CU62" s="29">
-        <v>49208.706493700403</v>
+        <v>49298.673431774965</v>
       </c>
       <c r="CV62" s="29">
-        <v>53990.56912453995</v>
+        <v>53961.893408163036</v>
       </c>
       <c r="CW62" s="29">
-        <v>59490.561359232823</v>
+        <v>59455.740942592252</v>
       </c>
       <c r="CX62" s="29">
-        <v>56432.82642967737</v>
+        <v>56823.628505745306</v>
       </c>
       <c r="CY62" s="29">
-        <v>45614.879997066018</v>
+        <v>45951.388466038508</v>
       </c>
       <c r="CZ62" s="29">
-        <v>62699.453541318711</v>
+        <v>62657.969423143382</v>
       </c>
       <c r="DA62" s="29">
-        <v>61171.813604186515</v>
+        <v>62436.137977860148</v>
       </c>
       <c r="DB62" s="9"/>
       <c r="DC62" s="9"/>
@@ -15464,28 +15457,28 @@
         <v>10915.159529451423</v>
       </c>
       <c r="CT63" s="30">
-        <v>9872.0247809769062</v>
+        <v>9873.0474425522934</v>
       </c>
       <c r="CU63" s="30">
-        <v>8869.7432696788801</v>
+        <v>8868.0621263699941</v>
       </c>
       <c r="CV63" s="30">
-        <v>10168.765859021767</v>
+        <v>10167.498091628266</v>
       </c>
       <c r="CW63" s="30">
-        <v>12066.463000084617</v>
+        <v>12070.50943264204</v>
       </c>
       <c r="CX63" s="30">
-        <v>10738.987611302471</v>
+        <v>10746.569028048183</v>
       </c>
       <c r="CY63" s="30">
-        <v>8531.301288936229</v>
+        <v>8532.8771488758302</v>
       </c>
       <c r="CZ63" s="30">
-        <v>8026.500363262302</v>
+        <v>8026.6811766792543</v>
       </c>
       <c r="DA63" s="30">
-        <v>9840.3929286581588</v>
+        <v>10088.116006955095</v>
       </c>
       <c r="DB63" s="9"/>
       <c r="DC63" s="9"/>
@@ -15828,28 +15821,28 @@
         <v>5765.2188321841777</v>
       </c>
       <c r="CT64" s="30">
-        <v>5334.4319540243723</v>
+        <v>5335.2314484413218</v>
       </c>
       <c r="CU64" s="30">
-        <v>4923.743733596636</v>
+        <v>4918.8080670764093</v>
       </c>
       <c r="CV64" s="30">
-        <v>6536.2601496563775</v>
+        <v>6540.2214487612964</v>
       </c>
       <c r="CW64" s="30">
-        <v>6080.5562660015685</v>
+        <v>6066.07951641006</v>
       </c>
       <c r="CX64" s="30">
-        <v>6088.9228888010239</v>
+        <v>6099.2026750603236</v>
       </c>
       <c r="CY64" s="30">
-        <v>5216.1568518563172</v>
+        <v>5221.4139636707887</v>
       </c>
       <c r="CZ64" s="30">
-        <v>6188.3755962201858</v>
+        <v>6190.8447353703114</v>
       </c>
       <c r="DA64" s="30">
-        <v>6307.2438435892082</v>
+        <v>6464.440980921745</v>
       </c>
       <c r="DB64" s="9"/>
       <c r="DC64" s="9"/>
@@ -16192,28 +16185,28 @@
         <v>18838.165229520233</v>
       </c>
       <c r="CT65" s="30">
-        <v>20601.449909078714</v>
+        <v>20601.719393081337</v>
       </c>
       <c r="CU65" s="30">
-        <v>19299.970860464004</v>
+        <v>19366.964229580146</v>
       </c>
       <c r="CV65" s="30">
-        <v>19375.385788645519</v>
+        <v>19341.070193556145</v>
       </c>
       <c r="CW65" s="30">
-        <v>15550.0903345877</v>
+        <v>15509.52214914288</v>
       </c>
       <c r="CX65" s="30">
-        <v>13920.471783303368</v>
+        <v>14167.132461892998</v>
       </c>
       <c r="CY65" s="30">
-        <v>16123.065910201996</v>
+        <v>16371.168748868326</v>
       </c>
       <c r="CZ65" s="30">
-        <v>28648.130045759226</v>
+        <v>28604.587366205371</v>
       </c>
       <c r="DA65" s="30">
-        <v>18072.644213232466</v>
+        <v>18032.731078172961</v>
       </c>
       <c r="DB65" s="9"/>
       <c r="DC65" s="9"/>
@@ -16556,28 +16549,28 @@
         <v>22474.280963396886</v>
       </c>
       <c r="CT66" s="30">
-        <v>22112.507790076324</v>
+        <v>22118.118694934317</v>
       </c>
       <c r="CU66" s="30">
-        <v>16115.24862996089</v>
+        <v>16144.839008748411</v>
       </c>
       <c r="CV66" s="30">
-        <v>17910.157327216286</v>
+        <v>17913.103674217331</v>
       </c>
       <c r="CW66" s="30">
-        <v>25793.451758558935</v>
+        <v>25809.62984439727</v>
       </c>
       <c r="CX66" s="30">
-        <v>25684.444146270511</v>
+        <v>25810.724340743807</v>
       </c>
       <c r="CY66" s="30">
-        <v>15744.355946071471</v>
+        <v>15825.928604623565</v>
       </c>
       <c r="CZ66" s="30">
-        <v>19836.447536077001</v>
+        <v>19835.856144888439</v>
       </c>
       <c r="DA66" s="30">
-        <v>26951.532618706682</v>
+        <v>27850.849911810343</v>
       </c>
       <c r="DB66" s="9"/>
       <c r="DC66" s="9"/>
@@ -16920,28 +16913,28 @@
         <v>181835.73921049997</v>
       </c>
       <c r="CT67" s="29">
-        <v>174540.13625792958</v>
+        <v>174678.31563849829</v>
       </c>
       <c r="CU67" s="29">
-        <v>154124.06825898663</v>
+        <v>154284.32727701656</v>
       </c>
       <c r="CV67" s="29">
-        <v>175664.26808746604</v>
+        <v>175710.65982192519</v>
       </c>
       <c r="CW67" s="29">
-        <v>180350.71838568209</v>
+        <v>180502.05214105369</v>
       </c>
       <c r="CX67" s="29">
-        <v>186438.68769879182</v>
+        <v>186586.76842142185</v>
       </c>
       <c r="CY67" s="29">
-        <v>188052.7838568989</v>
+        <v>188217.17269250588</v>
       </c>
       <c r="CZ67" s="29">
-        <v>167900.4267774967</v>
+        <v>169448.9807643434</v>
       </c>
       <c r="DA67" s="29">
-        <v>176528.66032909093</v>
+        <v>176929.54655802119</v>
       </c>
       <c r="DB67" s="9"/>
       <c r="DC67" s="9"/>
@@ -17284,28 +17277,28 @@
         <v>153714.12201430573</v>
       </c>
       <c r="CT68" s="30">
-        <v>157922.93056550907</v>
+        <v>158050.29629534268</v>
       </c>
       <c r="CU68" s="30">
-        <v>145196.20380902643</v>
+        <v>145345.95916193142</v>
       </c>
       <c r="CV68" s="30">
-        <v>147107.70986761266</v>
+        <v>147154.10160207181</v>
       </c>
       <c r="CW68" s="30">
-        <v>159933.084776228</v>
+        <v>160080.2343269588</v>
       </c>
       <c r="CX68" s="30">
-        <v>175053.69139751018</v>
+        <v>175196.25343212468</v>
       </c>
       <c r="CY68" s="30">
-        <v>170749.54998116096</v>
+        <v>170914.31144864854</v>
       </c>
       <c r="CZ68" s="30">
-        <v>155006.90957447994</v>
+        <v>156555.46356132664</v>
       </c>
       <c r="DA68" s="30">
-        <v>154948.76192025666</v>
+        <v>155291.63228520803</v>
       </c>
       <c r="DB68" s="9"/>
       <c r="DC68" s="9"/>
@@ -17648,10 +17641,10 @@
         <v>866.79407875069307</v>
       </c>
       <c r="CT69" s="30">
-        <v>2665.9003239419367</v>
+        <v>2665.900323864812</v>
       </c>
       <c r="CU69" s="30">
-        <v>1293.0840474016336</v>
+        <v>1293.084047394465</v>
       </c>
       <c r="CV69" s="30">
         <v>2510.7521933730795</v>
@@ -17660,16 +17653,16 @@
         <v>2550.4121154854361</v>
       </c>
       <c r="CX69" s="30">
-        <v>276.10661190038979</v>
+        <v>276.10661187855936</v>
       </c>
       <c r="CY69" s="30">
-        <v>48.088198525407201</v>
+        <v>48.088198525140633</v>
       </c>
       <c r="CZ69" s="30">
-        <v>305.23967946613186</v>
+        <v>305.23967946613192</v>
       </c>
       <c r="DA69" s="30">
-        <v>114.426230397045</v>
+        <v>114.79683451410673</v>
       </c>
       <c r="DB69" s="9"/>
       <c r="DC69" s="9"/>
@@ -18012,28 +18005,28 @@
         <v>20229.81014833376</v>
       </c>
       <c r="CT70" s="30">
-        <v>10189.475999401438</v>
+        <v>10189.475999343525</v>
       </c>
       <c r="CU70" s="30">
-        <v>6423.0717492768235</v>
+        <v>6422.7533157904445</v>
       </c>
       <c r="CV70" s="30">
         <v>24090.728951085177</v>
       </c>
       <c r="CW70" s="30">
-        <v>16096.183745759889</v>
+        <v>16096.154086512201</v>
       </c>
       <c r="CX70" s="30">
-        <v>8064.9325863015338</v>
+        <v>8064.9480981824299</v>
       </c>
       <c r="CY70" s="30">
-        <v>2166.1463551601464</v>
+        <v>2176.4536721081367</v>
       </c>
       <c r="CZ70" s="30">
-        <v>6838.5201509225599</v>
+        <v>6838.5201509225608</v>
       </c>
       <c r="DA70" s="30">
-        <v>20479.392064422791</v>
+        <v>20494.545638734577</v>
       </c>
       <c r="DB70" s="9"/>
       <c r="DC70" s="9"/>
@@ -18376,28 +18369,28 @@
         <v>7025.0129691097982</v>
       </c>
       <c r="CT71" s="30">
-        <v>3761.8293690771297</v>
+        <v>3772.6430199472834</v>
       </c>
       <c r="CU71" s="30">
-        <v>1211.708653281747</v>
+        <v>1222.5307519002465</v>
       </c>
       <c r="CV71" s="30">
         <v>1955.077075395136</v>
       </c>
       <c r="CW71" s="30">
-        <v>1771.0377482087692</v>
+        <v>1775.2516120972448</v>
       </c>
       <c r="CX71" s="30">
-        <v>3043.9571030797515</v>
+        <v>3049.4602792362011</v>
       </c>
       <c r="CY71" s="30">
-        <v>15088.999322052414</v>
+        <v>15078.319373224074</v>
       </c>
       <c r="CZ71" s="30">
         <v>5749.7573726280943</v>
       </c>
       <c r="DA71" s="30">
-        <v>986.080114014424</v>
+        <v>1028.5717995644927</v>
       </c>
       <c r="DB71" s="9"/>
       <c r="DC71" s="9"/>
@@ -18740,28 +18733,28 @@
         <v>42177.659199413305</v>
       </c>
       <c r="CT72" s="29">
-        <v>60220.788266899901</v>
+        <v>60225.785726452727</v>
       </c>
       <c r="CU72" s="29">
-        <v>76133.721109072823</v>
+        <v>76063.517077835917</v>
       </c>
       <c r="CV72" s="29">
-        <v>48389.704217485189</v>
+        <v>48401.156349706966</v>
       </c>
       <c r="CW72" s="29">
-        <v>44019.100463187635</v>
+        <v>43975.540997325399</v>
       </c>
       <c r="CX72" s="29">
-        <v>69256.805175519883</v>
+        <v>69377.365000833641</v>
       </c>
       <c r="CY72" s="29">
-        <v>80749.321461844695</v>
+        <v>80496.455658476916</v>
       </c>
       <c r="CZ72" s="29">
-        <v>49950.292736918535</v>
+        <v>49390.725306318032</v>
       </c>
       <c r="DA72" s="29">
-        <v>43532.790816274101</v>
+        <v>44391.039207315385</v>
       </c>
       <c r="DB72" s="9"/>
       <c r="DC72" s="9"/>
@@ -19104,28 +19097,28 @@
         <v>3545.8016584413149</v>
       </c>
       <c r="CT73" s="30">
-        <v>4123.6813570211834</v>
+        <v>4124.691441774482</v>
       </c>
       <c r="CU73" s="30">
-        <v>9007.4687065246453</v>
+        <v>9001.4718155904429</v>
       </c>
       <c r="CV73" s="30">
-        <v>3731.9975879184267</v>
+        <v>3722.7528776985268</v>
       </c>
       <c r="CW73" s="30">
-        <v>3469.4308373228855</v>
+        <v>3464.9274294351426</v>
       </c>
       <c r="CX73" s="30">
-        <v>5369.4165519681574</v>
+        <v>5374.3180714763212</v>
       </c>
       <c r="CY73" s="30">
-        <v>9632.4952784728848</v>
+        <v>9640.0065336045391</v>
       </c>
       <c r="CZ73" s="30">
-        <v>6296.1097454327773</v>
+        <v>6277.1663338019407</v>
       </c>
       <c r="DA73" s="30">
-        <v>4671.0382519146106</v>
+        <v>4757.3874154863979</v>
       </c>
       <c r="DB73" s="9"/>
       <c r="DC73" s="9"/>
@@ -19468,28 +19461,28 @@
         <v>8200.9558296596224</v>
       </c>
       <c r="CT74" s="30">
-        <v>14437.798501932941</v>
+        <v>14436.130169153781</v>
       </c>
       <c r="CU74" s="30">
-        <v>17865.101152959687</v>
+        <v>17858.743858077803</v>
       </c>
       <c r="CV74" s="30">
-        <v>8940.1536513729916</v>
+        <v>8944.5826243382926</v>
       </c>
       <c r="CW74" s="30">
-        <v>9116.9043491076845</v>
+        <v>9161.8498780089121</v>
       </c>
       <c r="CX74" s="30">
-        <v>15069.421632707592</v>
+        <v>14991.068337698469</v>
       </c>
       <c r="CY74" s="30">
-        <v>14985.612598107522</v>
+        <v>14891.522217254043</v>
       </c>
       <c r="CZ74" s="30">
-        <v>7641.1504239288997</v>
+        <v>7615.5901797382357</v>
       </c>
       <c r="DA74" s="30">
-        <v>7813.0703592440204</v>
+        <v>8175.5864664965393</v>
       </c>
       <c r="DB74" s="9"/>
       <c r="DC74" s="9"/>
@@ -19832,28 +19825,28 @@
         <v>21406.278082322577</v>
       </c>
       <c r="CT75" s="30">
-        <v>26593.957097621787</v>
+        <v>26599.66302896008</v>
       </c>
       <c r="CU75" s="30">
-        <v>35446.931156182414</v>
+        <v>35395.117253490462</v>
       </c>
       <c r="CV75" s="30">
-        <v>27251.773437378855</v>
+        <v>27269.628969383342</v>
       </c>
       <c r="CW75" s="30">
-        <v>21703.249480241808</v>
+        <v>21618.712361036705</v>
       </c>
       <c r="CX75" s="30">
-        <v>31280.408447191698</v>
+        <v>31351.81442482696</v>
       </c>
       <c r="CY75" s="30">
-        <v>41478.082206859923</v>
+        <v>41595.518927970406</v>
       </c>
       <c r="CZ75" s="30">
-        <v>26808.142960974685</v>
+        <v>26820.416990465943</v>
       </c>
       <c r="DA75" s="30">
-        <v>22460.916618922882</v>
+        <v>22821.629356303205</v>
       </c>
       <c r="DB75" s="9"/>
       <c r="DC75" s="9"/>
@@ -20196,28 +20189,28 @@
         <v>9024.6236289897915</v>
       </c>
       <c r="CT76" s="30">
-        <v>15065.351310323991</v>
+        <v>15065.301086564385</v>
       </c>
       <c r="CU76" s="30">
-        <v>13814.220093406075</v>
+        <v>13808.184150677214</v>
       </c>
       <c r="CV76" s="30">
-        <v>8465.7795408149177</v>
+        <v>8464.1918782868015</v>
       </c>
       <c r="CW76" s="30">
-        <v>9729.5157965152539</v>
+        <v>9730.0513288446364</v>
       </c>
       <c r="CX76" s="30">
-        <v>17537.558543652438</v>
+        <v>17660.164166831888</v>
       </c>
       <c r="CY76" s="30">
-        <v>14653.131378404356</v>
+        <v>14369.407979647924</v>
       </c>
       <c r="CZ76" s="30">
-        <v>9204.8896065821737</v>
+        <v>8677.5518023119148</v>
       </c>
       <c r="DA76" s="30">
-        <v>8587.7655861925905</v>
+        <v>8636.4359690292404</v>
       </c>
       <c r="DB76" s="9"/>
       <c r="DC76" s="9"/>
@@ -20713,28 +20706,28 @@
         <v>339734.98874793557</v>
       </c>
       <c r="CT78" s="32">
-        <v>340718.39703309909</v>
+        <v>340884.25287283439</v>
       </c>
       <c r="CU78" s="32">
-        <v>312061.64283497969</v>
+        <v>312239.04824027396</v>
       </c>
       <c r="CV78" s="32">
-        <v>319355.40939451527</v>
+        <v>319372.88534220628</v>
       </c>
       <c r="CW78" s="32">
-        <v>344513.73707790213</v>
+        <v>345045.65482173319</v>
       </c>
       <c r="CX78" s="32">
-        <v>368828.72990514821</v>
+        <v>369336.13939271594</v>
       </c>
       <c r="CY78" s="32">
-        <v>348805.39068775193</v>
+        <v>349122.68757959723</v>
       </c>
       <c r="CZ78" s="32">
-        <v>324518.18086715677</v>
+        <v>325922.38503255218</v>
       </c>
       <c r="DA78" s="32">
-        <v>335678.55238214211</v>
+        <v>339242.14874783735</v>
       </c>
       <c r="DB78" s="9"/>
       <c r="DC78" s="9"/>
@@ -21236,7 +21229,7 @@
     </row>
     <row r="85" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:152" x14ac:dyDescent="0.2">
@@ -21272,7 +21265,7 @@
     </row>
     <row r="88" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="CP88" s="36"/>
       <c r="CQ88" s="36"/>
@@ -21291,145 +21284,145 @@
       <c r="A89" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CX89" s="43"/>
-      <c r="CY89" s="43"/>
-      <c r="CZ89" s="43"/>
-      <c r="DA89" s="43"/>
+      <c r="CX89" s="41"/>
+      <c r="CY89" s="41"/>
+      <c r="CZ89" s="41"/>
+      <c r="DA89" s="41"/>
     </row>
     <row r="90" spans="1:152" x14ac:dyDescent="0.2">
-      <c r="CX90" s="43"/>
-      <c r="CY90" s="43"/>
-      <c r="CZ90" s="43"/>
-      <c r="DA90" s="43"/>
+      <c r="CX90" s="41"/>
+      <c r="CY90" s="41"/>
+      <c r="CZ90" s="41"/>
+      <c r="DA90" s="41"/>
     </row>
     <row r="91" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
-      <c r="B91" s="41" t="s">
+      <c r="B91" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C91" s="42"/>
-      <c r="D91" s="42"/>
-      <c r="E91" s="42"/>
-      <c r="F91" s="41" t="s">
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G91" s="42"/>
-      <c r="H91" s="42"/>
-      <c r="I91" s="42"/>
-      <c r="J91" s="41" t="s">
+      <c r="G91" s="44"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="44"/>
+      <c r="J91" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K91" s="42"/>
-      <c r="L91" s="42"/>
-      <c r="M91" s="42"/>
-      <c r="N91" s="41" t="s">
+      <c r="K91" s="44"/>
+      <c r="L91" s="44"/>
+      <c r="M91" s="44"/>
+      <c r="N91" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="O91" s="42"/>
-      <c r="P91" s="42"/>
-      <c r="Q91" s="42"/>
-      <c r="R91" s="41" t="s">
+      <c r="O91" s="44"/>
+      <c r="P91" s="44"/>
+      <c r="Q91" s="44"/>
+      <c r="R91" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="S91" s="42"/>
-      <c r="T91" s="42"/>
-      <c r="U91" s="42"/>
-      <c r="V91" s="41" t="s">
+      <c r="S91" s="44"/>
+      <c r="T91" s="44"/>
+      <c r="U91" s="44"/>
+      <c r="V91" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="W91" s="42"/>
-      <c r="X91" s="42"/>
-      <c r="Y91" s="42"/>
-      <c r="Z91" s="41" t="s">
+      <c r="W91" s="44"/>
+      <c r="X91" s="44"/>
+      <c r="Y91" s="44"/>
+      <c r="Z91" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="AA91" s="42"/>
-      <c r="AB91" s="42"/>
-      <c r="AC91" s="42"/>
-      <c r="AD91" s="41" t="s">
+      <c r="AA91" s="44"/>
+      <c r="AB91" s="44"/>
+      <c r="AC91" s="44"/>
+      <c r="AD91" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="AE91" s="42"/>
-      <c r="AF91" s="42"/>
-      <c r="AG91" s="42"/>
-      <c r="AH91" s="41" t="s">
+      <c r="AE91" s="44"/>
+      <c r="AF91" s="44"/>
+      <c r="AG91" s="44"/>
+      <c r="AH91" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="AI91" s="42"/>
-      <c r="AJ91" s="42"/>
-      <c r="AK91" s="42"/>
-      <c r="AL91" s="41" t="s">
+      <c r="AI91" s="44"/>
+      <c r="AJ91" s="44"/>
+      <c r="AK91" s="44"/>
+      <c r="AL91" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="AM91" s="42"/>
-      <c r="AN91" s="42"/>
-      <c r="AO91" s="42"/>
-      <c r="AP91" s="41" t="s">
+      <c r="AM91" s="44"/>
+      <c r="AN91" s="44"/>
+      <c r="AO91" s="44"/>
+      <c r="AP91" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="AQ91" s="42"/>
-      <c r="AR91" s="42"/>
-      <c r="AS91" s="42"/>
-      <c r="AT91" s="41" t="s">
+      <c r="AQ91" s="44"/>
+      <c r="AR91" s="44"/>
+      <c r="AS91" s="44"/>
+      <c r="AT91" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="AU91" s="42"/>
-      <c r="AV91" s="42"/>
-      <c r="AW91" s="42"/>
-      <c r="AX91" s="41" t="s">
+      <c r="AU91" s="44"/>
+      <c r="AV91" s="44"/>
+      <c r="AW91" s="44"/>
+      <c r="AX91" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="AY91" s="42"/>
-      <c r="AZ91" s="42"/>
-      <c r="BA91" s="42"/>
-      <c r="BB91" s="41" t="s">
+      <c r="AY91" s="44"/>
+      <c r="AZ91" s="44"/>
+      <c r="BA91" s="44"/>
+      <c r="BB91" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="BC91" s="42"/>
-      <c r="BD91" s="42"/>
-      <c r="BE91" s="42"/>
-      <c r="BF91" s="41" t="s">
+      <c r="BC91" s="44"/>
+      <c r="BD91" s="44"/>
+      <c r="BE91" s="44"/>
+      <c r="BF91" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="BG91" s="42"/>
-      <c r="BH91" s="42"/>
-      <c r="BI91" s="42"/>
-      <c r="BJ91" s="41" t="s">
+      <c r="BG91" s="44"/>
+      <c r="BH91" s="44"/>
+      <c r="BI91" s="44"/>
+      <c r="BJ91" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="BK91" s="42"/>
-      <c r="BL91" s="42"/>
-      <c r="BM91" s="42"/>
-      <c r="BN91" s="41" t="s">
+      <c r="BK91" s="44"/>
+      <c r="BL91" s="44"/>
+      <c r="BM91" s="44"/>
+      <c r="BN91" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="BO91" s="42"/>
-      <c r="BP91" s="42"/>
-      <c r="BQ91" s="42"/>
-      <c r="BR91" s="41" t="s">
+      <c r="BO91" s="44"/>
+      <c r="BP91" s="44"/>
+      <c r="BQ91" s="44"/>
+      <c r="BR91" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="BS91" s="42"/>
-      <c r="BT91" s="42"/>
-      <c r="BU91" s="42"/>
-      <c r="BV91" s="41" t="s">
+      <c r="BS91" s="44"/>
+      <c r="BT91" s="44"/>
+      <c r="BU91" s="44"/>
+      <c r="BV91" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="BW91" s="42"/>
-      <c r="BX91" s="42"/>
-      <c r="BY91" s="42"/>
-      <c r="BZ91" s="41" t="s">
+      <c r="BW91" s="44"/>
+      <c r="BX91" s="44"/>
+      <c r="BY91" s="44"/>
+      <c r="BZ91" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="CA91" s="42"/>
-      <c r="CB91" s="42"/>
-      <c r="CC91" s="42"/>
-      <c r="CD91" s="41" t="s">
+      <c r="CA91" s="44"/>
+      <c r="CB91" s="44"/>
+      <c r="CC91" s="44"/>
+      <c r="CD91" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="CE91" s="41"/>
-      <c r="CF91" s="41"/>
-      <c r="CG91" s="41"/>
+      <c r="CE91" s="45"/>
+      <c r="CF91" s="45"/>
+      <c r="CG91" s="45"/>
       <c r="CH91" s="26" t="s">
         <v>71</v>
       </c>
@@ -21454,10 +21447,10 @@
       <c r="CU91" s="28"/>
       <c r="CV91" s="28"/>
       <c r="CW91" s="28"/>
-      <c r="CX91" s="44"/>
-      <c r="CY91" s="44"/>
-      <c r="CZ91" s="44"/>
-      <c r="DA91" s="44"/>
+      <c r="CX91" s="42"/>
+      <c r="CY91" s="42"/>
+      <c r="CZ91" s="42"/>
+      <c r="DA91" s="42"/>
     </row>
     <row r="92" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
@@ -21763,17 +21756,17 @@
       <c r="CW92" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="CX92" s="45"/>
-      <c r="CY92" s="45"/>
-      <c r="CZ92" s="45"/>
-      <c r="DA92" s="45"/>
+      <c r="CX92" s="43"/>
+      <c r="CY92" s="43"/>
+      <c r="CZ92" s="43"/>
+      <c r="DA92" s="43"/>
     </row>
     <row r="93" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7"/>
-      <c r="CX93" s="43"/>
-      <c r="CY93" s="43"/>
-      <c r="CZ93" s="43"/>
-      <c r="DA93" s="43"/>
+      <c r="CX93" s="41"/>
+      <c r="CY93" s="41"/>
+      <c r="CZ93" s="41"/>
+      <c r="DA93" s="41"/>
     </row>
     <row r="94" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
@@ -22056,28 +22049,28 @@
         <v>0.29548969017395166</v>
       </c>
       <c r="CP94" s="35">
-        <v>-9.5307407381044413</v>
+        <v>-9.5008320970054569</v>
       </c>
       <c r="CQ94" s="35">
-        <v>4.1111438933449875</v>
+        <v>4.1217906342654516</v>
       </c>
       <c r="CR94" s="35">
-        <v>10.269321190255226</v>
+        <v>10.236960604013291</v>
       </c>
       <c r="CS94" s="35">
-        <v>9.6910216810497332</v>
+        <v>10.469948847327132</v>
       </c>
       <c r="CT94" s="35">
-        <v>21.589507782119483</v>
+        <v>21.319532291911841</v>
       </c>
       <c r="CU94" s="35">
-        <v>9.7093882831984075</v>
+        <v>10.608392571164771</v>
       </c>
       <c r="CV94" s="35">
-        <v>6.9295374459112224</v>
+        <v>7.8696181076234808</v>
       </c>
       <c r="CW94" s="35">
-        <v>-9.5991584643186343</v>
+        <v>-8.6188538314515739</v>
       </c>
       <c r="CX94" s="37"/>
       <c r="CY94" s="37"/>
@@ -22407,28 +22400,28 @@
         <v>70.280704139579598</v>
       </c>
       <c r="CP95" s="35">
-        <v>25.482838162700361</v>
+        <v>25.482838158124224</v>
       </c>
       <c r="CQ95" s="35">
-        <v>3.4760052694061869</v>
+        <v>3.461311344140114</v>
       </c>
       <c r="CR95" s="35">
-        <v>-12.800951737631067</v>
+        <v>-12.803440916994248</v>
       </c>
       <c r="CS95" s="35">
-        <v>-26.750315205857618</v>
+        <v>-26.611603483889496</v>
       </c>
       <c r="CT95" s="35">
-        <v>57.789762623163341</v>
+        <v>57.920614888906925</v>
       </c>
       <c r="CU95" s="35">
-        <v>31.497920150578693</v>
+        <v>31.521057283011004</v>
       </c>
       <c r="CV95" s="35">
-        <v>12.521690960463047</v>
+        <v>12.756761154892899</v>
       </c>
       <c r="CW95" s="35">
-        <v>-4.6654270792425621</v>
+        <v>-2.5352571270074833</v>
       </c>
       <c r="CX95" s="37"/>
       <c r="CY95" s="37"/>
@@ -22758,28 +22751,28 @@
         <v>-29.319656409501377</v>
       </c>
       <c r="CP96" s="35">
-        <v>-31.011809527430941</v>
+        <v>-30.872310461941922</v>
       </c>
       <c r="CQ96" s="35">
-        <v>-6.7216519630181466</v>
+        <v>-6.532223720514196</v>
       </c>
       <c r="CR96" s="35">
         <v>8.8471486305958962</v>
       </c>
       <c r="CS96" s="35">
-        <v>26.793083935472765</v>
+        <v>27.295309902841524</v>
       </c>
       <c r="CT96" s="35">
-        <v>20.955563725225531</v>
+        <v>20.840625482633101</v>
       </c>
       <c r="CU96" s="35">
-        <v>0.82892314342477391</v>
+        <v>0.73520360568188892</v>
       </c>
       <c r="CV96" s="35">
-        <v>-9.8036593310084896</v>
+        <v>-9.3419431614041173</v>
       </c>
       <c r="CW96" s="35">
-        <v>1.8590429036688079</v>
+        <v>4.2120389819592816</v>
       </c>
       <c r="CX96" s="37"/>
       <c r="CY96" s="37"/>
@@ -23109,28 +23102,28 @@
         <v>16.50249657133476</v>
       </c>
       <c r="CP97" s="35">
-        <v>-26.429984058861109</v>
+        <v>-26.429984060394446</v>
       </c>
       <c r="CQ97" s="35">
-        <v>-2.2678852635433628</v>
+        <v>-2.2678852635433486</v>
       </c>
       <c r="CR97" s="35">
         <v>22.089126859233559</v>
       </c>
       <c r="CS97" s="35">
-        <v>15.15547338825381</v>
+        <v>19.386811950990591</v>
       </c>
       <c r="CT97" s="35">
-        <v>49.301974744811048</v>
+        <v>51.81500914416722</v>
       </c>
       <c r="CU97" s="35">
-        <v>64.887131854422705</v>
+        <v>64.851998603981968</v>
       </c>
       <c r="CV97" s="35">
-        <v>-9.0783300060134309</v>
+        <v>-2.5434367156279052</v>
       </c>
       <c r="CW97" s="35">
-        <v>19.119629637994024</v>
+        <v>17.491086625573644</v>
       </c>
       <c r="CX97" s="37"/>
       <c r="CY97" s="37"/>
@@ -23460,28 +23453,28 @@
         <v>-9.5563103029400054</v>
       </c>
       <c r="CP98" s="35">
-        <v>81.672089343281527</v>
+        <v>81.672089336262786</v>
       </c>
       <c r="CQ98" s="35">
-        <v>60.012608017786135</v>
+        <v>60.152251937044014</v>
       </c>
       <c r="CR98" s="35">
-        <v>27.870946441779722</v>
+        <v>27.886645645397891</v>
       </c>
       <c r="CS98" s="35">
-        <v>40.994242014376169</v>
+        <v>43.346325123062684</v>
       </c>
       <c r="CT98" s="35">
-        <v>7.7672291798771056</v>
+        <v>7.8019110973489347</v>
       </c>
       <c r="CU98" s="35">
-        <v>32.814616914698377</v>
+        <v>32.708429130897827</v>
       </c>
       <c r="CV98" s="35">
-        <v>-1.6609441638606057</v>
+        <v>-0.59706859430399106</v>
       </c>
       <c r="CW98" s="35">
-        <v>-9.5337505834032186</v>
+        <v>-9.6098608166205111</v>
       </c>
       <c r="CX98" s="37"/>
       <c r="CY98" s="37"/>
@@ -23811,28 +23804,28 @@
         <v>-12.431413079558098</v>
       </c>
       <c r="CP99" s="35">
-        <v>-39.61935340886442</v>
+        <v>-39.619353411226818</v>
       </c>
       <c r="CQ99" s="35">
-        <v>-9.0817751418439912</v>
+        <v>-9.0817751418440196</v>
       </c>
       <c r="CR99" s="35">
         <v>-6.4566755179388622</v>
       </c>
       <c r="CS99" s="35">
-        <v>-5.8745282180339444</v>
+        <v>-4.7498109436099725</v>
       </c>
       <c r="CT99" s="35">
-        <v>45.211324511117738</v>
+        <v>45.490273945615598</v>
       </c>
       <c r="CU99" s="35">
-        <v>29.670586854738445</v>
+        <v>29.777851151046576</v>
       </c>
       <c r="CV99" s="35">
-        <v>20.913655147130214</v>
+        <v>20.638588347716876</v>
       </c>
       <c r="CW99" s="35">
-        <v>-2.8956925916552336</v>
+        <v>-0.80974295827819276</v>
       </c>
       <c r="CX99" s="37"/>
       <c r="CY99" s="37"/>
@@ -24162,28 +24155,28 @@
         <v>9.2257609351648284</v>
       </c>
       <c r="CP100" s="35">
-        <v>-1.7732613848616978</v>
+        <v>-1.7696265754131133</v>
       </c>
       <c r="CQ100" s="35">
-        <v>7.793004567559052</v>
+        <v>7.716763037518362</v>
       </c>
       <c r="CR100" s="35">
-        <v>10.772446975351329</v>
+        <v>10.705878476802326</v>
       </c>
       <c r="CS100" s="35">
-        <v>5.9199404092122592</v>
+        <v>5.8723506489400989</v>
       </c>
       <c r="CT100" s="35">
-        <v>9.9990740987005324</v>
+        <v>9.5180534418277176</v>
       </c>
       <c r="CU100" s="35">
-        <v>3.3553642930068861</v>
+        <v>4.1281683211845177</v>
       </c>
       <c r="CV100" s="35">
-        <v>0.32529061794205916</v>
+        <v>0.35486652692624432</v>
       </c>
       <c r="CW100" s="35">
-        <v>-16.52233653056949</v>
+        <v>-16.262585892117926</v>
       </c>
       <c r="CX100" s="37"/>
       <c r="CY100" s="37"/>
@@ -24513,28 +24506,28 @@
         <v>-15.272461641805776</v>
       </c>
       <c r="CP101" s="35">
-        <v>-22.358534757963284</v>
+        <v>-22.358534760691754</v>
       </c>
       <c r="CQ101" s="35">
         <v>12.874122918946867</v>
       </c>
       <c r="CR101" s="35">
-        <v>-18.70150620829159</v>
+        <v>-18.711096650515373</v>
       </c>
       <c r="CS101" s="35">
-        <v>90.977344931488005</v>
+        <v>91.708983871552789</v>
       </c>
       <c r="CT101" s="35">
-        <v>50.106239296261094</v>
+        <v>50.132360607916752</v>
       </c>
       <c r="CU101" s="35">
-        <v>45.455834506191394</v>
+        <v>45.587195689499822</v>
       </c>
       <c r="CV101" s="35">
-        <v>49.643740459778996</v>
+        <v>50.613937049439812</v>
       </c>
       <c r="CW101" s="35">
-        <v>-16.376405361353122</v>
+        <v>-15.881585527664527</v>
       </c>
       <c r="CX101" s="37"/>
       <c r="CY101" s="37"/>
@@ -24864,28 +24857,28 @@
         <v>-0.7643096254306414</v>
       </c>
       <c r="CP102" s="35">
-        <v>-6.5496987764694978</v>
+        <v>-6.5496987786966798</v>
       </c>
       <c r="CQ102" s="35">
-        <v>15.092968986707135</v>
+        <v>15.061970453181914</v>
       </c>
       <c r="CR102" s="35">
-        <v>33.19525294558369</v>
+        <v>33.157758490419326</v>
       </c>
       <c r="CS102" s="35">
-        <v>17.238905213430854</v>
+        <v>20.513760257371587</v>
       </c>
       <c r="CT102" s="35">
-        <v>41.018153345136312</v>
+        <v>40.820773695883872</v>
       </c>
       <c r="CU102" s="35">
-        <v>13.258383648990389</v>
+        <v>17.715287433185665</v>
       </c>
       <c r="CV102" s="35">
-        <v>29.037726450711006</v>
+        <v>32.325605780309701</v>
       </c>
       <c r="CW102" s="35">
-        <v>-7.7251825447785336</v>
+        <v>-6.6141807037474365</v>
       </c>
       <c r="CX102" s="37"/>
       <c r="CY102" s="37"/>
@@ -25215,28 +25208,28 @@
         <v>2.683085677518136</v>
       </c>
       <c r="CP103" s="35">
-        <v>3.7192754646683426</v>
+        <v>3.7344545285182988</v>
       </c>
       <c r="CQ103" s="35">
-        <v>16.491153734856653</v>
+        <v>16.734952840891395</v>
       </c>
       <c r="CR103" s="35">
-        <v>-4.0949089818353741</v>
+        <v>-4.1491996643075169</v>
       </c>
       <c r="CS103" s="35">
-        <v>5.3103668938619961</v>
+        <v>5.2123899502664983</v>
       </c>
       <c r="CT103" s="35">
-        <v>0.74344382982671675</v>
+        <v>1.4315647780005776</v>
       </c>
       <c r="CU103" s="35">
-        <v>-7.9476816237041845</v>
+        <v>-7.5666338856060094</v>
       </c>
       <c r="CV103" s="35">
-        <v>18.310702050984389</v>
+        <v>18.298413517505765</v>
       </c>
       <c r="CW103" s="35">
-        <v>9.4995204503004089</v>
+        <v>11.300172405380977</v>
       </c>
       <c r="CX103" s="37"/>
       <c r="CY103" s="37"/>
@@ -25566,28 +25559,28 @@
         <v>6.9083218410941072</v>
       </c>
       <c r="CP104" s="35">
-        <v>13.714698361993769</v>
+        <v>13.72700159646611</v>
       </c>
       <c r="CQ104" s="35">
-        <v>24.363090168329563</v>
+        <v>24.338610249650287</v>
       </c>
       <c r="CR104" s="35">
-        <v>28.372667584649491</v>
+        <v>28.3563446638654</v>
       </c>
       <c r="CS104" s="35">
-        <v>15.437552288292537</v>
+        <v>15.456499386692627</v>
       </c>
       <c r="CT104" s="35">
-        <v>13.536785768194477</v>
+        <v>13.600369060936174</v>
       </c>
       <c r="CU104" s="35">
-        <v>-2.3591362072109234</v>
+        <v>-2.3243837823753779</v>
       </c>
       <c r="CV104" s="35">
-        <v>-19.504187939281309</v>
+        <v>-19.49233520458543</v>
       </c>
       <c r="CW104" s="35">
-        <v>-15.845898648541493</v>
+        <v>-14.065456488146097</v>
       </c>
       <c r="CX104" s="37"/>
       <c r="CY104" s="37"/>
@@ -25917,28 +25910,28 @@
         <v>-3.8808300850576245</v>
       </c>
       <c r="CP105" s="35">
-        <v>-5.9549018531162972</v>
+        <v>-5.9404185223041992</v>
       </c>
       <c r="CQ105" s="35">
-        <v>5.7341362480170233</v>
+        <v>5.6260122677756357</v>
       </c>
       <c r="CR105" s="35">
-        <v>25.399684548879463</v>
+        <v>25.477235870738895</v>
       </c>
       <c r="CS105" s="35">
-        <v>11.371380957997232</v>
+        <v>11.091095237122744</v>
       </c>
       <c r="CT105" s="35">
-        <v>20.532913435804474</v>
+        <v>20.718816384211109</v>
       </c>
       <c r="CU105" s="35">
-        <v>6.2246047589556071</v>
+        <v>6.4406283227175436</v>
       </c>
       <c r="CV105" s="35">
-        <v>-2.8963114707288327</v>
+        <v>-2.9170517483825762</v>
       </c>
       <c r="CW105" s="35">
-        <v>8.6784725117861115</v>
+        <v>11.56369868126292</v>
       </c>
       <c r="CX105" s="37"/>
       <c r="CY105" s="37"/>
@@ -26268,28 +26261,28 @@
         <v>5.4778208282749432</v>
       </c>
       <c r="CP106" s="35">
-        <v>4.8656823864919829</v>
+        <v>4.8670899179457336</v>
       </c>
       <c r="CQ106" s="35">
-        <v>21.301894198451052</v>
+        <v>21.791404429760661</v>
       </c>
       <c r="CR106" s="35">
-        <v>-26.327752917983602</v>
+        <v>-26.461820005947359</v>
       </c>
       <c r="CS106" s="35">
-        <v>-13.696999675752224</v>
+        <v>-13.901618465889754</v>
       </c>
       <c r="CT106" s="35">
-        <v>-30.878831326588013</v>
+        <v>-29.75806847689762</v>
       </c>
       <c r="CU106" s="35">
-        <v>-20.836352080863975</v>
+        <v>-20.18260832094019</v>
       </c>
       <c r="CV106" s="35">
-        <v>49.164492301355722</v>
+        <v>49.210322995959388</v>
       </c>
       <c r="CW106" s="35">
-        <v>22.869446263548298</v>
+        <v>22.91512402902876</v>
       </c>
       <c r="CX106" s="37"/>
       <c r="CY106" s="37"/>
@@ -26619,28 +26612,28 @@
         <v>-0.4021888639197897</v>
       </c>
       <c r="CP107" s="35">
-        <v>0.90869422923825027</v>
+        <v>0.9402540821195231</v>
       </c>
       <c r="CQ107" s="35">
-        <v>10.461342871101053</v>
+        <v>10.7002717636677</v>
       </c>
       <c r="CR107" s="35">
-        <v>7.6792791998690149</v>
+        <v>7.6972589589586988</v>
       </c>
       <c r="CS107" s="35">
-        <v>18.523119502360856</v>
+        <v>18.534877872340431</v>
       </c>
       <c r="CT107" s="35">
-        <v>23.967779430302855</v>
+        <v>24.62667319732796</v>
       </c>
       <c r="CU107" s="35">
-        <v>-8.1912849238776175E-2</v>
+        <v>0.28255101103864888</v>
       </c>
       <c r="CV107" s="35">
-        <v>13.038377237984051</v>
+        <v>13.016074449562737</v>
       </c>
       <c r="CW107" s="35">
-        <v>13.760836671468439</v>
+        <v>16.69503261506695</v>
       </c>
       <c r="CX107" s="37"/>
       <c r="CY107" s="37"/>
@@ -26970,28 +26963,28 @@
         <v>28.827106236130533</v>
       </c>
       <c r="CP108" s="35">
-        <v>-5.4000857141086982</v>
+        <v>-5.3072031657254115</v>
       </c>
       <c r="CQ108" s="35">
-        <v>-7.0165706922119284</v>
+        <v>-6.9148839687122461</v>
       </c>
       <c r="CR108" s="35">
-        <v>16.002528094537723</v>
+        <v>16.038298305514289</v>
       </c>
       <c r="CS108" s="35">
-        <v>1.7907932588445448</v>
+        <v>1.8913488745830449</v>
       </c>
       <c r="CT108" s="35">
-        <v>13.497730304233627</v>
+        <v>13.493079278129997</v>
       </c>
       <c r="CU108" s="35">
-        <v>22.117925763804251</v>
+        <v>22.096820683980027</v>
       </c>
       <c r="CV108" s="35">
-        <v>-6.7004487966099902</v>
+        <v>-6.0549475152417216</v>
       </c>
       <c r="CW108" s="35">
-        <v>-0.76723707787466822</v>
+        <v>-0.64309506607362721</v>
       </c>
       <c r="CX108" s="37"/>
       <c r="CY108" s="37"/>
@@ -27321,28 +27314,28 @@
         <v>13.181256275929385</v>
       </c>
       <c r="CP109" s="35">
-        <v>-9.3336711873561882</v>
+        <v>-9.2416824230783021</v>
       </c>
       <c r="CQ109" s="35">
-        <v>1.4232072970800544</v>
+        <v>1.5333849990343964</v>
       </c>
       <c r="CR109" s="35">
-        <v>1.3119903916153817</v>
+        <v>1.3506915324665414</v>
       </c>
       <c r="CS109" s="35">
-        <v>7.1178145335787093</v>
+        <v>7.2370320909488157</v>
       </c>
       <c r="CT109" s="35">
-        <v>18.872898287719721</v>
+        <v>18.869377755482162</v>
       </c>
       <c r="CU109" s="35">
-        <v>17.23899797116259</v>
+        <v>17.231518139123892</v>
       </c>
       <c r="CV109" s="35">
-        <v>4.8251608500184489</v>
+        <v>5.6203620066272606</v>
       </c>
       <c r="CW109" s="35">
-        <v>-2.3869679215026594</v>
+        <v>-2.2845016140855421</v>
       </c>
       <c r="CX109" s="37"/>
       <c r="CY109" s="37"/>
@@ -27684,7 +27677,7 @@
         <v>212.80467453457857</v>
       </c>
       <c r="CT110" s="35">
-        <v>-88.952423212903156</v>
+        <v>-88.952423213457024</v>
       </c>
       <c r="CU110" s="35">
         <v>-96.275882563403385</v>
@@ -27693,7 +27686,7 @@
         <v>-87.61258398033965</v>
       </c>
       <c r="CW110" s="35">
-        <v>-95.35402678777622</v>
+        <v>-95.338979391788129</v>
       </c>
       <c r="CX110" s="37"/>
       <c r="CY110" s="37"/>
@@ -28023,28 +28016,28 @@
         <v>366.46746446798613</v>
       </c>
       <c r="CP111" s="35">
-        <v>64.077096280241847</v>
+        <v>64.07709627930484</v>
       </c>
       <c r="CQ111" s="35">
-        <v>-46.045784150873189</v>
+        <v>-46.048459070007375</v>
       </c>
       <c r="CR111" s="35">
         <v>219.5357641929445</v>
       </c>
       <c r="CS111" s="35">
-        <v>-15.46620610928359</v>
+        <v>-15.46636217468739</v>
       </c>
       <c r="CT111" s="35">
-        <v>-15.693725561822077</v>
+        <v>-15.693625939610783</v>
       </c>
       <c r="CU111" s="35">
-        <v>-66.229670747498744</v>
+        <v>-66.067287589775646</v>
       </c>
       <c r="CV111" s="35">
         <v>-71.105750195315608</v>
       </c>
       <c r="CW111" s="35">
-        <v>31.800826976016481</v>
+        <v>31.898747574430445</v>
       </c>
       <c r="CX111" s="37"/>
       <c r="CY111" s="37"/>
@@ -28374,19 +28367,19 @@
         <v>84.528007558240972</v>
       </c>
       <c r="CP112" s="35">
-        <v>-31.655040291126795</v>
+        <v>-31.43089455440267</v>
       </c>
       <c r="CQ112" s="35">
-        <v>-87.630846667401229</v>
+        <v>-87.520257929794468</v>
       </c>
       <c r="CR112" s="35">
         <v>-13.163066397897907</v>
       </c>
       <c r="CS112" s="35">
-        <v>-74.531348574706229</v>
+        <v>-74.466857040206406</v>
       </c>
       <c r="CT112" s="35">
-        <v>-17.323741381522126</v>
+        <v>-17.460823209149112</v>
       </c>
       <c r="CU112" s="37" t="s">
         <v>42</v>
@@ -28395,7 +28388,7 @@
         <v>214.56787587490169</v>
       </c>
       <c r="CW112" s="35">
-        <v>-42.769671274338826</v>
+        <v>-40.250147148520597</v>
       </c>
       <c r="CX112" s="37"/>
       <c r="CY112" s="37"/>
@@ -28725,28 +28718,28 @@
         <v>4.1468680377958265</v>
       </c>
       <c r="CP113" s="35">
-        <v>-0.35815642657109947</v>
+        <v>-0.34841840724023143</v>
       </c>
       <c r="CQ113" s="35">
-        <v>7.3670593073826183</v>
+        <v>7.2836422621842587</v>
       </c>
       <c r="CR113" s="35">
-        <v>9.2806030658861687</v>
+        <v>9.3011099405591722</v>
       </c>
       <c r="CS113" s="35">
-        <v>7.8444489989211093</v>
+        <v>7.6913406465177303</v>
       </c>
       <c r="CT113" s="35">
-        <v>16.134232832811392</v>
+        <v>16.347897189171917</v>
       </c>
       <c r="CU113" s="35">
-        <v>9.4593378753887265</v>
+        <v>9.0221995021968269</v>
       </c>
       <c r="CV113" s="35">
-        <v>17.354590207620532</v>
+        <v>16.220974135158556</v>
       </c>
       <c r="CW113" s="35">
-        <v>3.3335481489551881</v>
+        <v>5.4181405590148444</v>
       </c>
       <c r="CX113" s="37"/>
       <c r="CY113" s="37"/>
@@ -29076,28 +29069,28 @@
         <v>-4.8257960464572562</v>
       </c>
       <c r="CP114" s="35">
-        <v>-22.221695303738159</v>
+        <v>-22.202507377866212</v>
       </c>
       <c r="CQ114" s="35">
-        <v>25.625138500793</v>
+        <v>25.542969581594392</v>
       </c>
       <c r="CR114" s="35">
-        <v>3.9793590410578616</v>
+        <v>3.7096343826322311</v>
       </c>
       <c r="CS114" s="35">
-        <v>-0.22613029743688173</v>
+        <v>-0.36090532178043588</v>
       </c>
       <c r="CT114" s="35">
-        <v>18.244141956953769</v>
+        <v>18.322871957779682</v>
       </c>
       <c r="CU114" s="35">
-        <v>5.8147471400283024</v>
+        <v>5.9652416399955399</v>
       </c>
       <c r="CV114" s="35">
-        <v>74.647361802217404</v>
+        <v>74.568999689550054</v>
       </c>
       <c r="CW114" s="35">
-        <v>39.004649327728799</v>
+        <v>41.841228876531858</v>
       </c>
       <c r="CX114" s="37"/>
       <c r="CY114" s="37"/>
@@ -29427,28 +29420,28 @@
         <v>22.517390421981375</v>
       </c>
       <c r="CP115" s="35">
-        <v>26.965098668813184</v>
+        <v>26.948867958001827</v>
       </c>
       <c r="CQ115" s="35">
-        <v>20.256055414459382</v>
+        <v>20.217040400211033</v>
       </c>
       <c r="CR115" s="35">
-        <v>42.013376668805421</v>
+        <v>42.140600783556323</v>
       </c>
       <c r="CS115" s="35">
-        <v>13.707766038668879</v>
+        <v>14.065315174348143</v>
       </c>
       <c r="CT115" s="35">
-        <v>-0.35839953511440115</v>
+        <v>-0.82831518615846278</v>
       </c>
       <c r="CU115" s="35">
-        <v>-15.130108826985222</v>
+        <v>-15.763976971247331</v>
       </c>
       <c r="CV115" s="35">
-        <v>-14.774308079925831</v>
+        <v>-15.086305572660279</v>
       </c>
       <c r="CW115" s="35">
-        <v>-17.888925712659542</v>
+        <v>-15.135173015990489</v>
       </c>
       <c r="CX115" s="37"/>
       <c r="CY115" s="37"/>
@@ -29778,28 +29771,28 @@
         <v>0.81900932650660252</v>
       </c>
       <c r="CP116" s="35">
-        <v>-5.7788338081672208</v>
+        <v>-5.7572959288494729</v>
       </c>
       <c r="CQ116" s="35">
-        <v>1.7078195391821112</v>
+        <v>1.5822875470764615</v>
       </c>
       <c r="CR116" s="35">
-        <v>-1.373182606800853</v>
+        <v>-1.3222944752273946</v>
       </c>
       <c r="CS116" s="35">
-        <v>5.3397217007590285</v>
+        <v>4.9652615688657704</v>
       </c>
       <c r="CT116" s="35">
-        <v>22.994751473406211</v>
+        <v>23.22871749688295</v>
       </c>
       <c r="CU116" s="35">
-        <v>22.169950285915107</v>
+        <v>22.670818708013044</v>
       </c>
       <c r="CV116" s="35">
-        <v>21.736769827167322</v>
+        <v>21.724828082671337</v>
       </c>
       <c r="CW116" s="35">
-        <v>8.2341529089219136</v>
+        <v>10.494187956421385</v>
       </c>
       <c r="CX116" s="37"/>
       <c r="CY116" s="37"/>
@@ -30129,28 +30122,28 @@
         <v>5.1716544173731336</v>
       </c>
       <c r="CP117" s="35">
-        <v>-8.3775391515104047E-3</v>
+        <v>-8.6966621717294856E-3</v>
       </c>
       <c r="CQ117" s="35">
-        <v>3.6079442216013575</v>
+        <v>3.5738432379795739</v>
       </c>
       <c r="CR117" s="35">
-        <v>22.986168990676049</v>
+        <v>22.962085989393373</v>
       </c>
       <c r="CS117" s="35">
-        <v>14.772465119845293</v>
+        <v>14.779709044242239</v>
       </c>
       <c r="CT117" s="35">
-        <v>16.485795759220665</v>
+        <v>17.286439855624835</v>
       </c>
       <c r="CU117" s="35">
-        <v>6.5739520956790756</v>
+        <v>4.3444298271950288</v>
       </c>
       <c r="CV117" s="35">
-        <v>9.5441066180239886</v>
+        <v>3.5021281615727133</v>
       </c>
       <c r="CW117" s="35">
-        <v>-8.799188183762169</v>
+        <v>-8.1584786434592047</v>
       </c>
       <c r="CX117" s="37"/>
       <c r="CY117" s="37"/>
@@ -30628,28 +30621,28 @@
         <v>14.718983349588058</v>
       </c>
       <c r="CP119" s="38">
-        <v>-3.6416975949315713</v>
+        <v>-3.5870069198452086</v>
       </c>
       <c r="CQ119" s="38">
-        <v>0.97302236933998643</v>
+        <v>1.0528320512212588</v>
       </c>
       <c r="CR119" s="38">
-        <v>10.548732288921485</v>
+        <v>10.557538027272884</v>
       </c>
       <c r="CS119" s="38">
-        <v>4.535412250947445</v>
+        <v>4.6557660962716767</v>
       </c>
       <c r="CT119" s="38">
-        <v>12.947128765183692</v>
+        <v>13.067141552888842</v>
       </c>
       <c r="CU119" s="38">
-        <v>12.203793511848019</v>
+        <v>12.315573655718566</v>
       </c>
       <c r="CV119" s="38">
-        <v>2.7563713539139343</v>
+        <v>3.0410552056578268</v>
       </c>
       <c r="CW119" s="38">
-        <v>0.33952900070850944</v>
+        <v>1.2035193095950092</v>
       </c>
       <c r="CX119" s="40"/>
       <c r="CY119" s="40"/>
@@ -30800,19 +30793,19 @@
       <c r="CU120" s="33"/>
       <c r="CV120" s="33"/>
       <c r="CW120" s="33"/>
-      <c r="CX120" s="45"/>
-      <c r="CY120" s="45"/>
-      <c r="CZ120" s="45"/>
-      <c r="DA120" s="45"/>
+      <c r="CX120" s="43"/>
+      <c r="CY120" s="43"/>
+      <c r="CZ120" s="43"/>
+      <c r="DA120" s="43"/>
     </row>
     <row r="121" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CX121" s="43"/>
-      <c r="CY121" s="43"/>
-      <c r="CZ121" s="43"/>
-      <c r="DA121" s="43"/>
+      <c r="CX121" s="41"/>
+      <c r="CY121" s="41"/>
+      <c r="CZ121" s="41"/>
+      <c r="DA121" s="41"/>
     </row>
     <row r="122" spans="1:147" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
@@ -31117,196 +31110,196 @@
       <c r="A124" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="CX124" s="43"/>
-      <c r="CY124" s="43"/>
-      <c r="CZ124" s="43"/>
-      <c r="DA124" s="43"/>
+      <c r="CX124" s="41"/>
+      <c r="CY124" s="41"/>
+      <c r="CZ124" s="41"/>
+      <c r="DA124" s="41"/>
     </row>
     <row r="125" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="CX125" s="43"/>
-      <c r="CY125" s="43"/>
-      <c r="CZ125" s="43"/>
-      <c r="DA125" s="43"/>
+      <c r="CX125" s="41"/>
+      <c r="CY125" s="41"/>
+      <c r="CZ125" s="41"/>
+      <c r="DA125" s="41"/>
     </row>
     <row r="126" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="CX126" s="43"/>
-      <c r="CY126" s="43"/>
-      <c r="CZ126" s="43"/>
-      <c r="DA126" s="43"/>
+        <v>77</v>
+      </c>
+      <c r="CX126" s="41"/>
+      <c r="CY126" s="41"/>
+      <c r="CZ126" s="41"/>
+      <c r="DA126" s="41"/>
     </row>
     <row r="127" spans="1:147" x14ac:dyDescent="0.2">
-      <c r="CX127" s="43"/>
-      <c r="CY127" s="43"/>
-      <c r="CZ127" s="43"/>
-      <c r="DA127" s="43"/>
+      <c r="CX127" s="41"/>
+      <c r="CY127" s="41"/>
+      <c r="CZ127" s="41"/>
+      <c r="DA127" s="41"/>
     </row>
     <row r="128" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CX128" s="43"/>
-      <c r="CY128" s="43"/>
-      <c r="CZ128" s="43"/>
-      <c r="DA128" s="43"/>
+      <c r="CX128" s="41"/>
+      <c r="CY128" s="41"/>
+      <c r="CZ128" s="41"/>
+      <c r="DA128" s="41"/>
     </row>
     <row r="129" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CX129" s="43"/>
-      <c r="CY129" s="43"/>
-      <c r="CZ129" s="43"/>
-      <c r="DA129" s="43"/>
+        <v>76</v>
+      </c>
+      <c r="CX129" s="41"/>
+      <c r="CY129" s="41"/>
+      <c r="CZ129" s="41"/>
+      <c r="DA129" s="41"/>
     </row>
     <row r="130" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="CX130" s="43"/>
-      <c r="CY130" s="43"/>
-      <c r="CZ130" s="43"/>
-      <c r="DA130" s="43"/>
+      <c r="CX130" s="41"/>
+      <c r="CY130" s="41"/>
+      <c r="CZ130" s="41"/>
+      <c r="DA130" s="41"/>
     </row>
     <row r="131" spans="1:147" x14ac:dyDescent="0.2">
-      <c r="CX131" s="43"/>
-      <c r="CY131" s="43"/>
-      <c r="CZ131" s="43"/>
-      <c r="DA131" s="43"/>
+      <c r="CX131" s="41"/>
+      <c r="CY131" s="41"/>
+      <c r="CZ131" s="41"/>
+      <c r="DA131" s="41"/>
     </row>
     <row r="132" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
-      <c r="B132" s="41" t="s">
+      <c r="B132" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C132" s="42"/>
-      <c r="D132" s="42"/>
-      <c r="E132" s="42"/>
-      <c r="F132" s="41" t="s">
+      <c r="C132" s="44"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="44"/>
+      <c r="F132" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G132" s="42"/>
-      <c r="H132" s="42"/>
-      <c r="I132" s="42"/>
-      <c r="J132" s="41" t="s">
+      <c r="G132" s="44"/>
+      <c r="H132" s="44"/>
+      <c r="I132" s="44"/>
+      <c r="J132" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K132" s="42"/>
-      <c r="L132" s="42"/>
-      <c r="M132" s="42"/>
-      <c r="N132" s="41" t="s">
+      <c r="K132" s="44"/>
+      <c r="L132" s="44"/>
+      <c r="M132" s="44"/>
+      <c r="N132" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="O132" s="42"/>
-      <c r="P132" s="42"/>
-      <c r="Q132" s="42"/>
-      <c r="R132" s="41" t="s">
+      <c r="O132" s="44"/>
+      <c r="P132" s="44"/>
+      <c r="Q132" s="44"/>
+      <c r="R132" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="S132" s="42"/>
-      <c r="T132" s="42"/>
-      <c r="U132" s="42"/>
-      <c r="V132" s="41" t="s">
+      <c r="S132" s="44"/>
+      <c r="T132" s="44"/>
+      <c r="U132" s="44"/>
+      <c r="V132" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="W132" s="42"/>
-      <c r="X132" s="42"/>
-      <c r="Y132" s="42"/>
-      <c r="Z132" s="41" t="s">
+      <c r="W132" s="44"/>
+      <c r="X132" s="44"/>
+      <c r="Y132" s="44"/>
+      <c r="Z132" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="AA132" s="42"/>
-      <c r="AB132" s="42"/>
-      <c r="AC132" s="42"/>
-      <c r="AD132" s="41" t="s">
+      <c r="AA132" s="44"/>
+      <c r="AB132" s="44"/>
+      <c r="AC132" s="44"/>
+      <c r="AD132" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="AE132" s="42"/>
-      <c r="AF132" s="42"/>
-      <c r="AG132" s="42"/>
-      <c r="AH132" s="41" t="s">
+      <c r="AE132" s="44"/>
+      <c r="AF132" s="44"/>
+      <c r="AG132" s="44"/>
+      <c r="AH132" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="AI132" s="42"/>
-      <c r="AJ132" s="42"/>
-      <c r="AK132" s="42"/>
-      <c r="AL132" s="41" t="s">
+      <c r="AI132" s="44"/>
+      <c r="AJ132" s="44"/>
+      <c r="AK132" s="44"/>
+      <c r="AL132" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="AM132" s="42"/>
-      <c r="AN132" s="42"/>
-      <c r="AO132" s="42"/>
-      <c r="AP132" s="41" t="s">
+      <c r="AM132" s="44"/>
+      <c r="AN132" s="44"/>
+      <c r="AO132" s="44"/>
+      <c r="AP132" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="AQ132" s="42"/>
-      <c r="AR132" s="42"/>
-      <c r="AS132" s="42"/>
-      <c r="AT132" s="41" t="s">
+      <c r="AQ132" s="44"/>
+      <c r="AR132" s="44"/>
+      <c r="AS132" s="44"/>
+      <c r="AT132" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="AU132" s="42"/>
-      <c r="AV132" s="42"/>
-      <c r="AW132" s="42"/>
-      <c r="AX132" s="41" t="s">
+      <c r="AU132" s="44"/>
+      <c r="AV132" s="44"/>
+      <c r="AW132" s="44"/>
+      <c r="AX132" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="AY132" s="42"/>
-      <c r="AZ132" s="42"/>
-      <c r="BA132" s="42"/>
-      <c r="BB132" s="41" t="s">
+      <c r="AY132" s="44"/>
+      <c r="AZ132" s="44"/>
+      <c r="BA132" s="44"/>
+      <c r="BB132" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="BC132" s="42"/>
-      <c r="BD132" s="42"/>
-      <c r="BE132" s="42"/>
-      <c r="BF132" s="41" t="s">
+      <c r="BC132" s="44"/>
+      <c r="BD132" s="44"/>
+      <c r="BE132" s="44"/>
+      <c r="BF132" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="BG132" s="42"/>
-      <c r="BH132" s="42"/>
-      <c r="BI132" s="42"/>
-      <c r="BJ132" s="41" t="s">
+      <c r="BG132" s="44"/>
+      <c r="BH132" s="44"/>
+      <c r="BI132" s="44"/>
+      <c r="BJ132" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="BK132" s="42"/>
-      <c r="BL132" s="42"/>
-      <c r="BM132" s="42"/>
-      <c r="BN132" s="41" t="s">
+      <c r="BK132" s="44"/>
+      <c r="BL132" s="44"/>
+      <c r="BM132" s="44"/>
+      <c r="BN132" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="BO132" s="42"/>
-      <c r="BP132" s="42"/>
-      <c r="BQ132" s="42"/>
-      <c r="BR132" s="41" t="s">
+      <c r="BO132" s="44"/>
+      <c r="BP132" s="44"/>
+      <c r="BQ132" s="44"/>
+      <c r="BR132" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="BS132" s="42"/>
-      <c r="BT132" s="42"/>
-      <c r="BU132" s="42"/>
-      <c r="BV132" s="41" t="s">
+      <c r="BS132" s="44"/>
+      <c r="BT132" s="44"/>
+      <c r="BU132" s="44"/>
+      <c r="BV132" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="BW132" s="42"/>
-      <c r="BX132" s="42"/>
-      <c r="BY132" s="42"/>
-      <c r="BZ132" s="41" t="s">
+      <c r="BW132" s="44"/>
+      <c r="BX132" s="44"/>
+      <c r="BY132" s="44"/>
+      <c r="BZ132" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="CA132" s="42"/>
-      <c r="CB132" s="42"/>
-      <c r="CC132" s="42"/>
-      <c r="CD132" s="41" t="s">
+      <c r="CA132" s="44"/>
+      <c r="CB132" s="44"/>
+      <c r="CC132" s="44"/>
+      <c r="CD132" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="CE132" s="41"/>
-      <c r="CF132" s="41"/>
-      <c r="CG132" s="41"/>
+      <c r="CE132" s="45"/>
+      <c r="CF132" s="45"/>
+      <c r="CG132" s="45"/>
       <c r="CH132" s="26" t="s">
         <v>71</v>
       </c>
@@ -31331,10 +31324,10 @@
       <c r="CU132" s="28"/>
       <c r="CV132" s="28"/>
       <c r="CW132" s="28"/>
-      <c r="CX132" s="44"/>
-      <c r="CY132" s="44"/>
-      <c r="CZ132" s="44"/>
-      <c r="DA132" s="44"/>
+      <c r="CX132" s="42"/>
+      <c r="CY132" s="42"/>
+      <c r="CZ132" s="42"/>
+      <c r="DA132" s="42"/>
     </row>
     <row r="133" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
@@ -31640,17 +31633,17 @@
       <c r="CW133" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="CX133" s="45"/>
-      <c r="CY133" s="45"/>
-      <c r="CZ133" s="45"/>
-      <c r="DA133" s="45"/>
+      <c r="CX133" s="43"/>
+      <c r="CY133" s="43"/>
+      <c r="CZ133" s="43"/>
+      <c r="DA133" s="43"/>
     </row>
     <row r="134" spans="1:147" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
-      <c r="CX134" s="43"/>
-      <c r="CY134" s="43"/>
-      <c r="CZ134" s="43"/>
-      <c r="DA134" s="43"/>
+      <c r="CX134" s="41"/>
+      <c r="CY134" s="41"/>
+      <c r="CZ134" s="41"/>
+      <c r="DA134" s="41"/>
     </row>
     <row r="135" spans="1:147" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
@@ -31933,28 +31926,28 @@
         <v>3.1591046266430993</v>
       </c>
       <c r="CP135" s="35">
-        <v>-9.466016132027022</v>
+        <v>-9.4377904627609155</v>
       </c>
       <c r="CQ135" s="35">
-        <v>3.4905061582370251</v>
+        <v>3.4821986351804242</v>
       </c>
       <c r="CR135" s="35">
-        <v>8.8849576004606803</v>
+        <v>8.8541399234551363</v>
       </c>
       <c r="CS135" s="35">
-        <v>5.0660897502982749</v>
+        <v>5.8611247120428942</v>
       </c>
       <c r="CT135" s="35">
-        <v>18.034727509082089</v>
+        <v>17.6815467214726</v>
       </c>
       <c r="CU135" s="35">
-        <v>5.5016116362226484</v>
+        <v>5.7226004945583213</v>
       </c>
       <c r="CV135" s="35">
-        <v>6.4320600783513981</v>
+        <v>7.5680294307011593</v>
       </c>
       <c r="CW135" s="35">
-        <v>-10.2353267116534</v>
+        <v>-9.2074653161846953</v>
       </c>
       <c r="CX135" s="37"/>
       <c r="CY135" s="37"/>
@@ -32284,28 +32277,28 @@
         <v>72.488584764718411</v>
       </c>
       <c r="CP136" s="35">
-        <v>25.222721148203348</v>
+        <v>25.222721143655335</v>
       </c>
       <c r="CQ136" s="35">
-        <v>-0.70774980682753608</v>
+        <v>-0.72167262560238044</v>
       </c>
       <c r="CR136" s="35">
-        <v>-14.073697112571679</v>
+        <v>-14.076143514675493</v>
       </c>
       <c r="CS136" s="35">
-        <v>-30.891206753871458</v>
+        <v>-30.771792514284684</v>
       </c>
       <c r="CT136" s="35">
-        <v>49.978634610005201</v>
+        <v>50.097653435346075</v>
       </c>
       <c r="CU136" s="35">
-        <v>29.882378744418702</v>
+        <v>29.902047870125301</v>
       </c>
       <c r="CV136" s="35">
-        <v>12.91668661588416</v>
+        <v>13.178988807694481</v>
       </c>
       <c r="CW136" s="35">
-        <v>-9.0622163774952753</v>
+        <v>-7.0178251160777307</v>
       </c>
       <c r="CX136" s="37"/>
       <c r="CY136" s="37"/>
@@ -32635,28 +32628,28 @@
         <v>-28.596500140346421</v>
       </c>
       <c r="CP137" s="35">
-        <v>-30.869837568454244</v>
+        <v>-30.731361933506733</v>
       </c>
       <c r="CQ137" s="35">
-        <v>-10.018733448853538</v>
+        <v>-9.8413253501225171</v>
       </c>
       <c r="CR137" s="35">
         <v>7.2263326151664273</v>
       </c>
       <c r="CS137" s="35">
-        <v>19.823905886220516</v>
+        <v>20.271664092571257</v>
       </c>
       <c r="CT137" s="35">
-        <v>15.244116189437307</v>
+        <v>15.124404832074646</v>
       </c>
       <c r="CU137" s="35">
-        <v>0.15439951591109491</v>
+        <v>5.6855194804072084E-2</v>
       </c>
       <c r="CV137" s="35">
-        <v>-9.4816996692711086</v>
+        <v>-8.9753140548645121</v>
       </c>
       <c r="CW137" s="35">
-        <v>-2.7750774719853837</v>
+        <v>-0.5111894945355715</v>
       </c>
       <c r="CX137" s="37"/>
       <c r="CY137" s="37"/>
@@ -32986,7 +32979,7 @@
         <v>17.771108312824381</v>
       </c>
       <c r="CP138" s="35">
-        <v>-23.134086063835312</v>
+        <v>-23.134086065147713</v>
       </c>
       <c r="CQ138" s="35">
         <v>0.79721130801905815</v>
@@ -32995,19 +32988,19 @@
         <v>20.230701455442031</v>
       </c>
       <c r="CS138" s="35">
-        <v>10.095030614372405</v>
+        <v>14.038780202920904</v>
       </c>
       <c r="CT138" s="35">
-        <v>41.678230559714819</v>
+        <v>43.427293598001029</v>
       </c>
       <c r="CU138" s="35">
-        <v>46.98260657726965</v>
+        <v>46.883705592034886</v>
       </c>
       <c r="CV138" s="35">
-        <v>-10.076973730043662</v>
+        <v>-3.1471626189733684</v>
       </c>
       <c r="CW138" s="35">
-        <v>16.578962917027113</v>
+        <v>15.078692809835132</v>
       </c>
       <c r="CX138" s="37"/>
       <c r="CY138" s="37"/>
@@ -33337,28 +33330,28 @@
         <v>-9.0202090323205084</v>
       </c>
       <c r="CP139" s="35">
-        <v>75.535924096271287</v>
+        <v>75.535924089750608</v>
       </c>
       <c r="CQ139" s="35">
-        <v>48.981961475696465</v>
+        <v>49.098697719465406</v>
       </c>
       <c r="CR139" s="35">
-        <v>25.824261782228319</v>
+        <v>25.839507173852283</v>
       </c>
       <c r="CS139" s="35">
-        <v>34.471634023210527</v>
+        <v>36.611709286223572</v>
       </c>
       <c r="CT139" s="35">
-        <v>3.6391457761254742</v>
+        <v>3.6287983334188425</v>
       </c>
       <c r="CU139" s="35">
-        <v>29.582449958280819</v>
+        <v>29.465932843479294</v>
       </c>
       <c r="CV139" s="35">
-        <v>-1.5459166081189863</v>
+        <v>-0.35596253149022061</v>
       </c>
       <c r="CW139" s="35">
-        <v>-12.748250239006722</v>
+        <v>-12.765076251092168</v>
       </c>
       <c r="CX139" s="37"/>
       <c r="CY139" s="37"/>
@@ -33688,7 +33681,7 @@
         <v>-11.556115019566704</v>
       </c>
       <c r="CP140" s="35">
-        <v>-39.359650808897761</v>
+        <v>-39.359650811239874</v>
       </c>
       <c r="CQ140" s="35">
         <v>-10.832764992999159</v>
@@ -33697,19 +33690,19 @@
         <v>-7.6448955638106497</v>
       </c>
       <c r="CS140" s="35">
-        <v>-11.115018521460726</v>
+        <v>-10.091079957529487</v>
       </c>
       <c r="CT140" s="35">
-        <v>38.225817484159819</v>
+        <v>38.471569667395698</v>
       </c>
       <c r="CU140" s="35">
-        <v>27.016794750060697</v>
+        <v>27.093695208814907</v>
       </c>
       <c r="CV140" s="35">
-        <v>20.927792363203991</v>
+        <v>20.773941033869022</v>
       </c>
       <c r="CW140" s="35">
-        <v>-6.9921971266414147</v>
+        <v>-4.9595381667371754</v>
       </c>
       <c r="CX140" s="37"/>
       <c r="CY140" s="37"/>
@@ -34039,28 +34032,28 @@
         <v>20.294919302068863</v>
       </c>
       <c r="CP141" s="35">
-        <v>-2.3074547038208948</v>
+        <v>-2.3045997355992967</v>
       </c>
       <c r="CQ141" s="35">
-        <v>5.0981695800951172</v>
+        <v>5.0591848549171203</v>
       </c>
       <c r="CR141" s="35">
-        <v>8.8845304951411492</v>
+        <v>8.8202196186115742</v>
       </c>
       <c r="CS141" s="35">
-        <v>1.609250031565935</v>
+        <v>1.554771664585374</v>
       </c>
       <c r="CT141" s="35">
-        <v>8.9777242354731897</v>
+        <v>8.4006095628520399</v>
       </c>
       <c r="CU141" s="35">
-        <v>2.4110911784449058</v>
+        <v>2.4083770566579545</v>
       </c>
       <c r="CV141" s="35">
-        <v>-6.9372704287587794E-2</v>
+        <v>-4.0672008423342731E-2</v>
       </c>
       <c r="CW141" s="35">
-        <v>-15.056697327189241</v>
+        <v>-14.858434191282882</v>
       </c>
       <c r="CX141" s="37"/>
       <c r="CY141" s="37"/>
@@ -34390,28 +34383,28 @@
         <v>-14.53533047106562</v>
       </c>
       <c r="CP142" s="35">
-        <v>-22.112929787977848</v>
+        <v>-22.112929790663401</v>
       </c>
       <c r="CQ142" s="35">
         <v>8.6487998397508363</v>
       </c>
       <c r="CR142" s="35">
-        <v>-19.712894560997768</v>
+        <v>-19.722280308113454</v>
       </c>
       <c r="CS142" s="35">
-        <v>81.37720097291151</v>
+        <v>81.993587476641011</v>
       </c>
       <c r="CT142" s="35">
-        <v>42.733103706682698</v>
+        <v>42.735138555319509</v>
       </c>
       <c r="CU142" s="35">
-        <v>42.28488826719331</v>
+        <v>42.395562368013998</v>
       </c>
       <c r="CV142" s="35">
-        <v>49.597485600484987</v>
+        <v>50.652781744221443</v>
       </c>
       <c r="CW142" s="35">
-        <v>-20.071272336008704</v>
+        <v>-19.577366501743072</v>
       </c>
       <c r="CX142" s="37"/>
       <c r="CY142" s="37"/>
@@ -34741,28 +34734,28 @@
         <v>-0.1522937808870779</v>
       </c>
       <c r="CP143" s="35">
-        <v>-6.2860025064501457</v>
+        <v>-6.2860025084546862</v>
       </c>
       <c r="CQ143" s="35">
-        <v>13.17471919180791</v>
+        <v>13.154107006081333</v>
       </c>
       <c r="CR143" s="35">
-        <v>31.696986870419209</v>
+        <v>31.662681519298673</v>
       </c>
       <c r="CS143" s="35">
-        <v>11.804739954757878</v>
+        <v>14.817426443434627</v>
       </c>
       <c r="CT143" s="35">
-        <v>34.573448376116801</v>
+        <v>34.288325908487991</v>
       </c>
       <c r="CU143" s="35">
-        <v>12.578101662041405</v>
+        <v>15.484536761779339</v>
       </c>
       <c r="CV143" s="35">
-        <v>25.810899078043036</v>
+        <v>29.682595330009576</v>
       </c>
       <c r="CW143" s="35">
-        <v>-10.236663875933345</v>
+        <v>-9.0759610173663674</v>
       </c>
       <c r="CX143" s="37"/>
       <c r="CY143" s="37"/>
@@ -35092,28 +35085,28 @@
         <v>2.7569094478234462</v>
       </c>
       <c r="CP144" s="35">
-        <v>4.2060656406738559</v>
+        <v>4.2199234816853135</v>
       </c>
       <c r="CQ144" s="35">
-        <v>11.136255754791065</v>
+        <v>11.339443144823562</v>
       </c>
       <c r="CR144" s="35">
-        <v>-5.6427757606728619</v>
+        <v>-5.6928911983182502</v>
       </c>
       <c r="CS144" s="35">
-        <v>2.5826243439327641</v>
+        <v>2.5225817146798875</v>
       </c>
       <c r="CT144" s="35">
-        <v>-2.568331078103796</v>
+        <v>-1.9066535058686327</v>
       </c>
       <c r="CU144" s="35">
-        <v>-7.3032330103910681</v>
+        <v>-6.7898073776139256</v>
       </c>
       <c r="CV144" s="35">
-        <v>16.130380838716476</v>
+        <v>16.115216620002542</v>
       </c>
       <c r="CW144" s="35">
-        <v>2.8260823339713852</v>
+        <v>5.0127994168731789</v>
       </c>
       <c r="CX144" s="37"/>
       <c r="CY144" s="37"/>
@@ -35443,28 +35436,28 @@
         <v>7.8369999257095486</v>
       </c>
       <c r="CP145" s="35">
-        <v>13.192259177632536</v>
+        <v>13.203984976205831</v>
       </c>
       <c r="CQ145" s="35">
-        <v>19.862588382704118</v>
+        <v>19.839870003792953</v>
       </c>
       <c r="CR145" s="35">
-        <v>26.706725986376284</v>
+        <v>26.690929118008015</v>
       </c>
       <c r="CS145" s="35">
-        <v>10.547747538886014</v>
+        <v>10.584819214719104</v>
       </c>
       <c r="CT145" s="35">
-        <v>8.7820163498391537</v>
+        <v>8.8475376075988379</v>
       </c>
       <c r="CU145" s="35">
-        <v>-3.8156908317697429</v>
+        <v>-3.7796868438422422</v>
       </c>
       <c r="CV145" s="35">
-        <v>-21.067113998488225</v>
+        <v>-21.05549364903959</v>
       </c>
       <c r="CW145" s="35">
-        <v>-18.448405895007085</v>
+        <v>-16.423444567517578</v>
       </c>
       <c r="CX145" s="37"/>
       <c r="CY145" s="37"/>
@@ -35794,28 +35787,28 @@
         <v>-5.3315699133340928</v>
       </c>
       <c r="CP146" s="35">
-        <v>-7.6042393510577284</v>
+        <v>-7.5903915983025598</v>
       </c>
       <c r="CQ146" s="35">
-        <v>1.9097722042687337E-2</v>
+        <v>-8.1163570729628987E-2</v>
       </c>
       <c r="CR146" s="35">
-        <v>23.614514120029199</v>
+        <v>23.689430670614215</v>
       </c>
       <c r="CS146" s="35">
-        <v>5.4696524624013847</v>
+        <v>5.2185475171616389</v>
       </c>
       <c r="CT146" s="35">
-        <v>14.143791527933033</v>
+        <v>14.319364286289684</v>
       </c>
       <c r="CU146" s="35">
-        <v>5.9388370735956784</v>
+        <v>6.152016758284276</v>
       </c>
       <c r="CV146" s="35">
-        <v>-5.3223792424247449</v>
+        <v>-5.3419706982116963</v>
       </c>
       <c r="CW146" s="35">
-        <v>3.7280730194887894</v>
+        <v>6.567033343925516</v>
       </c>
       <c r="CX146" s="37"/>
       <c r="CY146" s="37"/>
@@ -36145,28 +36138,28 @@
         <v>6.0582110130462041</v>
       </c>
       <c r="CP147" s="35">
-        <v>5.118278495009676</v>
+        <v>5.1196535290273175</v>
       </c>
       <c r="CQ147" s="35">
-        <v>12.493842762416691</v>
+        <v>12.884327369153283</v>
       </c>
       <c r="CR147" s="35">
-        <v>-27.242943720786215</v>
+        <v>-27.371803177336261</v>
       </c>
       <c r="CS147" s="35">
-        <v>-17.454326654805925</v>
+        <v>-17.669677698554338</v>
       </c>
       <c r="CT147" s="35">
-        <v>-32.429650122980675</v>
+        <v>-31.233251984537091</v>
       </c>
       <c r="CU147" s="35">
-        <v>-16.460672263344705</v>
+        <v>-15.468585810347037</v>
       </c>
       <c r="CV147" s="35">
-        <v>47.858372257794088</v>
+        <v>47.895577028284322</v>
       </c>
       <c r="CW147" s="35">
-        <v>16.222117199113043</v>
+        <v>16.268772853001948</v>
       </c>
       <c r="CX147" s="37"/>
       <c r="CY147" s="37"/>
@@ -36496,28 +36489,28 @@
         <v>5.0228797665738512E-2</v>
       </c>
       <c r="CP148" s="35">
-        <v>2.900097684629884</v>
+        <v>2.9262079143454827</v>
       </c>
       <c r="CQ148" s="35">
-        <v>8.8969902862235557</v>
+        <v>9.0969439614898135</v>
       </c>
       <c r="CR148" s="35">
-        <v>3.6705776126724174</v>
+        <v>3.6876321527228129</v>
       </c>
       <c r="CS148" s="35">
-        <v>14.768751892742955</v>
+        <v>14.840736780111257</v>
       </c>
       <c r="CT148" s="35">
-        <v>16.153465677001151</v>
+        <v>16.694935481358101</v>
       </c>
       <c r="CU148" s="35">
-        <v>-2.3015014686144468</v>
+        <v>-1.9753086664539552</v>
       </c>
       <c r="CV148" s="35">
-        <v>10.755294739558337</v>
+        <v>10.733776265910649</v>
       </c>
       <c r="CW148" s="35">
-        <v>4.4898250571037579</v>
+        <v>7.9087537470289533</v>
       </c>
       <c r="CX148" s="37"/>
       <c r="CY148" s="37"/>
@@ -36847,28 +36840,28 @@
         <v>27.274537247893747</v>
       </c>
       <c r="CP149" s="35">
-        <v>-8.5169217101792611</v>
+        <v>-8.4444966773952501</v>
       </c>
       <c r="CQ149" s="35">
-        <v>-12.528084529356136</v>
+        <v>-12.437130770888203</v>
       </c>
       <c r="CR149" s="35">
-        <v>12.521698876080748</v>
+        <v>12.551415088899589</v>
       </c>
       <c r="CS149" s="35">
-        <v>-0.81668259015835076</v>
+        <v>-0.73345706143189204</v>
       </c>
       <c r="CT149" s="35">
-        <v>6.817086141882541</v>
+        <v>6.8173618112785164</v>
       </c>
       <c r="CU149" s="35">
-        <v>22.01389827116374</v>
+        <v>21.993708638054414</v>
       </c>
       <c r="CV149" s="35">
-        <v>-4.4197043567810823</v>
+        <v>-3.5636307233310305</v>
       </c>
       <c r="CW149" s="35">
-        <v>-2.1192363916275951</v>
+        <v>-1.9792049678420085</v>
       </c>
       <c r="CX149" s="37"/>
       <c r="CY149" s="37"/>
@@ -37198,28 +37191,28 @@
         <v>14.433930414791504</v>
       </c>
       <c r="CP150" s="35">
-        <v>-11.65004063760658</v>
+        <v>-11.578785899522217</v>
       </c>
       <c r="CQ150" s="35">
-        <v>-4.7919917733530468</v>
+        <v>-4.6937942413423883</v>
       </c>
       <c r="CR150" s="35">
-        <v>0.64219291074745399</v>
+        <v>0.67393132808194878</v>
       </c>
       <c r="CS150" s="35">
-        <v>4.0457979269747852</v>
+        <v>4.1415272905508402</v>
       </c>
       <c r="CT150" s="35">
-        <v>10.847544919953833</v>
+        <v>10.848418217920951</v>
       </c>
       <c r="CU150" s="35">
-        <v>17.599183382056125</v>
+        <v>17.591374699472141</v>
       </c>
       <c r="CV150" s="35">
-        <v>5.369670776586787</v>
+        <v>6.3887868954394662</v>
       </c>
       <c r="CW150" s="35">
-        <v>-3.1165051702374313</v>
+        <v>-2.9913762069901821</v>
       </c>
       <c r="CX150" s="37"/>
       <c r="CY150" s="37"/>
@@ -37561,7 +37554,7 @@
         <v>194.23506436053822</v>
       </c>
       <c r="CT151" s="35">
-        <v>-89.643025681765764</v>
+        <v>-89.643025682285014</v>
       </c>
       <c r="CU151" s="35">
         <v>-96.281123518456724</v>
@@ -37570,7 +37563,7 @@
         <v>-87.842699878076914</v>
       </c>
       <c r="CW151" s="35">
-        <v>-95.513421940623687</v>
+        <v>-95.498890794272413</v>
       </c>
       <c r="CX151" s="37"/>
       <c r="CY151" s="37"/>
@@ -37900,28 +37893,28 @@
         <v>345.73805304785105</v>
       </c>
       <c r="CP152" s="35">
-        <v>56.362892946677931</v>
+        <v>56.362892945789213</v>
       </c>
       <c r="CQ152" s="35">
-        <v>-50.590669883241254</v>
+        <v>-50.593119425432725</v>
       </c>
       <c r="CR152" s="35">
         <v>213.15767745182387</v>
       </c>
       <c r="CS152" s="35">
-        <v>-20.433342538878634</v>
+        <v>-20.433489150475452</v>
       </c>
       <c r="CT152" s="35">
-        <v>-20.850369667927055</v>
+        <v>-20.850217433143499</v>
       </c>
       <c r="CU152" s="35">
-        <v>-66.275538562930834</v>
+        <v>-66.113385255552487</v>
       </c>
       <c r="CV152" s="35">
         <v>-71.613477679285765</v>
       </c>
       <c r="CW152" s="35">
-        <v>27.231351156869962</v>
+        <v>27.325729665498272</v>
       </c>
       <c r="CX152" s="37"/>
       <c r="CY152" s="37"/>
@@ -38251,19 +38244,19 @@
         <v>75.886718543472256</v>
       </c>
       <c r="CP153" s="35">
-        <v>-31.675817500047827</v>
+        <v>-31.479414690920834</v>
       </c>
       <c r="CQ153" s="35">
-        <v>-88.661710205367655</v>
+        <v>-88.560444864074327</v>
       </c>
       <c r="CR153" s="35">
         <v>-13.223632153112888</v>
       </c>
       <c r="CS153" s="35">
-        <v>-74.789544788083248</v>
+        <v>-74.729561071227423</v>
       </c>
       <c r="CT153" s="35">
-        <v>-19.083062934709616</v>
+        <v>-19.169127237519206</v>
       </c>
       <c r="CU153" s="37" t="s">
         <v>42</v>
@@ -38272,7 +38265,7 @@
         <v>194.09364188192041</v>
       </c>
       <c r="CW153" s="35">
-        <v>-44.321903075654532</v>
+        <v>-42.06050609640851</v>
       </c>
       <c r="CX153" s="37"/>
       <c r="CY153" s="37"/>
@@ -38602,28 +38595,28 @@
         <v>3.211420163402039</v>
       </c>
       <c r="CP154" s="35">
-        <v>-1.8489413104616119</v>
+        <v>-1.8407961838369857</v>
       </c>
       <c r="CQ154" s="35">
-        <v>1.9416040235637979</v>
+        <v>1.847602161459136</v>
       </c>
       <c r="CR154" s="35">
-        <v>8.997175845847778</v>
+        <v>9.0229716238913369</v>
       </c>
       <c r="CS154" s="35">
-        <v>4.3659162189824627</v>
+        <v>4.2626400612035411</v>
       </c>
       <c r="CT154" s="35">
-        <v>15.004813401930491</v>
+        <v>15.195450194618715</v>
       </c>
       <c r="CU154" s="35">
-        <v>6.0624914762268673</v>
+        <v>5.8279432123875807</v>
       </c>
       <c r="CV154" s="35">
-        <v>3.2250424851107908</v>
+        <v>2.0445151133606316</v>
       </c>
       <c r="CW154" s="35">
-        <v>-1.1047696154541455</v>
+        <v>0.94483933697429734</v>
       </c>
       <c r="CX154" s="37"/>
       <c r="CY154" s="37"/>
@@ -38953,28 +38946,28 @@
         <v>0.32605165641288636</v>
       </c>
       <c r="CP155" s="35">
-        <v>-27.371466252819886</v>
+        <v>-27.35367608713031</v>
       </c>
       <c r="CQ155" s="35">
-        <v>23.09524091939177</v>
+        <v>23.013287958092192</v>
       </c>
       <c r="CR155" s="35">
-        <v>4.8029283445273734</v>
+        <v>4.5433159841446837</v>
       </c>
       <c r="CS155" s="35">
-        <v>-2.1538379321532943</v>
+        <v>-2.2808446945598035</v>
       </c>
       <c r="CT155" s="35">
-        <v>30.209298126925432</v>
+        <v>30.29624512141055</v>
       </c>
       <c r="CU155" s="35">
-        <v>6.9389813310757944</v>
+        <v>7.0936701363454944</v>
       </c>
       <c r="CV155" s="35">
-        <v>68.706157951846905</v>
+        <v>68.616250931020659</v>
       </c>
       <c r="CW155" s="35">
-        <v>34.634136575523172</v>
+        <v>37.301213730238345</v>
       </c>
       <c r="CX155" s="37"/>
       <c r="CY155" s="37"/>
@@ -39304,28 +39297,28 @@
         <v>18.822336856370242</v>
       </c>
       <c r="CP156" s="35">
-        <v>22.120410439699739</v>
+        <v>22.106299044273797</v>
       </c>
       <c r="CQ156" s="35">
-        <v>17.166693365640228</v>
+        <v>17.124999606747778</v>
       </c>
       <c r="CR156" s="35">
-        <v>41.173392379996812</v>
+        <v>41.24333000776619</v>
       </c>
       <c r="CS156" s="35">
-        <v>11.168802008851657</v>
+        <v>11.716854331468468</v>
       </c>
       <c r="CT156" s="35">
-        <v>4.3747883771205807</v>
+        <v>3.8440923020384332</v>
       </c>
       <c r="CU156" s="35">
-        <v>-16.117952706778411</v>
+        <v>-16.614951557646293</v>
       </c>
       <c r="CV156" s="35">
-        <v>-14.529987717208826</v>
+        <v>-14.85807108521594</v>
       </c>
       <c r="CW156" s="35">
-        <v>-14.301279688113397</v>
+        <v>-10.764893822149276</v>
       </c>
       <c r="CX156" s="37"/>
       <c r="CY156" s="37"/>
@@ -39655,28 +39648,28 @@
         <v>-1.9987097298638048</v>
       </c>
       <c r="CP157" s="35">
-        <v>-7.3262707307693233</v>
+        <v>-7.3063868927179669</v>
       </c>
       <c r="CQ157" s="35">
-        <v>-7.2500365433816825</v>
+        <v>-7.3856121044944132</v>
       </c>
       <c r="CR157" s="35">
-        <v>-0.69783309715954545</v>
+        <v>-0.63276969776929093</v>
       </c>
       <c r="CS157" s="35">
-        <v>1.3873098199376841</v>
+        <v>0.99239240888661584</v>
       </c>
       <c r="CT157" s="35">
-        <v>17.622241520382858</v>
+        <v>17.865457132644977</v>
       </c>
       <c r="CU157" s="35">
-        <v>17.014592953346821</v>
+        <v>17.517675192525317</v>
       </c>
       <c r="CV157" s="35">
-        <v>-1.6278958043724288</v>
+        <v>-1.6472977297261622</v>
       </c>
       <c r="CW157" s="35">
-        <v>3.4910308678469448</v>
+        <v>5.5642397899447076</v>
       </c>
       <c r="CX157" s="37"/>
       <c r="CY157" s="37"/>
@@ -40006,28 +39999,28 @@
         <v>5.104827464797097</v>
       </c>
       <c r="CP158" s="35">
-        <v>-0.61462570109463854</v>
+        <v>-0.61495702474215364</v>
       </c>
       <c r="CQ158" s="35">
-        <v>-0.62324721559667751</v>
+        <v>-0.66666858751133873</v>
       </c>
       <c r="CR158" s="35">
-        <v>19.939433970295539</v>
+        <v>19.916940667222846</v>
       </c>
       <c r="CS158" s="35">
-        <v>7.8107652629538791</v>
+        <v>7.816699386651436</v>
       </c>
       <c r="CT158" s="35">
-        <v>16.40988771124303</v>
+        <v>17.224103689382403</v>
       </c>
       <c r="CU158" s="35">
-        <v>6.0728096072446363</v>
+        <v>4.0644289129297562</v>
       </c>
       <c r="CV158" s="35">
-        <v>8.7305612224353837</v>
+        <v>2.5207359083203755</v>
       </c>
       <c r="CW158" s="35">
-        <v>-11.734912961769339</v>
+        <v>-11.239564138509579</v>
       </c>
       <c r="CX158" s="37"/>
       <c r="CY158" s="37"/>
@@ -40505,28 +40498,28 @@
         <v>14.724165048018392</v>
       </c>
       <c r="CP160" s="38">
-        <v>-5.5624554150564052</v>
+        <v>-5.5164848469976562</v>
       </c>
       <c r="CQ160" s="38">
-        <v>-4.4676911649066966</v>
+        <v>-4.4133815489807517</v>
       </c>
       <c r="CR160" s="38">
-        <v>8.0105653881918926</v>
+        <v>8.0164760035604559</v>
       </c>
       <c r="CS160" s="38">
-        <v>1.4066105900891301</v>
+        <v>1.5631790217927204</v>
       </c>
       <c r="CT160" s="38">
-        <v>8.2503126091305177</v>
+        <v>8.3464948234189649</v>
       </c>
       <c r="CU160" s="38">
-        <v>11.77451593184189</v>
+        <v>11.812628672548527</v>
       </c>
       <c r="CV160" s="38">
-        <v>1.6166225217321113</v>
+        <v>2.0507375519146223</v>
       </c>
       <c r="CW160" s="38">
-        <v>-2.5645377077553775</v>
+        <v>-1.6819530960023883</v>
       </c>
       <c r="CX160" s="40"/>
       <c r="CY160" s="40"/>
@@ -40677,19 +40670,19 @@
       <c r="CU161" s="33"/>
       <c r="CV161" s="33"/>
       <c r="CW161" s="33"/>
-      <c r="CX161" s="45"/>
-      <c r="CY161" s="45"/>
-      <c r="CZ161" s="45"/>
-      <c r="DA161" s="45"/>
+      <c r="CX161" s="43"/>
+      <c r="CY161" s="43"/>
+      <c r="CZ161" s="43"/>
+      <c r="DA161" s="43"/>
     </row>
     <row r="162" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CX162" s="43"/>
-      <c r="CY162" s="43"/>
-      <c r="CZ162" s="43"/>
-      <c r="DA162" s="43"/>
+      <c r="CX162" s="41"/>
+      <c r="CY162" s="41"/>
+      <c r="CZ162" s="41"/>
+      <c r="DA162" s="41"/>
     </row>
     <row r="163" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
@@ -41002,7 +40995,7 @@
     </row>
     <row r="166" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="168" spans="1:152" x14ac:dyDescent="0.2">
@@ -41012,7 +41005,7 @@
     </row>
     <row r="169" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="170" spans="1:152" x14ac:dyDescent="0.2">
@@ -41022,132 +41015,132 @@
     </row>
     <row r="172" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
-      <c r="B172" s="42">
+      <c r="B172" s="44">
         <v>2000</v>
       </c>
-      <c r="C172" s="42"/>
-      <c r="D172" s="42"/>
-      <c r="E172" s="42"/>
-      <c r="F172" s="42">
+      <c r="C172" s="44"/>
+      <c r="D172" s="44"/>
+      <c r="E172" s="44"/>
+      <c r="F172" s="44">
         <v>2001</v>
       </c>
-      <c r="G172" s="42"/>
-      <c r="H172" s="42"/>
-      <c r="I172" s="42"/>
-      <c r="J172" s="42">
+      <c r="G172" s="44"/>
+      <c r="H172" s="44"/>
+      <c r="I172" s="44"/>
+      <c r="J172" s="44">
         <v>2002</v>
       </c>
-      <c r="K172" s="42"/>
-      <c r="L172" s="42"/>
-      <c r="M172" s="42"/>
-      <c r="N172" s="42">
+      <c r="K172" s="44"/>
+      <c r="L172" s="44"/>
+      <c r="M172" s="44"/>
+      <c r="N172" s="44">
         <v>2003</v>
       </c>
-      <c r="O172" s="42"/>
-      <c r="P172" s="42"/>
-      <c r="Q172" s="42"/>
-      <c r="R172" s="42">
+      <c r="O172" s="44"/>
+      <c r="P172" s="44"/>
+      <c r="Q172" s="44"/>
+      <c r="R172" s="44">
         <v>2004</v>
       </c>
-      <c r="S172" s="42"/>
-      <c r="T172" s="42"/>
-      <c r="U172" s="42"/>
-      <c r="V172" s="42">
+      <c r="S172" s="44"/>
+      <c r="T172" s="44"/>
+      <c r="U172" s="44"/>
+      <c r="V172" s="44">
         <v>2005</v>
       </c>
-      <c r="W172" s="42"/>
-      <c r="X172" s="42"/>
-      <c r="Y172" s="42"/>
-      <c r="Z172" s="42">
+      <c r="W172" s="44"/>
+      <c r="X172" s="44"/>
+      <c r="Y172" s="44"/>
+      <c r="Z172" s="44">
         <v>2006</v>
       </c>
-      <c r="AA172" s="42"/>
-      <c r="AB172" s="42"/>
-      <c r="AC172" s="42"/>
-      <c r="AD172" s="42">
+      <c r="AA172" s="44"/>
+      <c r="AB172" s="44"/>
+      <c r="AC172" s="44"/>
+      <c r="AD172" s="44">
         <v>2007</v>
       </c>
-      <c r="AE172" s="42"/>
-      <c r="AF172" s="42"/>
-      <c r="AG172" s="42"/>
-      <c r="AH172" s="42">
+      <c r="AE172" s="44"/>
+      <c r="AF172" s="44"/>
+      <c r="AG172" s="44"/>
+      <c r="AH172" s="44">
         <v>2008</v>
       </c>
-      <c r="AI172" s="42"/>
-      <c r="AJ172" s="42"/>
-      <c r="AK172" s="42"/>
-      <c r="AL172" s="42">
+      <c r="AI172" s="44"/>
+      <c r="AJ172" s="44"/>
+      <c r="AK172" s="44"/>
+      <c r="AL172" s="44">
         <v>2009</v>
       </c>
-      <c r="AM172" s="42"/>
-      <c r="AN172" s="42"/>
-      <c r="AO172" s="42"/>
-      <c r="AP172" s="42">
+      <c r="AM172" s="44"/>
+      <c r="AN172" s="44"/>
+      <c r="AO172" s="44"/>
+      <c r="AP172" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ172" s="42"/>
-      <c r="AR172" s="42"/>
-      <c r="AS172" s="42"/>
-      <c r="AT172" s="42">
+      <c r="AQ172" s="44"/>
+      <c r="AR172" s="44"/>
+      <c r="AS172" s="44"/>
+      <c r="AT172" s="44">
         <v>2011</v>
       </c>
-      <c r="AU172" s="42"/>
-      <c r="AV172" s="42"/>
-      <c r="AW172" s="42"/>
-      <c r="AX172" s="42">
+      <c r="AU172" s="44"/>
+      <c r="AV172" s="44"/>
+      <c r="AW172" s="44"/>
+      <c r="AX172" s="44">
         <v>2012</v>
       </c>
-      <c r="AY172" s="42"/>
-      <c r="AZ172" s="42"/>
-      <c r="BA172" s="42"/>
-      <c r="BB172" s="42">
+      <c r="AY172" s="44"/>
+      <c r="AZ172" s="44"/>
+      <c r="BA172" s="44"/>
+      <c r="BB172" s="44">
         <v>2013</v>
       </c>
-      <c r="BC172" s="42"/>
-      <c r="BD172" s="42"/>
-      <c r="BE172" s="42"/>
-      <c r="BF172" s="42">
+      <c r="BC172" s="44"/>
+      <c r="BD172" s="44"/>
+      <c r="BE172" s="44"/>
+      <c r="BF172" s="44">
         <v>2014</v>
       </c>
-      <c r="BG172" s="42"/>
-      <c r="BH172" s="42"/>
-      <c r="BI172" s="42"/>
-      <c r="BJ172" s="42">
+      <c r="BG172" s="44"/>
+      <c r="BH172" s="44"/>
+      <c r="BI172" s="44"/>
+      <c r="BJ172" s="44">
         <v>2015</v>
       </c>
-      <c r="BK172" s="42"/>
-      <c r="BL172" s="42"/>
-      <c r="BM172" s="42"/>
-      <c r="BN172" s="42">
+      <c r="BK172" s="44"/>
+      <c r="BL172" s="44"/>
+      <c r="BM172" s="44"/>
+      <c r="BN172" s="44">
         <v>2016</v>
       </c>
-      <c r="BO172" s="42"/>
-      <c r="BP172" s="42"/>
-      <c r="BQ172" s="42"/>
-      <c r="BR172" s="42">
+      <c r="BO172" s="44"/>
+      <c r="BP172" s="44"/>
+      <c r="BQ172" s="44"/>
+      <c r="BR172" s="44">
         <v>2017</v>
       </c>
-      <c r="BS172" s="42"/>
-      <c r="BT172" s="42"/>
-      <c r="BU172" s="42"/>
-      <c r="BV172" s="42">
+      <c r="BS172" s="44"/>
+      <c r="BT172" s="44"/>
+      <c r="BU172" s="44"/>
+      <c r="BV172" s="44">
         <v>2018</v>
       </c>
-      <c r="BW172" s="42"/>
-      <c r="BX172" s="42"/>
-      <c r="BY172" s="42"/>
-      <c r="BZ172" s="42">
+      <c r="BW172" s="44"/>
+      <c r="BX172" s="44"/>
+      <c r="BY172" s="44"/>
+      <c r="BZ172" s="44">
         <v>2019</v>
       </c>
-      <c r="CA172" s="42"/>
-      <c r="CB172" s="42"/>
-      <c r="CC172" s="42"/>
-      <c r="CD172" s="41">
+      <c r="CA172" s="44"/>
+      <c r="CB172" s="44"/>
+      <c r="CC172" s="44"/>
+      <c r="CD172" s="45">
         <v>2020</v>
       </c>
-      <c r="CE172" s="41"/>
-      <c r="CF172" s="41"/>
-      <c r="CG172" s="41"/>
+      <c r="CE172" s="45"/>
+      <c r="CF172" s="45"/>
+      <c r="CG172" s="45"/>
       <c r="CH172" s="26">
         <v>2021</v>
       </c>
@@ -41792,28 +41785,28 @@
         <v>97.949053574598537</v>
       </c>
       <c r="CT175" s="38">
-        <v>120.80219683719848</v>
+        <v>120.80447031940209</v>
       </c>
       <c r="CU175" s="38">
-        <v>163.93689996841988</v>
+        <v>163.96682683993413</v>
       </c>
       <c r="CV175" s="38">
-        <v>102.79308471470398</v>
+        <v>102.79201136156505</v>
       </c>
       <c r="CW175" s="38">
-        <v>102.26069881180753</v>
+        <v>102.21341372919551</v>
       </c>
       <c r="CX175" s="38">
-        <v>124.44032330488074</v>
+        <v>124.5389973723708</v>
       </c>
       <c r="CY175" s="38">
-        <v>170.47528216530264</v>
+        <v>171.54427782632078</v>
       </c>
       <c r="CZ175" s="38">
-        <v>103.27355303552368</v>
+        <v>103.08020950806626</v>
       </c>
       <c r="DA175" s="38">
-        <v>102.98542722835691</v>
+        <v>102.87606721083147</v>
       </c>
       <c r="DB175" s="9"/>
       <c r="DC175" s="9"/>
@@ -42156,28 +42149,28 @@
         <v>83.541007361583311</v>
       </c>
       <c r="CT176" s="38">
-        <v>123.85551825619565</v>
+        <v>123.85551825617721</v>
       </c>
       <c r="CU176" s="38">
-        <v>372.87912818935871</v>
+        <v>372.87846339632125</v>
       </c>
       <c r="CV176" s="38">
-        <v>103.79072170166286</v>
+        <v>103.79071391585026</v>
       </c>
       <c r="CW176" s="38">
-        <v>88.546654762545856</v>
+        <v>88.561307540315141</v>
       </c>
       <c r="CX176" s="38">
-        <v>130.30611244083326</v>
+        <v>130.31076204548958</v>
       </c>
       <c r="CY176" s="38">
-        <v>377.51718361232059</v>
+        <v>377.52576305016936</v>
       </c>
       <c r="CZ176" s="38">
-        <v>103.42764972909744</v>
+        <v>103.40351033697969</v>
       </c>
       <c r="DA176" s="38">
-        <v>92.827834361909794</v>
+        <v>92.830750395851794</v>
       </c>
       <c r="DB176" s="9"/>
       <c r="DC176" s="9"/>
@@ -42520,28 +42513,28 @@
         <v>82.869983082908732</v>
       </c>
       <c r="CT177" s="38">
-        <v>125.69238577366923</v>
+        <v>125.69476377450638</v>
       </c>
       <c r="CU177" s="38">
-        <v>362.20218187973165</v>
+        <v>362.22357237472977</v>
       </c>
       <c r="CV177" s="38">
         <v>102.98701215739914</v>
       </c>
       <c r="CW177" s="38">
-        <v>87.689853231288936</v>
+        <v>87.709438942016547</v>
       </c>
       <c r="CX177" s="38">
-        <v>131.92164493874719</v>
+        <v>131.93582973617572</v>
       </c>
       <c r="CY177" s="38">
-        <v>364.6415547959067</v>
+        <v>364.67931400507081</v>
       </c>
       <c r="CZ177" s="38">
-        <v>102.62070320687322</v>
+        <v>102.57220120957331</v>
       </c>
       <c r="DA177" s="38">
-        <v>91.869494881094823</v>
+        <v>91.87344208532042</v>
       </c>
       <c r="DB177" s="9"/>
       <c r="DC177" s="9"/>
@@ -42884,28 +42877,28 @@
         <v>90.048509957599137</v>
       </c>
       <c r="CT178" s="38">
-        <v>107.79707099293951</v>
+        <v>107.79707099253338</v>
       </c>
       <c r="CU178" s="38">
-        <v>259.0902438632088</v>
+        <v>259.09024386320885</v>
       </c>
       <c r="CV178" s="38">
         <v>98.459837895284878</v>
       </c>
       <c r="CW178" s="38">
-        <v>94.187528121914283</v>
+        <v>94.271479453262629</v>
       </c>
       <c r="CX178" s="38">
-        <v>113.59766075119772</v>
+        <v>114.10110940470244</v>
       </c>
       <c r="CY178" s="38">
-        <v>290.65103822069545</v>
+        <v>290.78476981152079</v>
       </c>
       <c r="CZ178" s="38">
-        <v>99.553287518387805</v>
+        <v>99.073580932494281</v>
       </c>
       <c r="DA178" s="38">
-        <v>96.240206514668571</v>
+        <v>96.247691803965779</v>
       </c>
       <c r="DB178" s="9"/>
       <c r="DC178" s="9"/>
@@ -43248,28 +43241,28 @@
         <v>88.002365402622701</v>
       </c>
       <c r="CT179" s="38">
-        <v>150.68310827791962</v>
+        <v>150.6831082776956</v>
       </c>
       <c r="CU179" s="38">
-        <v>341.57344315050682</v>
+        <v>341.60386926449189</v>
       </c>
       <c r="CV179" s="38">
-        <v>103.85051823946651</v>
+        <v>103.8506853819476</v>
       </c>
       <c r="CW179" s="38">
-        <v>92.27096030731127</v>
+        <v>92.340662074382223</v>
       </c>
       <c r="CX179" s="38">
-        <v>156.68501454460642</v>
+        <v>156.75108950082176</v>
       </c>
       <c r="CY179" s="38">
-        <v>350.0932882105152</v>
+        <v>350.15939621687579</v>
       </c>
       <c r="CZ179" s="38">
-        <v>103.72918582882352</v>
+        <v>103.59940060355963</v>
       </c>
       <c r="DA179" s="38">
-        <v>95.670376031838742</v>
+        <v>95.68054786421844</v>
       </c>
       <c r="DB179" s="9"/>
       <c r="DC179" s="9"/>
@@ -43612,7 +43605,7 @@
         <v>85.14176621861607</v>
       </c>
       <c r="CT180" s="38">
-        <v>130.04006388736528</v>
+        <v>130.04006388729999</v>
       </c>
       <c r="CU180" s="38">
         <v>348.66568891287568</v>
@@ -43621,19 +43614,19 @@
         <v>106.12196948199627</v>
       </c>
       <c r="CW180" s="38">
-        <v>90.161563633919755</v>
+        <v>90.199830284773853</v>
       </c>
       <c r="CX180" s="38">
-        <v>136.61188814281121</v>
+        <v>136.63140068616846</v>
       </c>
       <c r="CY180" s="38">
-        <v>355.95044408426668</v>
+        <v>356.02933570282977</v>
       </c>
       <c r="CZ180" s="38">
-        <v>106.10956315931874</v>
+        <v>106.0030374217672</v>
       </c>
       <c r="DA180" s="38">
-        <v>94.132706300419557</v>
+        <v>94.138266781181585</v>
       </c>
       <c r="DB180" s="9"/>
       <c r="DC180" s="9"/>
@@ -43976,28 +43969,28 @@
         <v>115.05106553133906</v>
       </c>
       <c r="CT181" s="38">
-        <v>118.08935622164611</v>
+        <v>118.09027496115927</v>
       </c>
       <c r="CU181" s="38">
-        <v>105.66407188135338</v>
+        <v>105.62851758677563</v>
       </c>
       <c r="CV181" s="38">
-        <v>105.05295273330519</v>
+        <v>105.05186853140873</v>
       </c>
       <c r="CW181" s="38">
-        <v>119.93201407657317</v>
+        <v>119.9424365080408</v>
       </c>
       <c r="CX181" s="38">
-        <v>119.19610118876412</v>
+        <v>119.30760441580028</v>
       </c>
       <c r="CY181" s="38">
-        <v>106.63833883920518</v>
+        <v>107.40238616131737</v>
       </c>
       <c r="CZ181" s="38">
-        <v>105.46784602936219</v>
+        <v>105.46755822290157</v>
       </c>
       <c r="DA181" s="38">
-        <v>117.86266833606147</v>
+        <v>117.96435007487089</v>
       </c>
       <c r="DB181" s="9"/>
       <c r="DC181" s="9"/>
@@ -44340,28 +44333,28 @@
         <v>81.592696224375288</v>
       </c>
       <c r="CT182" s="38">
-        <v>121.54963334611742</v>
+        <v>121.54963334603697</v>
       </c>
       <c r="CU182" s="38">
         <v>350.47572867873657</v>
       </c>
       <c r="CV182" s="38">
-        <v>101.20943381803762</v>
+        <v>101.20932616855116</v>
       </c>
       <c r="CW182" s="38">
-        <v>85.911329578075495</v>
+        <v>85.948373793790594</v>
       </c>
       <c r="CX182" s="38">
-        <v>127.82849861458496</v>
+        <v>127.84892052488355</v>
       </c>
       <c r="CY182" s="38">
-        <v>358.28639435973997</v>
+        <v>358.33124043360539</v>
       </c>
       <c r="CZ182" s="38">
-        <v>101.24072731272229</v>
+        <v>101.18323009957351</v>
       </c>
       <c r="DA182" s="38">
-        <v>89.882754417229904</v>
+        <v>89.898087335898964</v>
       </c>
       <c r="DB182" s="9"/>
       <c r="DC182" s="9"/>
@@ -44704,28 +44697,28 @@
         <v>88.963120328539617</v>
       </c>
       <c r="CT183" s="38">
-        <v>121.14950433643376</v>
+        <v>121.14950433613782</v>
       </c>
       <c r="CU183" s="38">
-        <v>253.59996913228224</v>
+        <v>253.57784925703535</v>
       </c>
       <c r="CV183" s="38">
-        <v>97.694812335972784</v>
+        <v>97.692758944854972</v>
       </c>
       <c r="CW183" s="38">
-        <v>93.287089938308569</v>
+        <v>93.376767683459775</v>
       </c>
       <c r="CX183" s="38">
-        <v>126.95133836842723</v>
+        <v>127.04281491388694</v>
       </c>
       <c r="CY183" s="38">
-        <v>255.13241183956302</v>
+        <v>258.47607176669277</v>
       </c>
       <c r="CZ183" s="38">
-        <v>100.20051173819886</v>
+        <v>99.683797003222352</v>
       </c>
       <c r="DA183" s="38">
-        <v>95.897162100666691</v>
+        <v>95.90495594923199</v>
       </c>
       <c r="DB183" s="9"/>
       <c r="DC183" s="9"/>
@@ -45068,28 +45061,28 @@
         <v>112.14376673255705</v>
       </c>
       <c r="CT184" s="38">
-        <v>117.52925671555701</v>
+        <v>117.53082700252943</v>
       </c>
       <c r="CU184" s="38">
-        <v>140.19816057769216</v>
+        <v>140.23518684073312</v>
       </c>
       <c r="CV184" s="38">
-        <v>107.37187628730646</v>
+        <v>107.3681202437667</v>
       </c>
       <c r="CW184" s="38">
-        <v>115.12574663589947</v>
+        <v>115.08599879774648</v>
       </c>
       <c r="CX184" s="38">
-        <v>121.5241635835726</v>
+        <v>121.53052290077862</v>
       </c>
       <c r="CY184" s="38">
-        <v>139.22347167421108</v>
+        <v>139.06644759209283</v>
       </c>
       <c r="CZ184" s="38">
-        <v>109.38775858941784</v>
+        <v>109.38685434107332</v>
       </c>
       <c r="DA184" s="38">
-        <v>122.59743600042779</v>
+        <v>121.97647885555291</v>
       </c>
       <c r="DB184" s="9"/>
       <c r="DC184" s="9"/>
@@ -45432,28 +45425,28 @@
         <v>117.80630965942107</v>
       </c>
       <c r="CT185" s="38">
-        <v>121.0708501903472</v>
+        <v>121.07140730111514</v>
       </c>
       <c r="CU185" s="38">
-        <v>150.90112300577758</v>
+        <v>150.90002039564482</v>
       </c>
       <c r="CV185" s="38">
-        <v>107.11491454522148</v>
+        <v>107.114648874805</v>
       </c>
       <c r="CW185" s="38">
-        <v>123.01717885673386</v>
+        <v>122.99612383985409</v>
       </c>
       <c r="CX185" s="38">
-        <v>126.36275408453525</v>
+        <v>126.35799444280151</v>
       </c>
       <c r="CY185" s="38">
-        <v>153.18627461175058</v>
+        <v>153.18233744964144</v>
       </c>
       <c r="CZ185" s="38">
-        <v>109.23586437681946</v>
+        <v>109.23559655885313</v>
       </c>
       <c r="DA185" s="38">
-        <v>126.94295250871454</v>
+        <v>126.46627635239179</v>
       </c>
       <c r="DB185" s="9"/>
       <c r="DC185" s="9"/>
@@ -45796,28 +45789,28 @@
         <v>122.60991651889815</v>
       </c>
       <c r="CT186" s="38">
-        <v>125.2108481769812</v>
+        <v>125.21136519160352</v>
       </c>
       <c r="CU186" s="38">
-        <v>151.06674885558644</v>
+        <v>151.06369713350068</v>
       </c>
       <c r="CV186" s="38">
-        <v>107.6735690766931</v>
+        <v>107.67490162938435</v>
       </c>
       <c r="CW186" s="38">
-        <v>129.47075678212138</v>
+        <v>129.45312622563009</v>
       </c>
       <c r="CX186" s="38">
-        <v>132.21944113225328</v>
+        <v>132.2205375978842</v>
       </c>
       <c r="CY186" s="38">
-        <v>151.47424809144573</v>
+        <v>151.47441688513811</v>
       </c>
       <c r="CZ186" s="38">
-        <v>110.43265167414566</v>
+        <v>110.43328262789038</v>
       </c>
       <c r="DA186" s="38">
-        <v>135.64972020045408</v>
+        <v>135.5228640078017</v>
       </c>
       <c r="DB186" s="9"/>
       <c r="DC186" s="9"/>
@@ -46160,28 +46153,28 @@
         <v>126.70613356289905</v>
       </c>
       <c r="CT187" s="38">
-        <v>126.85370818085879</v>
+        <v>126.85375148870246</v>
       </c>
       <c r="CU187" s="38">
-        <v>139.57611935185611</v>
+        <v>139.6546105886901</v>
       </c>
       <c r="CV187" s="38">
-        <v>110.3278652373515</v>
+        <v>110.32248437913606</v>
       </c>
       <c r="CW187" s="38">
-        <v>132.47356333546364</v>
+        <v>132.50516608288387</v>
       </c>
       <c r="CX187" s="38">
-        <v>129.76514959557747</v>
+        <v>129.57501674376806</v>
       </c>
       <c r="CY187" s="38">
-        <v>132.26530628928467</v>
+        <v>131.86655943239242</v>
       </c>
       <c r="CZ187" s="38">
-        <v>111.30245621890664</v>
+        <v>111.3032171663892</v>
       </c>
       <c r="DA187" s="38">
-        <v>140.05039457078249</v>
+        <v>140.07964928086204</v>
       </c>
       <c r="DB187" s="9"/>
       <c r="DC187" s="9"/>
@@ -46524,28 +46517,28 @@
         <v>94.502469270522312</v>
       </c>
       <c r="CT188" s="38">
-        <v>105.40775300220628</v>
+        <v>105.41397185617333</v>
       </c>
       <c r="CU188" s="38">
-        <v>131.73156487142731</v>
+        <v>131.77454064073328</v>
       </c>
       <c r="CV188" s="38">
-        <v>104.20985017965442</v>
+        <v>104.21010733397587</v>
       </c>
       <c r="CW188" s="38">
-        <v>97.59387702574243</v>
+        <v>97.542378843009686</v>
       </c>
       <c r="CX188" s="38">
-        <v>112.49914066928011</v>
+        <v>112.57894412264642</v>
       </c>
       <c r="CY188" s="38">
-        <v>134.72434251485481</v>
+        <v>134.80978020930721</v>
       </c>
       <c r="CZ188" s="38">
-        <v>106.35800648828241</v>
+        <v>106.3579482792299</v>
       </c>
       <c r="DA188" s="38">
-        <v>106.25303562709011</v>
+        <v>105.48459402210111</v>
       </c>
       <c r="DB188" s="9"/>
       <c r="DC188" s="9"/>
@@ -46888,28 +46881,28 @@
         <v>114.38955179990322</v>
       </c>
       <c r="CT189" s="38">
-        <v>105.1898204563963</v>
+        <v>105.20980849495507</v>
       </c>
       <c r="CU189" s="38">
-        <v>111.77615392027107</v>
+        <v>111.78216069703457</v>
       </c>
       <c r="CV189" s="38">
-        <v>116.76528566993841</v>
+        <v>116.77045280294315</v>
       </c>
       <c r="CW189" s="38">
-        <v>117.39679133862546</v>
+        <v>117.41424033739251</v>
       </c>
       <c r="CX189" s="38">
-        <v>111.76869079776992</v>
+        <v>111.7850594124488</v>
       </c>
       <c r="CY189" s="38">
-        <v>111.87145284272239</v>
+        <v>111.87664169458873</v>
       </c>
       <c r="CZ189" s="38">
-        <v>113.97902335232817</v>
+        <v>113.75382959274762</v>
       </c>
       <c r="DA189" s="38">
-        <v>119.01836002562167</v>
+        <v>119.0147000058938</v>
       </c>
       <c r="DB189" s="9"/>
       <c r="DC189" s="9"/>
@@ -47252,28 +47245,28 @@
         <v>110.96305172023544</v>
       </c>
       <c r="CT190" s="38">
-        <v>102.4839567613074</v>
+        <v>102.50526445129391</v>
       </c>
       <c r="CU190" s="38">
-        <v>111.57376850000024</v>
+        <v>111.57988943494269</v>
       </c>
       <c r="CV190" s="38">
-        <v>112.55191012188853</v>
+        <v>112.55940828970881</v>
       </c>
       <c r="CW190" s="38">
-        <v>114.23930452809283</v>
+        <v>114.26131964661685</v>
       </c>
       <c r="CX190" s="38">
-        <v>109.90378701672947</v>
+        <v>109.9225157911774</v>
       </c>
       <c r="CY190" s="38">
-        <v>111.23203786466451</v>
+        <v>111.23842939742958</v>
       </c>
       <c r="CZ190" s="38">
-        <v>111.97028514513845</v>
+        <v>111.74641423907832</v>
       </c>
       <c r="DA190" s="38">
-        <v>115.09953183584263</v>
+        <v>115.09390978811074</v>
       </c>
       <c r="DB190" s="9"/>
       <c r="DC190" s="9"/>
@@ -47980,28 +47973,28 @@
         <v>134.24908991407179</v>
       </c>
       <c r="CT192" s="38">
-        <v>135.02119012513322</v>
+        <v>135.02119012512958</v>
       </c>
       <c r="CU192" s="38">
-        <v>117.39275462646452</v>
+        <v>117.3927545016427</v>
       </c>
       <c r="CV192" s="38">
         <v>140.59561820632979</v>
       </c>
       <c r="CW192" s="38">
-        <v>142.62990628150564</v>
+        <v>142.62990577325013</v>
       </c>
       <c r="CX192" s="38">
-        <v>143.81789860421136</v>
+        <v>143.81779193332522</v>
       </c>
       <c r="CY192" s="38">
-        <v>117.55241764176037</v>
+        <v>117.55244976782524</v>
       </c>
       <c r="CZ192" s="38">
         <v>143.11034187281564</v>
       </c>
       <c r="DA192" s="38">
-        <v>147.75241658980934</v>
+        <v>147.75258690897914</v>
       </c>
       <c r="DB192" s="9"/>
       <c r="DC192" s="9"/>
@@ -48344,28 +48337,28 @@
         <v>129.22706067010051</v>
       </c>
       <c r="CT193" s="38">
-        <v>130.16620763764081</v>
+        <v>130.21878048049146</v>
       </c>
       <c r="CU193" s="38">
-        <v>118.04564549868974</v>
+        <v>118.04674723877532</v>
       </c>
       <c r="CV193" s="38">
         <v>123.90888041311652</v>
       </c>
       <c r="CW193" s="38">
-        <v>130.55055671372173</v>
+        <v>130.57046708463565</v>
       </c>
       <c r="CX193" s="38">
-        <v>132.9963223565012</v>
+        <v>132.97086343668985</v>
       </c>
       <c r="CY193" s="38">
-        <v>118.32669152444308</v>
+        <v>118.32668447786405</v>
       </c>
       <c r="CZ193" s="38">
         <v>132.53517846958749</v>
       </c>
       <c r="DA193" s="38">
-        <v>134.19013380066596</v>
+        <v>134.65023025636614</v>
       </c>
       <c r="DB193" s="9"/>
       <c r="DC193" s="9"/>
@@ -48708,28 +48701,28 @@
         <v>164.05081533106201</v>
       </c>
       <c r="CT194" s="38">
-        <v>118.86704313743573</v>
+        <v>118.8687956388514</v>
       </c>
       <c r="CU194" s="38">
-        <v>88.258756136302935</v>
+        <v>88.271581500391179</v>
       </c>
       <c r="CV194" s="38">
-        <v>121.86052775012163</v>
+        <v>121.85455662468294</v>
       </c>
       <c r="CW194" s="38">
-        <v>169.51865540164027</v>
+        <v>169.44566363162969</v>
       </c>
       <c r="CX194" s="38">
-        <v>120.03439208779301</v>
+        <v>120.05799179242094</v>
       </c>
       <c r="CY194" s="38">
-        <v>91.085405159942965</v>
+        <v>90.935925584383838</v>
       </c>
       <c r="CZ194" s="38">
-        <v>138.54091945433359</v>
+        <v>138.78311105693382</v>
       </c>
       <c r="DA194" s="38">
-        <v>177.12648094330015</v>
+        <v>176.95453183302971</v>
       </c>
       <c r="DB194" s="9"/>
       <c r="DC194" s="9"/>
@@ -49072,28 +49065,28 @@
         <v>212.42556937664406</v>
       </c>
       <c r="CT195" s="38">
-        <v>117.79226453959231</v>
+        <v>117.79247096698155</v>
       </c>
       <c r="CU195" s="38">
-        <v>70.479374786281795</v>
+        <v>70.480199132913853</v>
       </c>
       <c r="CV195" s="38">
-        <v>141.43918012863207</v>
+        <v>141.42260862811622</v>
       </c>
       <c r="CW195" s="38">
-        <v>216.61065321889419</v>
+        <v>216.5992056832259</v>
       </c>
       <c r="CX195" s="38">
-        <v>106.96813092467197</v>
+        <v>106.96811290939033</v>
       </c>
       <c r="CY195" s="38">
-        <v>69.738435215770266</v>
+        <v>69.737560795571</v>
       </c>
       <c r="CZ195" s="38">
-        <v>146.4201423636521</v>
+        <v>146.41532583829425</v>
       </c>
       <c r="DA195" s="38">
-        <v>223.64229947322821</v>
+        <v>223.76129586262556</v>
       </c>
       <c r="DB195" s="9"/>
       <c r="DC195" s="9"/>
@@ -49436,28 +49429,28 @@
         <v>148.81564477059527</v>
       </c>
       <c r="CT196" s="38">
-        <v>105.10666475333198</v>
+        <v>105.10537359205171</v>
       </c>
       <c r="CU196" s="38">
-        <v>73.578113280932499</v>
+        <v>73.580425713147889</v>
       </c>
       <c r="CV196" s="38">
-        <v>126.69770080418881</v>
+        <v>126.74841275713102</v>
       </c>
       <c r="CW196" s="38">
-        <v>152.21441818830749</v>
+        <v>151.94397949361468</v>
       </c>
       <c r="CX196" s="38">
-        <v>100.34028771112611</v>
+        <v>100.37621544993183</v>
       </c>
       <c r="CY196" s="38">
-        <v>74.444612028122364</v>
+        <v>74.33134057747867</v>
       </c>
       <c r="CZ196" s="38">
-        <v>126.33552900393829</v>
+        <v>126.40864644705646</v>
       </c>
       <c r="DA196" s="38">
-        <v>145.84219407218913</v>
+        <v>144.50254034872353</v>
       </c>
       <c r="DB196" s="9"/>
       <c r="DC196" s="9"/>
@@ -49800,28 +49793,28 @@
         <v>175.02116789973269</v>
       </c>
       <c r="CT197" s="38">
-        <v>128.19573276722898</v>
+        <v>128.19753110928613</v>
       </c>
       <c r="CU197" s="38">
-        <v>87.549101474705481</v>
+        <v>87.56904720892166</v>
       </c>
       <c r="CV197" s="38">
-        <v>118.08834781714319</v>
+        <v>118.07191598990599</v>
       </c>
       <c r="CW197" s="38">
-        <v>181.84407053548344</v>
+        <v>181.90620333366104</v>
       </c>
       <c r="CX197" s="38">
-        <v>134.05119718726138</v>
+        <v>134.03093433121421</v>
       </c>
       <c r="CY197" s="38">
-        <v>91.406286214281835</v>
+        <v>91.408945054439926</v>
       </c>
       <c r="CZ197" s="38">
-        <v>146.13588003462678</v>
+        <v>146.13003347653623</v>
       </c>
       <c r="DA197" s="38">
-        <v>190.17820936628726</v>
+        <v>190.40139219098597</v>
       </c>
       <c r="DB197" s="9"/>
       <c r="DC197" s="9"/>
@@ -50164,28 +50157,28 @@
         <v>132.8673830226073</v>
       </c>
       <c r="CT198" s="38">
-        <v>115.88104194979476</v>
+        <v>115.88105843147625</v>
       </c>
       <c r="CU198" s="38">
-        <v>120.65823056492447</v>
+        <v>120.67124345912559</v>
       </c>
       <c r="CV198" s="38">
-        <v>120.26422337800471</v>
+        <v>120.26322741170594</v>
       </c>
       <c r="CW198" s="38">
-        <v>141.44707206495809</v>
+        <v>141.44821397391888</v>
       </c>
       <c r="CX198" s="38">
-        <v>115.95660515035246</v>
+        <v>115.94268040763463</v>
       </c>
       <c r="CY198" s="38">
-        <v>121.22828208085295</v>
+        <v>120.99592749234456</v>
       </c>
       <c r="CZ198" s="38">
-        <v>121.16406610927746</v>
+        <v>121.41446182967303</v>
       </c>
       <c r="DA198" s="38">
-        <v>146.15164652550106</v>
+        <v>146.35821735713688</v>
       </c>
       <c r="DB198" s="9"/>
       <c r="DC198" s="9"/>
@@ -50681,28 +50674,28 @@
         <v>117.37795979862346</v>
       </c>
       <c r="CT200" s="38">
-        <v>111.90601495594301</v>
+        <v>111.91505182481667</v>
       </c>
       <c r="CU200" s="38">
-        <v>115.96869213566248</v>
+        <v>115.99441227049563</v>
       </c>
       <c r="CV200" s="38">
-        <v>114.14186992181486</v>
+        <v>114.14471557905294</v>
       </c>
       <c r="CW200" s="38">
-        <v>120.99954179834754</v>
+        <v>120.95210512174339</v>
       </c>
       <c r="CX200" s="38">
-        <v>116.76144646774327</v>
+        <v>116.79118025182579</v>
       </c>
       <c r="CY200" s="38">
-        <v>116.41407773274106</v>
+        <v>116.51616735683787</v>
       </c>
       <c r="CZ200" s="38">
-        <v>115.42210399885886</v>
+        <v>115.25239524537507</v>
       </c>
       <c r="DA200" s="38">
-        <v>124.60593656273029</v>
+        <v>124.50184977918649</v>
       </c>
       <c r="DB200" s="9"/>
       <c r="DC200" s="9"/>
@@ -51194,7 +51187,7 @@
     </row>
     <row r="207" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="209" spans="1:152" x14ac:dyDescent="0.2">
@@ -51204,7 +51197,7 @@
     </row>
     <row r="210" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="211" spans="1:152" x14ac:dyDescent="0.2">
@@ -51214,132 +51207,132 @@
     </row>
     <row r="213" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
-      <c r="B213" s="42">
+      <c r="B213" s="44">
         <v>2000</v>
       </c>
-      <c r="C213" s="42"/>
-      <c r="D213" s="42"/>
-      <c r="E213" s="42"/>
-      <c r="F213" s="42">
+      <c r="C213" s="44"/>
+      <c r="D213" s="44"/>
+      <c r="E213" s="44"/>
+      <c r="F213" s="44">
         <v>2001</v>
       </c>
-      <c r="G213" s="42"/>
-      <c r="H213" s="42"/>
-      <c r="I213" s="42"/>
-      <c r="J213" s="42">
+      <c r="G213" s="44"/>
+      <c r="H213" s="44"/>
+      <c r="I213" s="44"/>
+      <c r="J213" s="44">
         <v>2002</v>
       </c>
-      <c r="K213" s="42"/>
-      <c r="L213" s="42"/>
-      <c r="M213" s="42"/>
-      <c r="N213" s="42">
+      <c r="K213" s="44"/>
+      <c r="L213" s="44"/>
+      <c r="M213" s="44"/>
+      <c r="N213" s="44">
         <v>2003</v>
       </c>
-      <c r="O213" s="42"/>
-      <c r="P213" s="42"/>
-      <c r="Q213" s="42"/>
-      <c r="R213" s="42">
+      <c r="O213" s="44"/>
+      <c r="P213" s="44"/>
+      <c r="Q213" s="44"/>
+      <c r="R213" s="44">
         <v>2004</v>
       </c>
-      <c r="S213" s="42"/>
-      <c r="T213" s="42"/>
-      <c r="U213" s="42"/>
-      <c r="V213" s="42">
+      <c r="S213" s="44"/>
+      <c r="T213" s="44"/>
+      <c r="U213" s="44"/>
+      <c r="V213" s="44">
         <v>2005</v>
       </c>
-      <c r="W213" s="42"/>
-      <c r="X213" s="42"/>
-      <c r="Y213" s="42"/>
-      <c r="Z213" s="42">
+      <c r="W213" s="44"/>
+      <c r="X213" s="44"/>
+      <c r="Y213" s="44"/>
+      <c r="Z213" s="44">
         <v>2006</v>
       </c>
-      <c r="AA213" s="42"/>
-      <c r="AB213" s="42"/>
-      <c r="AC213" s="42"/>
-      <c r="AD213" s="42">
+      <c r="AA213" s="44"/>
+      <c r="AB213" s="44"/>
+      <c r="AC213" s="44"/>
+      <c r="AD213" s="44">
         <v>2007</v>
       </c>
-      <c r="AE213" s="42"/>
-      <c r="AF213" s="42"/>
-      <c r="AG213" s="42"/>
-      <c r="AH213" s="42">
+      <c r="AE213" s="44"/>
+      <c r="AF213" s="44"/>
+      <c r="AG213" s="44"/>
+      <c r="AH213" s="44">
         <v>2008</v>
       </c>
-      <c r="AI213" s="42"/>
-      <c r="AJ213" s="42"/>
-      <c r="AK213" s="42"/>
-      <c r="AL213" s="42">
+      <c r="AI213" s="44"/>
+      <c r="AJ213" s="44"/>
+      <c r="AK213" s="44"/>
+      <c r="AL213" s="44">
         <v>2009</v>
       </c>
-      <c r="AM213" s="42"/>
-      <c r="AN213" s="42"/>
-      <c r="AO213" s="42"/>
-      <c r="AP213" s="42">
+      <c r="AM213" s="44"/>
+      <c r="AN213" s="44"/>
+      <c r="AO213" s="44"/>
+      <c r="AP213" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ213" s="42"/>
-      <c r="AR213" s="42"/>
-      <c r="AS213" s="42"/>
-      <c r="AT213" s="42">
+      <c r="AQ213" s="44"/>
+      <c r="AR213" s="44"/>
+      <c r="AS213" s="44"/>
+      <c r="AT213" s="44">
         <v>2011</v>
       </c>
-      <c r="AU213" s="42"/>
-      <c r="AV213" s="42"/>
-      <c r="AW213" s="42"/>
-      <c r="AX213" s="42">
+      <c r="AU213" s="44"/>
+      <c r="AV213" s="44"/>
+      <c r="AW213" s="44"/>
+      <c r="AX213" s="44">
         <v>2012</v>
       </c>
-      <c r="AY213" s="42"/>
-      <c r="AZ213" s="42"/>
-      <c r="BA213" s="42"/>
-      <c r="BB213" s="42">
+      <c r="AY213" s="44"/>
+      <c r="AZ213" s="44"/>
+      <c r="BA213" s="44"/>
+      <c r="BB213" s="44">
         <v>2013</v>
       </c>
-      <c r="BC213" s="42"/>
-      <c r="BD213" s="42"/>
-      <c r="BE213" s="42"/>
-      <c r="BF213" s="42">
+      <c r="BC213" s="44"/>
+      <c r="BD213" s="44"/>
+      <c r="BE213" s="44"/>
+      <c r="BF213" s="44">
         <v>2014</v>
       </c>
-      <c r="BG213" s="42"/>
-      <c r="BH213" s="42"/>
-      <c r="BI213" s="42"/>
-      <c r="BJ213" s="42">
+      <c r="BG213" s="44"/>
+      <c r="BH213" s="44"/>
+      <c r="BI213" s="44"/>
+      <c r="BJ213" s="44">
         <v>2015</v>
       </c>
-      <c r="BK213" s="42"/>
-      <c r="BL213" s="42"/>
-      <c r="BM213" s="42"/>
-      <c r="BN213" s="42">
+      <c r="BK213" s="44"/>
+      <c r="BL213" s="44"/>
+      <c r="BM213" s="44"/>
+      <c r="BN213" s="44">
         <v>2016</v>
       </c>
-      <c r="BO213" s="42"/>
-      <c r="BP213" s="42"/>
-      <c r="BQ213" s="42"/>
-      <c r="BR213" s="42">
+      <c r="BO213" s="44"/>
+      <c r="BP213" s="44"/>
+      <c r="BQ213" s="44"/>
+      <c r="BR213" s="44">
         <v>2017</v>
       </c>
-      <c r="BS213" s="42"/>
-      <c r="BT213" s="42"/>
-      <c r="BU213" s="42"/>
-      <c r="BV213" s="42">
+      <c r="BS213" s="44"/>
+      <c r="BT213" s="44"/>
+      <c r="BU213" s="44"/>
+      <c r="BV213" s="44">
         <v>2018</v>
       </c>
-      <c r="BW213" s="42"/>
-      <c r="BX213" s="42"/>
-      <c r="BY213" s="42"/>
-      <c r="BZ213" s="42">
+      <c r="BW213" s="44"/>
+      <c r="BX213" s="44"/>
+      <c r="BY213" s="44"/>
+      <c r="BZ213" s="44">
         <v>2019</v>
       </c>
-      <c r="CA213" s="42"/>
-      <c r="CB213" s="42"/>
-      <c r="CC213" s="42"/>
-      <c r="CD213" s="41">
+      <c r="CA213" s="44"/>
+      <c r="CB213" s="44"/>
+      <c r="CC213" s="44"/>
+      <c r="CD213" s="45">
         <v>2020</v>
       </c>
-      <c r="CE213" s="41"/>
-      <c r="CF213" s="41"/>
-      <c r="CG213" s="41"/>
+      <c r="CE213" s="45"/>
+      <c r="CF213" s="45"/>
+      <c r="CG213" s="45"/>
       <c r="CH213" s="26">
         <v>2021</v>
       </c>
@@ -51984,28 +51977,28 @@
         <v>14.179655628465424</v>
       </c>
       <c r="CT216" s="38">
-        <v>15.219564304604733</v>
+        <v>15.215959593231283</v>
       </c>
       <c r="CU216" s="38">
-        <v>14.765512043547751</v>
+        <v>14.755359287978623</v>
       </c>
       <c r="CV216" s="38">
-        <v>11.649544882048184</v>
+        <v>11.645198510027845</v>
       </c>
       <c r="CW216" s="38">
-        <v>14.878985785582172</v>
+        <v>14.967410687227222</v>
       </c>
       <c r="CX216" s="38">
-        <v>16.384120186910316</v>
+        <v>16.32652135598526</v>
       </c>
       <c r="CY216" s="38">
-        <v>14.437259590646278</v>
+        <v>14.531079880837389</v>
       </c>
       <c r="CZ216" s="38">
-        <v>12.122658958074892</v>
+        <v>12.190899186319625</v>
       </c>
       <c r="DA216" s="38">
-        <v>13.405213773771768</v>
+        <v>13.514738944898836</v>
       </c>
       <c r="DB216" s="9"/>
       <c r="DC216" s="9"/>
@@ -52348,28 +52341,28 @@
         <v>1.2180355635034359</v>
       </c>
       <c r="CT217" s="38">
-        <v>0.97931881997468939</v>
+        <v>0.9787632972269823</v>
       </c>
       <c r="CU217" s="38">
-        <v>1.0286631180242118</v>
+        <v>1.0277047405712159</v>
       </c>
       <c r="CV217" s="38">
-        <v>0.87545137388506855</v>
+        <v>0.87535665692815601</v>
       </c>
       <c r="CW217" s="38">
-        <v>0.85349757726596254</v>
+        <v>0.85413045300232837</v>
       </c>
       <c r="CX217" s="38">
-        <v>1.3681311408762074</v>
+        <v>1.3670364316805341</v>
       </c>
       <c r="CY217" s="38">
-        <v>1.2055480151079718</v>
+        <v>1.2034378640045962</v>
       </c>
       <c r="CZ217" s="38">
-        <v>0.95864876936856114</v>
+        <v>0.95789373753592955</v>
       </c>
       <c r="DA217" s="38">
-        <v>0.81092494481389454</v>
+        <v>0.82257618657706022</v>
       </c>
       <c r="DB217" s="9"/>
       <c r="DC217" s="9"/>
@@ -52712,28 +52705,28 @@
         <v>2.1954851550850489</v>
       </c>
       <c r="CT218" s="38">
-        <v>2.3324866946008327</v>
+        <v>2.3358773615667956</v>
       </c>
       <c r="CU218" s="38">
-        <v>3.3972087736727317</v>
+        <v>3.4014192711179079</v>
       </c>
       <c r="CV218" s="38">
-        <v>2.4795441234062787</v>
+        <v>2.4793466315195105</v>
       </c>
       <c r="CW218" s="38">
-        <v>2.6629476801557268</v>
+        <v>2.6704210730878746</v>
       </c>
       <c r="CX218" s="38">
-        <v>2.4978699867047731</v>
+        <v>2.496471366886186</v>
       </c>
       <c r="CY218" s="38">
-        <v>3.0528103517876737</v>
+        <v>3.0507137316028556</v>
       </c>
       <c r="CZ218" s="38">
-        <v>2.1764665636962484</v>
+        <v>2.1813901982492037</v>
       </c>
       <c r="DA218" s="38">
-        <v>2.703274618732685</v>
+        <v>2.7498058058193902</v>
       </c>
       <c r="DB218" s="9"/>
       <c r="DC218" s="9"/>
@@ -53076,28 +53069,28 @@
         <v>0.2717746691678633</v>
       </c>
       <c r="CT219" s="38">
-        <v>0.1422673764568804</v>
+        <v>0.14218667468735399</v>
       </c>
       <c r="CU219" s="38">
-        <v>0.23683620260355917</v>
+        <v>0.2366491536945472</v>
       </c>
       <c r="CV219" s="38">
-        <v>0.23025155837357886</v>
+        <v>0.23023321919007123</v>
       </c>
       <c r="CW219" s="38">
-        <v>0.29938506013475558</v>
+        <v>0.31002889311554394</v>
       </c>
       <c r="CX219" s="38">
-        <v>0.18805967428295731</v>
+        <v>0.1909137440053012</v>
       </c>
       <c r="CY219" s="38">
-        <v>0.3480385194148562</v>
+        <v>0.34734351332319185</v>
       </c>
       <c r="CZ219" s="38">
-        <v>0.20373292604834933</v>
+        <v>0.2177553233648355</v>
       </c>
       <c r="DA219" s="38">
-        <v>0.3554196221326576</v>
+        <v>0.35992455386890493</v>
       </c>
       <c r="DB219" s="9"/>
       <c r="DC219" s="9"/>
@@ -53440,28 +53433,28 @@
         <v>0.13907313389543774</v>
       </c>
       <c r="CT220" s="38">
-        <v>0.22088011610679761</v>
+        <v>0.22075482092510701</v>
       </c>
       <c r="CU220" s="38">
-        <v>0.21574175652980038</v>
+        <v>0.21575949799608943</v>
       </c>
       <c r="CV220" s="38">
-        <v>0.18754899812837764</v>
+        <v>0.18755708440986388</v>
       </c>
       <c r="CW220" s="38">
-        <v>0.1875776894731036</v>
+        <v>0.19048757092772214</v>
       </c>
       <c r="CX220" s="38">
-        <v>0.21075027186611114</v>
+        <v>0.21047486699350051</v>
       </c>
       <c r="CY220" s="38">
-        <v>0.25537156854669013</v>
+        <v>0.25493440595247552</v>
       </c>
       <c r="CZ220" s="38">
-        <v>0.1794865968498997</v>
+        <v>0.18093490947889998</v>
       </c>
       <c r="DA220" s="38">
-        <v>0.16912028798483703</v>
+        <v>0.17013438036861073</v>
       </c>
       <c r="DB220" s="9"/>
       <c r="DC220" s="9"/>
@@ -53804,28 +53797,28 @@
         <v>0.72786854888753683</v>
       </c>
       <c r="CT221" s="38">
-        <v>0.65392819035311367</v>
+        <v>0.65355724681623983</v>
       </c>
       <c r="CU221" s="38">
-        <v>0.69724602839091054</v>
+        <v>0.69669535620697154</v>
       </c>
       <c r="CV221" s="38">
-        <v>0.76779859372418313</v>
+        <v>0.7677374397436989</v>
       </c>
       <c r="CW221" s="38">
-        <v>0.65538528125595519</v>
+        <v>0.66245386638288617</v>
       </c>
       <c r="CX221" s="38">
-        <v>0.8407276899774101</v>
+        <v>0.84097131644527368</v>
       </c>
       <c r="CY221" s="38">
-        <v>0.80578649663959889</v>
+        <v>0.80501415157799172</v>
       </c>
       <c r="CZ221" s="38">
-        <v>0.9034703460310668</v>
+        <v>0.89885299376558248</v>
       </c>
       <c r="DA221" s="38">
-        <v>0.63425386241880211</v>
+        <v>0.64927553639501856</v>
       </c>
       <c r="DB221" s="9"/>
       <c r="DC221" s="9"/>
@@ -54168,28 +54161,28 @@
         <v>7.0382289179454869</v>
       </c>
       <c r="CT222" s="38">
-        <v>8.5138640136524479</v>
+        <v>8.5093493592173139</v>
       </c>
       <c r="CU222" s="38">
-        <v>6.9855423169515793</v>
+        <v>6.9750883212148507</v>
       </c>
       <c r="CV222" s="38">
-        <v>4.5380155776092028</v>
+        <v>4.5349272367121216</v>
       </c>
       <c r="CW222" s="38">
-        <v>7.131447339448588</v>
+        <v>7.1200457245974969</v>
       </c>
       <c r="CX222" s="38">
-        <v>8.2916420164254756</v>
+        <v>8.2422476156967441</v>
       </c>
       <c r="CY222" s="38">
-        <v>6.4346600801559157</v>
+        <v>6.4666292227018207</v>
       </c>
       <c r="CZ222" s="38">
-        <v>4.4306520914826972</v>
+        <v>4.4167057163888455</v>
       </c>
       <c r="DA222" s="38">
-        <v>5.9330212826517386</v>
+        <v>5.8912399625528575</v>
       </c>
       <c r="DB222" s="9"/>
       <c r="DC222" s="9"/>
@@ -54532,28 +54525,28 @@
         <v>0.26213586436585767</v>
       </c>
       <c r="CT223" s="38">
-        <v>0.24114983151424316</v>
+        <v>0.24101303825145021</v>
       </c>
       <c r="CU223" s="38">
-        <v>0.38351994136479278</v>
+        <v>0.38321704431684134</v>
       </c>
       <c r="CV223" s="38">
-        <v>0.20802148660346681</v>
+        <v>0.20798038054359269</v>
       </c>
       <c r="CW223" s="38">
-        <v>0.47890002354162453</v>
+        <v>0.48018185780267325</v>
       </c>
       <c r="CX223" s="38">
-        <v>0.32048706958089762</v>
+        <v>0.32002097048726419</v>
       </c>
       <c r="CY223" s="38">
-        <v>0.49717760313594878</v>
+        <v>0.49673872470727559</v>
       </c>
       <c r="CZ223" s="38">
-        <v>0.30294095578882935</v>
+        <v>0.30400255393532905</v>
       </c>
       <c r="DA223" s="38">
-        <v>0.39911829206214916</v>
+        <v>0.39911790432086086</v>
       </c>
       <c r="DB223" s="9"/>
       <c r="DC223" s="9"/>
@@ -54896,28 +54889,28 @@
         <v>2.3270537756147545</v>
       </c>
       <c r="CT224" s="38">
-        <v>2.1356692619457265</v>
+        <v>2.1344577945400367</v>
       </c>
       <c r="CU224" s="38">
-        <v>1.8207539060101678</v>
+        <v>1.8188259028601983</v>
       </c>
       <c r="CV224" s="38">
-        <v>2.3629131703180284</v>
+        <v>2.3620598609808274</v>
       </c>
       <c r="CW224" s="38">
-        <v>2.6098451343064553</v>
+        <v>2.6796612483106994</v>
       </c>
       <c r="CX224" s="38">
-        <v>2.6664523371964868</v>
+        <v>2.6583850437904548</v>
       </c>
       <c r="CY224" s="38">
-        <v>1.8378669558576224</v>
+        <v>1.9062682669671835</v>
       </c>
       <c r="CZ224" s="38">
-        <v>2.9672607088092393</v>
+        <v>3.0333637536010003</v>
       </c>
       <c r="DA224" s="38">
-        <v>2.4000808629750061</v>
+        <v>2.4726646149961335</v>
       </c>
       <c r="DB224" s="9"/>
       <c r="DC224" s="9"/>
@@ -55260,28 +55253,28 @@
         <v>16.308821069668767</v>
       </c>
       <c r="CT225" s="38">
-        <v>17.853716564539585</v>
+        <v>17.846200334737279</v>
       </c>
       <c r="CU225" s="38">
-        <v>19.063520909309808</v>
+        <v>19.088330565554941</v>
       </c>
       <c r="CV225" s="38">
-        <v>15.903370905837225</v>
+        <v>15.893102242772267</v>
       </c>
       <c r="CW225" s="38">
-        <v>16.429723607251553</v>
+        <v>16.395561429770474</v>
       </c>
       <c r="CX225" s="38">
-        <v>15.924662375550163</v>
+        <v>16.009673548237235</v>
       </c>
       <c r="CY225" s="38">
-        <v>15.63976797211993</v>
+        <v>15.709296496022329</v>
       </c>
       <c r="CZ225" s="38">
-        <v>18.31067944552457</v>
+        <v>18.246404575719417</v>
       </c>
       <c r="DA225" s="38">
-        <v>17.929592395359176</v>
+        <v>18.031278222984266</v>
       </c>
       <c r="DB225" s="9"/>
       <c r="DC225" s="9"/>
@@ -55624,28 +55617,28 @@
         <v>3.2245699777290513</v>
       </c>
       <c r="CT226" s="38">
-        <v>3.1347059962501462</v>
+        <v>3.1332667847315561</v>
       </c>
       <c r="CU226" s="38">
-        <v>3.6984723101669754</v>
+        <v>3.6948238833764933</v>
       </c>
       <c r="CV226" s="38">
-        <v>2.9881261854925047</v>
+        <v>2.9875082680188507</v>
       </c>
       <c r="CW226" s="38">
-        <v>3.5608647576551933</v>
+        <v>3.5573535557854425</v>
       </c>
       <c r="CX226" s="38">
-        <v>3.1510711873203125</v>
+        <v>3.1480433503785119</v>
       </c>
       <c r="CY226" s="38">
-        <v>3.2184476101539592</v>
+        <v>3.213216011616042</v>
       </c>
       <c r="CZ226" s="38">
-        <v>2.3407954238932476</v>
+        <v>2.3341891611566568</v>
       </c>
       <c r="DA226" s="38">
-        <v>2.9864737925213496</v>
+        <v>3.0206415351181293</v>
       </c>
       <c r="DB226" s="9"/>
       <c r="DC226" s="9"/>
@@ -55988,28 +55981,28 @@
         <v>1.7726155726317707</v>
       </c>
       <c r="CT227" s="38">
-        <v>1.7517862885112991</v>
+        <v>1.7510622096225048</v>
       </c>
       <c r="CU227" s="38">
-        <v>2.0553376322088268</v>
+        <v>2.0516142308568384</v>
       </c>
       <c r="CV227" s="38">
-        <v>1.9307194791952711</v>
+        <v>1.9317596261760765</v>
       </c>
       <c r="CW227" s="38">
-        <v>1.8885336555398917</v>
+        <v>1.8816144847374843</v>
       </c>
       <c r="CX227" s="38">
-        <v>1.8694402184418226</v>
+        <v>1.8695631149556489</v>
       </c>
       <c r="CY227" s="38">
-        <v>1.9458114631795962</v>
+        <v>1.9442994475335806</v>
       </c>
       <c r="CZ227" s="38">
-        <v>1.8245095703063989</v>
+        <v>1.8200601638667835</v>
       </c>
       <c r="DA227" s="38">
-        <v>2.0454845165729831</v>
+        <v>2.0742348965887216</v>
       </c>
       <c r="DB227" s="9"/>
       <c r="DC227" s="9"/>
@@ -56352,28 +56345,28 @@
         <v>5.9856236578707129</v>
       </c>
       <c r="CT228" s="38">
-        <v>6.8541237187007376</v>
+        <v>6.8503276336947545</v>
       </c>
       <c r="CU228" s="38">
-        <v>7.443661628746594</v>
+        <v>7.4677977145650054</v>
       </c>
       <c r="CV228" s="38">
-        <v>5.8643018132359686</v>
+        <v>5.853163856851789</v>
       </c>
       <c r="CW228" s="38">
-        <v>4.9416486658697734</v>
+        <v>4.924262930156015</v>
       </c>
       <c r="CX228" s="38">
-        <v>4.1945735748068627</v>
+        <v>4.2557036283766285</v>
       </c>
       <c r="CY228" s="38">
-        <v>5.2517601229325193</v>
+        <v>5.3070123382045722</v>
       </c>
       <c r="CZ228" s="38">
-        <v>8.5128113337173055</v>
+        <v>8.4757717968437127</v>
       </c>
       <c r="DA228" s="38">
-        <v>6.0512306690231119</v>
+        <v>5.980685187044581</v>
       </c>
       <c r="DB228" s="9"/>
       <c r="DC228" s="9"/>
@@ -56716,28 +56709,28 @@
         <v>5.3260118614372303</v>
       </c>
       <c r="CT229" s="38">
-        <v>6.1131005610773981</v>
+        <v>6.1115437066884599</v>
       </c>
       <c r="CU229" s="38">
-        <v>5.8660493381874135</v>
+        <v>5.8740947367566028</v>
       </c>
       <c r="CV229" s="38">
-        <v>5.1202234279134808</v>
+        <v>5.1206704917255506</v>
       </c>
       <c r="CW229" s="38">
-        <v>6.0386765281866941</v>
+        <v>6.0323304590915328</v>
       </c>
       <c r="CX229" s="38">
-        <v>6.7095773949811672</v>
+        <v>6.7363634545264466</v>
       </c>
       <c r="CY229" s="38">
-        <v>5.2237487758538581</v>
+        <v>5.244768698668131</v>
       </c>
       <c r="CZ229" s="38">
-        <v>5.6325631176076207</v>
+        <v>5.6163834538522615</v>
       </c>
       <c r="DA229" s="38">
-        <v>6.8464034172417323</v>
+        <v>6.9557166042328342</v>
       </c>
       <c r="DB229" s="9"/>
       <c r="DC229" s="9"/>
@@ -57080,28 +57073,28 @@
         <v>52.16014280515224</v>
       </c>
       <c r="CT230" s="38">
-        <v>48.152629748331151</v>
+        <v>48.172566615429645</v>
       </c>
       <c r="CU230" s="38">
-        <v>47.603455206809045</v>
+        <v>47.617876913343522</v>
       </c>
       <c r="CV230" s="38">
-        <v>56.270129778622767</v>
+        <v>56.282997864907024</v>
       </c>
       <c r="CW230" s="38">
-        <v>50.790657427028393</v>
+        <v>50.782364948902448</v>
       </c>
       <c r="CX230" s="38">
-        <v>48.387367119157574</v>
+        <v>48.354038554680947</v>
       </c>
       <c r="CY230" s="38">
-        <v>51.809613802690613</v>
+        <v>51.764783721463147</v>
       </c>
       <c r="CZ230" s="38">
-        <v>51.091506884960147</v>
+        <v>51.314586965991204</v>
       </c>
       <c r="DA230" s="38">
-        <v>50.230425808353196</v>
+        <v>49.85576233878745</v>
       </c>
       <c r="DB230" s="9"/>
       <c r="DC230" s="9"/>
@@ -57444,28 +57437,28 @@
         <v>42.772568258578794</v>
       </c>
       <c r="CT231" s="38">
-        <v>42.447494893964375</v>
+        <v>42.46645856756215</v>
       </c>
       <c r="CU231" s="38">
-        <v>44.764755209590597</v>
+        <v>44.777991108611495</v>
       </c>
       <c r="CV231" s="38">
-        <v>45.422291959608835</v>
+        <v>45.436024059538994</v>
       </c>
       <c r="CW231" s="38">
-        <v>43.829205196497924</v>
+        <v>43.827525668658929</v>
       </c>
       <c r="CX231" s="38">
-        <v>44.674502116729606</v>
+        <v>44.645698441432849</v>
       </c>
       <c r="CY231" s="38">
-        <v>46.773597228177557</v>
+        <v>46.73788065200737</v>
       </c>
       <c r="CZ231" s="38">
-        <v>46.336776961919618</v>
+        <v>46.573371164844502</v>
       </c>
       <c r="DA231" s="38">
-        <v>42.63824691453938</v>
+        <v>42.316991967772751</v>
       </c>
       <c r="DB231" s="9"/>
       <c r="DC231" s="9"/>
@@ -57808,28 +57801,28 @@
         <v>0.30058444136297735</v>
       </c>
       <c r="CT232" s="38">
-        <v>0.81257083883463621</v>
+        <v>0.81210990459147281</v>
       </c>
       <c r="CU232" s="38">
-        <v>0.3599092540883192</v>
+        <v>0.3596250043281361</v>
       </c>
       <c r="CV232" s="38">
-        <v>0.89140221929283059</v>
+        <v>0.89133122047313007</v>
       </c>
       <c r="CW232" s="38">
-        <v>0.89944848665244581</v>
+        <v>0.89841412334808568</v>
       </c>
       <c r="CX232" s="38">
-        <v>7.9479122976594957E-2</v>
+        <v>7.9349724481092232E-2</v>
       </c>
       <c r="CY232" s="38">
-        <v>1.1945624000682834E-2</v>
+        <v>1.1924310277396311E-2</v>
       </c>
       <c r="CZ232" s="38">
-        <v>0.10745971257779537</v>
+        <v>0.10715428541832325</v>
       </c>
       <c r="DA232" s="38">
-        <v>4.1646733011204098E-2</v>
+        <v>4.1377283835592943E-2</v>
       </c>
       <c r="DB232" s="9"/>
       <c r="DC232" s="9"/>
@@ -58172,28 +58165,28 @@
         <v>6.8104580831895021</v>
       </c>
       <c r="CT233" s="38">
-        <v>3.6083176944158843</v>
+        <v>3.6062708610346697</v>
       </c>
       <c r="CU233" s="38">
-        <v>2.083545155005369</v>
+        <v>2.0817963935480894</v>
       </c>
       <c r="CV233" s="38">
-        <v>9.2918559227052402</v>
+        <v>9.2911158406311092</v>
       </c>
       <c r="CW233" s="38">
-        <v>5.5073572439131704</v>
+        <v>5.5010136421840565</v>
       </c>
       <c r="CX233" s="38">
-        <v>2.6933293934190807</v>
+        <v>2.6889476111081789</v>
       </c>
       <c r="CY233" s="38">
-        <v>0.62709114990443948</v>
+        <v>0.62895105299863174</v>
       </c>
       <c r="CZ233" s="38">
-        <v>2.6127937629782321</v>
+        <v>2.6053675549773954</v>
       </c>
       <c r="DA233" s="38">
-        <v>7.234180252081762</v>
+        <v>7.1694819976990845</v>
       </c>
       <c r="DB233" s="9"/>
       <c r="DC233" s="9"/>
@@ -58536,28 +58529,28 @@
         <v>2.2765320220209655</v>
       </c>
       <c r="CT234" s="38">
-        <v>1.2842463211162418</v>
+        <v>1.2877272822413566</v>
       </c>
       <c r="CU234" s="38">
-        <v>0.39524558812475696</v>
+        <v>0.39846440685578882</v>
       </c>
       <c r="CV234" s="38">
-        <v>0.66457967701586762</v>
+        <v>0.66452674426380143</v>
       </c>
       <c r="CW234" s="38">
-        <v>0.5546464999648546</v>
+        <v>0.55541151471137185</v>
       </c>
       <c r="CX234" s="38">
-        <v>0.94005648603229019</v>
+        <v>0.94004277765882605</v>
       </c>
       <c r="CY234" s="38">
-        <v>4.3969798006079275</v>
+        <v>4.3860277061797559</v>
       </c>
       <c r="CZ234" s="38">
-        <v>2.0344764474845078</v>
+        <v>2.0286939607509957</v>
       </c>
       <c r="DA234" s="38">
-        <v>0.31635190872085822</v>
+        <v>0.32791108948002207</v>
       </c>
       <c r="DB234" s="9"/>
       <c r="DC234" s="9"/>
@@ -58900,28 +58893,28 @@
         <v>17.351380496713585</v>
       </c>
       <c r="CT235" s="38">
-        <v>18.774089382524537</v>
+        <v>18.76527345660179</v>
       </c>
       <c r="CU235" s="38">
-        <v>18.567511840333388</v>
+        <v>18.538433233122912</v>
       </c>
       <c r="CV235" s="38">
-        <v>16.176954433491805</v>
+        <v>16.178701382292854</v>
       </c>
       <c r="CW235" s="38">
-        <v>17.900633180137891</v>
+        <v>17.854662934099856</v>
       </c>
       <c r="CX235" s="38">
-        <v>19.303850318381937</v>
+        <v>19.309766541096561</v>
       </c>
       <c r="CY235" s="38">
-        <v>18.113358634543186</v>
+        <v>17.994839901677139</v>
       </c>
       <c r="CZ235" s="38">
-        <v>18.475154711440389</v>
+        <v>18.248109271969749</v>
       </c>
       <c r="DA235" s="38">
-        <v>18.434768022515858</v>
+        <v>18.598220493329435</v>
       </c>
       <c r="DB235" s="9"/>
       <c r="DC235" s="9"/>
@@ -59264,28 +59257,28 @@
         <v>1.8888366317690783</v>
       </c>
       <c r="CT236" s="38">
-        <v>1.2739513872772816</v>
+        <v>1.2735428388293215</v>
       </c>
       <c r="CU236" s="38">
-        <v>1.7542183717316706</v>
+        <v>1.7516864287307521</v>
       </c>
       <c r="CV236" s="38">
-        <v>1.4480775636890031</v>
+        <v>1.4442061818652281</v>
       </c>
       <c r="CW236" s="38">
-        <v>1.8028009449577516</v>
+        <v>1.7982952970924089</v>
       </c>
       <c r="CX236" s="38">
-        <v>1.3336973708879929</v>
+        <v>1.3327412737418669</v>
       </c>
       <c r="CY236" s="38">
-        <v>1.6543306391292227</v>
+        <v>1.6526459301799972</v>
       </c>
       <c r="CZ236" s="38">
-        <v>2.4611897330649937</v>
+        <v>2.4467298787894602</v>
       </c>
       <c r="DA236" s="38">
-        <v>2.49749740363821</v>
+        <v>2.5203907587657581</v>
       </c>
       <c r="DB236" s="9"/>
       <c r="DC236" s="9"/>
@@ -59628,28 +59621,28 @@
         <v>3.0604566347669442</v>
       </c>
       <c r="CT237" s="38">
-        <v>3.9799921663709927</v>
+        <v>3.9772260014240159</v>
       </c>
       <c r="CU237" s="38">
-        <v>3.6322269548390453</v>
+        <v>3.6281808052650666</v>
       </c>
       <c r="CV237" s="38">
-        <v>3.1073806483833808</v>
+        <v>3.1099167068277462</v>
       </c>
       <c r="CW237" s="38">
-        <v>3.3289933000136753</v>
+        <v>3.335620803740432</v>
       </c>
       <c r="CX237" s="38">
-        <v>3.5111365258286917</v>
+        <v>3.4884423363806198</v>
       </c>
       <c r="CY237" s="38">
-        <v>2.7473822116391244</v>
+        <v>2.7211143736986623</v>
       </c>
       <c r="CZ237" s="38">
-        <v>2.5772481290274278</v>
+        <v>2.5628087407586055</v>
       </c>
       <c r="DA237" s="38">
-        <v>2.7242226357027395</v>
+        <v>2.7971051236639779</v>
       </c>
       <c r="DB237" s="9"/>
       <c r="DC237" s="9"/>
@@ -59992,28 +59985,28 @@
         <v>9.3951757243750329</v>
       </c>
       <c r="CT238" s="38">
-        <v>8.9414410688848331</v>
+        <v>8.9384117504903564</v>
       </c>
       <c r="CU238" s="38">
-        <v>8.5752972904485087</v>
+        <v>8.5579490501081477</v>
       </c>
       <c r="CV238" s="38">
-        <v>8.8284112635981682</v>
+        <v>8.8322628956315778</v>
       </c>
       <c r="CW238" s="38">
-        <v>9.467463463573063</v>
+        <v>9.422959806030363</v>
       </c>
       <c r="CX238" s="38">
-        <v>9.7368594855383286</v>
+        <v>9.7417251497135151</v>
       </c>
       <c r="CY238" s="38">
-        <v>9.3369716911613345</v>
+        <v>9.3469728397258454</v>
       </c>
       <c r="CZ238" s="38">
-        <v>10.459130229838397</v>
+        <v>10.433760411380941</v>
       </c>
       <c r="DA238" s="38">
-        <v>10.212354974964681</v>
+        <v>10.288004794855087</v>
       </c>
       <c r="DB238" s="9"/>
       <c r="DC238" s="9"/>
@@ -60356,28 +60349,28 @@
         <v>3.006911505802528</v>
       </c>
       <c r="CT239" s="38">
-        <v>4.5787047599914272</v>
+        <v>4.5760928658580964</v>
       </c>
       <c r="CU239" s="38">
-        <v>4.6057692233141623</v>
+        <v>4.6006169490189457</v>
       </c>
       <c r="CV239" s="38">
-        <v>2.7930849578212529</v>
+        <v>2.7923155979683023</v>
       </c>
       <c r="CW239" s="38">
-        <v>3.3013754715933992</v>
+        <v>3.2977870272366552</v>
       </c>
       <c r="CX239" s="38">
-        <v>4.7221569361269244</v>
+        <v>4.7468577812605597</v>
       </c>
       <c r="CY239" s="38">
-        <v>4.3746740926135024</v>
+        <v>4.2741067580726346</v>
       </c>
       <c r="CZ239" s="38">
-        <v>2.9775866195095673</v>
+        <v>2.8048102410407449</v>
       </c>
       <c r="DA239" s="38">
-        <v>3.0006930082102241</v>
+        <v>2.9927198160446111</v>
       </c>
       <c r="DB239" s="9"/>
       <c r="DC239" s="9"/>
@@ -61374,7 +61367,7 @@
     </row>
     <row r="248" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="250" spans="1:152" x14ac:dyDescent="0.2">
@@ -61384,7 +61377,7 @@
     </row>
     <row r="251" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="252" spans="1:152" x14ac:dyDescent="0.2">
@@ -61394,132 +61387,132 @@
     </row>
     <row r="254" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
-      <c r="B254" s="42">
+      <c r="B254" s="44">
         <v>2000</v>
       </c>
-      <c r="C254" s="42"/>
-      <c r="D254" s="42"/>
-      <c r="E254" s="42"/>
-      <c r="F254" s="42">
+      <c r="C254" s="44"/>
+      <c r="D254" s="44"/>
+      <c r="E254" s="44"/>
+      <c r="F254" s="44">
         <v>2001</v>
       </c>
-      <c r="G254" s="42"/>
-      <c r="H254" s="42"/>
-      <c r="I254" s="42"/>
-      <c r="J254" s="42">
+      <c r="G254" s="44"/>
+      <c r="H254" s="44"/>
+      <c r="I254" s="44"/>
+      <c r="J254" s="44">
         <v>2002</v>
       </c>
-      <c r="K254" s="42"/>
-      <c r="L254" s="42"/>
-      <c r="M254" s="42"/>
-      <c r="N254" s="42">
+      <c r="K254" s="44"/>
+      <c r="L254" s="44"/>
+      <c r="M254" s="44"/>
+      <c r="N254" s="44">
         <v>2003</v>
       </c>
-      <c r="O254" s="42"/>
-      <c r="P254" s="42"/>
-      <c r="Q254" s="42"/>
-      <c r="R254" s="42">
+      <c r="O254" s="44"/>
+      <c r="P254" s="44"/>
+      <c r="Q254" s="44"/>
+      <c r="R254" s="44">
         <v>2004</v>
       </c>
-      <c r="S254" s="42"/>
-      <c r="T254" s="42"/>
-      <c r="U254" s="42"/>
-      <c r="V254" s="42">
+      <c r="S254" s="44"/>
+      <c r="T254" s="44"/>
+      <c r="U254" s="44"/>
+      <c r="V254" s="44">
         <v>2005</v>
       </c>
-      <c r="W254" s="42"/>
-      <c r="X254" s="42"/>
-      <c r="Y254" s="42"/>
-      <c r="Z254" s="42">
+      <c r="W254" s="44"/>
+      <c r="X254" s="44"/>
+      <c r="Y254" s="44"/>
+      <c r="Z254" s="44">
         <v>2006</v>
       </c>
-      <c r="AA254" s="42"/>
-      <c r="AB254" s="42"/>
-      <c r="AC254" s="42"/>
-      <c r="AD254" s="42">
+      <c r="AA254" s="44"/>
+      <c r="AB254" s="44"/>
+      <c r="AC254" s="44"/>
+      <c r="AD254" s="44">
         <v>2007</v>
       </c>
-      <c r="AE254" s="42"/>
-      <c r="AF254" s="42"/>
-      <c r="AG254" s="42"/>
-      <c r="AH254" s="42">
+      <c r="AE254" s="44"/>
+      <c r="AF254" s="44"/>
+      <c r="AG254" s="44"/>
+      <c r="AH254" s="44">
         <v>2008</v>
       </c>
-      <c r="AI254" s="42"/>
-      <c r="AJ254" s="42"/>
-      <c r="AK254" s="42"/>
-      <c r="AL254" s="42">
+      <c r="AI254" s="44"/>
+      <c r="AJ254" s="44"/>
+      <c r="AK254" s="44"/>
+      <c r="AL254" s="44">
         <v>2009</v>
       </c>
-      <c r="AM254" s="42"/>
-      <c r="AN254" s="42"/>
-      <c r="AO254" s="42"/>
-      <c r="AP254" s="42">
+      <c r="AM254" s="44"/>
+      <c r="AN254" s="44"/>
+      <c r="AO254" s="44"/>
+      <c r="AP254" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ254" s="42"/>
-      <c r="AR254" s="42"/>
-      <c r="AS254" s="42"/>
-      <c r="AT254" s="42">
+      <c r="AQ254" s="44"/>
+      <c r="AR254" s="44"/>
+      <c r="AS254" s="44"/>
+      <c r="AT254" s="44">
         <v>2011</v>
       </c>
-      <c r="AU254" s="42"/>
-      <c r="AV254" s="42"/>
-      <c r="AW254" s="42"/>
-      <c r="AX254" s="42">
+      <c r="AU254" s="44"/>
+      <c r="AV254" s="44"/>
+      <c r="AW254" s="44"/>
+      <c r="AX254" s="44">
         <v>2012</v>
       </c>
-      <c r="AY254" s="42"/>
-      <c r="AZ254" s="42"/>
-      <c r="BA254" s="42"/>
-      <c r="BB254" s="42">
+      <c r="AY254" s="44"/>
+      <c r="AZ254" s="44"/>
+      <c r="BA254" s="44"/>
+      <c r="BB254" s="44">
         <v>2013</v>
       </c>
-      <c r="BC254" s="42"/>
-      <c r="BD254" s="42"/>
-      <c r="BE254" s="42"/>
-      <c r="BF254" s="42">
+      <c r="BC254" s="44"/>
+      <c r="BD254" s="44"/>
+      <c r="BE254" s="44"/>
+      <c r="BF254" s="44">
         <v>2014</v>
       </c>
-      <c r="BG254" s="42"/>
-      <c r="BH254" s="42"/>
-      <c r="BI254" s="42"/>
-      <c r="BJ254" s="42">
+      <c r="BG254" s="44"/>
+      <c r="BH254" s="44"/>
+      <c r="BI254" s="44"/>
+      <c r="BJ254" s="44">
         <v>2015</v>
       </c>
-      <c r="BK254" s="42"/>
-      <c r="BL254" s="42"/>
-      <c r="BM254" s="42"/>
-      <c r="BN254" s="42">
+      <c r="BK254" s="44"/>
+      <c r="BL254" s="44"/>
+      <c r="BM254" s="44"/>
+      <c r="BN254" s="44">
         <v>2016</v>
       </c>
-      <c r="BO254" s="42"/>
-      <c r="BP254" s="42"/>
-      <c r="BQ254" s="42"/>
-      <c r="BR254" s="42">
+      <c r="BO254" s="44"/>
+      <c r="BP254" s="44"/>
+      <c r="BQ254" s="44"/>
+      <c r="BR254" s="44">
         <v>2017</v>
       </c>
-      <c r="BS254" s="42"/>
-      <c r="BT254" s="42"/>
-      <c r="BU254" s="42"/>
-      <c r="BV254" s="42">
+      <c r="BS254" s="44"/>
+      <c r="BT254" s="44"/>
+      <c r="BU254" s="44"/>
+      <c r="BV254" s="44">
         <v>2018</v>
       </c>
-      <c r="BW254" s="42"/>
-      <c r="BX254" s="42"/>
-      <c r="BY254" s="42"/>
-      <c r="BZ254" s="42">
+      <c r="BW254" s="44"/>
+      <c r="BX254" s="44"/>
+      <c r="BY254" s="44"/>
+      <c r="BZ254" s="44">
         <v>2019</v>
       </c>
-      <c r="CA254" s="42"/>
-      <c r="CB254" s="42"/>
-      <c r="CC254" s="42"/>
-      <c r="CD254" s="41">
+      <c r="CA254" s="44"/>
+      <c r="CB254" s="44"/>
+      <c r="CC254" s="44"/>
+      <c r="CD254" s="45">
         <v>2020</v>
       </c>
-      <c r="CE254" s="41"/>
-      <c r="CF254" s="41"/>
-      <c r="CG254" s="41"/>
+      <c r="CE254" s="45"/>
+      <c r="CF254" s="45"/>
+      <c r="CG254" s="45"/>
       <c r="CH254" s="26">
         <v>2021</v>
       </c>
@@ -62164,28 +62157,28 @@
         <v>16.99229331551161</v>
       </c>
       <c r="CT257" s="38">
-        <v>14.098756771694578</v>
+        <v>14.09629049271447</v>
       </c>
       <c r="CU257" s="38">
-        <v>10.445098819932932</v>
+        <v>10.438326223876363</v>
       </c>
       <c r="CV257" s="38">
-        <v>12.935703216472124</v>
+        <v>12.931334392448271</v>
       </c>
       <c r="CW257" s="38">
-        <v>17.605497355272242</v>
+        <v>17.711372360951881</v>
       </c>
       <c r="CX257" s="38">
-        <v>15.37310030477853</v>
+        <v>15.310816200574164</v>
       </c>
       <c r="CY257" s="38">
-        <v>9.8589088041722874</v>
+        <v>9.8697884693385483</v>
       </c>
       <c r="CZ257" s="38">
-        <v>13.548704018349387</v>
+        <v>13.630456691187495</v>
       </c>
       <c r="DA257" s="38">
-        <v>16.2194716481645</v>
+        <v>16.355699080860276</v>
       </c>
       <c r="DB257" s="9"/>
       <c r="DC257" s="9"/>
@@ -62528,28 +62521,28 @@
         <v>1.7113814391463227</v>
       </c>
       <c r="CT258" s="38">
-        <v>0.88483474985775956</v>
+        <v>0.88440423709520921</v>
       </c>
       <c r="CU258" s="38">
-        <v>0.31992328727200897</v>
+        <v>0.31969668155239572</v>
       </c>
       <c r="CV258" s="38">
-        <v>0.96276097904098756</v>
+        <v>0.9626808879675337</v>
       </c>
       <c r="CW258" s="38">
-        <v>1.1663096257235945</v>
+        <v>1.1665238376498828</v>
       </c>
       <c r="CX258" s="38">
-        <v>1.2259207797240022</v>
+        <v>1.2252080779596686</v>
       </c>
       <c r="CY258" s="38">
-        <v>0.37175197960115031</v>
+        <v>0.3714182746974044</v>
       </c>
       <c r="CZ258" s="38">
-        <v>1.0698228012166366</v>
+        <v>1.0676576383314411</v>
       </c>
       <c r="DA258" s="38">
-        <v>1.0885319357625574</v>
+        <v>1.1032147901039653</v>
       </c>
       <c r="DB258" s="9"/>
       <c r="DC258" s="9"/>
@@ -62892,28 +62885,28 @@
         <v>3.1097094350100858</v>
       </c>
       <c r="CT259" s="38">
-        <v>2.0766515753830066</v>
+        <v>2.0797989361366338</v>
       </c>
       <c r="CU259" s="38">
-        <v>1.0877070269152638</v>
+        <v>1.0892323397183317</v>
       </c>
       <c r="CV259" s="38">
-        <v>2.7481116003898585</v>
+        <v>2.7479612248984449</v>
       </c>
       <c r="CW259" s="38">
-        <v>3.6744895476326853</v>
+        <v>3.6825346763986198</v>
       </c>
       <c r="CX259" s="38">
-        <v>2.2108192546524932</v>
+        <v>2.2099064218306239</v>
       </c>
       <c r="CY259" s="38">
-        <v>0.97462863714269199</v>
+        <v>0.97471246121818444</v>
       </c>
       <c r="CZ259" s="38">
-        <v>2.4479694858314116</v>
+        <v>2.4510583018426981</v>
       </c>
       <c r="DA259" s="38">
-        <v>3.6665496647109643</v>
+        <v>3.7263860108792235</v>
       </c>
       <c r="DB259" s="9"/>
       <c r="DC259" s="9"/>
@@ -63256,28 +63249,28 @@
         <v>0.35425745752917481</v>
       </c>
       <c r="CT260" s="38">
-        <v>0.14769023880592447</v>
+        <v>0.14761838072145561</v>
       </c>
       <c r="CU260" s="38">
-        <v>0.10600779194454141</v>
+        <v>0.10594756131227342</v>
       </c>
       <c r="CV260" s="38">
-        <v>0.26692450431538628</v>
+        <v>0.26690989832067302</v>
       </c>
       <c r="CW260" s="38">
-        <v>0.38460989283726299</v>
+        <v>0.39777297957310487</v>
       </c>
       <c r="CX260" s="38">
-        <v>0.19329728663712151</v>
+        <v>0.19541476507111974</v>
       </c>
       <c r="CY260" s="38">
-        <v>0.13939941003198605</v>
+        <v>0.1391790049902181</v>
       </c>
       <c r="CZ260" s="38">
-        <v>0.2362080004038144</v>
+        <v>0.25331498426738702</v>
       </c>
       <c r="DA260" s="38">
-        <v>0.46017560115959838</v>
+        <v>0.46558283006825013</v>
       </c>
       <c r="DB260" s="9"/>
       <c r="DC260" s="9"/>
@@ -63620,28 +63613,28 @@
         <v>0.18549638574784005</v>
       </c>
       <c r="CT261" s="38">
-        <v>0.16403838399011675</v>
+        <v>0.16395857177886788</v>
       </c>
       <c r="CU261" s="38">
-        <v>7.3247173764581189E-2</v>
+        <v>7.3262917705584074E-2</v>
       </c>
       <c r="CV261" s="38">
-        <v>0.20613468003090385</v>
+        <v>0.20614837519908955</v>
       </c>
       <c r="CW261" s="38">
-        <v>0.24598003968145354</v>
+        <v>0.24950950302561536</v>
       </c>
       <c r="CX261" s="38">
-        <v>0.15705079811287123</v>
+        <v>0.1568193765529656</v>
       </c>
       <c r="CY261" s="38">
-        <v>8.4916925381471733E-2</v>
+        <v>8.4829880991047685E-2</v>
       </c>
       <c r="CZ261" s="38">
-        <v>0.19971930255191267</v>
+        <v>0.20128670223437403</v>
       </c>
       <c r="DA261" s="38">
-        <v>0.2202708168419463</v>
+        <v>0.22138298264123102</v>
       </c>
       <c r="DB261" s="9"/>
       <c r="DC261" s="9"/>
@@ -63984,28 +63977,28 @@
         <v>1.0034525834316479</v>
       </c>
       <c r="CT262" s="38">
-        <v>0.56273809518543549</v>
+        <v>0.56246429724391478</v>
       </c>
       <c r="CU262" s="38">
-        <v>0.23190899644124088</v>
+        <v>0.23177723230175568</v>
       </c>
       <c r="CV262" s="38">
-        <v>0.82582303776303312</v>
+        <v>0.82577784907960894</v>
       </c>
       <c r="CW262" s="38">
-        <v>0.87954684387835635</v>
+        <v>0.88830754372908949</v>
       </c>
       <c r="CX262" s="38">
-        <v>0.71856543747223234</v>
+        <v>0.71885402705615442</v>
       </c>
       <c r="CY262" s="38">
-        <v>0.26353357163838309</v>
+        <v>0.26345346914944862</v>
       </c>
       <c r="CZ262" s="38">
-        <v>0.98276201630300153</v>
+        <v>0.97728294419313355</v>
       </c>
       <c r="DA262" s="38">
-        <v>0.8395785020033113</v>
+        <v>0.85869442960376019</v>
       </c>
       <c r="DB262" s="9"/>
       <c r="DC262" s="9"/>
@@ -64348,28 +64341,28 @@
         <v>7.1805762699266973</v>
       </c>
       <c r="CT263" s="38">
-        <v>8.0680649309019898</v>
+        <v>8.0643751134079622</v>
       </c>
       <c r="CU263" s="38">
-        <v>7.6667895901725114</v>
+        <v>7.6595912622691955</v>
       </c>
       <c r="CV263" s="38">
-        <v>4.9306332690868144</v>
+        <v>4.9274514279718948</v>
       </c>
       <c r="CW263" s="38">
-        <v>7.1949251171700119</v>
+        <v>7.1799818648456695</v>
       </c>
       <c r="CX263" s="38">
-        <v>8.1222800559337003</v>
+        <v>8.068402946137244</v>
       </c>
       <c r="CY263" s="38">
-        <v>7.0245375810340214</v>
+        <v>7.0153641802263467</v>
       </c>
       <c r="CZ263" s="38">
-        <v>4.8488255495756052</v>
+        <v>4.826469119839933</v>
       </c>
       <c r="DA263" s="38">
-        <v>6.2724667955378104</v>
+        <v>6.2177282574385329</v>
       </c>
       <c r="DB263" s="9"/>
       <c r="DC263" s="9"/>
@@ -64712,28 +64705,28 @@
         <v>0.37710450044082533</v>
       </c>
       <c r="CT264" s="38">
-        <v>0.22201726084365869</v>
+        <v>0.22190923924532766</v>
       </c>
       <c r="CU264" s="38">
-        <v>0.12690267076608366</v>
+        <v>0.12683056825402739</v>
       </c>
       <c r="CV264" s="38">
-        <v>0.23460225563087569</v>
+        <v>0.23456199425373001</v>
       </c>
       <c r="CW264" s="38">
-        <v>0.67449408244919495</v>
+        <v>0.67574293705483635</v>
       </c>
       <c r="CX264" s="38">
-        <v>0.2927401496852462</v>
+        <v>0.29234213863595182</v>
       </c>
       <c r="CY264" s="38">
-        <v>0.16154247844625924</v>
+        <v>0.16152120119523677</v>
       </c>
       <c r="CZ264" s="38">
-        <v>0.34537565496309908</v>
+        <v>0.34627301843673469</v>
       </c>
       <c r="DA264" s="38">
-        <v>0.5533042339898302</v>
+        <v>0.55274721454609288</v>
       </c>
       <c r="DB264" s="9"/>
       <c r="DC264" s="9"/>
@@ -65076,28 +65069,28 @@
         <v>3.070315244279016</v>
       </c>
       <c r="CT265" s="38">
-        <v>1.9727215367266884</v>
+        <v>1.9717617170851016</v>
       </c>
       <c r="CU265" s="38">
-        <v>0.83261228265669951</v>
+        <v>0.83198766076279818</v>
       </c>
       <c r="CV265" s="38">
-        <v>2.7607128902142639</v>
+        <v>2.7598427347572962</v>
       </c>
       <c r="CW265" s="38">
-        <v>3.3851422058996818</v>
+        <v>3.4709990186750592</v>
       </c>
       <c r="CX265" s="38">
-        <v>2.4524265425608651</v>
+        <v>2.4438684473304364</v>
       </c>
       <c r="CY265" s="38">
-        <v>0.83859822089632252</v>
+        <v>0.85930999687066167</v>
       </c>
       <c r="CZ265" s="38">
-        <v>3.4180212075039051</v>
+        <v>3.5071139820417945</v>
       </c>
       <c r="DA265" s="38">
-        <v>3.1185940981584839</v>
+        <v>3.2099625655792186</v>
       </c>
       <c r="DB265" s="9"/>
       <c r="DC265" s="9"/>
@@ -65440,28 +65433,28 @@
         <v>17.070018242242384</v>
       </c>
       <c r="CT266" s="38">
-        <v>16.999497220729658</v>
+        <v>16.993485762634844</v>
       </c>
       <c r="CU266" s="38">
-        <v>15.768905799077107</v>
+        <v>15.788759833087465</v>
       </c>
       <c r="CV266" s="38">
-        <v>16.906107595579435</v>
+        <v>16.89620374326492</v>
       </c>
       <c r="CW266" s="38">
-        <v>17.267979461086249</v>
+        <v>17.23126783709532</v>
       </c>
       <c r="CX266" s="38">
-        <v>15.300550595445808</v>
+        <v>15.385342089506333</v>
       </c>
       <c r="CY266" s="38">
-        <v>13.077458438106573</v>
+        <v>13.161959993093244</v>
       </c>
       <c r="CZ266" s="38">
-        <v>19.320783006294821</v>
+        <v>19.224813115210019</v>
       </c>
       <c r="DA266" s="38">
-        <v>18.223330972467817</v>
+        <v>18.404593358553939</v>
       </c>
       <c r="DB266" s="9"/>
       <c r="DC266" s="9"/>
@@ -65804,28 +65797,28 @@
         <v>3.2128452738054194</v>
       </c>
       <c r="CT267" s="38">
-        <v>2.8974146588327274</v>
+        <v>2.8963049361612478</v>
       </c>
       <c r="CU267" s="38">
-        <v>2.8423048693521298</v>
+        <v>2.8401515365707395</v>
       </c>
       <c r="CV267" s="38">
-        <v>3.1841533163008982</v>
+        <v>3.1835821255564158</v>
       </c>
       <c r="CW267" s="38">
-        <v>3.5024620795762713</v>
+        <v>3.4982354549221126</v>
       </c>
       <c r="CX267" s="38">
-        <v>2.9116461762792234</v>
+        <v>2.9096987491444297</v>
       </c>
       <c r="CY267" s="38">
-        <v>2.4458627981966563</v>
+        <v>2.4440912757726183</v>
       </c>
       <c r="CZ267" s="38">
-        <v>2.4733592249945442</v>
+        <v>2.4627584803288589</v>
       </c>
       <c r="DA267" s="38">
-        <v>2.9314928996284784</v>
+        <v>2.9737212914700968</v>
       </c>
       <c r="DB267" s="9"/>
       <c r="DC267" s="9"/>
@@ -66168,28 +66161,28 @@
         <v>1.6969752963718578</v>
       </c>
       <c r="CT268" s="38">
-        <v>1.5656424779159077</v>
+        <v>1.5651152564186093</v>
       </c>
       <c r="CU268" s="38">
-        <v>1.5778112583353747</v>
+        <v>1.5753340572865477</v>
       </c>
       <c r="CV268" s="38">
-        <v>2.0467040661840854</v>
+        <v>2.0478324081123813</v>
       </c>
       <c r="CW268" s="38">
-        <v>1.7649677245312925</v>
+        <v>1.7580512699237094</v>
       </c>
       <c r="CX268" s="38">
-        <v>1.6508808547443996</v>
+        <v>1.6513961198297542</v>
       </c>
       <c r="CY268" s="38">
-        <v>1.495434701158556</v>
+        <v>1.4955813957179016</v>
       </c>
       <c r="CZ268" s="38">
-        <v>1.9069426494638924</v>
+        <v>1.8994843618219066</v>
       </c>
       <c r="DA268" s="38">
-        <v>1.8789534805932242</v>
+        <v>1.9055536008076757</v>
       </c>
       <c r="DB268" s="9"/>
       <c r="DC268" s="9"/>
@@ -66532,28 +66525,28 @@
         <v>5.5449588218589705</v>
       </c>
       <c r="CT269" s="38">
-        <v>6.0464741817499768</v>
+        <v>6.043611348854748</v>
       </c>
       <c r="CU269" s="38">
-        <v>6.1846661720838148</v>
+        <v>6.2026080141894662</v>
       </c>
       <c r="CV269" s="38">
-        <v>6.0670291526861728</v>
+        <v>6.0559524872727675</v>
       </c>
       <c r="CW269" s="38">
-        <v>4.5136343376262769</v>
+        <v>4.4949188411475074</v>
       </c>
       <c r="CX269" s="38">
-        <v>3.7742373775717799</v>
+        <v>3.8358370467583875</v>
       </c>
       <c r="CY269" s="38">
-        <v>4.6223671825746662</v>
+        <v>4.6892308438522283</v>
       </c>
       <c r="CZ269" s="38">
-        <v>8.8278967819946228</v>
+        <v>8.7765028362039104</v>
       </c>
       <c r="DA269" s="38">
-        <v>5.3839138917217042</v>
+        <v>5.3155927542414254</v>
       </c>
       <c r="DB269" s="9"/>
       <c r="DC269" s="9"/>
@@ -66896,28 +66889,28 @@
         <v>6.6152388502061381</v>
       </c>
       <c r="CT270" s="38">
-        <v>6.4899659022310461</v>
+        <v>6.4884542212002376</v>
       </c>
       <c r="CU270" s="38">
-        <v>5.1641234993057905</v>
+        <v>5.1706662250407094</v>
       </c>
       <c r="CV270" s="38">
-        <v>5.6082210604082787</v>
+        <v>5.6088367223233559</v>
       </c>
       <c r="CW270" s="38">
-        <v>7.4869153193524092</v>
+        <v>7.4800622711019908</v>
       </c>
       <c r="CX270" s="38">
-        <v>6.9637861868504087</v>
+        <v>6.9884101737737625</v>
       </c>
       <c r="CY270" s="38">
-        <v>4.5137937561766943</v>
+        <v>4.533056477750498</v>
       </c>
       <c r="CZ270" s="38">
-        <v>6.11258434984176</v>
+        <v>6.0860674368553394</v>
       </c>
       <c r="DA270" s="38">
-        <v>8.0289707005244129</v>
+        <v>8.2097257120347411</v>
       </c>
       <c r="DB270" s="9"/>
       <c r="DC270" s="9"/>
@@ -67260,28 +67253,28 @@
         <v>53.522817853009528</v>
       </c>
       <c r="CT271" s="38">
-        <v>51.227094802566199</v>
+        <v>51.242706040651683</v>
       </c>
       <c r="CU271" s="38">
-        <v>49.388981887943366</v>
+        <v>49.412246208966089</v>
       </c>
       <c r="CV271" s="38">
-        <v>55.005884641352488</v>
+        <v>55.017400626747694</v>
       </c>
       <c r="CW271" s="38">
-        <v>52.349354750083833</v>
+        <v>52.312512741048579</v>
       </c>
       <c r="CX271" s="38">
-        <v>50.548851697843148</v>
+        <v>50.519499317943463</v>
       </c>
       <c r="CY271" s="38">
-        <v>53.913382326491167</v>
+        <v>53.911469918320286</v>
       </c>
       <c r="CZ271" s="38">
-        <v>51.738372971537025</v>
+        <v>51.99059302030431</v>
       </c>
       <c r="DA271" s="38">
-        <v>52.588602720178478</v>
+        <v>52.154352638986204</v>
       </c>
       <c r="DB271" s="9"/>
       <c r="DC271" s="9"/>
@@ -67624,28 +67617,28 @@
         <v>45.245302104680498</v>
       </c>
       <c r="CT272" s="38">
-        <v>46.349986364301792</v>
+        <v>46.364798304221679</v>
       </c>
       <c r="CU272" s="38">
-        <v>46.52805211494934</v>
+        <v>46.549577953518771</v>
       </c>
       <c r="CV272" s="38">
-        <v>46.063948046636455</v>
+        <v>46.075953330977676</v>
       </c>
       <c r="CW272" s="38">
-        <v>46.422846918311308</v>
+        <v>46.393928481627675</v>
       </c>
       <c r="CX272" s="38">
-        <v>47.462054119951226</v>
+        <v>47.435448293847607</v>
       </c>
       <c r="CY272" s="38">
-        <v>48.952669465482749</v>
+        <v>48.955372288626023</v>
       </c>
       <c r="CZ272" s="38">
-        <v>47.765246668239165</v>
+        <v>48.034584536343012</v>
       </c>
       <c r="DA272" s="38">
-        <v>46.159863601848592</v>
+        <v>45.77604311799066</v>
       </c>
       <c r="DB272" s="9"/>
       <c r="DC272" s="9"/>
@@ -67988,28 +67981,28 @@
         <v>0.25513830116385389</v>
       </c>
       <c r="CT273" s="38">
-        <v>0.78243509806221523</v>
+        <v>0.78205440744114285</v>
       </c>
       <c r="CU273" s="38">
-        <v>0.41436814715656206</v>
+        <v>0.41413271488049497</v>
       </c>
       <c r="CV273" s="38">
-        <v>0.78619372633560913</v>
+        <v>0.78615070615115701</v>
       </c>
       <c r="CW273" s="38">
-        <v>0.74029330067286458</v>
+        <v>0.73915207447057951</v>
       </c>
       <c r="CX273" s="38">
-        <v>7.486038627505949E-2</v>
+        <v>7.4757539928951983E-2</v>
       </c>
       <c r="CY273" s="38">
-        <v>1.3786541094043873E-2</v>
+        <v>1.3774011324937713E-2</v>
       </c>
       <c r="CZ273" s="38">
-        <v>9.405934627468017E-2</v>
+        <v>9.3654100940518542E-2</v>
       </c>
       <c r="DA273" s="38">
-        <v>3.4088037375345999E-2</v>
+        <v>3.3839201566735908E-2</v>
       </c>
       <c r="DB273" s="9"/>
       <c r="DC273" s="9"/>
@@ -68352,28 +68345,28 @@
         <v>5.9545854322773772</v>
       </c>
       <c r="CT274" s="38">
-        <v>2.9905857999242649</v>
+        <v>2.9891307426115317</v>
       </c>
       <c r="CU274" s="38">
-        <v>2.0582701837128337</v>
+        <v>2.0569987488714139</v>
       </c>
       <c r="CV274" s="38">
-        <v>7.5435481104767277</v>
+        <v>7.543135330750478</v>
       </c>
       <c r="CW274" s="38">
-        <v>4.6721456979581015</v>
+        <v>4.6649345852009727</v>
       </c>
       <c r="CX274" s="38">
-        <v>2.1866335055773978</v>
+        <v>2.1836336166407353</v>
       </c>
       <c r="CY274" s="38">
-        <v>0.6210186003401722</v>
+        <v>0.62340654146457397</v>
       </c>
       <c r="CZ274" s="38">
-        <v>2.1072841381795939</v>
+        <v>2.0982051141530365</v>
       </c>
       <c r="DA274" s="38">
-        <v>6.1008938221077367</v>
+        <v>6.0412733837411263</v>
       </c>
       <c r="DB274" s="9"/>
       <c r="DC274" s="9"/>
@@ -68716,28 +68709,28 @@
         <v>2.067792014887806</v>
       </c>
       <c r="CT275" s="38">
-        <v>1.1040875402779284</v>
+        <v>1.1067225863773338</v>
       </c>
       <c r="CU275" s="38">
-        <v>0.38829144212462752</v>
+        <v>0.39153679169540817</v>
       </c>
       <c r="CV275" s="38">
-        <v>0.61219475790370415</v>
+        <v>0.61216125886838568</v>
       </c>
       <c r="CW275" s="38">
-        <v>0.5140688331415646</v>
+        <v>0.51449759974935005</v>
       </c>
       <c r="CX275" s="38">
-        <v>0.82530368603947069</v>
+        <v>0.82565986752617881</v>
       </c>
       <c r="CY275" s="38">
-        <v>4.3259077195742011</v>
+        <v>4.3189170769047589</v>
       </c>
       <c r="CZ275" s="38">
-        <v>1.7717828188436036</v>
+        <v>1.7641492688677474</v>
       </c>
       <c r="DA275" s="38">
-        <v>0.29375725884680703</v>
+        <v>0.30319693568768252</v>
       </c>
       <c r="DB275" s="9"/>
       <c r="DC275" s="9"/>
@@ -69080,28 +69073,28 @@
         <v>12.414870589236477</v>
       </c>
       <c r="CT276" s="38">
-        <v>17.67465120500956</v>
+        <v>17.667517703998996</v>
       </c>
       <c r="CU276" s="38">
-        <v>24.397013493046579</v>
+        <v>24.360667734070077</v>
       </c>
       <c r="CV276" s="38">
-        <v>15.152304546595932</v>
+        <v>15.155061237539122</v>
       </c>
       <c r="CW276" s="38">
-        <v>12.777168433557687</v>
+        <v>12.744847060904224</v>
       </c>
       <c r="CX276" s="38">
-        <v>18.777497401932511</v>
+        <v>18.784342391976036</v>
       </c>
       <c r="CY276" s="38">
-        <v>23.150250431229978</v>
+        <v>23.056781619247921</v>
       </c>
       <c r="CZ276" s="38">
-        <v>15.392140003818755</v>
+        <v>15.154137173298185</v>
       </c>
       <c r="DA276" s="38">
-        <v>12.968594659189201</v>
+        <v>13.085354921599604</v>
       </c>
       <c r="DB276" s="9"/>
       <c r="DC276" s="9"/>
@@ -69444,28 +69437,28 @@
         <v>1.0436963444681</v>
       </c>
       <c r="CT277" s="38">
-        <v>1.2102901965169168</v>
+        <v>1.2099976478858303</v>
       </c>
       <c r="CU277" s="38">
-        <v>2.8864389178672165</v>
+        <v>2.8828783159317206</v>
       </c>
       <c r="CV277" s="38">
-        <v>1.1686032170221075</v>
+        <v>1.1656446268785834</v>
       </c>
       <c r="CW277" s="38">
-        <v>1.0070515233296404</v>
+        <v>1.0041939033329623</v>
       </c>
       <c r="CX277" s="38">
-        <v>1.4558021424602721</v>
+        <v>1.4551292165215917</v>
       </c>
       <c r="CY277" s="38">
-        <v>2.7615672049907691</v>
+        <v>2.7612088462187647</v>
       </c>
       <c r="CZ277" s="38">
-        <v>1.940140835440626</v>
+        <v>1.9259696854436663</v>
       </c>
       <c r="DA277" s="38">
-        <v>1.3915212094328333</v>
+        <v>1.4023574113789203</v>
       </c>
       <c r="DB277" s="9"/>
       <c r="DC277" s="9"/>
@@ -69808,28 +69801,28 @@
         <v>2.4139273555201211</v>
       </c>
       <c r="CT278" s="38">
-        <v>4.2374578618748258</v>
+        <v>4.2349067308014154</v>
       </c>
       <c r="CU278" s="38">
-        <v>5.7248628798659738</v>
+        <v>5.7195741399823756</v>
       </c>
       <c r="CV278" s="38">
-        <v>2.7994370498759218</v>
+        <v>2.8006706376323156</v>
       </c>
       <c r="CW278" s="38">
-        <v>2.6463108340571488</v>
+        <v>2.6552572826173839</v>
       </c>
       <c r="CX278" s="38">
-        <v>4.0857504881962425</v>
+        <v>4.0589226828297003</v>
       </c>
       <c r="CY278" s="38">
-        <v>4.2962674884582084</v>
+        <v>4.2654123455837833</v>
       </c>
       <c r="CZ278" s="38">
-        <v>2.35461397062892</v>
+        <v>2.3366269177790939</v>
       </c>
       <c r="DA278" s="38">
-        <v>2.3275452970702428</v>
+        <v>2.4099559847363037</v>
       </c>
       <c r="DB278" s="9"/>
       <c r="DC278" s="9"/>
@@ -70172,28 +70165,28 @@
         <v>6.3008753267402904</v>
       </c>
       <c r="CT279" s="38">
-        <v>7.8052601001871693</v>
+        <v>7.8031363446063855</v>
       </c>
       <c r="CU279" s="38">
-        <v>11.358951659088392</v>
+        <v>11.335903517824343</v>
       </c>
       <c r="CV279" s="38">
-        <v>8.5333683525345947</v>
+        <v>8.5384922205164937</v>
       </c>
       <c r="CW279" s="38">
-        <v>6.299676078035235</v>
+        <v>6.2654643114419013</v>
       </c>
       <c r="CX279" s="38">
-        <v>8.4810118927655367</v>
+        <v>8.4886939242873556</v>
       </c>
       <c r="CY279" s="38">
-        <v>11.891468226759947</v>
+        <v>11.914298442288128</v>
       </c>
       <c r="CZ279" s="38">
-        <v>8.2609063348437601</v>
+        <v>8.2290809782173131</v>
       </c>
       <c r="DA279" s="38">
-        <v>6.6911980105756053</v>
+        <v>6.727238770459147</v>
       </c>
       <c r="DB279" s="9"/>
       <c r="DC279" s="9"/>
@@ -70536,28 +70529,28 @@
         <v>2.6563715625079638</v>
       </c>
       <c r="CT280" s="38">
-        <v>4.4216430464306473</v>
+        <v>4.4194769807053653</v>
       </c>
       <c r="CU280" s="38">
-        <v>4.4267600362249988</v>
+        <v>4.4223117603316391</v>
       </c>
       <c r="CV280" s="38">
-        <v>2.6508959271633095</v>
+        <v>2.6502537525117282</v>
       </c>
       <c r="CW280" s="38">
-        <v>2.8241299981356613</v>
+        <v>2.8199315635119757</v>
       </c>
       <c r="CX280" s="38">
-        <v>4.7549328785104619</v>
+        <v>4.7815965683373856</v>
       </c>
       <c r="CY280" s="38">
-        <v>4.2009475110210479</v>
+        <v>4.1158619851572409</v>
       </c>
       <c r="CZ280" s="38">
-        <v>2.836478862905448</v>
+        <v>2.6624595918581124</v>
       </c>
       <c r="DA280" s="38">
-        <v>2.5583301421105196</v>
+        <v>2.5458027550252322</v>
       </c>
       <c r="DB280" s="9"/>
       <c r="DC280" s="9"/>
@@ -71248,6 +71241,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="CD132:CG132"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="CD254:CG254"/>
+    <mergeCell ref="CD213:CG213"/>
+    <mergeCell ref="CD172:CG172"/>
+    <mergeCell ref="CD50:CG50"/>
+    <mergeCell ref="CD91:CG91"/>
+    <mergeCell ref="BJ9:BM9"/>
+    <mergeCell ref="BN9:BQ9"/>
+    <mergeCell ref="BZ50:CC50"/>
+    <mergeCell ref="BV254:BY254"/>
+    <mergeCell ref="BN132:BQ132"/>
+    <mergeCell ref="BJ91:BM91"/>
+    <mergeCell ref="BN91:BQ91"/>
+    <mergeCell ref="BJ132:BM132"/>
+    <mergeCell ref="BJ172:BM172"/>
+    <mergeCell ref="BR132:BU132"/>
+    <mergeCell ref="BV132:BY132"/>
+    <mergeCell ref="BR50:BU50"/>
+    <mergeCell ref="BV50:BY50"/>
+    <mergeCell ref="BF254:BI254"/>
+    <mergeCell ref="BJ254:BM254"/>
+    <mergeCell ref="BN254:BQ254"/>
+    <mergeCell ref="BV9:BY9"/>
+    <mergeCell ref="BZ9:CC9"/>
+    <mergeCell ref="BR9:BU9"/>
+    <mergeCell ref="BR91:BU91"/>
+    <mergeCell ref="BV91:BY91"/>
+    <mergeCell ref="BR213:BU213"/>
+    <mergeCell ref="BV213:BY213"/>
+    <mergeCell ref="BZ213:CC213"/>
+    <mergeCell ref="BZ172:CC172"/>
+    <mergeCell ref="BR172:BU172"/>
+    <mergeCell ref="BV172:BY172"/>
+    <mergeCell ref="BZ91:CC91"/>
+    <mergeCell ref="BZ132:CC132"/>
+    <mergeCell ref="BF213:BI213"/>
+    <mergeCell ref="BJ213:BM213"/>
+    <mergeCell ref="BN213:BQ213"/>
+    <mergeCell ref="BJ50:BM50"/>
+    <mergeCell ref="BN50:BQ50"/>
+    <mergeCell ref="BN172:BQ172"/>
+    <mergeCell ref="BZ254:CC254"/>
+    <mergeCell ref="BR254:BU254"/>
+    <mergeCell ref="AX254:BA254"/>
+    <mergeCell ref="BB254:BE254"/>
+    <mergeCell ref="N213:Q213"/>
+    <mergeCell ref="R213:U213"/>
+    <mergeCell ref="V213:Y213"/>
+    <mergeCell ref="Z213:AC213"/>
+    <mergeCell ref="AD213:AG213"/>
+    <mergeCell ref="AH213:AK213"/>
+    <mergeCell ref="AL213:AO213"/>
+    <mergeCell ref="AL254:AO254"/>
+    <mergeCell ref="AP254:AS254"/>
+    <mergeCell ref="AT254:AW254"/>
+    <mergeCell ref="AL91:AO91"/>
+    <mergeCell ref="Z172:AC172"/>
+    <mergeCell ref="AD172:AG172"/>
+    <mergeCell ref="AH172:AK172"/>
+    <mergeCell ref="AP91:AS91"/>
+    <mergeCell ref="Z132:AC132"/>
+    <mergeCell ref="AD132:AG132"/>
+    <mergeCell ref="AH132:AK132"/>
+    <mergeCell ref="AL132:AO132"/>
+    <mergeCell ref="AL172:AO172"/>
+    <mergeCell ref="AP172:AS172"/>
+    <mergeCell ref="AD91:AG91"/>
+    <mergeCell ref="AH91:AK91"/>
+    <mergeCell ref="AT172:AW172"/>
+    <mergeCell ref="AX172:BA172"/>
+    <mergeCell ref="BB172:BE172"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="F132:I132"/>
+    <mergeCell ref="J132:M132"/>
+    <mergeCell ref="N132:Q132"/>
+    <mergeCell ref="R132:U132"/>
+    <mergeCell ref="V132:Y132"/>
+    <mergeCell ref="AX132:BA132"/>
+    <mergeCell ref="BB132:BE132"/>
+    <mergeCell ref="F254:I254"/>
+    <mergeCell ref="J254:M254"/>
+    <mergeCell ref="N254:Q254"/>
+    <mergeCell ref="R254:U254"/>
+    <mergeCell ref="V254:Y254"/>
+    <mergeCell ref="Z254:AC254"/>
+    <mergeCell ref="AD254:AG254"/>
+    <mergeCell ref="AH254:AK254"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="F213:I213"/>
+    <mergeCell ref="J213:M213"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="F172:I172"/>
+    <mergeCell ref="J172:M172"/>
+    <mergeCell ref="N172:Q172"/>
+    <mergeCell ref="R172:U172"/>
+    <mergeCell ref="V172:Y172"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="N91:Q91"/>
+    <mergeCell ref="R91:U91"/>
+    <mergeCell ref="V91:Y91"/>
+    <mergeCell ref="Z91:AC91"/>
+    <mergeCell ref="V50:Y50"/>
+    <mergeCell ref="Z50:AC50"/>
+    <mergeCell ref="AD50:AG50"/>
+    <mergeCell ref="AH50:AK50"/>
+    <mergeCell ref="AL50:AO50"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AH9:AK9"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="N50:Q50"/>
+    <mergeCell ref="R50:U50"/>
     <mergeCell ref="B254:E254"/>
     <mergeCell ref="AT50:AW50"/>
     <mergeCell ref="AX50:BA50"/>
@@ -71272,129 +71388,6 @@
     <mergeCell ref="BF91:BI91"/>
     <mergeCell ref="AX213:BA213"/>
     <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="N50:Q50"/>
-    <mergeCell ref="R50:U50"/>
-    <mergeCell ref="V50:Y50"/>
-    <mergeCell ref="Z50:AC50"/>
-    <mergeCell ref="AD50:AG50"/>
-    <mergeCell ref="AH50:AK50"/>
-    <mergeCell ref="AL50:AO50"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AH9:AK9"/>
-    <mergeCell ref="F254:I254"/>
-    <mergeCell ref="J254:M254"/>
-    <mergeCell ref="N254:Q254"/>
-    <mergeCell ref="R254:U254"/>
-    <mergeCell ref="V254:Y254"/>
-    <mergeCell ref="Z254:AC254"/>
-    <mergeCell ref="AD254:AG254"/>
-    <mergeCell ref="AH254:AK254"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B213:E213"/>
-    <mergeCell ref="F213:I213"/>
-    <mergeCell ref="J213:M213"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="F172:I172"/>
-    <mergeCell ref="J172:M172"/>
-    <mergeCell ref="N172:Q172"/>
-    <mergeCell ref="R172:U172"/>
-    <mergeCell ref="V172:Y172"/>
-    <mergeCell ref="F91:I91"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="N91:Q91"/>
-    <mergeCell ref="R91:U91"/>
-    <mergeCell ref="V91:Y91"/>
-    <mergeCell ref="Z91:AC91"/>
-    <mergeCell ref="AT172:AW172"/>
-    <mergeCell ref="AX172:BA172"/>
-    <mergeCell ref="BB172:BE172"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="F132:I132"/>
-    <mergeCell ref="J132:M132"/>
-    <mergeCell ref="N132:Q132"/>
-    <mergeCell ref="R132:U132"/>
-    <mergeCell ref="V132:Y132"/>
-    <mergeCell ref="AX132:BA132"/>
-    <mergeCell ref="BB132:BE132"/>
-    <mergeCell ref="AL91:AO91"/>
-    <mergeCell ref="Z172:AC172"/>
-    <mergeCell ref="AD172:AG172"/>
-    <mergeCell ref="AH172:AK172"/>
-    <mergeCell ref="AP91:AS91"/>
-    <mergeCell ref="Z132:AC132"/>
-    <mergeCell ref="AD132:AG132"/>
-    <mergeCell ref="AH132:AK132"/>
-    <mergeCell ref="AL132:AO132"/>
-    <mergeCell ref="AL172:AO172"/>
-    <mergeCell ref="AP172:AS172"/>
-    <mergeCell ref="AD91:AG91"/>
-    <mergeCell ref="AH91:AK91"/>
-    <mergeCell ref="AX254:BA254"/>
-    <mergeCell ref="BB254:BE254"/>
-    <mergeCell ref="N213:Q213"/>
-    <mergeCell ref="R213:U213"/>
-    <mergeCell ref="V213:Y213"/>
-    <mergeCell ref="Z213:AC213"/>
-    <mergeCell ref="AD213:AG213"/>
-    <mergeCell ref="AH213:AK213"/>
-    <mergeCell ref="AL213:AO213"/>
-    <mergeCell ref="AL254:AO254"/>
-    <mergeCell ref="AP254:AS254"/>
-    <mergeCell ref="AT254:AW254"/>
-    <mergeCell ref="BF254:BI254"/>
-    <mergeCell ref="BJ254:BM254"/>
-    <mergeCell ref="BN254:BQ254"/>
-    <mergeCell ref="BV9:BY9"/>
-    <mergeCell ref="BZ9:CC9"/>
-    <mergeCell ref="BR9:BU9"/>
-    <mergeCell ref="BR91:BU91"/>
-    <mergeCell ref="BV91:BY91"/>
-    <mergeCell ref="BR213:BU213"/>
-    <mergeCell ref="BV213:BY213"/>
-    <mergeCell ref="BZ213:CC213"/>
-    <mergeCell ref="BZ172:CC172"/>
-    <mergeCell ref="BR172:BU172"/>
-    <mergeCell ref="BV172:BY172"/>
-    <mergeCell ref="BZ91:CC91"/>
-    <mergeCell ref="BZ132:CC132"/>
-    <mergeCell ref="BF213:BI213"/>
-    <mergeCell ref="BJ213:BM213"/>
-    <mergeCell ref="BN213:BQ213"/>
-    <mergeCell ref="BJ50:BM50"/>
-    <mergeCell ref="BN50:BQ50"/>
-    <mergeCell ref="BN172:BQ172"/>
-    <mergeCell ref="BZ254:CC254"/>
-    <mergeCell ref="BR254:BU254"/>
-    <mergeCell ref="CD132:CG132"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="CD254:CG254"/>
-    <mergeCell ref="CD213:CG213"/>
-    <mergeCell ref="CD172:CG172"/>
-    <mergeCell ref="CD50:CG50"/>
-    <mergeCell ref="CD91:CG91"/>
-    <mergeCell ref="BJ9:BM9"/>
-    <mergeCell ref="BN9:BQ9"/>
-    <mergeCell ref="BZ50:CC50"/>
-    <mergeCell ref="BV254:BY254"/>
-    <mergeCell ref="BN132:BQ132"/>
-    <mergeCell ref="BJ91:BM91"/>
-    <mergeCell ref="BN91:BQ91"/>
-    <mergeCell ref="BJ132:BM132"/>
-    <mergeCell ref="BJ172:BM172"/>
-    <mergeCell ref="BR132:BU132"/>
-    <mergeCell ref="BV132:BY132"/>
-    <mergeCell ref="BR50:BU50"/>
-    <mergeCell ref="BV50:BY50"/>
   </mergeCells>
   <conditionalFormatting sqref="CP94:DA109 CS110:DA110 CP111:DA111 CP112:CT112 CV112:DA112 CP113:DA119 CP135:DA150 CS151:DA151 CP152:DA152 CP153:CT153 CV153:DA153 CP154:DA160 CP175:DA200">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">

--- a/Data/National Accounts/PSA-03DEQ_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-03DEQ_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DD0AE7-E191-47DD-92BC-2761FD9611B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244EE6C5-F3BD-4DF3-95D6-A29FF34912D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEQ" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="PCE_Per_Anl">#REF!</definedName>
     <definedName name="PCE_Per_Con_Qrt">[1]HFCE!#REF!</definedName>
     <definedName name="PCE_Per_Cur_Qrt">[1]HFCE!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DEQ!$A$1:$DA$286</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DEQ!$A$1:$DB$286</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="manual"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="79">
   <si>
     <t>Source: Philippine Statistics Authority</t>
   </si>
@@ -270,13 +270,16 @@
     <t>2024 - 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>Q1 2001 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2001 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -450,10 +453,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +469,21 @@
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{008F8423-7867-4CB4-A558-4D234F15232D}"/>
     <cellStyle name="Normal 3" xfId="6" xr:uid="{8C6D19FF-306C-41BE-9C1F-A9A8F7C52269}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -811,8 +828,8 @@
     <col min="22" max="69" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="73" width="10" style="1" customWidth="1"/>
     <col min="74" max="89" width="9.21875" style="1" customWidth="1"/>
-    <col min="90" max="105" width="9.21875" style="27" customWidth="1"/>
-    <col min="106" max="16384" width="7.77734375" style="1"/>
+    <col min="90" max="106" width="9.21875" style="27" customWidth="1"/>
+    <col min="107" max="16384" width="7.77734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:152" x14ac:dyDescent="0.2">
@@ -827,7 +844,7 @@
     </row>
     <row r="3" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.2">
@@ -837,7 +854,7 @@
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.2">
@@ -847,132 +864,132 @@
     </row>
     <row r="9" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="45">
+      <c r="B9" s="44">
         <v>2000</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45">
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44">
         <v>2001</v>
       </c>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45">
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44">
         <v>2002</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45">
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44">
         <v>2003</v>
       </c>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45">
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44">
         <v>2004</v>
       </c>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45">
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44">
         <v>2005</v>
       </c>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="45">
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44">
         <v>2006</v>
       </c>
-      <c r="AA9" s="45"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="45">
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44">
         <v>2007</v>
       </c>
-      <c r="AE9" s="45"/>
-      <c r="AF9" s="45"/>
-      <c r="AG9" s="45"/>
-      <c r="AH9" s="45">
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="44">
         <v>2008</v>
       </c>
-      <c r="AI9" s="45"/>
-      <c r="AJ9" s="45"/>
-      <c r="AK9" s="45"/>
-      <c r="AL9" s="45">
+      <c r="AI9" s="44"/>
+      <c r="AJ9" s="44"/>
+      <c r="AK9" s="44"/>
+      <c r="AL9" s="44">
         <v>2009</v>
       </c>
-      <c r="AM9" s="45"/>
-      <c r="AN9" s="45"/>
-      <c r="AO9" s="45"/>
-      <c r="AP9" s="45">
+      <c r="AM9" s="44"/>
+      <c r="AN9" s="44"/>
+      <c r="AO9" s="44"/>
+      <c r="AP9" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ9" s="45"/>
-      <c r="AR9" s="45"/>
-      <c r="AS9" s="45"/>
-      <c r="AT9" s="45">
+      <c r="AQ9" s="44"/>
+      <c r="AR9" s="44"/>
+      <c r="AS9" s="44"/>
+      <c r="AT9" s="44">
         <v>2011</v>
       </c>
-      <c r="AU9" s="45"/>
-      <c r="AV9" s="45"/>
-      <c r="AW9" s="45"/>
-      <c r="AX9" s="45">
+      <c r="AU9" s="44"/>
+      <c r="AV9" s="44"/>
+      <c r="AW9" s="44"/>
+      <c r="AX9" s="44">
         <v>2012</v>
       </c>
-      <c r="AY9" s="45"/>
-      <c r="AZ9" s="45"/>
-      <c r="BA9" s="45"/>
-      <c r="BB9" s="45">
+      <c r="AY9" s="44"/>
+      <c r="AZ9" s="44"/>
+      <c r="BA9" s="44"/>
+      <c r="BB9" s="44">
         <v>2013</v>
       </c>
-      <c r="BC9" s="45"/>
-      <c r="BD9" s="45"/>
-      <c r="BE9" s="45"/>
-      <c r="BF9" s="45">
+      <c r="BC9" s="44"/>
+      <c r="BD9" s="44"/>
+      <c r="BE9" s="44"/>
+      <c r="BF9" s="44">
         <v>2014</v>
       </c>
-      <c r="BG9" s="45"/>
-      <c r="BH9" s="45"/>
-      <c r="BI9" s="45"/>
-      <c r="BJ9" s="45">
+      <c r="BG9" s="44"/>
+      <c r="BH9" s="44"/>
+      <c r="BI9" s="44"/>
+      <c r="BJ9" s="44">
         <v>2015</v>
       </c>
-      <c r="BK9" s="45"/>
-      <c r="BL9" s="45"/>
-      <c r="BM9" s="45"/>
-      <c r="BN9" s="45">
+      <c r="BK9" s="44"/>
+      <c r="BL9" s="44"/>
+      <c r="BM9" s="44"/>
+      <c r="BN9" s="44">
         <v>2016</v>
       </c>
-      <c r="BO9" s="45"/>
-      <c r="BP9" s="45"/>
-      <c r="BQ9" s="45"/>
-      <c r="BR9" s="45">
+      <c r="BO9" s="44"/>
+      <c r="BP9" s="44"/>
+      <c r="BQ9" s="44"/>
+      <c r="BR9" s="44">
         <v>2017</v>
       </c>
-      <c r="BS9" s="45"/>
-      <c r="BT9" s="45"/>
-      <c r="BU9" s="45"/>
-      <c r="BV9" s="45">
+      <c r="BS9" s="44"/>
+      <c r="BT9" s="44"/>
+      <c r="BU9" s="44"/>
+      <c r="BV9" s="44">
         <v>2018</v>
       </c>
-      <c r="BW9" s="45"/>
-      <c r="BX9" s="45"/>
-      <c r="BY9" s="45"/>
-      <c r="BZ9" s="45">
+      <c r="BW9" s="44"/>
+      <c r="BX9" s="44"/>
+      <c r="BY9" s="44"/>
+      <c r="BZ9" s="44">
         <v>2019</v>
       </c>
-      <c r="CA9" s="45"/>
-      <c r="CB9" s="45"/>
-      <c r="CC9" s="45"/>
-      <c r="CD9" s="45">
+      <c r="CA9" s="44"/>
+      <c r="CB9" s="44"/>
+      <c r="CC9" s="44"/>
+      <c r="CD9" s="44">
         <v>2020</v>
       </c>
-      <c r="CE9" s="45"/>
-      <c r="CF9" s="45"/>
-      <c r="CG9" s="45"/>
+      <c r="CE9" s="44"/>
+      <c r="CF9" s="44"/>
+      <c r="CG9" s="44"/>
       <c r="CH9" s="26">
         <v>2021</v>
       </c>
@@ -1003,6 +1020,9 @@
       <c r="CY9" s="28"/>
       <c r="CZ9" s="28"/>
       <c r="DA9" s="28"/>
+      <c r="DB9" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1319,6 +1339,9 @@
       </c>
       <c r="DA10" s="17" t="s">
         <v>9</v>
+      </c>
+      <c r="DB10" s="17" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1640,7 +1663,9 @@
       <c r="DA12" s="29">
         <v>57081.223119989634</v>
       </c>
-      <c r="DB12" s="9"/>
+      <c r="DB12" s="29">
+        <v>66190.694189807284</v>
+      </c>
       <c r="DC12" s="9"/>
       <c r="DD12" s="9"/>
       <c r="DE12" s="9"/>
@@ -2004,7 +2029,9 @@
       <c r="DA13" s="30">
         <v>3474.2554059409449</v>
       </c>
-      <c r="DB13" s="9"/>
+      <c r="DB13" s="30">
+        <v>3217.3354066386246</v>
+      </c>
       <c r="DC13" s="9"/>
       <c r="DD13" s="9"/>
       <c r="DE13" s="9"/>
@@ -2368,7 +2395,9 @@
       <c r="DA14" s="30">
         <v>11614.15543271483</v>
       </c>
-      <c r="DB14" s="9"/>
+      <c r="DB14" s="30">
+        <v>9685.6897878389591</v>
+      </c>
       <c r="DC14" s="9"/>
       <c r="DD14" s="9"/>
       <c r="DE14" s="9"/>
@@ -2732,7 +2761,9 @@
       <c r="DA15" s="30">
         <v>1520.1872451638005</v>
       </c>
-      <c r="DB15" s="9"/>
+      <c r="DB15" s="30">
+        <v>908.11698230020988</v>
+      </c>
       <c r="DC15" s="9"/>
       <c r="DD15" s="9"/>
       <c r="DE15" s="9"/>
@@ -3096,7 +3127,9 @@
       <c r="DA16" s="30">
         <v>718.58424833780975</v>
       </c>
-      <c r="DB16" s="9"/>
+      <c r="DB16" s="30">
+        <v>855.5453701479338</v>
+      </c>
       <c r="DC16" s="9"/>
       <c r="DD16" s="9"/>
       <c r="DE16" s="9"/>
@@ -3460,7 +3493,9 @@
       <c r="DA17" s="30">
         <v>2742.2980133333554</v>
       </c>
-      <c r="DB17" s="9"/>
+      <c r="DB17" s="30">
+        <v>3813.5271106651448</v>
+      </c>
       <c r="DC17" s="9"/>
       <c r="DD17" s="9"/>
       <c r="DE17" s="9"/>
@@ -3824,7 +3859,9 @@
       <c r="DA18" s="30">
         <v>24882.403139781571</v>
       </c>
-      <c r="DB18" s="9"/>
+      <c r="DB18" s="30">
+        <v>34646.730348328027</v>
+      </c>
       <c r="DC18" s="9"/>
       <c r="DD18" s="9"/>
       <c r="DE18" s="9"/>
@@ -4188,7 +4225,9 @@
       <c r="DA19" s="30">
         <v>1685.725358115104</v>
       </c>
-      <c r="DB19" s="9"/>
+      <c r="DB19" s="30">
+        <v>1208.423840789643</v>
+      </c>
       <c r="DC19" s="9"/>
       <c r="DD19" s="9"/>
       <c r="DE19" s="9"/>
@@ -4552,7 +4591,9 @@
       <c r="DA20" s="30">
         <v>10443.614276602226</v>
       </c>
-      <c r="DB20" s="9"/>
+      <c r="DB20" s="30">
+        <v>11855.325343098744</v>
+      </c>
       <c r="DC20" s="9"/>
       <c r="DD20" s="9"/>
       <c r="DE20" s="9"/>
@@ -4916,7 +4957,9 @@
       <c r="DA21" s="29">
         <v>76157.402638788422</v>
       </c>
-      <c r="DB21" s="9"/>
+      <c r="DB21" s="29">
+        <v>94076.628715065191</v>
+      </c>
       <c r="DC21" s="9"/>
       <c r="DD21" s="9"/>
       <c r="DE21" s="9"/>
@@ -5280,7 +5323,9 @@
       <c r="DA22" s="30">
         <v>12758.064668105701</v>
       </c>
-      <c r="DB22" s="9"/>
+      <c r="DB22" s="30">
+        <v>13738.92676174718</v>
+      </c>
       <c r="DC22" s="9"/>
       <c r="DD22" s="9"/>
       <c r="DE22" s="9"/>
@@ -5644,7 +5689,9 @@
       <c r="DA23" s="30">
         <v>8760.7955594391788</v>
       </c>
-      <c r="DB23" s="9"/>
+      <c r="DB23" s="30">
+        <v>8531.5448412824007</v>
+      </c>
       <c r="DC23" s="9"/>
       <c r="DD23" s="9"/>
       <c r="DE23" s="9"/>
@@ -6008,7 +6055,9 @@
       <c r="DA24" s="30">
         <v>25260.186450065692</v>
       </c>
-      <c r="DB24" s="9"/>
+      <c r="DB24" s="30">
+        <v>39815.54297528755</v>
+      </c>
       <c r="DC24" s="9"/>
       <c r="DD24" s="9"/>
       <c r="DE24" s="9"/>
@@ -6372,7 +6421,9 @@
       <c r="DA25" s="30">
         <v>29378.355961177844</v>
       </c>
-      <c r="DB25" s="9"/>
+      <c r="DB25" s="30">
+        <v>31990.614136748056</v>
+      </c>
       <c r="DC25" s="9"/>
       <c r="DD25" s="9"/>
       <c r="DE25" s="9"/>
@@ -6736,7 +6787,9 @@
       <c r="DA26" s="29">
         <v>210572.16905781714</v>
       </c>
-      <c r="DB26" s="9"/>
+      <c r="DB26" s="29">
+        <v>206756.45873945567</v>
+      </c>
       <c r="DC26" s="9"/>
       <c r="DD26" s="9"/>
       <c r="DE26" s="9"/>
@@ -7100,7 +7153,9 @@
       <c r="DA27" s="30">
         <v>178731.21117082197</v>
       </c>
-      <c r="DB27" s="9"/>
+      <c r="DB27" s="30">
+        <v>184365.79691856503</v>
+      </c>
       <c r="DC27" s="9"/>
       <c r="DD27" s="9"/>
       <c r="DE27" s="9"/>
@@ -7464,7 +7519,9 @@
       <c r="DA28" s="30">
         <v>174.76223405781082</v>
       </c>
-      <c r="DB28" s="9"/>
+      <c r="DB28" s="30">
+        <v>219.74189519852126</v>
+      </c>
       <c r="DC28" s="9"/>
       <c r="DD28" s="9"/>
       <c r="DE28" s="9"/>
@@ -7828,7 +7885,9 @@
       <c r="DA29" s="30">
         <v>30281.221356471702</v>
       </c>
-      <c r="DB29" s="9"/>
+      <c r="DB29" s="30">
+        <v>8898.0264254574322</v>
+      </c>
       <c r="DC29" s="9"/>
       <c r="DD29" s="9"/>
       <c r="DE29" s="9"/>
@@ -8192,7 +8251,9 @@
       <c r="DA30" s="30">
         <v>1384.9742964656382</v>
       </c>
-      <c r="DB30" s="9"/>
+      <c r="DB30" s="30">
+        <v>13272.893500234679</v>
+      </c>
       <c r="DC30" s="9"/>
       <c r="DD30" s="9"/>
       <c r="DE30" s="9"/>
@@ -8556,7 +8617,9 @@
       <c r="DA31" s="29">
         <v>78551.955605121591</v>
       </c>
-      <c r="DB31" s="9"/>
+      <c r="DB31" s="29">
+        <v>85168.415839454872</v>
+      </c>
       <c r="DC31" s="9"/>
       <c r="DD31" s="9"/>
       <c r="DE31" s="9"/>
@@ -8920,7 +8983,9 @@
       <c r="DA32" s="30">
         <v>10645.191730097835</v>
       </c>
-      <c r="DB32" s="9"/>
+      <c r="DB32" s="30">
+        <v>8238.7061846340857</v>
+      </c>
       <c r="DC32" s="9"/>
       <c r="DD32" s="9"/>
       <c r="DE32" s="9"/>
@@ -9284,7 +9349,9 @@
       <c r="DA33" s="30">
         <v>11813.930132493941</v>
       </c>
-      <c r="DB33" s="9"/>
+      <c r="DB33" s="30">
+        <v>13233.097550791606</v>
+      </c>
       <c r="DC33" s="9"/>
       <c r="DD33" s="9"/>
       <c r="DE33" s="9"/>
@@ -9648,7 +9715,9 @@
       <c r="DA34" s="30">
         <v>43452.700015068054</v>
       </c>
-      <c r="DB34" s="9"/>
+      <c r="DB34" s="30">
+        <v>44990.250594156445</v>
+      </c>
       <c r="DC34" s="9"/>
       <c r="DD34" s="9"/>
       <c r="DE34" s="9"/>
@@ -10012,7 +10081,9 @@
       <c r="DA35" s="30">
         <v>12640.133727461765</v>
       </c>
-      <c r="DB35" s="9"/>
+      <c r="DB35" s="30">
+        <v>18706.361509872735</v>
+      </c>
       <c r="DC35" s="9"/>
       <c r="DD35" s="9"/>
       <c r="DE35" s="9"/>
@@ -10165,7 +10236,7 @@
       <c r="CY36" s="31"/>
       <c r="CZ36" s="31"/>
       <c r="DA36" s="31"/>
-      <c r="DB36" s="9"/>
+      <c r="DB36" s="31"/>
       <c r="DC36" s="9"/>
       <c r="DD36" s="9"/>
       <c r="DE36" s="9"/>
@@ -10529,7 +10600,9 @@
       <c r="DA37" s="32">
         <v>422362.75042171683</v>
       </c>
-      <c r="DB37" s="9"/>
+      <c r="DB37" s="32">
+        <v>452192.19748378301</v>
+      </c>
       <c r="DC37" s="9"/>
       <c r="DD37" s="9"/>
       <c r="DE37" s="9"/>
@@ -10683,6 +10756,7 @@
       <c r="CY38" s="33"/>
       <c r="CZ38" s="33"/>
       <c r="DA38" s="33"/>
+      <c r="DB38" s="33"/>
     </row>
     <row r="39" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
@@ -10814,7 +10888,7 @@
       <c r="CY40" s="31"/>
       <c r="CZ40" s="31"/>
       <c r="DA40" s="31"/>
-      <c r="DB40" s="9"/>
+      <c r="DB40" s="31"/>
       <c r="DC40" s="9"/>
       <c r="DD40" s="9"/>
       <c r="DE40" s="9"/>
@@ -10967,7 +11041,7 @@
       <c r="CY41" s="31"/>
       <c r="CZ41" s="31"/>
       <c r="DA41" s="31"/>
-      <c r="DB41" s="9"/>
+      <c r="DB41" s="31"/>
       <c r="DC41" s="9"/>
       <c r="DD41" s="9"/>
       <c r="DE41" s="9"/>
@@ -11027,7 +11101,7 @@
     </row>
     <row r="44" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:152" x14ac:dyDescent="0.2">
@@ -11037,7 +11111,7 @@
     </row>
     <row r="47" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:152" x14ac:dyDescent="0.2">
@@ -11047,132 +11121,132 @@
     </row>
     <row r="50" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
-      <c r="B50" s="44">
+      <c r="B50" s="45">
         <v>2000</v>
       </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44">
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45">
         <v>2001</v>
       </c>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="44">
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45">
         <v>2002</v>
       </c>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
-      <c r="M50" s="44"/>
-      <c r="N50" s="44">
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45">
         <v>2003</v>
       </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="R50" s="44">
+      <c r="O50" s="45"/>
+      <c r="P50" s="45"/>
+      <c r="Q50" s="45"/>
+      <c r="R50" s="45">
         <v>2004</v>
       </c>
-      <c r="S50" s="44"/>
-      <c r="T50" s="44"/>
-      <c r="U50" s="44"/>
-      <c r="V50" s="44">
+      <c r="S50" s="45"/>
+      <c r="T50" s="45"/>
+      <c r="U50" s="45"/>
+      <c r="V50" s="45">
         <v>2005</v>
       </c>
-      <c r="W50" s="44"/>
-      <c r="X50" s="44"/>
-      <c r="Y50" s="44"/>
-      <c r="Z50" s="44">
+      <c r="W50" s="45"/>
+      <c r="X50" s="45"/>
+      <c r="Y50" s="45"/>
+      <c r="Z50" s="45">
         <v>2006</v>
       </c>
-      <c r="AA50" s="44"/>
-      <c r="AB50" s="44"/>
-      <c r="AC50" s="44"/>
-      <c r="AD50" s="44">
+      <c r="AA50" s="45"/>
+      <c r="AB50" s="45"/>
+      <c r="AC50" s="45"/>
+      <c r="AD50" s="45">
         <v>2007</v>
       </c>
-      <c r="AE50" s="44"/>
-      <c r="AF50" s="44"/>
-      <c r="AG50" s="44"/>
-      <c r="AH50" s="44">
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="45">
         <v>2008</v>
       </c>
-      <c r="AI50" s="44"/>
-      <c r="AJ50" s="44"/>
-      <c r="AK50" s="44"/>
-      <c r="AL50" s="44">
+      <c r="AI50" s="45"/>
+      <c r="AJ50" s="45"/>
+      <c r="AK50" s="45"/>
+      <c r="AL50" s="45">
         <v>2009</v>
       </c>
-      <c r="AM50" s="44"/>
-      <c r="AN50" s="44"/>
-      <c r="AO50" s="44"/>
-      <c r="AP50" s="44">
+      <c r="AM50" s="45"/>
+      <c r="AN50" s="45"/>
+      <c r="AO50" s="45"/>
+      <c r="AP50" s="45">
         <v>2010</v>
       </c>
-      <c r="AQ50" s="44"/>
-      <c r="AR50" s="44"/>
-      <c r="AS50" s="44"/>
-      <c r="AT50" s="44">
+      <c r="AQ50" s="45"/>
+      <c r="AR50" s="45"/>
+      <c r="AS50" s="45"/>
+      <c r="AT50" s="45">
         <v>2011</v>
       </c>
-      <c r="AU50" s="44"/>
-      <c r="AV50" s="44"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="44">
+      <c r="AU50" s="45"/>
+      <c r="AV50" s="45"/>
+      <c r="AW50" s="45"/>
+      <c r="AX50" s="45">
         <v>2012</v>
       </c>
-      <c r="AY50" s="44"/>
-      <c r="AZ50" s="44"/>
-      <c r="BA50" s="44"/>
-      <c r="BB50" s="44">
+      <c r="AY50" s="45"/>
+      <c r="AZ50" s="45"/>
+      <c r="BA50" s="45"/>
+      <c r="BB50" s="45">
         <v>2013</v>
       </c>
-      <c r="BC50" s="44"/>
-      <c r="BD50" s="44"/>
-      <c r="BE50" s="44"/>
-      <c r="BF50" s="44">
+      <c r="BC50" s="45"/>
+      <c r="BD50" s="45"/>
+      <c r="BE50" s="45"/>
+      <c r="BF50" s="45">
         <v>2014</v>
       </c>
-      <c r="BG50" s="44"/>
-      <c r="BH50" s="44"/>
-      <c r="BI50" s="44"/>
-      <c r="BJ50" s="44">
+      <c r="BG50" s="45"/>
+      <c r="BH50" s="45"/>
+      <c r="BI50" s="45"/>
+      <c r="BJ50" s="45">
         <v>2015</v>
       </c>
-      <c r="BK50" s="44"/>
-      <c r="BL50" s="44"/>
-      <c r="BM50" s="44"/>
-      <c r="BN50" s="44">
+      <c r="BK50" s="45"/>
+      <c r="BL50" s="45"/>
+      <c r="BM50" s="45"/>
+      <c r="BN50" s="45">
         <v>2016</v>
       </c>
-      <c r="BO50" s="44"/>
-      <c r="BP50" s="44"/>
-      <c r="BQ50" s="44"/>
-      <c r="BR50" s="44">
+      <c r="BO50" s="45"/>
+      <c r="BP50" s="45"/>
+      <c r="BQ50" s="45"/>
+      <c r="BR50" s="45">
         <v>2017</v>
       </c>
-      <c r="BS50" s="44"/>
-      <c r="BT50" s="44"/>
-      <c r="BU50" s="44"/>
-      <c r="BV50" s="44">
+      <c r="BS50" s="45"/>
+      <c r="BT50" s="45"/>
+      <c r="BU50" s="45"/>
+      <c r="BV50" s="45">
         <v>2018</v>
       </c>
-      <c r="BW50" s="44"/>
-      <c r="BX50" s="44"/>
-      <c r="BY50" s="44"/>
-      <c r="BZ50" s="44">
+      <c r="BW50" s="45"/>
+      <c r="BX50" s="45"/>
+      <c r="BY50" s="45"/>
+      <c r="BZ50" s="45">
         <v>2019</v>
       </c>
-      <c r="CA50" s="44"/>
-      <c r="CB50" s="44"/>
-      <c r="CC50" s="44"/>
-      <c r="CD50" s="45">
+      <c r="CA50" s="45"/>
+      <c r="CB50" s="45"/>
+      <c r="CC50" s="45"/>
+      <c r="CD50" s="44">
         <v>2020</v>
       </c>
-      <c r="CE50" s="45"/>
-      <c r="CF50" s="45"/>
-      <c r="CG50" s="45"/>
+      <c r="CE50" s="44"/>
+      <c r="CF50" s="44"/>
+      <c r="CG50" s="44"/>
       <c r="CH50" s="26">
         <v>2021</v>
       </c>
@@ -11203,6 +11277,9 @@
       <c r="CY50" s="28"/>
       <c r="CZ50" s="28"/>
       <c r="DA50" s="28"/>
+      <c r="DB50" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="51" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
@@ -11519,6 +11596,9 @@
       </c>
       <c r="DA51" s="34" t="s">
         <v>9</v>
+      </c>
+      <c r="DB51" s="34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -11840,7 +11920,9 @@
       <c r="DA53" s="29">
         <v>55485.425004640681</v>
       </c>
-      <c r="DB53" s="9"/>
+      <c r="DB53" s="29">
+        <v>51858.32542975407</v>
+      </c>
       <c r="DC53" s="9"/>
       <c r="DD53" s="9"/>
       <c r="DE53" s="9"/>
@@ -12204,7 +12286,9 @@
       <c r="DA54" s="30">
         <v>3742.5695592526358</v>
       </c>
-      <c r="DB54" s="9"/>
+      <c r="DB54" s="30">
+        <v>2365.4175792992501</v>
+      </c>
       <c r="DC54" s="9"/>
       <c r="DD54" s="9"/>
       <c r="DE54" s="9"/>
@@ -12568,7 +12652,9 @@
       <c r="DA55" s="30">
         <v>12641.471973945498</v>
       </c>
-      <c r="DB55" s="9"/>
+      <c r="DB55" s="30">
+        <v>7017.0289261715379</v>
+      </c>
       <c r="DC55" s="9"/>
       <c r="DD55" s="9"/>
       <c r="DE55" s="9"/>
@@ -12932,7 +13018,9 @@
       <c r="DA56" s="30">
         <v>1579.4531969245238</v>
       </c>
-      <c r="DB56" s="9"/>
+      <c r="DB56" s="30">
+        <v>740.66992933069241</v>
+      </c>
       <c r="DC56" s="9"/>
       <c r="DD56" s="9"/>
       <c r="DE56" s="9"/>
@@ -13296,7 +13384,9 @@
       <c r="DA57" s="30">
         <v>751.02438727416393</v>
       </c>
-      <c r="DB57" s="9"/>
+      <c r="DB57" s="30">
+        <v>521.01161232576021</v>
+      </c>
       <c r="DC57" s="9"/>
       <c r="DD57" s="9"/>
       <c r="DE57" s="9"/>
@@ -13660,7 +13750,9 @@
       <c r="DA58" s="30">
         <v>2913.0534341657817</v>
       </c>
-      <c r="DB58" s="9"/>
+      <c r="DB58" s="30">
+        <v>2667.4471869178847</v>
+      </c>
       <c r="DC58" s="9"/>
       <c r="DD58" s="9"/>
       <c r="DE58" s="9"/>
@@ -14024,7 +14116,9 @@
       <c r="DA59" s="30">
         <v>21093.154943835943</v>
       </c>
-      <c r="DB59" s="9"/>
+      <c r="DB59" s="30">
+        <v>28812.631125805601</v>
+      </c>
       <c r="DC59" s="9"/>
       <c r="DD59" s="9"/>
       <c r="DE59" s="9"/>
@@ -14388,7 +14482,9 @@
       <c r="DA60" s="30">
         <v>1875.1515277699841</v>
       </c>
-      <c r="DB60" s="9"/>
+      <c r="DB60" s="30">
+        <v>906.40131485679854</v>
+      </c>
       <c r="DC60" s="9"/>
       <c r="DD60" s="9"/>
       <c r="DE60" s="9"/>
@@ -14752,7 +14848,9 @@
       <c r="DA61" s="30">
         <v>10889.545981472149</v>
       </c>
-      <c r="DB61" s="9"/>
+      <c r="DB61" s="30">
+        <v>8827.7177550465531</v>
+      </c>
       <c r="DC61" s="9"/>
       <c r="DD61" s="9"/>
       <c r="DE61" s="9"/>
@@ -15116,7 +15214,9 @@
       <c r="DA62" s="29">
         <v>62436.137977860148</v>
       </c>
-      <c r="DB62" s="9"/>
+      <c r="DB62" s="29">
+        <v>71690.170204316179</v>
+      </c>
       <c r="DC62" s="9"/>
       <c r="DD62" s="9"/>
       <c r="DE62" s="9"/>
@@ -15480,7 +15580,9 @@
       <c r="DA63" s="30">
         <v>10088.116006955095</v>
       </c>
-      <c r="DB63" s="9"/>
+      <c r="DB63" s="30">
+        <v>10446.140727455169</v>
+      </c>
       <c r="DC63" s="9"/>
       <c r="DD63" s="9"/>
       <c r="DE63" s="9"/>
@@ -15844,7 +15946,9 @@
       <c r="DA64" s="30">
         <v>6464.440980921745</v>
       </c>
-      <c r="DB64" s="9"/>
+      <c r="DB64" s="30">
+        <v>6155.7226556496362</v>
+      </c>
       <c r="DC64" s="9"/>
       <c r="DD64" s="9"/>
       <c r="DE64" s="9"/>
@@ -16208,7 +16312,9 @@
       <c r="DA65" s="30">
         <v>18032.731078172961</v>
       </c>
-      <c r="DB65" s="9"/>
+      <c r="DB65" s="30">
+        <v>28407.525674064516</v>
+      </c>
       <c r="DC65" s="9"/>
       <c r="DD65" s="9"/>
       <c r="DE65" s="9"/>
@@ -16572,7 +16678,9 @@
       <c r="DA66" s="30">
         <v>27850.849911810343</v>
       </c>
-      <c r="DB66" s="9"/>
+      <c r="DB66" s="30">
+        <v>26680.781147146856</v>
+      </c>
       <c r="DC66" s="9"/>
       <c r="DD66" s="9"/>
       <c r="DE66" s="9"/>
@@ -16936,7 +17044,9 @@
       <c r="DA67" s="29">
         <v>176929.54655802119</v>
       </c>
-      <c r="DB67" s="9"/>
+      <c r="DB67" s="29">
+        <v>175997.47458898905</v>
+      </c>
       <c r="DC67" s="9"/>
       <c r="DD67" s="9"/>
       <c r="DE67" s="9"/>
@@ -17300,7 +17410,9 @@
       <c r="DA68" s="30">
         <v>155291.63228520803</v>
       </c>
-      <c r="DB68" s="9"/>
+      <c r="DB68" s="30">
+        <v>161334.53463606464</v>
+      </c>
       <c r="DC68" s="9"/>
       <c r="DD68" s="9"/>
       <c r="DE68" s="9"/>
@@ -17664,7 +17776,9 @@
       <c r="DA69" s="30">
         <v>114.79683451410673</v>
       </c>
-      <c r="DB69" s="9"/>
+      <c r="DB69" s="30">
+        <v>169.55452404218499</v>
+      </c>
       <c r="DC69" s="9"/>
       <c r="DD69" s="9"/>
       <c r="DE69" s="9"/>
@@ -18028,7 +18142,9 @@
       <c r="DA70" s="30">
         <v>20494.545638734577</v>
       </c>
-      <c r="DB70" s="9"/>
+      <c r="DB70" s="30">
+        <v>5963.0282430744028</v>
+      </c>
       <c r="DC70" s="9"/>
       <c r="DD70" s="9"/>
       <c r="DE70" s="9"/>
@@ -18392,7 +18508,9 @@
       <c r="DA71" s="30">
         <v>1028.5717995644927</v>
       </c>
-      <c r="DB71" s="9"/>
+      <c r="DB71" s="30">
+        <v>8530.3571858078485</v>
+      </c>
       <c r="DC71" s="9"/>
       <c r="DD71" s="9"/>
       <c r="DE71" s="9"/>
@@ -18756,7 +18874,9 @@
       <c r="DA72" s="29">
         <v>44391.039207315385</v>
       </c>
-      <c r="DB72" s="9"/>
+      <c r="DB72" s="29">
+        <v>69364.585006435023</v>
+      </c>
       <c r="DC72" s="9"/>
       <c r="DD72" s="9"/>
       <c r="DE72" s="9"/>
@@ -19120,7 +19240,9 @@
       <c r="DA73" s="30">
         <v>4757.3874154863979</v>
       </c>
-      <c r="DB73" s="9"/>
+      <c r="DB73" s="30">
+        <v>7498.8912870855947</v>
+      </c>
       <c r="DC73" s="9"/>
       <c r="DD73" s="9"/>
       <c r="DE73" s="9"/>
@@ -19484,7 +19606,9 @@
       <c r="DA74" s="30">
         <v>8175.5864664965393</v>
       </c>
-      <c r="DB74" s="9"/>
+      <c r="DB74" s="30">
+        <v>13000.643964755536</v>
+      </c>
       <c r="DC74" s="9"/>
       <c r="DD74" s="9"/>
       <c r="DE74" s="9"/>
@@ -19848,7 +19972,9 @@
       <c r="DA75" s="30">
         <v>22821.629356303205</v>
       </c>
-      <c r="DB75" s="9"/>
+      <c r="DB75" s="30">
+        <v>32750.223486286122</v>
+      </c>
       <c r="DC75" s="9"/>
       <c r="DD75" s="9"/>
       <c r="DE75" s="9"/>
@@ -20212,7 +20338,9 @@
       <c r="DA76" s="30">
         <v>8636.4359690292404</v>
       </c>
-      <c r="DB76" s="9"/>
+      <c r="DB76" s="30">
+        <v>16114.82626830777</v>
+      </c>
       <c r="DC76" s="9"/>
       <c r="DD76" s="9"/>
       <c r="DE76" s="9"/>
@@ -20365,7 +20493,7 @@
       <c r="CY77" s="31"/>
       <c r="CZ77" s="31"/>
       <c r="DA77" s="31"/>
-      <c r="DB77" s="9"/>
+      <c r="DB77" s="31"/>
       <c r="DC77" s="9"/>
       <c r="DD77" s="9"/>
       <c r="DE77" s="9"/>
@@ -20729,7 +20857,9 @@
       <c r="DA78" s="32">
         <v>339242.14874783735</v>
       </c>
-      <c r="DB78" s="9"/>
+      <c r="DB78" s="32">
+        <v>368910.55522949435</v>
+      </c>
       <c r="DC78" s="9"/>
       <c r="DD78" s="9"/>
       <c r="DE78" s="9"/>
@@ -20883,6 +21013,7 @@
       <c r="CY79" s="33"/>
       <c r="CZ79" s="33"/>
       <c r="DA79" s="33"/>
+      <c r="DB79" s="33"/>
     </row>
     <row r="80" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A80" s="15" t="s">
@@ -21015,7 +21146,7 @@
       <c r="CY81" s="35"/>
       <c r="CZ81" s="35"/>
       <c r="DA81" s="35"/>
-      <c r="DB81" s="18"/>
+      <c r="DB81" s="35"/>
       <c r="DC81" s="18"/>
       <c r="DD81" s="18"/>
       <c r="DE81" s="18"/>
@@ -21169,7 +21300,7 @@
       <c r="CY82" s="35"/>
       <c r="CZ82" s="35"/>
       <c r="DA82" s="35"/>
-      <c r="DB82" s="18"/>
+      <c r="DB82" s="35"/>
       <c r="DC82" s="18"/>
       <c r="DD82" s="18"/>
       <c r="DE82" s="18"/>
@@ -21229,7 +21360,7 @@
     </row>
     <row r="85" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:152" x14ac:dyDescent="0.2">
@@ -21245,6 +21376,7 @@
       <c r="CY86" s="36"/>
       <c r="CZ86" s="36"/>
       <c r="DA86" s="36"/>
+      <c r="DB86" s="36"/>
     </row>
     <row r="87" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
@@ -21262,10 +21394,11 @@
       <c r="CY87" s="36"/>
       <c r="CZ87" s="36"/>
       <c r="DA87" s="36"/>
+      <c r="DB87" s="36"/>
     </row>
     <row r="88" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CP88" s="36"/>
       <c r="CQ88" s="36"/>
@@ -21279,6 +21412,7 @@
       <c r="CY88" s="36"/>
       <c r="CZ88" s="36"/>
       <c r="DA88" s="36"/>
+      <c r="DB88" s="36"/>
     </row>
     <row r="89" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
@@ -21288,141 +21422,143 @@
       <c r="CY89" s="41"/>
       <c r="CZ89" s="41"/>
       <c r="DA89" s="41"/>
+      <c r="DB89" s="41"/>
     </row>
     <row r="90" spans="1:152" x14ac:dyDescent="0.2">
       <c r="CX90" s="41"/>
       <c r="CY90" s="41"/>
       <c r="CZ90" s="41"/>
       <c r="DA90" s="41"/>
+      <c r="DB90" s="41"/>
     </row>
     <row r="91" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
-      <c r="B91" s="45" t="s">
+      <c r="B91" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C91" s="44"/>
-      <c r="D91" s="44"/>
-      <c r="E91" s="44"/>
-      <c r="F91" s="45" t="s">
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="G91" s="44"/>
-      <c r="H91" s="44"/>
-      <c r="I91" s="44"/>
-      <c r="J91" s="45" t="s">
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="K91" s="44"/>
-      <c r="L91" s="44"/>
-      <c r="M91" s="44"/>
-      <c r="N91" s="45" t="s">
+      <c r="K91" s="45"/>
+      <c r="L91" s="45"/>
+      <c r="M91" s="45"/>
+      <c r="N91" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="O91" s="44"/>
-      <c r="P91" s="44"/>
-      <c r="Q91" s="44"/>
-      <c r="R91" s="45" t="s">
+      <c r="O91" s="45"/>
+      <c r="P91" s="45"/>
+      <c r="Q91" s="45"/>
+      <c r="R91" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="S91" s="44"/>
-      <c r="T91" s="44"/>
-      <c r="U91" s="44"/>
-      <c r="V91" s="45" t="s">
+      <c r="S91" s="45"/>
+      <c r="T91" s="45"/>
+      <c r="U91" s="45"/>
+      <c r="V91" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="W91" s="44"/>
-      <c r="X91" s="44"/>
-      <c r="Y91" s="44"/>
-      <c r="Z91" s="45" t="s">
+      <c r="W91" s="45"/>
+      <c r="X91" s="45"/>
+      <c r="Y91" s="45"/>
+      <c r="Z91" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="AA91" s="44"/>
-      <c r="AB91" s="44"/>
-      <c r="AC91" s="44"/>
-      <c r="AD91" s="45" t="s">
+      <c r="AA91" s="45"/>
+      <c r="AB91" s="45"/>
+      <c r="AC91" s="45"/>
+      <c r="AD91" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="AE91" s="44"/>
-      <c r="AF91" s="44"/>
-      <c r="AG91" s="44"/>
-      <c r="AH91" s="45" t="s">
+      <c r="AE91" s="45"/>
+      <c r="AF91" s="45"/>
+      <c r="AG91" s="45"/>
+      <c r="AH91" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="AI91" s="44"/>
-      <c r="AJ91" s="44"/>
-      <c r="AK91" s="44"/>
-      <c r="AL91" s="45" t="s">
+      <c r="AI91" s="45"/>
+      <c r="AJ91" s="45"/>
+      <c r="AK91" s="45"/>
+      <c r="AL91" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="AM91" s="44"/>
-      <c r="AN91" s="44"/>
-      <c r="AO91" s="44"/>
-      <c r="AP91" s="45" t="s">
+      <c r="AM91" s="45"/>
+      <c r="AN91" s="45"/>
+      <c r="AO91" s="45"/>
+      <c r="AP91" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="AQ91" s="44"/>
-      <c r="AR91" s="44"/>
-      <c r="AS91" s="44"/>
-      <c r="AT91" s="45" t="s">
+      <c r="AQ91" s="45"/>
+      <c r="AR91" s="45"/>
+      <c r="AS91" s="45"/>
+      <c r="AT91" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="AU91" s="44"/>
-      <c r="AV91" s="44"/>
-      <c r="AW91" s="44"/>
-      <c r="AX91" s="45" t="s">
+      <c r="AU91" s="45"/>
+      <c r="AV91" s="45"/>
+      <c r="AW91" s="45"/>
+      <c r="AX91" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="AY91" s="44"/>
-      <c r="AZ91" s="44"/>
-      <c r="BA91" s="44"/>
-      <c r="BB91" s="45" t="s">
+      <c r="AY91" s="45"/>
+      <c r="AZ91" s="45"/>
+      <c r="BA91" s="45"/>
+      <c r="BB91" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="BC91" s="44"/>
-      <c r="BD91" s="44"/>
-      <c r="BE91" s="44"/>
-      <c r="BF91" s="45" t="s">
+      <c r="BC91" s="45"/>
+      <c r="BD91" s="45"/>
+      <c r="BE91" s="45"/>
+      <c r="BF91" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="BG91" s="44"/>
-      <c r="BH91" s="44"/>
-      <c r="BI91" s="44"/>
-      <c r="BJ91" s="45" t="s">
+      <c r="BG91" s="45"/>
+      <c r="BH91" s="45"/>
+      <c r="BI91" s="45"/>
+      <c r="BJ91" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BK91" s="44"/>
-      <c r="BL91" s="44"/>
-      <c r="BM91" s="44"/>
-      <c r="BN91" s="45" t="s">
+      <c r="BK91" s="45"/>
+      <c r="BL91" s="45"/>
+      <c r="BM91" s="45"/>
+      <c r="BN91" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="BO91" s="44"/>
-      <c r="BP91" s="44"/>
-      <c r="BQ91" s="44"/>
-      <c r="BR91" s="45" t="s">
+      <c r="BO91" s="45"/>
+      <c r="BP91" s="45"/>
+      <c r="BQ91" s="45"/>
+      <c r="BR91" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="BS91" s="44"/>
-      <c r="BT91" s="44"/>
-      <c r="BU91" s="44"/>
-      <c r="BV91" s="45" t="s">
+      <c r="BS91" s="45"/>
+      <c r="BT91" s="45"/>
+      <c r="BU91" s="45"/>
+      <c r="BV91" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="BW91" s="44"/>
-      <c r="BX91" s="44"/>
-      <c r="BY91" s="44"/>
-      <c r="BZ91" s="45" t="s">
+      <c r="BW91" s="45"/>
+      <c r="BX91" s="45"/>
+      <c r="BY91" s="45"/>
+      <c r="BZ91" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="CA91" s="44"/>
-      <c r="CB91" s="44"/>
-      <c r="CC91" s="44"/>
-      <c r="CD91" s="45" t="s">
+      <c r="CA91" s="45"/>
+      <c r="CB91" s="45"/>
+      <c r="CC91" s="45"/>
+      <c r="CD91" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="CE91" s="45"/>
-      <c r="CF91" s="45"/>
-      <c r="CG91" s="45"/>
+      <c r="CE91" s="44"/>
+      <c r="CF91" s="44"/>
+      <c r="CG91" s="44"/>
       <c r="CH91" s="26" t="s">
         <v>71</v>
       </c>
@@ -21447,10 +21583,13 @@
       <c r="CU91" s="28"/>
       <c r="CV91" s="28"/>
       <c r="CW91" s="28"/>
-      <c r="CX91" s="42"/>
+      <c r="CX91" s="28" t="s">
+        <v>78</v>
+      </c>
       <c r="CY91" s="42"/>
       <c r="CZ91" s="42"/>
       <c r="DA91" s="42"/>
+      <c r="DB91" s="42"/>
     </row>
     <row r="92" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
@@ -21756,17 +21895,20 @@
       <c r="CW92" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="CX92" s="43"/>
+      <c r="CX92" s="34" t="s">
+        <v>6</v>
+      </c>
       <c r="CY92" s="43"/>
       <c r="CZ92" s="43"/>
       <c r="DA92" s="43"/>
+      <c r="DB92" s="43"/>
     </row>
     <row r="93" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7"/>
-      <c r="CX93" s="41"/>
       <c r="CY93" s="41"/>
       <c r="CZ93" s="41"/>
       <c r="DA93" s="41"/>
+      <c r="DB93" s="41"/>
     </row>
     <row r="94" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
@@ -22072,11 +22214,13 @@
       <c r="CW94" s="35">
         <v>-8.6188538314515739</v>
       </c>
-      <c r="CX94" s="37"/>
+      <c r="CX94" s="35">
+        <v>-6.0122133080354132</v>
+      </c>
       <c r="CY94" s="37"/>
       <c r="CZ94" s="37"/>
       <c r="DA94" s="37"/>
-      <c r="DB94" s="9"/>
+      <c r="DB94" s="37"/>
       <c r="DC94" s="9"/>
       <c r="DD94" s="9"/>
       <c r="DE94" s="9"/>
@@ -22423,11 +22567,13 @@
       <c r="CW95" s="35">
         <v>-2.5352571270074833</v>
       </c>
-      <c r="CX95" s="37"/>
+      <c r="CX95" s="35">
+        <v>-45.438739241173266</v>
+      </c>
       <c r="CY95" s="37"/>
       <c r="CZ95" s="37"/>
       <c r="DA95" s="37"/>
-      <c r="DB95" s="9"/>
+      <c r="DB95" s="37"/>
       <c r="DC95" s="9"/>
       <c r="DD95" s="9"/>
       <c r="DE95" s="9"/>
@@ -22774,11 +22920,13 @@
       <c r="CW96" s="35">
         <v>4.2120389819592816</v>
       </c>
-      <c r="CX96" s="37"/>
+      <c r="CX96" s="35">
+        <v>-10.056017422967713</v>
+      </c>
       <c r="CY96" s="37"/>
       <c r="CZ96" s="37"/>
       <c r="DA96" s="37"/>
-      <c r="DB96" s="9"/>
+      <c r="DB96" s="37"/>
       <c r="DC96" s="9"/>
       <c r="DD96" s="9"/>
       <c r="DE96" s="9"/>
@@ -23125,11 +23273,13 @@
       <c r="CW97" s="35">
         <v>17.491086625573644</v>
       </c>
-      <c r="CX97" s="37"/>
+      <c r="CX97" s="35">
+        <v>10.273904002824878</v>
+      </c>
       <c r="CY97" s="37"/>
       <c r="CZ97" s="37"/>
       <c r="DA97" s="37"/>
-      <c r="DB97" s="9"/>
+      <c r="DB97" s="37"/>
       <c r="DC97" s="9"/>
       <c r="DD97" s="9"/>
       <c r="DE97" s="9"/>
@@ -23476,11 +23626,13 @@
       <c r="CW98" s="35">
         <v>-9.6098608166205111</v>
       </c>
-      <c r="CX98" s="37"/>
+      <c r="CX98" s="35">
+        <v>-5.7652789940374873</v>
+      </c>
       <c r="CY98" s="37"/>
       <c r="CZ98" s="37"/>
       <c r="DA98" s="37"/>
-      <c r="DB98" s="9"/>
+      <c r="DB98" s="37"/>
       <c r="DC98" s="9"/>
       <c r="DD98" s="9"/>
       <c r="DE98" s="9"/>
@@ -23827,11 +23979,13 @@
       <c r="CW99" s="35">
         <v>-0.80974295827819276</v>
       </c>
-      <c r="CX99" s="37"/>
+      <c r="CX99" s="35">
+        <v>5.1268865092263667</v>
+      </c>
       <c r="CY99" s="37"/>
       <c r="CZ99" s="37"/>
       <c r="DA99" s="37"/>
-      <c r="DB99" s="9"/>
+      <c r="DB99" s="37"/>
       <c r="DC99" s="9"/>
       <c r="DD99" s="9"/>
       <c r="DE99" s="9"/>
@@ -24178,11 +24332,13 @@
       <c r="CW100" s="35">
         <v>-16.262585892117926</v>
       </c>
-      <c r="CX100" s="37"/>
+      <c r="CX100" s="35">
+        <v>-2.549348731064228</v>
+      </c>
       <c r="CY100" s="37"/>
       <c r="CZ100" s="37"/>
       <c r="DA100" s="37"/>
-      <c r="DB100" s="9"/>
+      <c r="DB100" s="37"/>
       <c r="DC100" s="9"/>
       <c r="DD100" s="9"/>
       <c r="DE100" s="9"/>
@@ -24529,11 +24685,13 @@
       <c r="CW101" s="35">
         <v>-15.881585527664527</v>
       </c>
-      <c r="CX101" s="37"/>
+      <c r="CX101" s="35">
+        <v>-12.45950574111815</v>
+      </c>
       <c r="CY101" s="37"/>
       <c r="CZ101" s="37"/>
       <c r="DA101" s="37"/>
-      <c r="DB101" s="9"/>
+      <c r="DB101" s="37"/>
       <c r="DC101" s="9"/>
       <c r="DD101" s="9"/>
       <c r="DE101" s="9"/>
@@ -24880,11 +25038,13 @@
       <c r="CW102" s="35">
         <v>-6.6141807037474365</v>
       </c>
-      <c r="CX102" s="37"/>
+      <c r="CX102" s="35">
+        <v>3.3864776426430154</v>
+      </c>
       <c r="CY102" s="37"/>
       <c r="CZ102" s="37"/>
       <c r="DA102" s="37"/>
-      <c r="DB102" s="9"/>
+      <c r="DB102" s="37"/>
       <c r="DC102" s="9"/>
       <c r="DD102" s="9"/>
       <c r="DE102" s="9"/>
@@ -25231,11 +25391,13 @@
       <c r="CW103" s="35">
         <v>11.300172405380977</v>
       </c>
-      <c r="CX103" s="37"/>
+      <c r="CX103" s="35">
+        <v>36.228325049430111</v>
+      </c>
       <c r="CY103" s="37"/>
       <c r="CZ103" s="37"/>
       <c r="DA103" s="37"/>
-      <c r="DB103" s="9"/>
+      <c r="DB103" s="37"/>
       <c r="DC103" s="9"/>
       <c r="DD103" s="9"/>
       <c r="DE103" s="9"/>
@@ -25582,11 +25744,13 @@
       <c r="CW104" s="35">
         <v>-14.065456488146097</v>
       </c>
-      <c r="CX104" s="37"/>
+      <c r="CX104" s="35">
+        <v>1.1766397538862208</v>
+      </c>
       <c r="CY104" s="37"/>
       <c r="CZ104" s="37"/>
       <c r="DA104" s="37"/>
-      <c r="DB104" s="9"/>
+      <c r="DB104" s="37"/>
       <c r="DC104" s="9"/>
       <c r="DD104" s="9"/>
       <c r="DE104" s="9"/>
@@ -25933,11 +26097,13 @@
       <c r="CW105" s="35">
         <v>11.56369868126292</v>
       </c>
-      <c r="CX105" s="37"/>
+      <c r="CX105" s="35">
+        <v>5.7926982564326011</v>
+      </c>
       <c r="CY105" s="37"/>
       <c r="CZ105" s="37"/>
       <c r="DA105" s="37"/>
-      <c r="DB105" s="9"/>
+      <c r="DB105" s="37"/>
       <c r="DC105" s="9"/>
       <c r="DD105" s="9"/>
       <c r="DE105" s="9"/>
@@ -26284,11 +26450,13 @@
       <c r="CW106" s="35">
         <v>22.91512402902876</v>
       </c>
-      <c r="CX106" s="37"/>
+      <c r="CX106" s="35">
+        <v>116.89493707821339</v>
+      </c>
       <c r="CY106" s="37"/>
       <c r="CZ106" s="37"/>
       <c r="DA106" s="37"/>
-      <c r="DB106" s="9"/>
+      <c r="DB106" s="37"/>
       <c r="DC106" s="9"/>
       <c r="DD106" s="9"/>
       <c r="DE106" s="9"/>
@@ -26635,11 +26803,13 @@
       <c r="CW107" s="35">
         <v>16.69503261506695</v>
       </c>
-      <c r="CX107" s="37"/>
+      <c r="CX107" s="35">
+        <v>10.094396166108368</v>
+      </c>
       <c r="CY107" s="37"/>
       <c r="CZ107" s="37"/>
       <c r="DA107" s="37"/>
-      <c r="DB107" s="9"/>
+      <c r="DB107" s="37"/>
       <c r="DC107" s="9"/>
       <c r="DD107" s="9"/>
       <c r="DE107" s="9"/>
@@ -26986,11 +27156,13 @@
       <c r="CW108" s="35">
         <v>-0.64309506607362721</v>
       </c>
-      <c r="CX108" s="37"/>
+      <c r="CX108" s="35">
+        <v>-0.87242542891191022</v>
+      </c>
       <c r="CY108" s="37"/>
       <c r="CZ108" s="37"/>
       <c r="DA108" s="37"/>
-      <c r="DB108" s="9"/>
+      <c r="DB108" s="37"/>
       <c r="DC108" s="9"/>
       <c r="DD108" s="9"/>
       <c r="DE108" s="9"/>
@@ -27337,11 +27509,13 @@
       <c r="CW109" s="35">
         <v>-2.2845016140855421</v>
       </c>
-      <c r="CX109" s="37"/>
+      <c r="CX109" s="35">
+        <v>-4.2654101717939881</v>
+      </c>
       <c r="CY109" s="37"/>
       <c r="CZ109" s="37"/>
       <c r="DA109" s="37"/>
-      <c r="DB109" s="9"/>
+      <c r="DB109" s="37"/>
       <c r="DC109" s="9"/>
       <c r="DD109" s="9"/>
       <c r="DE109" s="9"/>
@@ -27688,11 +27862,13 @@
       <c r="CW110" s="35">
         <v>-95.338979391788129</v>
       </c>
-      <c r="CX110" s="37"/>
+      <c r="CX110" s="35">
+        <v>-35.799916910848921</v>
+      </c>
       <c r="CY110" s="37"/>
       <c r="CZ110" s="37"/>
       <c r="DA110" s="37"/>
-      <c r="DB110" s="9"/>
+      <c r="DB110" s="37"/>
       <c r="DC110" s="9"/>
       <c r="DD110" s="9"/>
       <c r="DE110" s="9"/>
@@ -28039,11 +28215,13 @@
       <c r="CW111" s="35">
         <v>31.898747574430445</v>
       </c>
-      <c r="CX111" s="37"/>
+      <c r="CX111" s="35">
+        <v>-23.285139844241769</v>
+      </c>
       <c r="CY111" s="37"/>
       <c r="CZ111" s="37"/>
       <c r="DA111" s="37"/>
-      <c r="DB111" s="9"/>
+      <c r="DB111" s="37"/>
       <c r="DC111" s="9"/>
       <c r="DD111" s="9"/>
       <c r="DE111" s="9"/>
@@ -28390,11 +28568,13 @@
       <c r="CW112" s="35">
         <v>-40.250147148520597</v>
       </c>
-      <c r="CX112" s="37"/>
+      <c r="CX112" s="35">
+        <v>227.33024838218421</v>
+      </c>
       <c r="CY112" s="37"/>
       <c r="CZ112" s="37"/>
       <c r="DA112" s="37"/>
-      <c r="DB112" s="9"/>
+      <c r="DB112" s="37"/>
       <c r="DC112" s="9"/>
       <c r="DD112" s="9"/>
       <c r="DE112" s="9"/>
@@ -28741,11 +28921,13 @@
       <c r="CW113" s="35">
         <v>5.4181405590148444</v>
       </c>
-      <c r="CX113" s="37"/>
+      <c r="CX113" s="35">
+        <v>2.2515013967214799</v>
+      </c>
       <c r="CY113" s="37"/>
       <c r="CZ113" s="37"/>
       <c r="DA113" s="37"/>
-      <c r="DB113" s="9"/>
+      <c r="DB113" s="37"/>
       <c r="DC113" s="9"/>
       <c r="DD113" s="9"/>
       <c r="DE113" s="9"/>
@@ -29092,11 +29274,13 @@
       <c r="CW114" s="35">
         <v>41.841228876531858</v>
       </c>
-      <c r="CX114" s="37"/>
+      <c r="CX114" s="35">
+        <v>43.311590129847843</v>
+      </c>
       <c r="CY114" s="37"/>
       <c r="CZ114" s="37"/>
       <c r="DA114" s="37"/>
-      <c r="DB114" s="9"/>
+      <c r="DB114" s="37"/>
       <c r="DC114" s="9"/>
       <c r="DD114" s="9"/>
       <c r="DE114" s="9"/>
@@ -29443,11 +29627,13 @@
       <c r="CW115" s="35">
         <v>-15.135173015990489</v>
       </c>
-      <c r="CX115" s="37"/>
+      <c r="CX115" s="35">
+        <v>-12.057640636296227</v>
+      </c>
       <c r="CY115" s="37"/>
       <c r="CZ115" s="37"/>
       <c r="DA115" s="37"/>
-      <c r="DB115" s="9"/>
+      <c r="DB115" s="37"/>
       <c r="DC115" s="9"/>
       <c r="DD115" s="9"/>
       <c r="DE115" s="9"/>
@@ -29794,11 +29980,13 @@
       <c r="CW116" s="35">
         <v>10.494187956421385</v>
       </c>
-      <c r="CX116" s="37"/>
+      <c r="CX116" s="35">
+        <v>7.0657804886849362</v>
+      </c>
       <c r="CY116" s="37"/>
       <c r="CZ116" s="37"/>
       <c r="DA116" s="37"/>
-      <c r="DB116" s="9"/>
+      <c r="DB116" s="37"/>
       <c r="DC116" s="9"/>
       <c r="DD116" s="9"/>
       <c r="DE116" s="9"/>
@@ -30145,11 +30333,13 @@
       <c r="CW117" s="35">
         <v>-8.1584786434592047</v>
       </c>
-      <c r="CX117" s="37"/>
+      <c r="CX117" s="35">
+        <v>-8.6410182833326985</v>
+      </c>
       <c r="CY117" s="37"/>
       <c r="CZ117" s="37"/>
       <c r="DA117" s="37"/>
-      <c r="DB117" s="9"/>
+      <c r="DB117" s="37"/>
       <c r="DC117" s="9"/>
       <c r="DD117" s="9"/>
       <c r="DE117" s="9"/>
@@ -30293,11 +30483,11 @@
       <c r="CU118" s="31"/>
       <c r="CV118" s="31"/>
       <c r="CW118" s="31"/>
-      <c r="CX118" s="39"/>
+      <c r="CX118" s="31"/>
       <c r="CY118" s="39"/>
       <c r="CZ118" s="39"/>
       <c r="DA118" s="39"/>
-      <c r="DB118" s="9"/>
+      <c r="DB118" s="39"/>
       <c r="DC118" s="9"/>
       <c r="DD118" s="9"/>
       <c r="DE118" s="9"/>
@@ -30644,11 +30834,13 @@
       <c r="CW119" s="38">
         <v>1.2035193095950092</v>
       </c>
-      <c r="CX119" s="40"/>
+      <c r="CX119" s="38">
+        <v>4.8313580178237743</v>
+      </c>
       <c r="CY119" s="40"/>
       <c r="CZ119" s="40"/>
       <c r="DA119" s="40"/>
-      <c r="DB119" s="9"/>
+      <c r="DB119" s="40"/>
       <c r="DC119" s="9"/>
       <c r="DD119" s="9"/>
       <c r="DE119" s="9"/>
@@ -30793,19 +30985,20 @@
       <c r="CU120" s="33"/>
       <c r="CV120" s="33"/>
       <c r="CW120" s="33"/>
-      <c r="CX120" s="43"/>
+      <c r="CX120" s="33"/>
       <c r="CY120" s="43"/>
       <c r="CZ120" s="43"/>
       <c r="DA120" s="43"/>
+      <c r="DB120" s="43"/>
     </row>
     <row r="121" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CX121" s="41"/>
       <c r="CY121" s="41"/>
       <c r="CZ121" s="41"/>
       <c r="DA121" s="41"/>
+      <c r="DB121" s="41"/>
     </row>
     <row r="122" spans="1:147" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
@@ -30911,11 +31104,11 @@
       <c r="CU122" s="31"/>
       <c r="CV122" s="31"/>
       <c r="CW122" s="31"/>
-      <c r="CX122" s="39"/>
+      <c r="CX122" s="31"/>
       <c r="CY122" s="39"/>
       <c r="CZ122" s="39"/>
       <c r="DA122" s="39"/>
-      <c r="DB122" s="9"/>
+      <c r="DB122" s="39"/>
       <c r="DC122" s="9"/>
       <c r="DD122" s="9"/>
       <c r="DE122" s="9"/>
@@ -31059,11 +31252,11 @@
       <c r="CU123" s="31"/>
       <c r="CV123" s="31"/>
       <c r="CW123" s="31"/>
-      <c r="CX123" s="39"/>
+      <c r="CX123" s="31"/>
       <c r="CY123" s="39"/>
       <c r="CZ123" s="39"/>
       <c r="DA123" s="39"/>
-      <c r="DB123" s="9"/>
+      <c r="DB123" s="39"/>
       <c r="DC123" s="9"/>
       <c r="DD123" s="9"/>
       <c r="DE123" s="9"/>
@@ -31110,196 +31303,196 @@
       <c r="A124" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="CX124" s="41"/>
       <c r="CY124" s="41"/>
       <c r="CZ124" s="41"/>
       <c r="DA124" s="41"/>
+      <c r="DB124" s="41"/>
     </row>
     <row r="125" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="CX125" s="41"/>
       <c r="CY125" s="41"/>
       <c r="CZ125" s="41"/>
       <c r="DA125" s="41"/>
+      <c r="DB125" s="41"/>
     </row>
     <row r="126" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CX126" s="41"/>
+        <v>75</v>
+      </c>
       <c r="CY126" s="41"/>
       <c r="CZ126" s="41"/>
       <c r="DA126" s="41"/>
+      <c r="DB126" s="41"/>
     </row>
     <row r="127" spans="1:147" x14ac:dyDescent="0.2">
-      <c r="CX127" s="41"/>
       <c r="CY127" s="41"/>
       <c r="CZ127" s="41"/>
       <c r="DA127" s="41"/>
+      <c r="DB127" s="41"/>
     </row>
     <row r="128" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CX128" s="41"/>
       <c r="CY128" s="41"/>
       <c r="CZ128" s="41"/>
       <c r="DA128" s="41"/>
+      <c r="DB128" s="41"/>
     </row>
     <row r="129" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="CX129" s="41"/>
+        <v>77</v>
+      </c>
       <c r="CY129" s="41"/>
       <c r="CZ129" s="41"/>
       <c r="DA129" s="41"/>
+      <c r="DB129" s="41"/>
     </row>
     <row r="130" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="CX130" s="41"/>
       <c r="CY130" s="41"/>
       <c r="CZ130" s="41"/>
       <c r="DA130" s="41"/>
+      <c r="DB130" s="41"/>
     </row>
     <row r="131" spans="1:147" x14ac:dyDescent="0.2">
-      <c r="CX131" s="41"/>
       <c r="CY131" s="41"/>
       <c r="CZ131" s="41"/>
       <c r="DA131" s="41"/>
+      <c r="DB131" s="41"/>
     </row>
     <row r="132" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
-      <c r="B132" s="45" t="s">
+      <c r="B132" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C132" s="44"/>
-      <c r="D132" s="44"/>
-      <c r="E132" s="44"/>
-      <c r="F132" s="45" t="s">
+      <c r="C132" s="45"/>
+      <c r="D132" s="45"/>
+      <c r="E132" s="45"/>
+      <c r="F132" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="G132" s="44"/>
-      <c r="H132" s="44"/>
-      <c r="I132" s="44"/>
-      <c r="J132" s="45" t="s">
+      <c r="G132" s="45"/>
+      <c r="H132" s="45"/>
+      <c r="I132" s="45"/>
+      <c r="J132" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="K132" s="44"/>
-      <c r="L132" s="44"/>
-      <c r="M132" s="44"/>
-      <c r="N132" s="45" t="s">
+      <c r="K132" s="45"/>
+      <c r="L132" s="45"/>
+      <c r="M132" s="45"/>
+      <c r="N132" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="O132" s="44"/>
-      <c r="P132" s="44"/>
-      <c r="Q132" s="44"/>
-      <c r="R132" s="45" t="s">
+      <c r="O132" s="45"/>
+      <c r="P132" s="45"/>
+      <c r="Q132" s="45"/>
+      <c r="R132" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="S132" s="44"/>
-      <c r="T132" s="44"/>
-      <c r="U132" s="44"/>
-      <c r="V132" s="45" t="s">
+      <c r="S132" s="45"/>
+      <c r="T132" s="45"/>
+      <c r="U132" s="45"/>
+      <c r="V132" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="W132" s="44"/>
-      <c r="X132" s="44"/>
-      <c r="Y132" s="44"/>
-      <c r="Z132" s="45" t="s">
+      <c r="W132" s="45"/>
+      <c r="X132" s="45"/>
+      <c r="Y132" s="45"/>
+      <c r="Z132" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="AA132" s="44"/>
-      <c r="AB132" s="44"/>
-      <c r="AC132" s="44"/>
-      <c r="AD132" s="45" t="s">
+      <c r="AA132" s="45"/>
+      <c r="AB132" s="45"/>
+      <c r="AC132" s="45"/>
+      <c r="AD132" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="AE132" s="44"/>
-      <c r="AF132" s="44"/>
-      <c r="AG132" s="44"/>
-      <c r="AH132" s="45" t="s">
+      <c r="AE132" s="45"/>
+      <c r="AF132" s="45"/>
+      <c r="AG132" s="45"/>
+      <c r="AH132" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="AI132" s="44"/>
-      <c r="AJ132" s="44"/>
-      <c r="AK132" s="44"/>
-      <c r="AL132" s="45" t="s">
+      <c r="AI132" s="45"/>
+      <c r="AJ132" s="45"/>
+      <c r="AK132" s="45"/>
+      <c r="AL132" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="AM132" s="44"/>
-      <c r="AN132" s="44"/>
-      <c r="AO132" s="44"/>
-      <c r="AP132" s="45" t="s">
+      <c r="AM132" s="45"/>
+      <c r="AN132" s="45"/>
+      <c r="AO132" s="45"/>
+      <c r="AP132" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="AQ132" s="44"/>
-      <c r="AR132" s="44"/>
-      <c r="AS132" s="44"/>
-      <c r="AT132" s="45" t="s">
+      <c r="AQ132" s="45"/>
+      <c r="AR132" s="45"/>
+      <c r="AS132" s="45"/>
+      <c r="AT132" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="AU132" s="44"/>
-      <c r="AV132" s="44"/>
-      <c r="AW132" s="44"/>
-      <c r="AX132" s="45" t="s">
+      <c r="AU132" s="45"/>
+      <c r="AV132" s="45"/>
+      <c r="AW132" s="45"/>
+      <c r="AX132" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="AY132" s="44"/>
-      <c r="AZ132" s="44"/>
-      <c r="BA132" s="44"/>
-      <c r="BB132" s="45" t="s">
+      <c r="AY132" s="45"/>
+      <c r="AZ132" s="45"/>
+      <c r="BA132" s="45"/>
+      <c r="BB132" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="BC132" s="44"/>
-      <c r="BD132" s="44"/>
-      <c r="BE132" s="44"/>
-      <c r="BF132" s="45" t="s">
+      <c r="BC132" s="45"/>
+      <c r="BD132" s="45"/>
+      <c r="BE132" s="45"/>
+      <c r="BF132" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="BG132" s="44"/>
-      <c r="BH132" s="44"/>
-      <c r="BI132" s="44"/>
-      <c r="BJ132" s="45" t="s">
+      <c r="BG132" s="45"/>
+      <c r="BH132" s="45"/>
+      <c r="BI132" s="45"/>
+      <c r="BJ132" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="BK132" s="44"/>
-      <c r="BL132" s="44"/>
-      <c r="BM132" s="44"/>
-      <c r="BN132" s="45" t="s">
+      <c r="BK132" s="45"/>
+      <c r="BL132" s="45"/>
+      <c r="BM132" s="45"/>
+      <c r="BN132" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="BO132" s="44"/>
-      <c r="BP132" s="44"/>
-      <c r="BQ132" s="44"/>
-      <c r="BR132" s="45" t="s">
+      <c r="BO132" s="45"/>
+      <c r="BP132" s="45"/>
+      <c r="BQ132" s="45"/>
+      <c r="BR132" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="BS132" s="44"/>
-      <c r="BT132" s="44"/>
-      <c r="BU132" s="44"/>
-      <c r="BV132" s="45" t="s">
+      <c r="BS132" s="45"/>
+      <c r="BT132" s="45"/>
+      <c r="BU132" s="45"/>
+      <c r="BV132" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="BW132" s="44"/>
-      <c r="BX132" s="44"/>
-      <c r="BY132" s="44"/>
-      <c r="BZ132" s="45" t="s">
+      <c r="BW132" s="45"/>
+      <c r="BX132" s="45"/>
+      <c r="BY132" s="45"/>
+      <c r="BZ132" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="CA132" s="44"/>
-      <c r="CB132" s="44"/>
-      <c r="CC132" s="44"/>
-      <c r="CD132" s="45" t="s">
+      <c r="CA132" s="45"/>
+      <c r="CB132" s="45"/>
+      <c r="CC132" s="45"/>
+      <c r="CD132" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="CE132" s="45"/>
-      <c r="CF132" s="45"/>
-      <c r="CG132" s="45"/>
+      <c r="CE132" s="44"/>
+      <c r="CF132" s="44"/>
+      <c r="CG132" s="44"/>
       <c r="CH132" s="26" t="s">
         <v>71</v>
       </c>
@@ -31324,10 +31517,13 @@
       <c r="CU132" s="28"/>
       <c r="CV132" s="28"/>
       <c r="CW132" s="28"/>
-      <c r="CX132" s="42"/>
+      <c r="CX132" s="28" t="s">
+        <v>78</v>
+      </c>
       <c r="CY132" s="42"/>
       <c r="CZ132" s="42"/>
       <c r="DA132" s="42"/>
+      <c r="DB132" s="42"/>
     </row>
     <row r="133" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
@@ -31633,17 +31829,20 @@
       <c r="CW133" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="CX133" s="43"/>
+      <c r="CX133" s="34" t="s">
+        <v>6</v>
+      </c>
       <c r="CY133" s="43"/>
       <c r="CZ133" s="43"/>
       <c r="DA133" s="43"/>
+      <c r="DB133" s="43"/>
     </row>
     <row r="134" spans="1:147" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
-      <c r="CX134" s="41"/>
       <c r="CY134" s="41"/>
       <c r="CZ134" s="41"/>
       <c r="DA134" s="41"/>
+      <c r="DB134" s="41"/>
     </row>
     <row r="135" spans="1:147" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
@@ -31949,11 +32148,13 @@
       <c r="CW135" s="35">
         <v>-9.2074653161846953</v>
       </c>
-      <c r="CX135" s="37"/>
+      <c r="CX135" s="35">
+        <v>-8.293875519041265</v>
+      </c>
       <c r="CY135" s="37"/>
       <c r="CZ135" s="37"/>
       <c r="DA135" s="37"/>
-      <c r="DB135" s="9"/>
+      <c r="DB135" s="37"/>
       <c r="DC135" s="9"/>
       <c r="DD135" s="9"/>
       <c r="DE135" s="9"/>
@@ -32300,11 +32501,13 @@
       <c r="CW136" s="35">
         <v>-7.0178251160777307</v>
       </c>
-      <c r="CX136" s="37"/>
+      <c r="CX136" s="35">
+        <v>-47.727151911273026</v>
+      </c>
       <c r="CY136" s="37"/>
       <c r="CZ136" s="37"/>
       <c r="DA136" s="37"/>
-      <c r="DB136" s="9"/>
+      <c r="DB136" s="37"/>
       <c r="DC136" s="9"/>
       <c r="DD136" s="9"/>
       <c r="DE136" s="9"/>
@@ -32651,11 +32854,13 @@
       <c r="CW137" s="35">
         <v>-0.5111894945355715</v>
       </c>
-      <c r="CX137" s="37"/>
+      <c r="CX137" s="35">
+        <v>-14.027891599757197</v>
+      </c>
       <c r="CY137" s="37"/>
       <c r="CZ137" s="37"/>
       <c r="DA137" s="37"/>
-      <c r="DB137" s="9"/>
+      <c r="DB137" s="37"/>
       <c r="DC137" s="9"/>
       <c r="DD137" s="9"/>
       <c r="DE137" s="9"/>
@@ -33002,11 +33207,13 @@
       <c r="CW138" s="35">
         <v>15.078692809835132</v>
       </c>
-      <c r="CX138" s="37"/>
+      <c r="CX138" s="35">
+        <v>2.6231952990704315</v>
+      </c>
       <c r="CY138" s="37"/>
       <c r="CZ138" s="37"/>
       <c r="DA138" s="37"/>
-      <c r="DB138" s="9"/>
+      <c r="DB138" s="37"/>
       <c r="DC138" s="9"/>
       <c r="DD138" s="9"/>
       <c r="DE138" s="9"/>
@@ -33353,11 +33560,13 @@
       <c r="CW139" s="35">
         <v>-12.765076251092168</v>
       </c>
-      <c r="CX139" s="37"/>
+      <c r="CX139" s="35">
+        <v>-10.044882586604373</v>
+      </c>
       <c r="CY139" s="37"/>
       <c r="CZ139" s="37"/>
       <c r="DA139" s="37"/>
-      <c r="DB139" s="9"/>
+      <c r="DB139" s="37"/>
       <c r="DC139" s="9"/>
       <c r="DD139" s="9"/>
       <c r="DE139" s="9"/>
@@ -33704,11 +33913,13 @@
       <c r="CW140" s="35">
         <v>-4.9595381667371754</v>
       </c>
-      <c r="CX140" s="37"/>
+      <c r="CX140" s="35">
+        <v>0.46928561914332079</v>
+      </c>
       <c r="CY140" s="37"/>
       <c r="CZ140" s="37"/>
       <c r="DA140" s="37"/>
-      <c r="DB140" s="9"/>
+      <c r="DB140" s="37"/>
       <c r="DC140" s="9"/>
       <c r="DD140" s="9"/>
       <c r="DE140" s="9"/>
@@ -34055,11 +34266,13 @@
       <c r="CW141" s="35">
         <v>-14.858434191282882</v>
       </c>
-      <c r="CX141" s="37"/>
+      <c r="CX141" s="35">
+        <v>-3.3117867762819486</v>
+      </c>
       <c r="CY141" s="37"/>
       <c r="CZ141" s="37"/>
       <c r="DA141" s="37"/>
-      <c r="DB141" s="9"/>
+      <c r="DB141" s="37"/>
       <c r="DC141" s="9"/>
       <c r="DD141" s="9"/>
       <c r="DE141" s="9"/>
@@ -34406,11 +34619,13 @@
       <c r="CW142" s="35">
         <v>-19.577366501743072</v>
       </c>
-      <c r="CX142" s="37"/>
+      <c r="CX142" s="35">
+        <v>-16.052589939628263</v>
+      </c>
       <c r="CY142" s="37"/>
       <c r="CZ142" s="37"/>
       <c r="DA142" s="37"/>
-      <c r="DB142" s="9"/>
+      <c r="DB142" s="37"/>
       <c r="DC142" s="9"/>
       <c r="DD142" s="9"/>
       <c r="DE142" s="9"/>
@@ -34757,11 +34972,13 @@
       <c r="CW143" s="35">
         <v>-9.0759610173663674</v>
       </c>
-      <c r="CX143" s="37"/>
+      <c r="CX143" s="35">
+        <v>-2.1977582086133651</v>
+      </c>
       <c r="CY143" s="37"/>
       <c r="CZ143" s="37"/>
       <c r="DA143" s="37"/>
-      <c r="DB143" s="9"/>
+      <c r="DB143" s="37"/>
       <c r="DC143" s="9"/>
       <c r="DD143" s="9"/>
       <c r="DE143" s="9"/>
@@ -35108,11 +35325,13 @@
       <c r="CW144" s="35">
         <v>5.0127994168731789</v>
       </c>
-      <c r="CX144" s="37"/>
+      <c r="CX144" s="35">
+        <v>26.162605397625654</v>
+      </c>
       <c r="CY144" s="37"/>
       <c r="CZ144" s="37"/>
       <c r="DA144" s="37"/>
-      <c r="DB144" s="9"/>
+      <c r="DB144" s="37"/>
       <c r="DC144" s="9"/>
       <c r="DD144" s="9"/>
       <c r="DE144" s="9"/>
@@ -35459,11 +35678,13 @@
       <c r="CW145" s="35">
         <v>-16.423444567517578</v>
       </c>
-      <c r="CX145" s="37"/>
+      <c r="CX145" s="35">
+        <v>-2.7955741019194704</v>
+      </c>
       <c r="CY145" s="37"/>
       <c r="CZ145" s="37"/>
       <c r="DA145" s="37"/>
-      <c r="DB145" s="9"/>
+      <c r="DB145" s="37"/>
       <c r="DC145" s="9"/>
       <c r="DD145" s="9"/>
       <c r="DE145" s="9"/>
@@ -35810,11 +36031,13 @@
       <c r="CW146" s="35">
         <v>6.567033343925516</v>
       </c>
-      <c r="CX146" s="37"/>
+      <c r="CX146" s="35">
+        <v>0.92667818402595969</v>
+      </c>
       <c r="CY146" s="37"/>
       <c r="CZ146" s="37"/>
       <c r="DA146" s="37"/>
-      <c r="DB146" s="9"/>
+      <c r="DB146" s="37"/>
       <c r="DC146" s="9"/>
       <c r="DD146" s="9"/>
       <c r="DE146" s="9"/>
@@ -36161,11 +36384,13 @@
       <c r="CW147" s="35">
         <v>16.268772853001948</v>
       </c>
-      <c r="CX147" s="37"/>
+      <c r="CX147" s="35">
+        <v>100.5171177051925</v>
+      </c>
       <c r="CY147" s="37"/>
       <c r="CZ147" s="37"/>
       <c r="DA147" s="37"/>
-      <c r="DB147" s="9"/>
+      <c r="DB147" s="37"/>
       <c r="DC147" s="9"/>
       <c r="DD147" s="9"/>
       <c r="DE147" s="9"/>
@@ -36512,11 +36737,13 @@
       <c r="CW148" s="35">
         <v>7.9087537470289533</v>
       </c>
-      <c r="CX148" s="37"/>
+      <c r="CX148" s="35">
+        <v>3.3709120089652487</v>
+      </c>
       <c r="CY148" s="37"/>
       <c r="CZ148" s="37"/>
       <c r="DA148" s="37"/>
-      <c r="DB148" s="9"/>
+      <c r="DB148" s="37"/>
       <c r="DC148" s="9"/>
       <c r="DD148" s="9"/>
       <c r="DE148" s="9"/>
@@ -36863,11 +37090,13 @@
       <c r="CW149" s="35">
         <v>-1.9792049678420085</v>
       </c>
-      <c r="CX149" s="37"/>
+      <c r="CX149" s="35">
+        <v>-5.6752651444801216</v>
+      </c>
       <c r="CY149" s="37"/>
       <c r="CZ149" s="37"/>
       <c r="DA149" s="37"/>
-      <c r="DB149" s="9"/>
+      <c r="DB149" s="37"/>
       <c r="DC149" s="9"/>
       <c r="DD149" s="9"/>
       <c r="DE149" s="9"/>
@@ -37214,11 +37443,13 @@
       <c r="CW150" s="35">
         <v>-2.9913762069901821</v>
       </c>
-      <c r="CX150" s="37"/>
+      <c r="CX150" s="35">
+        <v>-7.9121091487441078</v>
+      </c>
       <c r="CY150" s="37"/>
       <c r="CZ150" s="37"/>
       <c r="DA150" s="37"/>
-      <c r="DB150" s="9"/>
+      <c r="DB150" s="37"/>
       <c r="DC150" s="9"/>
       <c r="DD150" s="9"/>
       <c r="DE150" s="9"/>
@@ -37565,11 +37796,13 @@
       <c r="CW151" s="35">
         <v>-95.498890794272413</v>
       </c>
-      <c r="CX151" s="37"/>
+      <c r="CX151" s="35">
+        <v>-38.590922220739657</v>
+      </c>
       <c r="CY151" s="37"/>
       <c r="CZ151" s="37"/>
       <c r="DA151" s="37"/>
-      <c r="DB151" s="9"/>
+      <c r="DB151" s="37"/>
       <c r="DC151" s="9"/>
       <c r="DD151" s="9"/>
       <c r="DE151" s="9"/>
@@ -37916,11 +38149,13 @@
       <c r="CW152" s="35">
         <v>27.325729665498272</v>
       </c>
-      <c r="CX152" s="37"/>
+      <c r="CX152" s="35">
+        <v>-26.062410191848969</v>
+      </c>
       <c r="CY152" s="37"/>
       <c r="CZ152" s="37"/>
       <c r="DA152" s="37"/>
-      <c r="DB152" s="9"/>
+      <c r="DB152" s="37"/>
       <c r="DC152" s="9"/>
       <c r="DD152" s="9"/>
       <c r="DE152" s="9"/>
@@ -38267,11 +38502,13 @@
       <c r="CW153" s="35">
         <v>-42.06050609640851</v>
       </c>
-      <c r="CX153" s="37"/>
+      <c r="CX153" s="35">
+        <v>179.73334310635613</v>
+      </c>
       <c r="CY153" s="37"/>
       <c r="CZ153" s="37"/>
       <c r="DA153" s="37"/>
-      <c r="DB153" s="9"/>
+      <c r="DB153" s="37"/>
       <c r="DC153" s="9"/>
       <c r="DD153" s="9"/>
       <c r="DE153" s="9"/>
@@ -38618,11 +38855,13 @@
       <c r="CW154" s="35">
         <v>0.94483933697429734</v>
       </c>
-      <c r="CX154" s="37"/>
+      <c r="CX154" s="35">
+        <v>-1.8420985574280735E-2</v>
+      </c>
       <c r="CY154" s="37"/>
       <c r="CZ154" s="37"/>
       <c r="DA154" s="37"/>
-      <c r="DB154" s="9"/>
+      <c r="DB154" s="37"/>
       <c r="DC154" s="9"/>
       <c r="DD154" s="9"/>
       <c r="DE154" s="9"/>
@@ -38969,11 +39208,13 @@
       <c r="CW155" s="35">
         <v>37.301213730238345</v>
       </c>
-      <c r="CX155" s="37"/>
+      <c r="CX155" s="35">
+        <v>39.531958982577578</v>
+      </c>
       <c r="CY155" s="37"/>
       <c r="CZ155" s="37"/>
       <c r="DA155" s="37"/>
-      <c r="DB155" s="9"/>
+      <c r="DB155" s="37"/>
       <c r="DC155" s="9"/>
       <c r="DD155" s="9"/>
       <c r="DE155" s="9"/>
@@ -39320,11 +39561,13 @@
       <c r="CW156" s="35">
         <v>-10.764893822149276</v>
       </c>
-      <c r="CX156" s="37"/>
+      <c r="CX156" s="35">
+        <v>-13.277401770876835</v>
+      </c>
       <c r="CY156" s="37"/>
       <c r="CZ156" s="37"/>
       <c r="DA156" s="37"/>
-      <c r="DB156" s="9"/>
+      <c r="DB156" s="37"/>
       <c r="DC156" s="9"/>
       <c r="DD156" s="9"/>
       <c r="DE156" s="9"/>
@@ -39671,11 +39914,13 @@
       <c r="CW157" s="35">
         <v>5.5642397899447076</v>
       </c>
-      <c r="CX157" s="37"/>
+      <c r="CX157" s="35">
+        <v>4.4603768142738858</v>
+      </c>
       <c r="CY157" s="37"/>
       <c r="CZ157" s="37"/>
       <c r="DA157" s="37"/>
-      <c r="DB157" s="9"/>
+      <c r="DB157" s="37"/>
       <c r="DC157" s="9"/>
       <c r="DD157" s="9"/>
       <c r="DE157" s="9"/>
@@ -40022,11 +40267,13 @@
       <c r="CW158" s="35">
         <v>-11.239564138509579</v>
       </c>
-      <c r="CX158" s="37"/>
+      <c r="CX158" s="35">
+        <v>-8.7504163830281101</v>
+      </c>
       <c r="CY158" s="37"/>
       <c r="CZ158" s="37"/>
       <c r="DA158" s="37"/>
-      <c r="DB158" s="9"/>
+      <c r="DB158" s="37"/>
       <c r="DC158" s="9"/>
       <c r="DD158" s="9"/>
       <c r="DE158" s="9"/>
@@ -40170,11 +40417,11 @@
       <c r="CU159" s="31"/>
       <c r="CV159" s="31"/>
       <c r="CW159" s="31"/>
-      <c r="CX159" s="39"/>
+      <c r="CX159" s="31"/>
       <c r="CY159" s="39"/>
       <c r="CZ159" s="39"/>
       <c r="DA159" s="39"/>
-      <c r="DB159" s="9"/>
+      <c r="DB159" s="39"/>
       <c r="DC159" s="9"/>
       <c r="DD159" s="9"/>
       <c r="DE159" s="9"/>
@@ -40521,11 +40768,13 @@
       <c r="CW160" s="38">
         <v>-1.6819530960023883</v>
       </c>
-      <c r="CX160" s="40"/>
+      <c r="CX160" s="38">
+        <v>-0.11522949363182988</v>
+      </c>
       <c r="CY160" s="40"/>
       <c r="CZ160" s="40"/>
       <c r="DA160" s="40"/>
-      <c r="DB160" s="9"/>
+      <c r="DB160" s="40"/>
       <c r="DC160" s="9"/>
       <c r="DD160" s="9"/>
       <c r="DE160" s="9"/>
@@ -40670,19 +40919,20 @@
       <c r="CU161" s="33"/>
       <c r="CV161" s="33"/>
       <c r="CW161" s="33"/>
-      <c r="CX161" s="43"/>
+      <c r="CX161" s="33"/>
       <c r="CY161" s="43"/>
       <c r="CZ161" s="43"/>
       <c r="DA161" s="43"/>
+      <c r="DB161" s="43"/>
     </row>
     <row r="162" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CX162" s="41"/>
       <c r="CY162" s="41"/>
       <c r="CZ162" s="41"/>
       <c r="DA162" s="41"/>
+      <c r="DB162" s="41"/>
     </row>
     <row r="163" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
@@ -40792,7 +41042,7 @@
       <c r="CY163" s="39"/>
       <c r="CZ163" s="39"/>
       <c r="DA163" s="39"/>
-      <c r="DB163" s="9"/>
+      <c r="DB163" s="39"/>
       <c r="DC163" s="9"/>
       <c r="DD163" s="9"/>
       <c r="DE163" s="9"/>
@@ -40940,7 +41190,7 @@
       <c r="CY164" s="31"/>
       <c r="CZ164" s="31"/>
       <c r="DA164" s="31"/>
-      <c r="DB164" s="9"/>
+      <c r="DB164" s="31"/>
       <c r="DC164" s="9"/>
       <c r="DD164" s="9"/>
       <c r="DE164" s="9"/>
@@ -40995,7 +41245,7 @@
     </row>
     <row r="166" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:152" x14ac:dyDescent="0.2">
@@ -41005,7 +41255,7 @@
     </row>
     <row r="169" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="170" spans="1:152" x14ac:dyDescent="0.2">
@@ -41015,132 +41265,132 @@
     </row>
     <row r="172" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
-      <c r="B172" s="44">
+      <c r="B172" s="45">
         <v>2000</v>
       </c>
-      <c r="C172" s="44"/>
-      <c r="D172" s="44"/>
-      <c r="E172" s="44"/>
-      <c r="F172" s="44">
+      <c r="C172" s="45"/>
+      <c r="D172" s="45"/>
+      <c r="E172" s="45"/>
+      <c r="F172" s="45">
         <v>2001</v>
       </c>
-      <c r="G172" s="44"/>
-      <c r="H172" s="44"/>
-      <c r="I172" s="44"/>
-      <c r="J172" s="44">
+      <c r="G172" s="45"/>
+      <c r="H172" s="45"/>
+      <c r="I172" s="45"/>
+      <c r="J172" s="45">
         <v>2002</v>
       </c>
-      <c r="K172" s="44"/>
-      <c r="L172" s="44"/>
-      <c r="M172" s="44"/>
-      <c r="N172" s="44">
+      <c r="K172" s="45"/>
+      <c r="L172" s="45"/>
+      <c r="M172" s="45"/>
+      <c r="N172" s="45">
         <v>2003</v>
       </c>
-      <c r="O172" s="44"/>
-      <c r="P172" s="44"/>
-      <c r="Q172" s="44"/>
-      <c r="R172" s="44">
+      <c r="O172" s="45"/>
+      <c r="P172" s="45"/>
+      <c r="Q172" s="45"/>
+      <c r="R172" s="45">
         <v>2004</v>
       </c>
-      <c r="S172" s="44"/>
-      <c r="T172" s="44"/>
-      <c r="U172" s="44"/>
-      <c r="V172" s="44">
+      <c r="S172" s="45"/>
+      <c r="T172" s="45"/>
+      <c r="U172" s="45"/>
+      <c r="V172" s="45">
         <v>2005</v>
       </c>
-      <c r="W172" s="44"/>
-      <c r="X172" s="44"/>
-      <c r="Y172" s="44"/>
-      <c r="Z172" s="44">
+      <c r="W172" s="45"/>
+      <c r="X172" s="45"/>
+      <c r="Y172" s="45"/>
+      <c r="Z172" s="45">
         <v>2006</v>
       </c>
-      <c r="AA172" s="44"/>
-      <c r="AB172" s="44"/>
-      <c r="AC172" s="44"/>
-      <c r="AD172" s="44">
+      <c r="AA172" s="45"/>
+      <c r="AB172" s="45"/>
+      <c r="AC172" s="45"/>
+      <c r="AD172" s="45">
         <v>2007</v>
       </c>
-      <c r="AE172" s="44"/>
-      <c r="AF172" s="44"/>
-      <c r="AG172" s="44"/>
-      <c r="AH172" s="44">
+      <c r="AE172" s="45"/>
+      <c r="AF172" s="45"/>
+      <c r="AG172" s="45"/>
+      <c r="AH172" s="45">
         <v>2008</v>
       </c>
-      <c r="AI172" s="44"/>
-      <c r="AJ172" s="44"/>
-      <c r="AK172" s="44"/>
-      <c r="AL172" s="44">
+      <c r="AI172" s="45"/>
+      <c r="AJ172" s="45"/>
+      <c r="AK172" s="45"/>
+      <c r="AL172" s="45">
         <v>2009</v>
       </c>
-      <c r="AM172" s="44"/>
-      <c r="AN172" s="44"/>
-      <c r="AO172" s="44"/>
-      <c r="AP172" s="44">
+      <c r="AM172" s="45"/>
+      <c r="AN172" s="45"/>
+      <c r="AO172" s="45"/>
+      <c r="AP172" s="45">
         <v>2010</v>
       </c>
-      <c r="AQ172" s="44"/>
-      <c r="AR172" s="44"/>
-      <c r="AS172" s="44"/>
-      <c r="AT172" s="44">
+      <c r="AQ172" s="45"/>
+      <c r="AR172" s="45"/>
+      <c r="AS172" s="45"/>
+      <c r="AT172" s="45">
         <v>2011</v>
       </c>
-      <c r="AU172" s="44"/>
-      <c r="AV172" s="44"/>
-      <c r="AW172" s="44"/>
-      <c r="AX172" s="44">
+      <c r="AU172" s="45"/>
+      <c r="AV172" s="45"/>
+      <c r="AW172" s="45"/>
+      <c r="AX172" s="45">
         <v>2012</v>
       </c>
-      <c r="AY172" s="44"/>
-      <c r="AZ172" s="44"/>
-      <c r="BA172" s="44"/>
-      <c r="BB172" s="44">
+      <c r="AY172" s="45"/>
+      <c r="AZ172" s="45"/>
+      <c r="BA172" s="45"/>
+      <c r="BB172" s="45">
         <v>2013</v>
       </c>
-      <c r="BC172" s="44"/>
-      <c r="BD172" s="44"/>
-      <c r="BE172" s="44"/>
-      <c r="BF172" s="44">
+      <c r="BC172" s="45"/>
+      <c r="BD172" s="45"/>
+      <c r="BE172" s="45"/>
+      <c r="BF172" s="45">
         <v>2014</v>
       </c>
-      <c r="BG172" s="44"/>
-      <c r="BH172" s="44"/>
-      <c r="BI172" s="44"/>
-      <c r="BJ172" s="44">
+      <c r="BG172" s="45"/>
+      <c r="BH172" s="45"/>
+      <c r="BI172" s="45"/>
+      <c r="BJ172" s="45">
         <v>2015</v>
       </c>
-      <c r="BK172" s="44"/>
-      <c r="BL172" s="44"/>
-      <c r="BM172" s="44"/>
-      <c r="BN172" s="44">
+      <c r="BK172" s="45"/>
+      <c r="BL172" s="45"/>
+      <c r="BM172" s="45"/>
+      <c r="BN172" s="45">
         <v>2016</v>
       </c>
-      <c r="BO172" s="44"/>
-      <c r="BP172" s="44"/>
-      <c r="BQ172" s="44"/>
-      <c r="BR172" s="44">
+      <c r="BO172" s="45"/>
+      <c r="BP172" s="45"/>
+      <c r="BQ172" s="45"/>
+      <c r="BR172" s="45">
         <v>2017</v>
       </c>
-      <c r="BS172" s="44"/>
-      <c r="BT172" s="44"/>
-      <c r="BU172" s="44"/>
-      <c r="BV172" s="44">
+      <c r="BS172" s="45"/>
+      <c r="BT172" s="45"/>
+      <c r="BU172" s="45"/>
+      <c r="BV172" s="45">
         <v>2018</v>
       </c>
-      <c r="BW172" s="44"/>
-      <c r="BX172" s="44"/>
-      <c r="BY172" s="44"/>
-      <c r="BZ172" s="44">
+      <c r="BW172" s="45"/>
+      <c r="BX172" s="45"/>
+      <c r="BY172" s="45"/>
+      <c r="BZ172" s="45">
         <v>2019</v>
       </c>
-      <c r="CA172" s="44"/>
-      <c r="CB172" s="44"/>
-      <c r="CC172" s="44"/>
-      <c r="CD172" s="45">
+      <c r="CA172" s="45"/>
+      <c r="CB172" s="45"/>
+      <c r="CC172" s="45"/>
+      <c r="CD172" s="44">
         <v>2020</v>
       </c>
-      <c r="CE172" s="45"/>
-      <c r="CF172" s="45"/>
-      <c r="CG172" s="45"/>
+      <c r="CE172" s="44"/>
+      <c r="CF172" s="44"/>
+      <c r="CG172" s="44"/>
       <c r="CH172" s="26">
         <v>2021</v>
       </c>
@@ -41171,6 +41421,9 @@
       <c r="CY172" s="28"/>
       <c r="CZ172" s="28"/>
       <c r="DA172" s="28"/>
+      <c r="DB172" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="173" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
@@ -41487,6 +41740,9 @@
       </c>
       <c r="DA173" s="34" t="s">
         <v>9</v>
+      </c>
+      <c r="DB173" s="34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -41808,7 +42064,9 @@
       <c r="DA175" s="38">
         <v>102.87606721083147</v>
       </c>
-      <c r="DB175" s="9"/>
+      <c r="DB175" s="38">
+        <v>127.63754641377201</v>
+      </c>
       <c r="DC175" s="9"/>
       <c r="DD175" s="9"/>
       <c r="DE175" s="9"/>
@@ -42172,7 +42430,9 @@
       <c r="DA176" s="38">
         <v>92.830750395851794</v>
       </c>
-      <c r="DB176" s="9"/>
+      <c r="DB176" s="38">
+        <v>136.01553631776736</v>
+      </c>
       <c r="DC176" s="9"/>
       <c r="DD176" s="9"/>
       <c r="DE176" s="9"/>
@@ -42536,7 +42796,9 @@
       <c r="DA177" s="38">
         <v>91.87344208532042</v>
       </c>
-      <c r="DB177" s="9"/>
+      <c r="DB177" s="38">
+        <v>138.03120793351826</v>
+      </c>
       <c r="DC177" s="9"/>
       <c r="DD177" s="9"/>
       <c r="DE177" s="9"/>
@@ -42900,7 +43162,9 @@
       <c r="DA178" s="38">
         <v>96.247691803965779</v>
       </c>
-      <c r="DB178" s="9"/>
+      <c r="DB178" s="38">
+        <v>122.6075133252448</v>
+      </c>
       <c r="DC178" s="9"/>
       <c r="DD178" s="9"/>
       <c r="DE178" s="9"/>
@@ -43264,7 +43528,9 @@
       <c r="DA179" s="38">
         <v>95.68054786421844</v>
       </c>
-      <c r="DB179" s="9"/>
+      <c r="DB179" s="38">
+        <v>164.20850320952306</v>
+      </c>
       <c r="DC179" s="9"/>
       <c r="DD179" s="9"/>
       <c r="DE179" s="9"/>
@@ -43628,7 +43894,9 @@
       <c r="DA180" s="38">
         <v>94.138266781181585</v>
       </c>
-      <c r="DB180" s="9"/>
+      <c r="DB180" s="38">
+        <v>142.96542137246601</v>
+      </c>
       <c r="DC180" s="9"/>
       <c r="DD180" s="9"/>
       <c r="DE180" s="9"/>
@@ -43992,7 +44260,9 @@
       <c r="DA181" s="38">
         <v>117.96435007487089</v>
       </c>
-      <c r="DB181" s="9"/>
+      <c r="DB181" s="38">
+        <v>120.2484084048027</v>
+      </c>
       <c r="DC181" s="9"/>
       <c r="DD181" s="9"/>
       <c r="DE181" s="9"/>
@@ -44356,7 +44626,9 @@
       <c r="DA182" s="38">
         <v>89.898087335898964</v>
       </c>
-      <c r="DB182" s="9"/>
+      <c r="DB182" s="38">
+        <v>133.32105999653814</v>
+      </c>
       <c r="DC182" s="9"/>
       <c r="DD182" s="9"/>
       <c r="DE182" s="9"/>
@@ -44720,7 +44992,9 @@
       <c r="DA183" s="38">
         <v>95.90495594923199</v>
       </c>
-      <c r="DB183" s="9"/>
+      <c r="DB183" s="38">
+        <v>134.29660612247594</v>
+      </c>
       <c r="DC183" s="9"/>
       <c r="DD183" s="9"/>
       <c r="DE183" s="9"/>
@@ -45084,7 +45358,9 @@
       <c r="DA184" s="38">
         <v>121.97647885555291</v>
       </c>
-      <c r="DB184" s="9"/>
+      <c r="DB184" s="38">
+        <v>131.2266778652469</v>
+      </c>
       <c r="DC184" s="9"/>
       <c r="DD184" s="9"/>
       <c r="DE184" s="9"/>
@@ -45448,7 +45724,9 @@
       <c r="DA185" s="38">
         <v>126.46627635239179</v>
       </c>
-      <c r="DB185" s="9"/>
+      <c r="DB185" s="38">
+        <v>131.52155537822415</v>
+      </c>
       <c r="DC185" s="9"/>
       <c r="DD185" s="9"/>
       <c r="DE185" s="9"/>
@@ -45812,7 +46090,9 @@
       <c r="DA186" s="38">
         <v>135.5228640078017</v>
       </c>
-      <c r="DB186" s="9"/>
+      <c r="DB186" s="38">
+        <v>138.59534157946945</v>
+      </c>
       <c r="DC186" s="9"/>
       <c r="DD186" s="9"/>
       <c r="DE186" s="9"/>
@@ -46176,7 +46456,9 @@
       <c r="DA187" s="38">
         <v>140.07964928086204</v>
       </c>
-      <c r="DB187" s="9"/>
+      <c r="DB187" s="38">
+        <v>140.15843348031652</v>
+      </c>
       <c r="DC187" s="9"/>
       <c r="DD187" s="9"/>
       <c r="DE187" s="9"/>
@@ -46540,7 +46822,9 @@
       <c r="DA188" s="38">
         <v>105.48459402210111</v>
       </c>
-      <c r="DB188" s="9"/>
+      <c r="DB188" s="38">
+        <v>119.90134007065612</v>
+      </c>
       <c r="DC188" s="9"/>
       <c r="DD188" s="9"/>
       <c r="DE188" s="9"/>
@@ -46904,7 +47188,9 @@
       <c r="DA189" s="38">
         <v>119.0147000058938</v>
       </c>
-      <c r="DB189" s="9"/>
+      <c r="DB189" s="38">
+        <v>117.47694631545072</v>
+      </c>
       <c r="DC189" s="9"/>
       <c r="DD189" s="9"/>
       <c r="DE189" s="9"/>
@@ -47268,7 +47554,9 @@
       <c r="DA190" s="38">
         <v>115.09390978811074</v>
       </c>
-      <c r="DB190" s="9"/>
+      <c r="DB190" s="38">
+        <v>114.27546949848887</v>
+      </c>
       <c r="DC190" s="9"/>
       <c r="DD190" s="9"/>
       <c r="DE190" s="9"/>
@@ -47632,7 +47920,9 @@
       <c r="DA191" s="38">
         <v>152.23610894631008</v>
       </c>
-      <c r="DB191" s="9"/>
+      <c r="DB191" s="38">
+        <v>129.59954707186091</v>
+      </c>
       <c r="DC191" s="9"/>
       <c r="DD191" s="9"/>
       <c r="DE191" s="9"/>
@@ -47996,7 +48286,9 @@
       <c r="DA192" s="38">
         <v>147.75258690897914</v>
       </c>
-      <c r="DB192" s="9"/>
+      <c r="DB192" s="38">
+        <v>149.21992757273628</v>
+      </c>
       <c r="DC192" s="9"/>
       <c r="DD192" s="9"/>
       <c r="DE192" s="9"/>
@@ -48360,7 +48652,9 @@
       <c r="DA193" s="38">
         <v>134.65023025636614</v>
       </c>
-      <c r="DB193" s="9"/>
+      <c r="DB193" s="38">
+        <v>155.59598749648018</v>
+      </c>
       <c r="DC193" s="9"/>
       <c r="DD193" s="9"/>
       <c r="DE193" s="9"/>
@@ -48724,7 +49018,9 @@
       <c r="DA194" s="38">
         <v>176.95453183302971</v>
       </c>
-      <c r="DB194" s="9"/>
+      <c r="DB194" s="38">
+        <v>122.78371712532226</v>
+      </c>
       <c r="DC194" s="9"/>
       <c r="DD194" s="9"/>
       <c r="DE194" s="9"/>
@@ -49088,7 +49384,9 @@
       <c r="DA195" s="38">
         <v>223.76129586262556</v>
       </c>
-      <c r="DB195" s="9"/>
+      <c r="DB195" s="38">
+        <v>109.86565705816514</v>
+      </c>
       <c r="DC195" s="9"/>
       <c r="DD195" s="9"/>
       <c r="DE195" s="9"/>
@@ -49452,7 +49750,9 @@
       <c r="DA196" s="38">
         <v>144.50254034872353</v>
       </c>
-      <c r="DB196" s="9"/>
+      <c r="DB196" s="38">
+        <v>101.78801593725855</v>
+      </c>
       <c r="DC196" s="9"/>
       <c r="DD196" s="9"/>
       <c r="DE196" s="9"/>
@@ -49816,7 +50116,9 @@
       <c r="DA197" s="38">
         <v>190.40139219098597</v>
       </c>
-      <c r="DB197" s="9"/>
+      <c r="DB197" s="38">
+        <v>137.37387353401033</v>
+      </c>
       <c r="DC197" s="9"/>
       <c r="DD197" s="9"/>
       <c r="DE197" s="9"/>
@@ -50180,7 +50482,9 @@
       <c r="DA198" s="38">
         <v>146.35821735713688</v>
       </c>
-      <c r="DB198" s="9"/>
+      <c r="DB198" s="38">
+        <v>116.08168278339809</v>
+      </c>
       <c r="DC198" s="9"/>
       <c r="DD198" s="9"/>
       <c r="DE198" s="9"/>
@@ -50333,7 +50637,7 @@
       <c r="CY199" s="31"/>
       <c r="CZ199" s="31"/>
       <c r="DA199" s="31"/>
-      <c r="DB199" s="9"/>
+      <c r="DB199" s="31"/>
       <c r="DC199" s="9"/>
       <c r="DD199" s="9"/>
       <c r="DE199" s="9"/>
@@ -50697,7 +51001,9 @@
       <c r="DA200" s="38">
         <v>124.50184977918649</v>
       </c>
-      <c r="DB200" s="9"/>
+      <c r="DB200" s="38">
+        <v>122.57502288121853</v>
+      </c>
       <c r="DC200" s="9"/>
       <c r="DD200" s="9"/>
       <c r="DE200" s="9"/>
@@ -50851,6 +51157,7 @@
       <c r="CY201" s="33"/>
       <c r="CZ201" s="33"/>
       <c r="DA201" s="33"/>
+      <c r="DB201" s="33"/>
     </row>
     <row r="202" spans="1:152" ht="15" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
@@ -50868,6 +51175,7 @@
       <c r="CY202"/>
       <c r="CZ202"/>
       <c r="DA202"/>
+      <c r="DB202"/>
     </row>
     <row r="203" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B203" s="9"/>
@@ -50974,7 +51282,7 @@
       <c r="CY203" s="31"/>
       <c r="CZ203" s="31"/>
       <c r="DA203" s="31"/>
-      <c r="DB203" s="9"/>
+      <c r="DB203" s="31"/>
       <c r="DC203" s="9"/>
       <c r="DD203" s="9"/>
       <c r="DE203" s="9"/>
@@ -51127,7 +51435,7 @@
       <c r="CY204" s="31"/>
       <c r="CZ204" s="31"/>
       <c r="DA204" s="31"/>
-      <c r="DB204" s="9"/>
+      <c r="DB204" s="31"/>
       <c r="DC204" s="9"/>
       <c r="DD204" s="9"/>
       <c r="DE204" s="9"/>
@@ -51187,7 +51495,7 @@
     </row>
     <row r="207" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="209" spans="1:152" x14ac:dyDescent="0.2">
@@ -51197,7 +51505,7 @@
     </row>
     <row r="210" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="211" spans="1:152" x14ac:dyDescent="0.2">
@@ -51207,132 +51515,132 @@
     </row>
     <row r="213" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
-      <c r="B213" s="44">
+      <c r="B213" s="45">
         <v>2000</v>
       </c>
-      <c r="C213" s="44"/>
-      <c r="D213" s="44"/>
-      <c r="E213" s="44"/>
-      <c r="F213" s="44">
+      <c r="C213" s="45"/>
+      <c r="D213" s="45"/>
+      <c r="E213" s="45"/>
+      <c r="F213" s="45">
         <v>2001</v>
       </c>
-      <c r="G213" s="44"/>
-      <c r="H213" s="44"/>
-      <c r="I213" s="44"/>
-      <c r="J213" s="44">
+      <c r="G213" s="45"/>
+      <c r="H213" s="45"/>
+      <c r="I213" s="45"/>
+      <c r="J213" s="45">
         <v>2002</v>
       </c>
-      <c r="K213" s="44"/>
-      <c r="L213" s="44"/>
-      <c r="M213" s="44"/>
-      <c r="N213" s="44">
+      <c r="K213" s="45"/>
+      <c r="L213" s="45"/>
+      <c r="M213" s="45"/>
+      <c r="N213" s="45">
         <v>2003</v>
       </c>
-      <c r="O213" s="44"/>
-      <c r="P213" s="44"/>
-      <c r="Q213" s="44"/>
-      <c r="R213" s="44">
+      <c r="O213" s="45"/>
+      <c r="P213" s="45"/>
+      <c r="Q213" s="45"/>
+      <c r="R213" s="45">
         <v>2004</v>
       </c>
-      <c r="S213" s="44"/>
-      <c r="T213" s="44"/>
-      <c r="U213" s="44"/>
-      <c r="V213" s="44">
+      <c r="S213" s="45"/>
+      <c r="T213" s="45"/>
+      <c r="U213" s="45"/>
+      <c r="V213" s="45">
         <v>2005</v>
       </c>
-      <c r="W213" s="44"/>
-      <c r="X213" s="44"/>
-      <c r="Y213" s="44"/>
-      <c r="Z213" s="44">
+      <c r="W213" s="45"/>
+      <c r="X213" s="45"/>
+      <c r="Y213" s="45"/>
+      <c r="Z213" s="45">
         <v>2006</v>
       </c>
-      <c r="AA213" s="44"/>
-      <c r="AB213" s="44"/>
-      <c r="AC213" s="44"/>
-      <c r="AD213" s="44">
+      <c r="AA213" s="45"/>
+      <c r="AB213" s="45"/>
+      <c r="AC213" s="45"/>
+      <c r="AD213" s="45">
         <v>2007</v>
       </c>
-      <c r="AE213" s="44"/>
-      <c r="AF213" s="44"/>
-      <c r="AG213" s="44"/>
-      <c r="AH213" s="44">
+      <c r="AE213" s="45"/>
+      <c r="AF213" s="45"/>
+      <c r="AG213" s="45"/>
+      <c r="AH213" s="45">
         <v>2008</v>
       </c>
-      <c r="AI213" s="44"/>
-      <c r="AJ213" s="44"/>
-      <c r="AK213" s="44"/>
-      <c r="AL213" s="44">
+      <c r="AI213" s="45"/>
+      <c r="AJ213" s="45"/>
+      <c r="AK213" s="45"/>
+      <c r="AL213" s="45">
         <v>2009</v>
       </c>
-      <c r="AM213" s="44"/>
-      <c r="AN213" s="44"/>
-      <c r="AO213" s="44"/>
-      <c r="AP213" s="44">
+      <c r="AM213" s="45"/>
+      <c r="AN213" s="45"/>
+      <c r="AO213" s="45"/>
+      <c r="AP213" s="45">
         <v>2010</v>
       </c>
-      <c r="AQ213" s="44"/>
-      <c r="AR213" s="44"/>
-      <c r="AS213" s="44"/>
-      <c r="AT213" s="44">
+      <c r="AQ213" s="45"/>
+      <c r="AR213" s="45"/>
+      <c r="AS213" s="45"/>
+      <c r="AT213" s="45">
         <v>2011</v>
       </c>
-      <c r="AU213" s="44"/>
-      <c r="AV213" s="44"/>
-      <c r="AW213" s="44"/>
-      <c r="AX213" s="44">
+      <c r="AU213" s="45"/>
+      <c r="AV213" s="45"/>
+      <c r="AW213" s="45"/>
+      <c r="AX213" s="45">
         <v>2012</v>
       </c>
-      <c r="AY213" s="44"/>
-      <c r="AZ213" s="44"/>
-      <c r="BA213" s="44"/>
-      <c r="BB213" s="44">
+      <c r="AY213" s="45"/>
+      <c r="AZ213" s="45"/>
+      <c r="BA213" s="45"/>
+      <c r="BB213" s="45">
         <v>2013</v>
       </c>
-      <c r="BC213" s="44"/>
-      <c r="BD213" s="44"/>
-      <c r="BE213" s="44"/>
-      <c r="BF213" s="44">
+      <c r="BC213" s="45"/>
+      <c r="BD213" s="45"/>
+      <c r="BE213" s="45"/>
+      <c r="BF213" s="45">
         <v>2014</v>
       </c>
-      <c r="BG213" s="44"/>
-      <c r="BH213" s="44"/>
-      <c r="BI213" s="44"/>
-      <c r="BJ213" s="44">
+      <c r="BG213" s="45"/>
+      <c r="BH213" s="45"/>
+      <c r="BI213" s="45"/>
+      <c r="BJ213" s="45">
         <v>2015</v>
       </c>
-      <c r="BK213" s="44"/>
-      <c r="BL213" s="44"/>
-      <c r="BM213" s="44"/>
-      <c r="BN213" s="44">
+      <c r="BK213" s="45"/>
+      <c r="BL213" s="45"/>
+      <c r="BM213" s="45"/>
+      <c r="BN213" s="45">
         <v>2016</v>
       </c>
-      <c r="BO213" s="44"/>
-      <c r="BP213" s="44"/>
-      <c r="BQ213" s="44"/>
-      <c r="BR213" s="44">
+      <c r="BO213" s="45"/>
+      <c r="BP213" s="45"/>
+      <c r="BQ213" s="45"/>
+      <c r="BR213" s="45">
         <v>2017</v>
       </c>
-      <c r="BS213" s="44"/>
-      <c r="BT213" s="44"/>
-      <c r="BU213" s="44"/>
-      <c r="BV213" s="44">
+      <c r="BS213" s="45"/>
+      <c r="BT213" s="45"/>
+      <c r="BU213" s="45"/>
+      <c r="BV213" s="45">
         <v>2018</v>
       </c>
-      <c r="BW213" s="44"/>
-      <c r="BX213" s="44"/>
-      <c r="BY213" s="44"/>
-      <c r="BZ213" s="44">
+      <c r="BW213" s="45"/>
+      <c r="BX213" s="45"/>
+      <c r="BY213" s="45"/>
+      <c r="BZ213" s="45">
         <v>2019</v>
       </c>
-      <c r="CA213" s="44"/>
-      <c r="CB213" s="44"/>
-      <c r="CC213" s="44"/>
-      <c r="CD213" s="45">
+      <c r="CA213" s="45"/>
+      <c r="CB213" s="45"/>
+      <c r="CC213" s="45"/>
+      <c r="CD213" s="44">
         <v>2020</v>
       </c>
-      <c r="CE213" s="45"/>
-      <c r="CF213" s="45"/>
-      <c r="CG213" s="45"/>
+      <c r="CE213" s="44"/>
+      <c r="CF213" s="44"/>
+      <c r="CG213" s="44"/>
       <c r="CH213" s="26">
         <v>2021</v>
       </c>
@@ -51363,6 +51671,9 @@
       <c r="CY213" s="28"/>
       <c r="CZ213" s="28"/>
       <c r="DA213" s="28"/>
+      <c r="DB213" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="214" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A214" s="5" t="s">
@@ -51679,6 +51990,9 @@
       </c>
       <c r="DA214" s="34" t="s">
         <v>9</v>
+      </c>
+      <c r="DB214" s="34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -52000,7 +52314,9 @@
       <c r="DA216" s="38">
         <v>13.514738944898836</v>
       </c>
-      <c r="DB216" s="9"/>
+      <c r="DB216" s="38">
+        <v>14.637734697353128</v>
+      </c>
       <c r="DC216" s="9"/>
       <c r="DD216" s="9"/>
       <c r="DE216" s="9"/>
@@ -52364,7 +52680,9 @@
       <c r="DA217" s="38">
         <v>0.82257618657706022</v>
       </c>
-      <c r="DB217" s="9"/>
+      <c r="DB217" s="38">
+        <v>0.71149732891045925</v>
+      </c>
       <c r="DC217" s="9"/>
       <c r="DD217" s="9"/>
       <c r="DE217" s="9"/>
@@ -52728,7 +53046,9 @@
       <c r="DA218" s="38">
         <v>2.7498058058193902</v>
       </c>
-      <c r="DB218" s="9"/>
+      <c r="DB218" s="38">
+        <v>2.1419409361185004</v>
+      </c>
       <c r="DC218" s="9"/>
       <c r="DD218" s="9"/>
       <c r="DE218" s="9"/>
@@ -53092,7 +53412,9 @@
       <c r="DA219" s="38">
         <v>0.35992455386890493</v>
       </c>
-      <c r="DB219" s="9"/>
+      <c r="DB219" s="38">
+        <v>0.20082544266650637</v>
+      </c>
       <c r="DC219" s="9"/>
       <c r="DD219" s="9"/>
       <c r="DE219" s="9"/>
@@ -53456,7 +53778,9 @@
       <c r="DA220" s="38">
         <v>0.17013438036861073</v>
       </c>
-      <c r="DB220" s="9"/>
+      <c r="DB220" s="38">
+        <v>0.18919949855583618</v>
+      </c>
       <c r="DC220" s="9"/>
       <c r="DD220" s="9"/>
       <c r="DE220" s="9"/>
@@ -53820,7 +54144,9 @@
       <c r="DA221" s="38">
         <v>0.64927553639501856</v>
       </c>
-      <c r="DB221" s="9"/>
+      <c r="DB221" s="38">
+        <v>0.84334208592838655</v>
+      </c>
       <c r="DC221" s="9"/>
       <c r="DD221" s="9"/>
       <c r="DE221" s="9"/>
@@ -54184,7 +54510,9 @@
       <c r="DA222" s="38">
         <v>5.8912399625528575</v>
       </c>
-      <c r="DB222" s="9"/>
+      <c r="DB222" s="38">
+        <v>7.6619478489720212</v>
+      </c>
       <c r="DC222" s="9"/>
       <c r="DD222" s="9"/>
       <c r="DE222" s="9"/>
@@ -54548,7 +54876,9 @@
       <c r="DA223" s="38">
         <v>0.39911790432086086</v>
       </c>
-      <c r="DB223" s="9"/>
+      <c r="DB223" s="38">
+        <v>0.26723677398988749</v>
+      </c>
       <c r="DC223" s="9"/>
       <c r="DD223" s="9"/>
       <c r="DE223" s="9"/>
@@ -54912,7 +55242,9 @@
       <c r="DA224" s="38">
         <v>2.4726646149961335</v>
       </c>
-      <c r="DB224" s="9"/>
+      <c r="DB224" s="38">
+        <v>2.6217447822115316</v>
+      </c>
       <c r="DC224" s="9"/>
       <c r="DD224" s="9"/>
       <c r="DE224" s="9"/>
@@ -55276,7 +55608,9 @@
       <c r="DA225" s="38">
         <v>18.031278222984266</v>
       </c>
-      <c r="DB225" s="9"/>
+      <c r="DB225" s="38">
+        <v>20.804567004595224</v>
+      </c>
       <c r="DC225" s="9"/>
       <c r="DD225" s="9"/>
       <c r="DE225" s="9"/>
@@ -55640,7 +55974,9 @@
       <c r="DA226" s="38">
         <v>3.0206415351181293</v>
       </c>
-      <c r="DB226" s="9"/>
+      <c r="DB226" s="38">
+        <v>3.0382936366875062</v>
+      </c>
       <c r="DC226" s="9"/>
       <c r="DD226" s="9"/>
       <c r="DE226" s="9"/>
@@ -56004,7 +56340,9 @@
       <c r="DA227" s="38">
         <v>2.0742348965887216</v>
       </c>
-      <c r="DB227" s="9"/>
+      <c r="DB227" s="38">
+        <v>1.8867076629707589</v>
+      </c>
       <c r="DC227" s="9"/>
       <c r="DD227" s="9"/>
       <c r="DE227" s="9"/>
@@ -56368,7 +56706,9 @@
       <c r="DA228" s="38">
         <v>5.980685187044581</v>
       </c>
-      <c r="DB228" s="9"/>
+      <c r="DB228" s="38">
+        <v>8.8050044199879096</v>
+      </c>
       <c r="DC228" s="9"/>
       <c r="DD228" s="9"/>
       <c r="DE228" s="9"/>
@@ -56732,7 +57072,9 @@
       <c r="DA229" s="38">
         <v>6.9557166042328342</v>
       </c>
-      <c r="DB229" s="9"/>
+      <c r="DB229" s="38">
+        <v>7.0745612849490476</v>
+      </c>
       <c r="DC229" s="9"/>
       <c r="DD229" s="9"/>
       <c r="DE229" s="9"/>
@@ -57096,7 +57438,9 @@
       <c r="DA230" s="38">
         <v>49.85576233878745</v>
       </c>
-      <c r="DB230" s="9"/>
+      <c r="DB230" s="38">
+        <v>45.723137172633457</v>
+      </c>
       <c r="DC230" s="9"/>
       <c r="DD230" s="9"/>
       <c r="DE230" s="9"/>
@@ -57460,7 +57804,9 @@
       <c r="DA231" s="38">
         <v>42.316991967772751</v>
       </c>
-      <c r="DB231" s="9"/>
+      <c r="DB231" s="38">
+        <v>40.771556418811706</v>
+      </c>
       <c r="DC231" s="9"/>
       <c r="DD231" s="9"/>
       <c r="DE231" s="9"/>
@@ -57824,7 +58170,9 @@
       <c r="DA232" s="38">
         <v>4.1377283835592943E-2</v>
       </c>
-      <c r="DB232" s="9"/>
+      <c r="DB232" s="38">
+        <v>4.8594800268839645E-2</v>
+      </c>
       <c r="DC232" s="9"/>
       <c r="DD232" s="9"/>
       <c r="DE232" s="9"/>
@@ -58188,7 +58536,9 @@
       <c r="DA233" s="38">
         <v>7.1694819976990845</v>
       </c>
-      <c r="DB233" s="9"/>
+      <c r="DB233" s="38">
+        <v>1.9677531976381664</v>
+      </c>
       <c r="DC233" s="9"/>
       <c r="DD233" s="9"/>
       <c r="DE233" s="9"/>
@@ -58552,7 +58902,9 @@
       <c r="DA234" s="38">
         <v>0.32791108948002207</v>
       </c>
-      <c r="DB234" s="9"/>
+      <c r="DB234" s="38">
+        <v>2.9352327559147424</v>
+      </c>
       <c r="DC234" s="9"/>
       <c r="DD234" s="9"/>
       <c r="DE234" s="9"/>
@@ -58916,7 +59268,9 @@
       <c r="DA235" s="38">
         <v>18.598220493329435</v>
       </c>
-      <c r="DB235" s="9"/>
+      <c r="DB235" s="38">
+        <v>18.834561125418194</v>
+      </c>
       <c r="DC235" s="9"/>
       <c r="DD235" s="9"/>
       <c r="DE235" s="9"/>
@@ -59280,7 +59634,9 @@
       <c r="DA236" s="38">
         <v>2.5203907587657581</v>
       </c>
-      <c r="DB236" s="9"/>
+      <c r="DB236" s="38">
+        <v>1.8219478864248981</v>
+      </c>
       <c r="DC236" s="9"/>
       <c r="DD236" s="9"/>
       <c r="DE236" s="9"/>
@@ -59644,7 +60000,9 @@
       <c r="DA237" s="38">
         <v>2.7971051236639779</v>
       </c>
-      <c r="DB237" s="9"/>
+      <c r="DB237" s="38">
+        <v>2.9264320845045511</v>
+      </c>
       <c r="DC237" s="9"/>
       <c r="DD237" s="9"/>
       <c r="DE237" s="9"/>
@@ -60008,7 +60366,9 @@
       <c r="DA238" s="38">
         <v>10.288004794855087</v>
       </c>
-      <c r="DB238" s="9"/>
+      <c r="DB238" s="38">
+        <v>9.9493646384223453</v>
+      </c>
       <c r="DC238" s="9"/>
       <c r="DD238" s="9"/>
       <c r="DE238" s="9"/>
@@ -60372,7 +60732,9 @@
       <c r="DA239" s="38">
         <v>2.9927198160446111</v>
       </c>
-      <c r="DB239" s="9"/>
+      <c r="DB239" s="38">
+        <v>4.1368165160664017</v>
+      </c>
       <c r="DC239" s="9"/>
       <c r="DD239" s="9"/>
       <c r="DE239" s="9"/>
@@ -60525,7 +60887,7 @@
       <c r="CY240" s="31"/>
       <c r="CZ240" s="31"/>
       <c r="DA240" s="31"/>
-      <c r="DB240" s="9"/>
+      <c r="DB240" s="31"/>
       <c r="DC240" s="9"/>
       <c r="DD240" s="9"/>
       <c r="DE240" s="9"/>
@@ -60889,7 +61251,9 @@
       <c r="DA241" s="38">
         <v>100</v>
       </c>
-      <c r="DB241" s="9"/>
+      <c r="DB241" s="38">
+        <v>100</v>
+      </c>
       <c r="DC241" s="9"/>
       <c r="DD241" s="9"/>
       <c r="DE241" s="9"/>
@@ -61043,6 +61407,7 @@
       <c r="CY242" s="33"/>
       <c r="CZ242" s="33"/>
       <c r="DA242" s="33"/>
+      <c r="DB242" s="33"/>
     </row>
     <row r="243" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
@@ -61154,7 +61519,7 @@
       <c r="CY244" s="31"/>
       <c r="CZ244" s="31"/>
       <c r="DA244" s="31"/>
-      <c r="DB244" s="9"/>
+      <c r="DB244" s="31"/>
       <c r="DC244" s="9"/>
       <c r="DD244" s="9"/>
       <c r="DE244" s="9"/>
@@ -61307,7 +61672,7 @@
       <c r="CY245" s="31"/>
       <c r="CZ245" s="31"/>
       <c r="DA245" s="31"/>
-      <c r="DB245" s="9"/>
+      <c r="DB245" s="31"/>
       <c r="DC245" s="9"/>
       <c r="DD245" s="9"/>
       <c r="DE245" s="9"/>
@@ -61367,7 +61732,7 @@
     </row>
     <row r="248" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="250" spans="1:152" x14ac:dyDescent="0.2">
@@ -61377,7 +61742,7 @@
     </row>
     <row r="251" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="252" spans="1:152" x14ac:dyDescent="0.2">
@@ -61387,132 +61752,132 @@
     </row>
     <row r="254" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
-      <c r="B254" s="44">
+      <c r="B254" s="45">
         <v>2000</v>
       </c>
-      <c r="C254" s="44"/>
-      <c r="D254" s="44"/>
-      <c r="E254" s="44"/>
-      <c r="F254" s="44">
+      <c r="C254" s="45"/>
+      <c r="D254" s="45"/>
+      <c r="E254" s="45"/>
+      <c r="F254" s="45">
         <v>2001</v>
       </c>
-      <c r="G254" s="44"/>
-      <c r="H254" s="44"/>
-      <c r="I254" s="44"/>
-      <c r="J254" s="44">
+      <c r="G254" s="45"/>
+      <c r="H254" s="45"/>
+      <c r="I254" s="45"/>
+      <c r="J254" s="45">
         <v>2002</v>
       </c>
-      <c r="K254" s="44"/>
-      <c r="L254" s="44"/>
-      <c r="M254" s="44"/>
-      <c r="N254" s="44">
+      <c r="K254" s="45"/>
+      <c r="L254" s="45"/>
+      <c r="M254" s="45"/>
+      <c r="N254" s="45">
         <v>2003</v>
       </c>
-      <c r="O254" s="44"/>
-      <c r="P254" s="44"/>
-      <c r="Q254" s="44"/>
-      <c r="R254" s="44">
+      <c r="O254" s="45"/>
+      <c r="P254" s="45"/>
+      <c r="Q254" s="45"/>
+      <c r="R254" s="45">
         <v>2004</v>
       </c>
-      <c r="S254" s="44"/>
-      <c r="T254" s="44"/>
-      <c r="U254" s="44"/>
-      <c r="V254" s="44">
+      <c r="S254" s="45"/>
+      <c r="T254" s="45"/>
+      <c r="U254" s="45"/>
+      <c r="V254" s="45">
         <v>2005</v>
       </c>
-      <c r="W254" s="44"/>
-      <c r="X254" s="44"/>
-      <c r="Y254" s="44"/>
-      <c r="Z254" s="44">
+      <c r="W254" s="45"/>
+      <c r="X254" s="45"/>
+      <c r="Y254" s="45"/>
+      <c r="Z254" s="45">
         <v>2006</v>
       </c>
-      <c r="AA254" s="44"/>
-      <c r="AB254" s="44"/>
-      <c r="AC254" s="44"/>
-      <c r="AD254" s="44">
+      <c r="AA254" s="45"/>
+      <c r="AB254" s="45"/>
+      <c r="AC254" s="45"/>
+      <c r="AD254" s="45">
         <v>2007</v>
       </c>
-      <c r="AE254" s="44"/>
-      <c r="AF254" s="44"/>
-      <c r="AG254" s="44"/>
-      <c r="AH254" s="44">
+      <c r="AE254" s="45"/>
+      <c r="AF254" s="45"/>
+      <c r="AG254" s="45"/>
+      <c r="AH254" s="45">
         <v>2008</v>
       </c>
-      <c r="AI254" s="44"/>
-      <c r="AJ254" s="44"/>
-      <c r="AK254" s="44"/>
-      <c r="AL254" s="44">
+      <c r="AI254" s="45"/>
+      <c r="AJ254" s="45"/>
+      <c r="AK254" s="45"/>
+      <c r="AL254" s="45">
         <v>2009</v>
       </c>
-      <c r="AM254" s="44"/>
-      <c r="AN254" s="44"/>
-      <c r="AO254" s="44"/>
-      <c r="AP254" s="44">
+      <c r="AM254" s="45"/>
+      <c r="AN254" s="45"/>
+      <c r="AO254" s="45"/>
+      <c r="AP254" s="45">
         <v>2010</v>
       </c>
-      <c r="AQ254" s="44"/>
-      <c r="AR254" s="44"/>
-      <c r="AS254" s="44"/>
-      <c r="AT254" s="44">
+      <c r="AQ254" s="45"/>
+      <c r="AR254" s="45"/>
+      <c r="AS254" s="45"/>
+      <c r="AT254" s="45">
         <v>2011</v>
       </c>
-      <c r="AU254" s="44"/>
-      <c r="AV254" s="44"/>
-      <c r="AW254" s="44"/>
-      <c r="AX254" s="44">
+      <c r="AU254" s="45"/>
+      <c r="AV254" s="45"/>
+      <c r="AW254" s="45"/>
+      <c r="AX254" s="45">
         <v>2012</v>
       </c>
-      <c r="AY254" s="44"/>
-      <c r="AZ254" s="44"/>
-      <c r="BA254" s="44"/>
-      <c r="BB254" s="44">
+      <c r="AY254" s="45"/>
+      <c r="AZ254" s="45"/>
+      <c r="BA254" s="45"/>
+      <c r="BB254" s="45">
         <v>2013</v>
       </c>
-      <c r="BC254" s="44"/>
-      <c r="BD254" s="44"/>
-      <c r="BE254" s="44"/>
-      <c r="BF254" s="44">
+      <c r="BC254" s="45"/>
+      <c r="BD254" s="45"/>
+      <c r="BE254" s="45"/>
+      <c r="BF254" s="45">
         <v>2014</v>
       </c>
-      <c r="BG254" s="44"/>
-      <c r="BH254" s="44"/>
-      <c r="BI254" s="44"/>
-      <c r="BJ254" s="44">
+      <c r="BG254" s="45"/>
+      <c r="BH254" s="45"/>
+      <c r="BI254" s="45"/>
+      <c r="BJ254" s="45">
         <v>2015</v>
       </c>
-      <c r="BK254" s="44"/>
-      <c r="BL254" s="44"/>
-      <c r="BM254" s="44"/>
-      <c r="BN254" s="44">
+      <c r="BK254" s="45"/>
+      <c r="BL254" s="45"/>
+      <c r="BM254" s="45"/>
+      <c r="BN254" s="45">
         <v>2016</v>
       </c>
-      <c r="BO254" s="44"/>
-      <c r="BP254" s="44"/>
-      <c r="BQ254" s="44"/>
-      <c r="BR254" s="44">
+      <c r="BO254" s="45"/>
+      <c r="BP254" s="45"/>
+      <c r="BQ254" s="45"/>
+      <c r="BR254" s="45">
         <v>2017</v>
       </c>
-      <c r="BS254" s="44"/>
-      <c r="BT254" s="44"/>
-      <c r="BU254" s="44"/>
-      <c r="BV254" s="44">
+      <c r="BS254" s="45"/>
+      <c r="BT254" s="45"/>
+      <c r="BU254" s="45"/>
+      <c r="BV254" s="45">
         <v>2018</v>
       </c>
-      <c r="BW254" s="44"/>
-      <c r="BX254" s="44"/>
-      <c r="BY254" s="44"/>
-      <c r="BZ254" s="44">
+      <c r="BW254" s="45"/>
+      <c r="BX254" s="45"/>
+      <c r="BY254" s="45"/>
+      <c r="BZ254" s="45">
         <v>2019</v>
       </c>
-      <c r="CA254" s="44"/>
-      <c r="CB254" s="44"/>
-      <c r="CC254" s="44"/>
-      <c r="CD254" s="45">
+      <c r="CA254" s="45"/>
+      <c r="CB254" s="45"/>
+      <c r="CC254" s="45"/>
+      <c r="CD254" s="44">
         <v>2020</v>
       </c>
-      <c r="CE254" s="45"/>
-      <c r="CF254" s="45"/>
-      <c r="CG254" s="45"/>
+      <c r="CE254" s="44"/>
+      <c r="CF254" s="44"/>
+      <c r="CG254" s="44"/>
       <c r="CH254" s="26">
         <v>2021</v>
       </c>
@@ -61543,6 +61908,9 @@
       <c r="CY254" s="28"/>
       <c r="CZ254" s="28"/>
       <c r="DA254" s="28"/>
+      <c r="DB254" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="255" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
@@ -61859,6 +62227,9 @@
       </c>
       <c r="DA255" s="34" t="s">
         <v>9</v>
+      </c>
+      <c r="DB255" s="34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -62180,7 +62551,9 @@
       <c r="DA257" s="38">
         <v>16.355699080860276</v>
       </c>
-      <c r="DB257" s="9"/>
+      <c r="DB257" s="38">
+        <v>14.057154151497157</v>
+      </c>
       <c r="DC257" s="9"/>
       <c r="DD257" s="9"/>
       <c r="DE257" s="9"/>
@@ -62544,7 +62917,9 @@
       <c r="DA258" s="38">
         <v>1.1032147901039653</v>
       </c>
-      <c r="DB258" s="9"/>
+      <c r="DB258" s="38">
+        <v>0.64118999734983328</v>
+      </c>
       <c r="DC258" s="9"/>
       <c r="DD258" s="9"/>
       <c r="DE258" s="9"/>
@@ -62908,7 +63283,9 @@
       <c r="DA259" s="38">
         <v>3.7263860108792235</v>
       </c>
-      <c r="DB259" s="9"/>
+      <c r="DB259" s="38">
+        <v>1.9020949188635543</v>
+      </c>
       <c r="DC259" s="9"/>
       <c r="DD259" s="9"/>
       <c r="DE259" s="9"/>
@@ -63272,7 +63649,9 @@
       <c r="DA260" s="38">
         <v>0.46558283006825013</v>
       </c>
-      <c r="DB260" s="9"/>
+      <c r="DB260" s="38">
+        <v>0.20077222482016854</v>
+      </c>
       <c r="DC260" s="9"/>
       <c r="DD260" s="9"/>
       <c r="DE260" s="9"/>
@@ -63636,7 +64015,9 @@
       <c r="DA261" s="38">
         <v>0.22138298264123102</v>
       </c>
-      <c r="DB261" s="9"/>
+      <c r="DB261" s="38">
+        <v>0.14122979268013783</v>
+      </c>
       <c r="DC261" s="9"/>
       <c r="DD261" s="9"/>
       <c r="DE261" s="9"/>
@@ -64000,7 +64381,9 @@
       <c r="DA262" s="38">
         <v>0.85869442960376019</v>
       </c>
-      <c r="DB262" s="9"/>
+      <c r="DB262" s="38">
+        <v>0.72306068479349994</v>
+      </c>
       <c r="DC262" s="9"/>
       <c r="DD262" s="9"/>
       <c r="DE262" s="9"/>
@@ -64364,7 +64747,9 @@
       <c r="DA263" s="38">
         <v>6.2177282574385329</v>
       </c>
-      <c r="DB263" s="9"/>
+      <c r="DB263" s="38">
+        <v>7.8101942916438505</v>
+      </c>
       <c r="DC263" s="9"/>
       <c r="DD263" s="9"/>
       <c r="DE263" s="9"/>
@@ -64728,7 +65113,9 @@
       <c r="DA264" s="38">
         <v>0.55274721454609288</v>
       </c>
-      <c r="DB264" s="9"/>
+      <c r="DB264" s="38">
+        <v>0.24569676904282076</v>
+      </c>
       <c r="DC264" s="9"/>
       <c r="DD264" s="9"/>
       <c r="DE264" s="9"/>
@@ -65092,7 +65479,9 @@
       <c r="DA265" s="38">
         <v>3.2099625655792186</v>
       </c>
-      <c r="DB265" s="9"/>
+      <c r="DB265" s="38">
+        <v>2.3929154723032924</v>
+      </c>
       <c r="DC265" s="9"/>
       <c r="DD265" s="9"/>
       <c r="DE265" s="9"/>
@@ -65456,7 +65845,9 @@
       <c r="DA266" s="38">
         <v>18.404593358553939</v>
       </c>
-      <c r="DB266" s="9"/>
+      <c r="DB266" s="38">
+        <v>19.432940908865749</v>
+      </c>
       <c r="DC266" s="9"/>
       <c r="DD266" s="9"/>
       <c r="DE266" s="9"/>
@@ -65820,7 +66211,9 @@
       <c r="DA267" s="38">
         <v>2.9737212914700968</v>
       </c>
-      <c r="DB267" s="9"/>
+      <c r="DB267" s="38">
+        <v>2.8316188245025313</v>
+      </c>
       <c r="DC267" s="9"/>
       <c r="DD267" s="9"/>
       <c r="DE267" s="9"/>
@@ -66184,7 +66577,9 @@
       <c r="DA268" s="38">
         <v>1.9055536008076757</v>
       </c>
-      <c r="DB268" s="9"/>
+      <c r="DB268" s="38">
+        <v>1.6686219920761667</v>
+      </c>
       <c r="DC268" s="9"/>
       <c r="DD268" s="9"/>
       <c r="DE268" s="9"/>
@@ -66548,7 +66943,9 @@
       <c r="DA269" s="38">
         <v>5.3155927542414254</v>
       </c>
-      <c r="DB269" s="9"/>
+      <c r="DB269" s="38">
+        <v>7.7003829983646233</v>
+      </c>
       <c r="DC269" s="9"/>
       <c r="DD269" s="9"/>
       <c r="DE269" s="9"/>
@@ -66912,7 +67309,9 @@
       <c r="DA270" s="38">
         <v>8.2097257120347411</v>
       </c>
-      <c r="DB270" s="9"/>
+      <c r="DB270" s="38">
+        <v>7.2323170939224273</v>
+      </c>
       <c r="DC270" s="9"/>
       <c r="DD270" s="9"/>
       <c r="DE270" s="9"/>
@@ -67276,7 +67675,9 @@
       <c r="DA271" s="38">
         <v>52.154352638986204</v>
       </c>
-      <c r="DB271" s="9"/>
+      <c r="DB271" s="38">
+        <v>47.707356727568659</v>
+      </c>
       <c r="DC271" s="9"/>
       <c r="DD271" s="9"/>
       <c r="DE271" s="9"/>
@@ -67640,7 +68041,9 @@
       <c r="DA272" s="38">
         <v>45.77604311799066</v>
       </c>
-      <c r="DB272" s="9"/>
+      <c r="DB272" s="38">
+        <v>43.732696814733465</v>
+      </c>
       <c r="DC272" s="9"/>
       <c r="DD272" s="9"/>
       <c r="DE272" s="9"/>
@@ -68004,7 +68407,9 @@
       <c r="DA273" s="38">
         <v>3.3839201566735908E-2</v>
       </c>
-      <c r="DB273" s="9"/>
+      <c r="DB273" s="38">
+        <v>4.5960876325890805E-2</v>
+      </c>
       <c r="DC273" s="9"/>
       <c r="DD273" s="9"/>
       <c r="DE273" s="9"/>
@@ -68368,7 +68773,9 @@
       <c r="DA274" s="38">
         <v>6.0412733837411263</v>
       </c>
-      <c r="DB274" s="9"/>
+      <c r="DB274" s="38">
+        <v>1.6163886228099063</v>
+      </c>
       <c r="DC274" s="9"/>
       <c r="DD274" s="9"/>
       <c r="DE274" s="9"/>
@@ -68732,7 +69139,9 @@
       <c r="DA275" s="38">
         <v>0.30319693568768252</v>
       </c>
-      <c r="DB275" s="9"/>
+      <c r="DB275" s="38">
+        <v>2.3123104136993931</v>
+      </c>
       <c r="DC275" s="9"/>
       <c r="DD275" s="9"/>
       <c r="DE275" s="9"/>
@@ -69096,7 +69505,9 @@
       <c r="DA276" s="38">
         <v>13.085354921599604</v>
       </c>
-      <c r="DB276" s="9"/>
+      <c r="DB276" s="38">
+        <v>18.802548212068434</v>
+      </c>
       <c r="DC276" s="9"/>
       <c r="DD276" s="9"/>
       <c r="DE276" s="9"/>
@@ -69460,7 +69871,9 @@
       <c r="DA277" s="38">
         <v>1.4023574113789203</v>
       </c>
-      <c r="DB277" s="9"/>
+      <c r="DB277" s="38">
+        <v>2.0327125859602022</v>
+      </c>
       <c r="DC277" s="9"/>
       <c r="DD277" s="9"/>
       <c r="DE277" s="9"/>
@@ -69824,7 +70237,9 @@
       <c r="DA278" s="38">
         <v>2.4099559847363037</v>
       </c>
-      <c r="DB278" s="9"/>
+      <c r="DB278" s="38">
+        <v>3.524063971731036</v>
+      </c>
       <c r="DC278" s="9"/>
       <c r="DD278" s="9"/>
       <c r="DE278" s="9"/>
@@ -70188,7 +70603,9 @@
       <c r="DA279" s="38">
         <v>6.727238770459147</v>
       </c>
-      <c r="DB279" s="9"/>
+      <c r="DB279" s="38">
+        <v>8.8775512172354745</v>
+      </c>
       <c r="DC279" s="9"/>
       <c r="DD279" s="9"/>
       <c r="DE279" s="9"/>
@@ -70552,7 +70969,9 @@
       <c r="DA280" s="38">
         <v>2.5458027550252322</v>
       </c>
-      <c r="DB280" s="9"/>
+      <c r="DB280" s="38">
+        <v>4.3682204371417219</v>
+      </c>
       <c r="DC280" s="9"/>
       <c r="DD280" s="9"/>
       <c r="DE280" s="9"/>
@@ -70705,7 +71124,7 @@
       <c r="CY281" s="31"/>
       <c r="CZ281" s="31"/>
       <c r="DA281" s="31"/>
-      <c r="DB281" s="9"/>
+      <c r="DB281" s="31"/>
       <c r="DC281" s="9"/>
       <c r="DD281" s="9"/>
       <c r="DE281" s="9"/>
@@ -71069,7 +71488,9 @@
       <c r="DA282" s="38">
         <v>100</v>
       </c>
-      <c r="DB282" s="9"/>
+      <c r="DB282" s="38">
+        <v>100</v>
+      </c>
       <c r="DC282" s="9"/>
       <c r="DD282" s="9"/>
       <c r="DE282" s="9"/>
@@ -71223,6 +71644,7 @@
       <c r="CY283" s="33"/>
       <c r="CZ283" s="33"/>
       <c r="DA283" s="33"/>
+      <c r="DB283" s="33"/>
     </row>
     <row r="284" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A284" s="15" t="s">
@@ -71241,26 +71663,109 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="CD132:CG132"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="CD254:CG254"/>
-    <mergeCell ref="CD213:CG213"/>
-    <mergeCell ref="CD172:CG172"/>
-    <mergeCell ref="CD50:CG50"/>
-    <mergeCell ref="CD91:CG91"/>
-    <mergeCell ref="BJ9:BM9"/>
-    <mergeCell ref="BN9:BQ9"/>
-    <mergeCell ref="BZ50:CC50"/>
-    <mergeCell ref="BV254:BY254"/>
-    <mergeCell ref="BN132:BQ132"/>
-    <mergeCell ref="BJ91:BM91"/>
-    <mergeCell ref="BN91:BQ91"/>
-    <mergeCell ref="BJ132:BM132"/>
-    <mergeCell ref="BJ172:BM172"/>
-    <mergeCell ref="BR132:BU132"/>
-    <mergeCell ref="BV132:BY132"/>
-    <mergeCell ref="BR50:BU50"/>
-    <mergeCell ref="BV50:BY50"/>
+    <mergeCell ref="B254:E254"/>
+    <mergeCell ref="AT50:AW50"/>
+    <mergeCell ref="AX50:BA50"/>
+    <mergeCell ref="BF9:BI9"/>
+    <mergeCell ref="BB50:BE50"/>
+    <mergeCell ref="AP9:AS9"/>
+    <mergeCell ref="AT9:AW9"/>
+    <mergeCell ref="AX9:BA9"/>
+    <mergeCell ref="BB9:BE9"/>
+    <mergeCell ref="AP213:AS213"/>
+    <mergeCell ref="AT213:AW213"/>
+    <mergeCell ref="BB213:BE213"/>
+    <mergeCell ref="BF172:BI172"/>
+    <mergeCell ref="AP132:AS132"/>
+    <mergeCell ref="AT132:AW132"/>
+    <mergeCell ref="AT91:AW91"/>
+    <mergeCell ref="AX91:BA91"/>
+    <mergeCell ref="BF50:BI50"/>
+    <mergeCell ref="AP50:AS50"/>
+    <mergeCell ref="BF132:BI132"/>
+    <mergeCell ref="BB91:BE91"/>
+    <mergeCell ref="BF91:BI91"/>
+    <mergeCell ref="AX213:BA213"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="N50:Q50"/>
+    <mergeCell ref="R50:U50"/>
+    <mergeCell ref="V50:Y50"/>
+    <mergeCell ref="Z50:AC50"/>
+    <mergeCell ref="AD50:AG50"/>
+    <mergeCell ref="AH50:AK50"/>
+    <mergeCell ref="AL50:AO50"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AH9:AK9"/>
+    <mergeCell ref="F254:I254"/>
+    <mergeCell ref="J254:M254"/>
+    <mergeCell ref="N254:Q254"/>
+    <mergeCell ref="R254:U254"/>
+    <mergeCell ref="V254:Y254"/>
+    <mergeCell ref="Z254:AC254"/>
+    <mergeCell ref="AD254:AG254"/>
+    <mergeCell ref="AH254:AK254"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="F213:I213"/>
+    <mergeCell ref="J213:M213"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="F172:I172"/>
+    <mergeCell ref="J172:M172"/>
+    <mergeCell ref="N172:Q172"/>
+    <mergeCell ref="R172:U172"/>
+    <mergeCell ref="V172:Y172"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="N91:Q91"/>
+    <mergeCell ref="R91:U91"/>
+    <mergeCell ref="V91:Y91"/>
+    <mergeCell ref="Z91:AC91"/>
+    <mergeCell ref="AT172:AW172"/>
+    <mergeCell ref="AX172:BA172"/>
+    <mergeCell ref="BB172:BE172"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="F132:I132"/>
+    <mergeCell ref="J132:M132"/>
+    <mergeCell ref="N132:Q132"/>
+    <mergeCell ref="R132:U132"/>
+    <mergeCell ref="V132:Y132"/>
+    <mergeCell ref="AX132:BA132"/>
+    <mergeCell ref="BB132:BE132"/>
+    <mergeCell ref="AL91:AO91"/>
+    <mergeCell ref="Z172:AC172"/>
+    <mergeCell ref="AD172:AG172"/>
+    <mergeCell ref="AH172:AK172"/>
+    <mergeCell ref="AP91:AS91"/>
+    <mergeCell ref="Z132:AC132"/>
+    <mergeCell ref="AD132:AG132"/>
+    <mergeCell ref="AH132:AK132"/>
+    <mergeCell ref="AL132:AO132"/>
+    <mergeCell ref="AL172:AO172"/>
+    <mergeCell ref="AP172:AS172"/>
+    <mergeCell ref="AD91:AG91"/>
+    <mergeCell ref="AH91:AK91"/>
+    <mergeCell ref="AX254:BA254"/>
+    <mergeCell ref="BB254:BE254"/>
+    <mergeCell ref="N213:Q213"/>
+    <mergeCell ref="R213:U213"/>
+    <mergeCell ref="V213:Y213"/>
+    <mergeCell ref="Z213:AC213"/>
+    <mergeCell ref="AD213:AG213"/>
+    <mergeCell ref="AH213:AK213"/>
+    <mergeCell ref="AL213:AO213"/>
+    <mergeCell ref="AL254:AO254"/>
+    <mergeCell ref="AP254:AS254"/>
+    <mergeCell ref="AT254:AW254"/>
     <mergeCell ref="BF254:BI254"/>
     <mergeCell ref="BJ254:BM254"/>
     <mergeCell ref="BN254:BQ254"/>
@@ -71285,111 +71790,38 @@
     <mergeCell ref="BN172:BQ172"/>
     <mergeCell ref="BZ254:CC254"/>
     <mergeCell ref="BR254:BU254"/>
-    <mergeCell ref="AX254:BA254"/>
-    <mergeCell ref="BB254:BE254"/>
-    <mergeCell ref="N213:Q213"/>
-    <mergeCell ref="R213:U213"/>
-    <mergeCell ref="V213:Y213"/>
-    <mergeCell ref="Z213:AC213"/>
-    <mergeCell ref="AD213:AG213"/>
-    <mergeCell ref="AH213:AK213"/>
-    <mergeCell ref="AL213:AO213"/>
-    <mergeCell ref="AL254:AO254"/>
-    <mergeCell ref="AP254:AS254"/>
-    <mergeCell ref="AT254:AW254"/>
-    <mergeCell ref="AL91:AO91"/>
-    <mergeCell ref="Z172:AC172"/>
-    <mergeCell ref="AD172:AG172"/>
-    <mergeCell ref="AH172:AK172"/>
-    <mergeCell ref="AP91:AS91"/>
-    <mergeCell ref="Z132:AC132"/>
-    <mergeCell ref="AD132:AG132"/>
-    <mergeCell ref="AH132:AK132"/>
-    <mergeCell ref="AL132:AO132"/>
-    <mergeCell ref="AL172:AO172"/>
-    <mergeCell ref="AP172:AS172"/>
-    <mergeCell ref="AD91:AG91"/>
-    <mergeCell ref="AH91:AK91"/>
-    <mergeCell ref="AT172:AW172"/>
-    <mergeCell ref="AX172:BA172"/>
-    <mergeCell ref="BB172:BE172"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="F132:I132"/>
-    <mergeCell ref="J132:M132"/>
-    <mergeCell ref="N132:Q132"/>
-    <mergeCell ref="R132:U132"/>
-    <mergeCell ref="V132:Y132"/>
-    <mergeCell ref="AX132:BA132"/>
-    <mergeCell ref="BB132:BE132"/>
-    <mergeCell ref="F254:I254"/>
-    <mergeCell ref="J254:M254"/>
-    <mergeCell ref="N254:Q254"/>
-    <mergeCell ref="R254:U254"/>
-    <mergeCell ref="V254:Y254"/>
-    <mergeCell ref="Z254:AC254"/>
-    <mergeCell ref="AD254:AG254"/>
-    <mergeCell ref="AH254:AK254"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B213:E213"/>
-    <mergeCell ref="F213:I213"/>
-    <mergeCell ref="J213:M213"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="F172:I172"/>
-    <mergeCell ref="J172:M172"/>
-    <mergeCell ref="N172:Q172"/>
-    <mergeCell ref="R172:U172"/>
-    <mergeCell ref="V172:Y172"/>
-    <mergeCell ref="F91:I91"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="N91:Q91"/>
-    <mergeCell ref="R91:U91"/>
-    <mergeCell ref="V91:Y91"/>
-    <mergeCell ref="Z91:AC91"/>
-    <mergeCell ref="V50:Y50"/>
-    <mergeCell ref="Z50:AC50"/>
-    <mergeCell ref="AD50:AG50"/>
-    <mergeCell ref="AH50:AK50"/>
-    <mergeCell ref="AL50:AO50"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AH9:AK9"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="N50:Q50"/>
-    <mergeCell ref="R50:U50"/>
-    <mergeCell ref="B254:E254"/>
-    <mergeCell ref="AT50:AW50"/>
-    <mergeCell ref="AX50:BA50"/>
-    <mergeCell ref="BF9:BI9"/>
-    <mergeCell ref="BB50:BE50"/>
-    <mergeCell ref="AP9:AS9"/>
-    <mergeCell ref="AT9:AW9"/>
-    <mergeCell ref="AX9:BA9"/>
-    <mergeCell ref="BB9:BE9"/>
-    <mergeCell ref="AP213:AS213"/>
-    <mergeCell ref="AT213:AW213"/>
-    <mergeCell ref="BB213:BE213"/>
-    <mergeCell ref="BF172:BI172"/>
-    <mergeCell ref="AP132:AS132"/>
-    <mergeCell ref="AT132:AW132"/>
-    <mergeCell ref="AT91:AW91"/>
-    <mergeCell ref="AX91:BA91"/>
-    <mergeCell ref="BF50:BI50"/>
-    <mergeCell ref="AP50:AS50"/>
-    <mergeCell ref="BF132:BI132"/>
-    <mergeCell ref="BB91:BE91"/>
-    <mergeCell ref="BF91:BI91"/>
-    <mergeCell ref="AX213:BA213"/>
-    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="CD132:CG132"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="CD254:CG254"/>
+    <mergeCell ref="CD213:CG213"/>
+    <mergeCell ref="CD172:CG172"/>
+    <mergeCell ref="CD50:CG50"/>
+    <mergeCell ref="CD91:CG91"/>
+    <mergeCell ref="BJ9:BM9"/>
+    <mergeCell ref="BN9:BQ9"/>
+    <mergeCell ref="BZ50:CC50"/>
+    <mergeCell ref="BV254:BY254"/>
+    <mergeCell ref="BN132:BQ132"/>
+    <mergeCell ref="BJ91:BM91"/>
+    <mergeCell ref="BN91:BQ91"/>
+    <mergeCell ref="BJ132:BM132"/>
+    <mergeCell ref="BJ172:BM172"/>
+    <mergeCell ref="BR132:BU132"/>
+    <mergeCell ref="BV132:BY132"/>
+    <mergeCell ref="BR50:BU50"/>
+    <mergeCell ref="BV50:BY50"/>
   </mergeCells>
-  <conditionalFormatting sqref="CP94:DA109 CS110:DA110 CP111:DA111 CP112:CT112 CV112:DA112 CP113:DA119 CP135:DA150 CS151:DA151 CP152:DA152 CP153:CT153 CV153:DA153 CP154:DA160 CP175:DA200">
+  <conditionalFormatting sqref="CP94:CW109 CS110:CW110 CP111:CW111 CP112:CT112 CV112:CW112 CP113:CW119 CP135:CW150 CS151:CW151 CP152:CW152 CP153:CT153 CV153:CW153 CP154:CW160 CP175:DA200 CY135:DA160 CY94:DA119">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DB94:DB119 DB135:DB160 DB175:DB200">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CX94:CX119 CX135:CX160">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
@@ -71398,12 +71830,12 @@
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="6" manualBreakCount="6">
-    <brk id="41" max="104" man="1"/>
-    <brk id="82" max="104" man="1"/>
-    <brk id="123" max="104" man="1"/>
-    <brk id="164" max="104" man="1"/>
-    <brk id="204" max="104" man="1"/>
-    <brk id="245" max="104" man="1"/>
+    <brk id="41" max="105" man="1"/>
+    <brk id="82" max="105" man="1"/>
+    <brk id="123" max="105" man="1"/>
+    <brk id="164" max="105" man="1"/>
+    <brk id="204" max="105" man="1"/>
+    <brk id="245" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-03DEQ_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-03DEQ_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244EE6C5-F3BD-4DF3-95D6-A29FF34912D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4762E1F0-058E-45B1-8198-BD5BF157BFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
     <definedName name="PCE_Per_Anl">#REF!</definedName>
     <definedName name="PCE_Per_Con_Qrt">[1]HFCE!#REF!</definedName>
     <definedName name="PCE_Per_Cur_Qrt">[1]HFCE!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">DEQ!$A$1:$DB$286</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">DEQ!$A$1:$DC$286</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="manual"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="79">
   <si>
     <t>Source: Philippine Statistics Authority</t>
   </si>
@@ -270,16 +270,16 @@
     <t>2024 - 2025</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>Q1 2001 to Q1 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2001 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -453,10 +453,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -469,7 +469,14 @@
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{008F8423-7867-4CB4-A558-4D234F15232D}"/>
     <cellStyle name="Normal 3" xfId="6" xr:uid="{8C6D19FF-306C-41BE-9C1F-A9A8F7C52269}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -828,8 +835,8 @@
     <col min="22" max="69" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="70" max="73" width="10" style="1" customWidth="1"/>
     <col min="74" max="89" width="9.21875" style="1" customWidth="1"/>
-    <col min="90" max="106" width="9.21875" style="27" customWidth="1"/>
-    <col min="107" max="16384" width="7.77734375" style="1"/>
+    <col min="90" max="107" width="9.21875" style="27" customWidth="1"/>
+    <col min="108" max="16384" width="7.77734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:152" x14ac:dyDescent="0.2">
@@ -844,7 +851,7 @@
     </row>
     <row r="3" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:152" x14ac:dyDescent="0.2">
@@ -854,7 +861,7 @@
     </row>
     <row r="6" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:152" x14ac:dyDescent="0.2">
@@ -864,132 +871,132 @@
     </row>
     <row r="9" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="44">
+      <c r="B9" s="45">
         <v>2000</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44">
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45">
         <v>2001</v>
       </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44">
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45">
         <v>2002</v>
       </c>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44">
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45">
         <v>2003</v>
       </c>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44">
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45">
         <v>2004</v>
       </c>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44">
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="45">
         <v>2005</v>
       </c>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44">
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45">
         <v>2006</v>
       </c>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="44">
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45">
         <v>2007</v>
       </c>
-      <c r="AE9" s="44"/>
-      <c r="AF9" s="44"/>
-      <c r="AG9" s="44"/>
-      <c r="AH9" s="44">
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45">
         <v>2008</v>
       </c>
-      <c r="AI9" s="44"/>
-      <c r="AJ9" s="44"/>
-      <c r="AK9" s="44"/>
-      <c r="AL9" s="44">
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45">
         <v>2009</v>
       </c>
-      <c r="AM9" s="44"/>
-      <c r="AN9" s="44"/>
-      <c r="AO9" s="44"/>
-      <c r="AP9" s="44">
+      <c r="AM9" s="45"/>
+      <c r="AN9" s="45"/>
+      <c r="AO9" s="45"/>
+      <c r="AP9" s="45">
         <v>2010</v>
       </c>
-      <c r="AQ9" s="44"/>
-      <c r="AR9" s="44"/>
-      <c r="AS9" s="44"/>
-      <c r="AT9" s="44">
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="45"/>
+      <c r="AS9" s="45"/>
+      <c r="AT9" s="45">
         <v>2011</v>
       </c>
-      <c r="AU9" s="44"/>
-      <c r="AV9" s="44"/>
-      <c r="AW9" s="44"/>
-      <c r="AX9" s="44">
+      <c r="AU9" s="45"/>
+      <c r="AV9" s="45"/>
+      <c r="AW9" s="45"/>
+      <c r="AX9" s="45">
         <v>2012</v>
       </c>
-      <c r="AY9" s="44"/>
-      <c r="AZ9" s="44"/>
-      <c r="BA9" s="44"/>
-      <c r="BB9" s="44">
+      <c r="AY9" s="45"/>
+      <c r="AZ9" s="45"/>
+      <c r="BA9" s="45"/>
+      <c r="BB9" s="45">
         <v>2013</v>
       </c>
-      <c r="BC9" s="44"/>
-      <c r="BD9" s="44"/>
-      <c r="BE9" s="44"/>
-      <c r="BF9" s="44">
+      <c r="BC9" s="45"/>
+      <c r="BD9" s="45"/>
+      <c r="BE9" s="45"/>
+      <c r="BF9" s="45">
         <v>2014</v>
       </c>
-      <c r="BG9" s="44"/>
-      <c r="BH9" s="44"/>
-      <c r="BI9" s="44"/>
-      <c r="BJ9" s="44">
+      <c r="BG9" s="45"/>
+      <c r="BH9" s="45"/>
+      <c r="BI9" s="45"/>
+      <c r="BJ9" s="45">
         <v>2015</v>
       </c>
-      <c r="BK9" s="44"/>
-      <c r="BL9" s="44"/>
-      <c r="BM9" s="44"/>
-      <c r="BN9" s="44">
+      <c r="BK9" s="45"/>
+      <c r="BL9" s="45"/>
+      <c r="BM9" s="45"/>
+      <c r="BN9" s="45">
         <v>2016</v>
       </c>
-      <c r="BO9" s="44"/>
-      <c r="BP9" s="44"/>
-      <c r="BQ9" s="44"/>
-      <c r="BR9" s="44">
+      <c r="BO9" s="45"/>
+      <c r="BP9" s="45"/>
+      <c r="BQ9" s="45"/>
+      <c r="BR9" s="45">
         <v>2017</v>
       </c>
-      <c r="BS9" s="44"/>
-      <c r="BT9" s="44"/>
-      <c r="BU9" s="44"/>
-      <c r="BV9" s="44">
+      <c r="BS9" s="45"/>
+      <c r="BT9" s="45"/>
+      <c r="BU9" s="45"/>
+      <c r="BV9" s="45">
         <v>2018</v>
       </c>
-      <c r="BW9" s="44"/>
-      <c r="BX9" s="44"/>
-      <c r="BY9" s="44"/>
-      <c r="BZ9" s="44">
+      <c r="BW9" s="45"/>
+      <c r="BX9" s="45"/>
+      <c r="BY9" s="45"/>
+      <c r="BZ9" s="45">
         <v>2019</v>
       </c>
-      <c r="CA9" s="44"/>
-      <c r="CB9" s="44"/>
-      <c r="CC9" s="44"/>
-      <c r="CD9" s="44">
+      <c r="CA9" s="45"/>
+      <c r="CB9" s="45"/>
+      <c r="CC9" s="45"/>
+      <c r="CD9" s="45">
         <v>2020</v>
       </c>
-      <c r="CE9" s="44"/>
-      <c r="CF9" s="44"/>
-      <c r="CG9" s="44"/>
+      <c r="CE9" s="45"/>
+      <c r="CF9" s="45"/>
+      <c r="CG9" s="45"/>
       <c r="CH9" s="26">
         <v>2021</v>
       </c>
@@ -1023,6 +1030,7 @@
       <c r="DB9" s="28">
         <v>2026</v>
       </c>
+      <c r="DC9" s="28"/>
     </row>
     <row r="10" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1342,6 +1350,9 @@
       </c>
       <c r="DB10" s="17" t="s">
         <v>6</v>
+      </c>
+      <c r="DC10" s="17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1664,9 +1675,11 @@
         <v>57081.223119989634</v>
       </c>
       <c r="DB12" s="29">
-        <v>66190.694189807284</v>
-      </c>
-      <c r="DC12" s="9"/>
+        <v>66713.580270666411</v>
+      </c>
+      <c r="DC12" s="29">
+        <v>57849.056613584951</v>
+      </c>
       <c r="DD12" s="9"/>
       <c r="DE12" s="9"/>
       <c r="DF12" s="9"/>
@@ -2030,9 +2043,11 @@
         <v>3474.2554059409449</v>
       </c>
       <c r="DB13" s="30">
-        <v>3217.3354066386246</v>
-      </c>
-      <c r="DC13" s="9"/>
+        <v>3255.4390858416618</v>
+      </c>
+      <c r="DC13" s="30">
+        <v>4710.6081079254773</v>
+      </c>
       <c r="DD13" s="9"/>
       <c r="DE13" s="9"/>
       <c r="DF13" s="9"/>
@@ -2396,9 +2411,11 @@
         <v>11614.15543271483</v>
       </c>
       <c r="DB14" s="30">
-        <v>9685.6897878389591</v>
-      </c>
-      <c r="DC14" s="9"/>
+        <v>10062.633078457186</v>
+      </c>
+      <c r="DC14" s="30">
+        <v>7802.7294252287757</v>
+      </c>
       <c r="DD14" s="9"/>
       <c r="DE14" s="9"/>
       <c r="DF14" s="9"/>
@@ -2762,9 +2779,11 @@
         <v>1520.1872451638005</v>
       </c>
       <c r="DB15" s="30">
-        <v>908.11698230020988</v>
-      </c>
-      <c r="DC15" s="9"/>
+        <v>909.6028317320995</v>
+      </c>
+      <c r="DC15" s="30">
+        <v>1681.8603220430366</v>
+      </c>
       <c r="DD15" s="9"/>
       <c r="DE15" s="9"/>
       <c r="DF15" s="9"/>
@@ -3128,9 +3147,11 @@
         <v>718.58424833780975</v>
       </c>
       <c r="DB16" s="30">
-        <v>855.5453701479338</v>
-      </c>
-      <c r="DC16" s="9"/>
+        <v>861.9989080655871</v>
+      </c>
+      <c r="DC16" s="30">
+        <v>772.52210906497248</v>
+      </c>
       <c r="DD16" s="9"/>
       <c r="DE16" s="9"/>
       <c r="DF16" s="9"/>
@@ -3494,9 +3515,11 @@
         <v>2742.2980133333554</v>
       </c>
       <c r="DB17" s="30">
-        <v>3813.5271106651448</v>
-      </c>
-      <c r="DC17" s="9"/>
+        <v>3841.3856097970006</v>
+      </c>
+      <c r="DC17" s="30">
+        <v>3957.5104146976273</v>
+      </c>
       <c r="DD17" s="9"/>
       <c r="DE17" s="9"/>
       <c r="DF17" s="9"/>
@@ -3860,9 +3883,11 @@
         <v>24882.403139781571</v>
       </c>
       <c r="DB18" s="30">
-        <v>34646.730348328027</v>
-      </c>
-      <c r="DC18" s="9"/>
+        <v>34748.022285218867</v>
+      </c>
+      <c r="DC18" s="30">
+        <v>27592.62736226328</v>
+      </c>
       <c r="DD18" s="9"/>
       <c r="DE18" s="9"/>
       <c r="DF18" s="9"/>
@@ -4226,9 +4251,11 @@
         <v>1685.725358115104</v>
       </c>
       <c r="DB19" s="30">
-        <v>1208.423840789643</v>
-      </c>
-      <c r="DC19" s="9"/>
+        <v>1211.394288309514</v>
+      </c>
+      <c r="DC19" s="30">
+        <v>2127.6955734498783</v>
+      </c>
       <c r="DD19" s="9"/>
       <c r="DE19" s="9"/>
       <c r="DF19" s="9"/>
@@ -4592,9 +4619,11 @@
         <v>10443.614276602226</v>
       </c>
       <c r="DB20" s="30">
-        <v>11855.325343098744</v>
-      </c>
-      <c r="DC20" s="9"/>
+        <v>11823.104183244484</v>
+      </c>
+      <c r="DC20" s="30">
+        <v>9203.50329891191</v>
+      </c>
       <c r="DD20" s="9"/>
       <c r="DE20" s="9"/>
       <c r="DF20" s="9"/>
@@ -4958,9 +4987,11 @@
         <v>76157.402638788422</v>
       </c>
       <c r="DB21" s="29">
-        <v>94076.628715065191</v>
-      </c>
-      <c r="DC21" s="9"/>
+        <v>95422.565059346089</v>
+      </c>
+      <c r="DC21" s="29">
+        <v>74871.853090109798</v>
+      </c>
       <c r="DD21" s="9"/>
       <c r="DE21" s="9"/>
       <c r="DF21" s="9"/>
@@ -5324,9 +5355,11 @@
         <v>12758.064668105701</v>
       </c>
       <c r="DB22" s="30">
-        <v>13738.92676174718</v>
-      </c>
-      <c r="DC22" s="9"/>
+        <v>13828.274386085619</v>
+      </c>
+      <c r="DC22" s="30">
+        <v>12388.207620592884</v>
+      </c>
       <c r="DD22" s="9"/>
       <c r="DE22" s="9"/>
       <c r="DF22" s="9"/>
@@ -5690,9 +5723,11 @@
         <v>8760.7955594391788</v>
       </c>
       <c r="DB23" s="30">
-        <v>8531.5448412824007</v>
-      </c>
-      <c r="DC23" s="9"/>
+        <v>8647.0946981302332</v>
+      </c>
+      <c r="DC23" s="30">
+        <v>7816.6967135903569</v>
+      </c>
       <c r="DD23" s="9"/>
       <c r="DE23" s="9"/>
       <c r="DF23" s="9"/>
@@ -6056,9 +6091,11 @@
         <v>25260.186450065692</v>
       </c>
       <c r="DB24" s="30">
-        <v>39815.54297528755</v>
-      </c>
-      <c r="DC24" s="9"/>
+        <v>40618.084885296899</v>
+      </c>
+      <c r="DC24" s="30">
+        <v>29872.293380271098</v>
+      </c>
       <c r="DD24" s="9"/>
       <c r="DE24" s="9"/>
       <c r="DF24" s="9"/>
@@ -6422,9 +6459,11 @@
         <v>29378.355961177844</v>
       </c>
       <c r="DB25" s="30">
-        <v>31990.614136748056</v>
-      </c>
-      <c r="DC25" s="9"/>
+        <v>32329.111089833339</v>
+      </c>
+      <c r="DC25" s="30">
+        <v>24794.655375655471</v>
+      </c>
       <c r="DD25" s="9"/>
       <c r="DE25" s="9"/>
       <c r="DF25" s="9"/>
@@ -6788,9 +6827,11 @@
         <v>210572.16905781714</v>
       </c>
       <c r="DB26" s="29">
-        <v>206756.45873945567</v>
-      </c>
-      <c r="DC26" s="9"/>
+        <v>207748.52598850132</v>
+      </c>
+      <c r="DC26" s="29">
+        <v>153346.22694598761</v>
+      </c>
       <c r="DD26" s="9"/>
       <c r="DE26" s="9"/>
       <c r="DF26" s="9"/>
@@ -7154,9 +7195,11 @@
         <v>178731.21117082197</v>
       </c>
       <c r="DB27" s="30">
-        <v>184365.79691856503</v>
-      </c>
-      <c r="DC27" s="9"/>
+        <v>185360.29573696663</v>
+      </c>
+      <c r="DC27" s="30">
+        <v>146285.45755813894</v>
+      </c>
       <c r="DD27" s="9"/>
       <c r="DE27" s="9"/>
       <c r="DF27" s="9"/>
@@ -7520,9 +7563,11 @@
         <v>174.76223405781082</v>
       </c>
       <c r="DB28" s="30">
-        <v>219.74189519852126</v>
-      </c>
-      <c r="DC28" s="9"/>
+        <v>225.31413220585262</v>
+      </c>
+      <c r="DC28" s="30">
+        <v>99.814935209045771</v>
+      </c>
       <c r="DD28" s="9"/>
       <c r="DE28" s="9"/>
       <c r="DF28" s="9"/>
@@ -7888,7 +7933,9 @@
       <c r="DB29" s="30">
         <v>8898.0264254574322</v>
       </c>
-      <c r="DC29" s="9"/>
+      <c r="DC29" s="30">
+        <v>3378.030527440942</v>
+      </c>
       <c r="DD29" s="9"/>
       <c r="DE29" s="9"/>
       <c r="DF29" s="9"/>
@@ -8252,9 +8299,11 @@
         <v>1384.9742964656382</v>
       </c>
       <c r="DB30" s="30">
-        <v>13272.893500234679</v>
-      </c>
-      <c r="DC30" s="9"/>
+        <v>13264.889693871406</v>
+      </c>
+      <c r="DC30" s="30">
+        <v>3582.9239251986705</v>
+      </c>
       <c r="DD30" s="9"/>
       <c r="DE30" s="9"/>
       <c r="DF30" s="9"/>
@@ -8618,9 +8667,11 @@
         <v>78551.955605121591</v>
       </c>
       <c r="DB31" s="29">
-        <v>85168.415839454872</v>
-      </c>
-      <c r="DC31" s="9"/>
+        <v>84902.059525325618</v>
+      </c>
+      <c r="DC31" s="29">
+        <v>88454.026049213382</v>
+      </c>
       <c r="DD31" s="9"/>
       <c r="DE31" s="9"/>
       <c r="DF31" s="9"/>
@@ -8984,9 +9035,11 @@
         <v>10645.191730097835</v>
       </c>
       <c r="DB32" s="30">
-        <v>8238.7061846340857</v>
-      </c>
-      <c r="DC32" s="9"/>
+        <v>8414.9422682290624</v>
+      </c>
+      <c r="DC32" s="30">
+        <v>9134.067808036214</v>
+      </c>
       <c r="DD32" s="9"/>
       <c r="DE32" s="9"/>
       <c r="DF32" s="9"/>
@@ -9350,9 +9403,11 @@
         <v>11813.930132493941</v>
       </c>
       <c r="DB33" s="30">
-        <v>13233.097550791606</v>
-      </c>
-      <c r="DC33" s="9"/>
+        <v>13455.041706794149</v>
+      </c>
+      <c r="DC33" s="30">
+        <v>16302.730919769263</v>
+      </c>
       <c r="DD33" s="9"/>
       <c r="DE33" s="9"/>
       <c r="DF33" s="9"/>
@@ -9716,9 +9771,11 @@
         <v>43452.700015068054</v>
       </c>
       <c r="DB34" s="30">
-        <v>44990.250594156445</v>
-      </c>
-      <c r="DC34" s="9"/>
+        <v>44915.184532068706</v>
+      </c>
+      <c r="DC34" s="30">
+        <v>45702.036924976623</v>
+      </c>
       <c r="DD34" s="9"/>
       <c r="DE34" s="9"/>
       <c r="DF34" s="9"/>
@@ -10082,9 +10139,11 @@
         <v>12640.133727461765</v>
       </c>
       <c r="DB35" s="30">
-        <v>18706.361509872735</v>
-      </c>
-      <c r="DC35" s="9"/>
+        <v>18116.891018233695</v>
+      </c>
+      <c r="DC35" s="30">
+        <v>17315.190396431284</v>
+      </c>
       <c r="DD35" s="9"/>
       <c r="DE35" s="9"/>
       <c r="DF35" s="9"/>
@@ -10237,7 +10296,7 @@
       <c r="CZ36" s="31"/>
       <c r="DA36" s="31"/>
       <c r="DB36" s="31"/>
-      <c r="DC36" s="9"/>
+      <c r="DC36" s="31"/>
       <c r="DD36" s="9"/>
       <c r="DE36" s="9"/>
       <c r="DF36" s="9"/>
@@ -10601,9 +10660,11 @@
         <v>422362.75042171683</v>
       </c>
       <c r="DB37" s="32">
-        <v>452192.19748378301</v>
-      </c>
-      <c r="DC37" s="9"/>
+        <v>454786.73084383941</v>
+      </c>
+      <c r="DC37" s="32">
+        <v>374521.16269889573</v>
+      </c>
       <c r="DD37" s="9"/>
       <c r="DE37" s="9"/>
       <c r="DF37" s="9"/>
@@ -10757,6 +10818,7 @@
       <c r="CZ38" s="33"/>
       <c r="DA38" s="33"/>
       <c r="DB38" s="33"/>
+      <c r="DC38" s="33"/>
     </row>
     <row r="39" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
@@ -10889,7 +10951,7 @@
       <c r="CZ40" s="31"/>
       <c r="DA40" s="31"/>
       <c r="DB40" s="31"/>
-      <c r="DC40" s="9"/>
+      <c r="DC40" s="31"/>
       <c r="DD40" s="9"/>
       <c r="DE40" s="9"/>
       <c r="DF40" s="9"/>
@@ -11042,7 +11104,7 @@
       <c r="CZ41" s="31"/>
       <c r="DA41" s="31"/>
       <c r="DB41" s="31"/>
-      <c r="DC41" s="9"/>
+      <c r="DC41" s="31"/>
       <c r="DD41" s="9"/>
       <c r="DE41" s="9"/>
       <c r="DF41" s="9"/>
@@ -11101,7 +11163,7 @@
     </row>
     <row r="44" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:152" x14ac:dyDescent="0.2">
@@ -11111,7 +11173,7 @@
     </row>
     <row r="47" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:152" x14ac:dyDescent="0.2">
@@ -11121,132 +11183,132 @@
     </row>
     <row r="50" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
-      <c r="B50" s="45">
+      <c r="B50" s="44">
         <v>2000</v>
       </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45">
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44">
         <v>2001</v>
       </c>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45">
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44">
         <v>2002</v>
       </c>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
-      <c r="N50" s="45">
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44">
         <v>2003</v>
       </c>
-      <c r="O50" s="45"/>
-      <c r="P50" s="45"/>
-      <c r="Q50" s="45"/>
-      <c r="R50" s="45">
+      <c r="O50" s="44"/>
+      <c r="P50" s="44"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="44">
         <v>2004</v>
       </c>
-      <c r="S50" s="45"/>
-      <c r="T50" s="45"/>
-      <c r="U50" s="45"/>
-      <c r="V50" s="45">
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44">
         <v>2005</v>
       </c>
-      <c r="W50" s="45"/>
-      <c r="X50" s="45"/>
-      <c r="Y50" s="45"/>
-      <c r="Z50" s="45">
+      <c r="W50" s="44"/>
+      <c r="X50" s="44"/>
+      <c r="Y50" s="44"/>
+      <c r="Z50" s="44">
         <v>2006</v>
       </c>
-      <c r="AA50" s="45"/>
-      <c r="AB50" s="45"/>
-      <c r="AC50" s="45"/>
-      <c r="AD50" s="45">
+      <c r="AA50" s="44"/>
+      <c r="AB50" s="44"/>
+      <c r="AC50" s="44"/>
+      <c r="AD50" s="44">
         <v>2007</v>
       </c>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="45"/>
-      <c r="AG50" s="45"/>
-      <c r="AH50" s="45">
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="44"/>
+      <c r="AG50" s="44"/>
+      <c r="AH50" s="44">
         <v>2008</v>
       </c>
-      <c r="AI50" s="45"/>
-      <c r="AJ50" s="45"/>
-      <c r="AK50" s="45"/>
-      <c r="AL50" s="45">
+      <c r="AI50" s="44"/>
+      <c r="AJ50" s="44"/>
+      <c r="AK50" s="44"/>
+      <c r="AL50" s="44">
         <v>2009</v>
       </c>
-      <c r="AM50" s="45"/>
-      <c r="AN50" s="45"/>
-      <c r="AO50" s="45"/>
-      <c r="AP50" s="45">
+      <c r="AM50" s="44"/>
+      <c r="AN50" s="44"/>
+      <c r="AO50" s="44"/>
+      <c r="AP50" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ50" s="45"/>
-      <c r="AR50" s="45"/>
-      <c r="AS50" s="45"/>
-      <c r="AT50" s="45">
+      <c r="AQ50" s="44"/>
+      <c r="AR50" s="44"/>
+      <c r="AS50" s="44"/>
+      <c r="AT50" s="44">
         <v>2011</v>
       </c>
-      <c r="AU50" s="45"/>
-      <c r="AV50" s="45"/>
-      <c r="AW50" s="45"/>
-      <c r="AX50" s="45">
+      <c r="AU50" s="44"/>
+      <c r="AV50" s="44"/>
+      <c r="AW50" s="44"/>
+      <c r="AX50" s="44">
         <v>2012</v>
       </c>
-      <c r="AY50" s="45"/>
-      <c r="AZ50" s="45"/>
-      <c r="BA50" s="45"/>
-      <c r="BB50" s="45">
+      <c r="AY50" s="44"/>
+      <c r="AZ50" s="44"/>
+      <c r="BA50" s="44"/>
+      <c r="BB50" s="44">
         <v>2013</v>
       </c>
-      <c r="BC50" s="45"/>
-      <c r="BD50" s="45"/>
-      <c r="BE50" s="45"/>
-      <c r="BF50" s="45">
+      <c r="BC50" s="44"/>
+      <c r="BD50" s="44"/>
+      <c r="BE50" s="44"/>
+      <c r="BF50" s="44">
         <v>2014</v>
       </c>
-      <c r="BG50" s="45"/>
-      <c r="BH50" s="45"/>
-      <c r="BI50" s="45"/>
-      <c r="BJ50" s="45">
+      <c r="BG50" s="44"/>
+      <c r="BH50" s="44"/>
+      <c r="BI50" s="44"/>
+      <c r="BJ50" s="44">
         <v>2015</v>
       </c>
-      <c r="BK50" s="45"/>
-      <c r="BL50" s="45"/>
-      <c r="BM50" s="45"/>
-      <c r="BN50" s="45">
+      <c r="BK50" s="44"/>
+      <c r="BL50" s="44"/>
+      <c r="BM50" s="44"/>
+      <c r="BN50" s="44">
         <v>2016</v>
       </c>
-      <c r="BO50" s="45"/>
-      <c r="BP50" s="45"/>
-      <c r="BQ50" s="45"/>
-      <c r="BR50" s="45">
+      <c r="BO50" s="44"/>
+      <c r="BP50" s="44"/>
+      <c r="BQ50" s="44"/>
+      <c r="BR50" s="44">
         <v>2017</v>
       </c>
-      <c r="BS50" s="45"/>
-      <c r="BT50" s="45"/>
-      <c r="BU50" s="45"/>
-      <c r="BV50" s="45">
+      <c r="BS50" s="44"/>
+      <c r="BT50" s="44"/>
+      <c r="BU50" s="44"/>
+      <c r="BV50" s="44">
         <v>2018</v>
       </c>
-      <c r="BW50" s="45"/>
-      <c r="BX50" s="45"/>
-      <c r="BY50" s="45"/>
-      <c r="BZ50" s="45">
+      <c r="BW50" s="44"/>
+      <c r="BX50" s="44"/>
+      <c r="BY50" s="44"/>
+      <c r="BZ50" s="44">
         <v>2019</v>
       </c>
-      <c r="CA50" s="45"/>
-      <c r="CB50" s="45"/>
-      <c r="CC50" s="45"/>
-      <c r="CD50" s="44">
+      <c r="CA50" s="44"/>
+      <c r="CB50" s="44"/>
+      <c r="CC50" s="44"/>
+      <c r="CD50" s="45">
         <v>2020</v>
       </c>
-      <c r="CE50" s="44"/>
-      <c r="CF50" s="44"/>
-      <c r="CG50" s="44"/>
+      <c r="CE50" s="45"/>
+      <c r="CF50" s="45"/>
+      <c r="CG50" s="45"/>
       <c r="CH50" s="26">
         <v>2021</v>
       </c>
@@ -11280,6 +11342,7 @@
       <c r="DB50" s="28">
         <v>2026</v>
       </c>
+      <c r="DC50" s="28"/>
     </row>
     <row r="51" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
@@ -11599,6 +11662,9 @@
       </c>
       <c r="DB51" s="34" t="s">
         <v>6</v>
+      </c>
+      <c r="DC51" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -11921,9 +11987,11 @@
         <v>55485.425004640681</v>
       </c>
       <c r="DB53" s="29">
-        <v>51858.32542975407</v>
-      </c>
-      <c r="DC53" s="9"/>
+        <v>52163.070010843498</v>
+      </c>
+      <c r="DC53" s="29">
+        <v>33644.073381919792</v>
+      </c>
       <c r="DD53" s="9"/>
       <c r="DE53" s="9"/>
       <c r="DF53" s="9"/>
@@ -12287,9 +12355,11 @@
         <v>3742.5695592526358</v>
       </c>
       <c r="DB54" s="30">
-        <v>2365.4175792992501</v>
-      </c>
-      <c r="DC54" s="9"/>
+        <v>2393.0448275901053</v>
+      </c>
+      <c r="DC54" s="30">
+        <v>1112.5374264184977</v>
+      </c>
       <c r="DD54" s="9"/>
       <c r="DE54" s="9"/>
       <c r="DF54" s="9"/>
@@ -12653,9 +12723,11 @@
         <v>12641.471973945498</v>
       </c>
       <c r="DB55" s="30">
-        <v>7017.0289261715379</v>
-      </c>
-      <c r="DC55" s="9"/>
+        <v>7285.7770227516612</v>
+      </c>
+      <c r="DC55" s="30">
+        <v>1948.2891103194752</v>
+      </c>
       <c r="DD55" s="9"/>
       <c r="DE55" s="9"/>
       <c r="DF55" s="9"/>
@@ -13019,9 +13091,11 @@
         <v>1579.4531969245238</v>
       </c>
       <c r="DB56" s="30">
-        <v>740.66992933069241</v>
-      </c>
-      <c r="DC56" s="9"/>
+        <v>740.30581068353104</v>
+      </c>
+      <c r="DC56" s="30">
+        <v>500.21047246833882</v>
+      </c>
       <c r="DD56" s="9"/>
       <c r="DE56" s="9"/>
       <c r="DF56" s="9"/>
@@ -13385,9 +13459,11 @@
         <v>751.02438727416393</v>
       </c>
       <c r="DB57" s="30">
-        <v>521.01161232576021</v>
-      </c>
-      <c r="DC57" s="9"/>
+        <v>524.44333361251734</v>
+      </c>
+      <c r="DC57" s="30">
+        <v>203.78985520089003</v>
+      </c>
       <c r="DD57" s="9"/>
       <c r="DE57" s="9"/>
       <c r="DF57" s="9"/>
@@ -13751,9 +13827,11 @@
         <v>2913.0534341657817</v>
       </c>
       <c r="DB58" s="30">
-        <v>2667.4471869178847</v>
-      </c>
-      <c r="DC58" s="9"/>
+        <v>2686.1824369929109</v>
+      </c>
+      <c r="DC58" s="30">
+        <v>980.25699794161699</v>
+      </c>
       <c r="DD58" s="9"/>
       <c r="DE58" s="9"/>
       <c r="DF58" s="9"/>
@@ -14117,9 +14195,11 @@
         <v>21093.154943835943</v>
       </c>
       <c r="DB59" s="30">
-        <v>28812.631125805601</v>
-      </c>
-      <c r="DC59" s="9"/>
+        <v>28829.337575806865</v>
+      </c>
+      <c r="DC59" s="30">
+        <v>25311.442064602659</v>
+      </c>
       <c r="DD59" s="9"/>
       <c r="DE59" s="9"/>
       <c r="DF59" s="9"/>
@@ -14483,9 +14563,11 @@
         <v>1875.1515277699841</v>
       </c>
       <c r="DB60" s="30">
-        <v>906.40131485679854</v>
-      </c>
-      <c r="DC60" s="9"/>
+        <v>908.32780080879354</v>
+      </c>
+      <c r="DC60" s="30">
+        <v>528.91299967120881</v>
+      </c>
       <c r="DD60" s="9"/>
       <c r="DE60" s="9"/>
       <c r="DF60" s="9"/>
@@ -14849,9 +14931,11 @@
         <v>10889.545981472149</v>
       </c>
       <c r="DB61" s="30">
-        <v>8827.7177550465531</v>
-      </c>
-      <c r="DC61" s="9"/>
+        <v>8795.6512025971169</v>
+      </c>
+      <c r="DC61" s="30">
+        <v>3058.6344552971054</v>
+      </c>
       <c r="DD61" s="9"/>
       <c r="DE61" s="9"/>
       <c r="DF61" s="9"/>
@@ -15215,9 +15299,11 @@
         <v>62436.137977860148</v>
       </c>
       <c r="DB62" s="29">
-        <v>71690.170204316179</v>
-      </c>
-      <c r="DC62" s="9"/>
+        <v>72520.55868799219</v>
+      </c>
+      <c r="DC62" s="29">
+        <v>47839.43958691397</v>
+      </c>
       <c r="DD62" s="9"/>
       <c r="DE62" s="9"/>
       <c r="DF62" s="9"/>
@@ -15581,9 +15667,11 @@
         <v>10088.116006955095</v>
       </c>
       <c r="DB63" s="30">
-        <v>10446.140727455169</v>
-      </c>
-      <c r="DC63" s="9"/>
+        <v>10507.106880728166</v>
+      </c>
+      <c r="DC63" s="30">
+        <v>7204.5315156122897</v>
+      </c>
       <c r="DD63" s="9"/>
       <c r="DE63" s="9"/>
       <c r="DF63" s="9"/>
@@ -15947,9 +16035,11 @@
         <v>6464.440980921745</v>
       </c>
       <c r="DB64" s="30">
-        <v>6155.7226556496362</v>
-      </c>
-      <c r="DC64" s="9"/>
+        <v>6235.7036995006874</v>
+      </c>
+      <c r="DC64" s="30">
+        <v>4588.7304230611899</v>
+      </c>
       <c r="DD64" s="9"/>
       <c r="DE64" s="9"/>
       <c r="DF64" s="9"/>
@@ -16313,9 +16403,11 @@
         <v>18032.731078172961</v>
       </c>
       <c r="DB65" s="30">
-        <v>28407.525674064516</v>
-      </c>
-      <c r="DC65" s="9"/>
+        <v>28885.02152268542</v>
+      </c>
+      <c r="DC65" s="30">
+        <v>20186.602690208063</v>
+      </c>
       <c r="DD65" s="9"/>
       <c r="DE65" s="9"/>
       <c r="DF65" s="9"/>
@@ -16679,9 +16771,11 @@
         <v>27850.849911810343</v>
       </c>
       <c r="DB66" s="30">
-        <v>26680.781147146856</v>
-      </c>
-      <c r="DC66" s="9"/>
+        <v>26892.726585077911</v>
+      </c>
+      <c r="DC66" s="30">
+        <v>15859.57495803243</v>
+      </c>
       <c r="DD66" s="9"/>
       <c r="DE66" s="9"/>
       <c r="DF66" s="9"/>
@@ -17045,9 +17139,11 @@
         <v>176929.54655802119</v>
       </c>
       <c r="DB67" s="29">
-        <v>175997.47458898905</v>
-      </c>
-      <c r="DC67" s="9"/>
+        <v>176684.17757331589</v>
+      </c>
+      <c r="DC67" s="29">
+        <v>127689.24945316053</v>
+      </c>
       <c r="DD67" s="9"/>
       <c r="DE67" s="9"/>
       <c r="DF67" s="9"/>
@@ -17411,9 +17507,11 @@
         <v>155291.63228520803</v>
       </c>
       <c r="DB68" s="30">
-        <v>161334.53463606464</v>
-      </c>
-      <c r="DC68" s="9"/>
+        <v>162026.52817991172</v>
+      </c>
+      <c r="DC68" s="30">
+        <v>122298.1485285598</v>
+      </c>
       <c r="DD68" s="9"/>
       <c r="DE68" s="9"/>
       <c r="DF68" s="9"/>
@@ -17777,9 +17875,11 @@
         <v>114.79683451410673</v>
       </c>
       <c r="DB69" s="30">
-        <v>169.55452404218499</v>
-      </c>
-      <c r="DC69" s="9"/>
+        <v>173.85410466050433</v>
+      </c>
+      <c r="DC69" s="30">
+        <v>88.893468890454599</v>
+      </c>
       <c r="DD69" s="9"/>
       <c r="DE69" s="9"/>
       <c r="DF69" s="9"/>
@@ -18145,7 +18245,9 @@
       <c r="DB70" s="30">
         <v>5963.0282430744028</v>
       </c>
-      <c r="DC70" s="9"/>
+      <c r="DC70" s="30">
+        <v>2580.2275571594132</v>
+      </c>
       <c r="DD70" s="9"/>
       <c r="DE70" s="9"/>
       <c r="DF70" s="9"/>
@@ -18509,9 +18611,11 @@
         <v>1028.5717995644927</v>
       </c>
       <c r="DB71" s="30">
-        <v>8530.3571858078485</v>
-      </c>
-      <c r="DC71" s="9"/>
+        <v>8520.7670456692667</v>
+      </c>
+      <c r="DC71" s="30">
+        <v>2721.9798985508687</v>
+      </c>
       <c r="DD71" s="9"/>
       <c r="DE71" s="9"/>
       <c r="DF71" s="9"/>
@@ -18875,9 +18979,11 @@
         <v>44391.039207315385</v>
       </c>
       <c r="DB72" s="29">
-        <v>69364.585006435023</v>
-      </c>
-      <c r="DC72" s="9"/>
+        <v>69025.443124988087</v>
+      </c>
+      <c r="DC72" s="29">
+        <v>92448.0105164329</v>
+      </c>
       <c r="DD72" s="9"/>
       <c r="DE72" s="9"/>
       <c r="DF72" s="9"/>
@@ -19241,9 +19347,11 @@
         <v>4757.3874154863979</v>
       </c>
       <c r="DB73" s="30">
-        <v>7498.8912870855947</v>
-      </c>
-      <c r="DC73" s="9"/>
+        <v>7657.9157737786136</v>
+      </c>
+      <c r="DC73" s="30">
+        <v>11857.856853931333</v>
+      </c>
       <c r="DD73" s="9"/>
       <c r="DE73" s="9"/>
       <c r="DF73" s="9"/>
@@ -19607,9 +19715,11 @@
         <v>8175.5864664965393</v>
       </c>
       <c r="DB74" s="30">
-        <v>13000.643964755536</v>
-      </c>
-      <c r="DC74" s="9"/>
+        <v>13221.596736159801</v>
+      </c>
+      <c r="DC74" s="30">
+        <v>20651.460185456363</v>
+      </c>
       <c r="DD74" s="9"/>
       <c r="DE74" s="9"/>
       <c r="DF74" s="9"/>
@@ -19973,9 +20083,11 @@
         <v>22821.629356303205</v>
       </c>
       <c r="DB75" s="30">
-        <v>32750.223486286122</v>
-      </c>
-      <c r="DC75" s="9"/>
+        <v>32568.977091785164</v>
+      </c>
+      <c r="DC75" s="30">
+        <v>46010.587417664239</v>
+      </c>
       <c r="DD75" s="9"/>
       <c r="DE75" s="9"/>
       <c r="DF75" s="9"/>
@@ -20339,9 +20451,11 @@
         <v>8636.4359690292404</v>
       </c>
       <c r="DB76" s="30">
-        <v>16114.82626830777</v>
-      </c>
-      <c r="DC76" s="9"/>
+        <v>15576.953523264505</v>
+      </c>
+      <c r="DC76" s="30">
+        <v>13928.106059380971</v>
+      </c>
       <c r="DD76" s="9"/>
       <c r="DE76" s="9"/>
       <c r="DF76" s="9"/>
@@ -20494,7 +20608,7 @@
       <c r="CZ77" s="31"/>
       <c r="DA77" s="31"/>
       <c r="DB77" s="31"/>
-      <c r="DC77" s="9"/>
+      <c r="DC77" s="31"/>
       <c r="DD77" s="9"/>
       <c r="DE77" s="9"/>
       <c r="DF77" s="9"/>
@@ -20858,9 +20972,11 @@
         <v>339242.14874783735</v>
       </c>
       <c r="DB78" s="32">
-        <v>368910.55522949435</v>
-      </c>
-      <c r="DC78" s="9"/>
+        <v>370393.24939713965</v>
+      </c>
+      <c r="DC78" s="32">
+        <v>301620.77293842717</v>
+      </c>
       <c r="DD78" s="9"/>
       <c r="DE78" s="9"/>
       <c r="DF78" s="9"/>
@@ -21014,6 +21130,7 @@
       <c r="CZ79" s="33"/>
       <c r="DA79" s="33"/>
       <c r="DB79" s="33"/>
+      <c r="DC79" s="33"/>
     </row>
     <row r="80" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A80" s="15" t="s">
@@ -21147,7 +21264,7 @@
       <c r="CZ81" s="35"/>
       <c r="DA81" s="35"/>
       <c r="DB81" s="35"/>
-      <c r="DC81" s="18"/>
+      <c r="DC81" s="35"/>
       <c r="DD81" s="18"/>
       <c r="DE81" s="18"/>
       <c r="DF81" s="18"/>
@@ -21301,7 +21418,7 @@
       <c r="CZ82" s="35"/>
       <c r="DA82" s="35"/>
       <c r="DB82" s="35"/>
-      <c r="DC82" s="18"/>
+      <c r="DC82" s="35"/>
       <c r="DD82" s="18"/>
       <c r="DE82" s="18"/>
       <c r="DF82" s="18"/>
@@ -21360,7 +21477,7 @@
     </row>
     <row r="85" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:152" x14ac:dyDescent="0.2">
@@ -21377,6 +21494,7 @@
       <c r="CZ86" s="36"/>
       <c r="DA86" s="36"/>
       <c r="DB86" s="36"/>
+      <c r="DC86" s="36"/>
     </row>
     <row r="87" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
@@ -21395,10 +21513,11 @@
       <c r="CZ87" s="36"/>
       <c r="DA87" s="36"/>
       <c r="DB87" s="36"/>
+      <c r="DC87" s="36"/>
     </row>
     <row r="88" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CP88" s="36"/>
       <c r="CQ88" s="36"/>
@@ -21413,6 +21532,7 @@
       <c r="CZ88" s="36"/>
       <c r="DA88" s="36"/>
       <c r="DB88" s="36"/>
+      <c r="DC88" s="36"/>
     </row>
     <row r="89" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
@@ -21423,142 +21543,142 @@
       <c r="CZ89" s="41"/>
       <c r="DA89" s="41"/>
       <c r="DB89" s="41"/>
+      <c r="DC89" s="41"/>
     </row>
     <row r="90" spans="1:152" x14ac:dyDescent="0.2">
-      <c r="CX90" s="41"/>
-      <c r="CY90" s="41"/>
       <c r="CZ90" s="41"/>
       <c r="DA90" s="41"/>
       <c r="DB90" s="41"/>
+      <c r="DC90" s="41"/>
     </row>
     <row r="91" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
-      <c r="B91" s="44" t="s">
+      <c r="B91" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C91" s="45"/>
-      <c r="D91" s="45"/>
-      <c r="E91" s="45"/>
-      <c r="F91" s="44" t="s">
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="44" t="s">
+      <c r="G91" s="44"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="44"/>
+      <c r="J91" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K91" s="45"/>
-      <c r="L91" s="45"/>
-      <c r="M91" s="45"/>
-      <c r="N91" s="44" t="s">
+      <c r="K91" s="44"/>
+      <c r="L91" s="44"/>
+      <c r="M91" s="44"/>
+      <c r="N91" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="O91" s="45"/>
-      <c r="P91" s="45"/>
-      <c r="Q91" s="45"/>
-      <c r="R91" s="44" t="s">
+      <c r="O91" s="44"/>
+      <c r="P91" s="44"/>
+      <c r="Q91" s="44"/>
+      <c r="R91" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="S91" s="45"/>
-      <c r="T91" s="45"/>
-      <c r="U91" s="45"/>
-      <c r="V91" s="44" t="s">
+      <c r="S91" s="44"/>
+      <c r="T91" s="44"/>
+      <c r="U91" s="44"/>
+      <c r="V91" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="W91" s="45"/>
-      <c r="X91" s="45"/>
-      <c r="Y91" s="45"/>
-      <c r="Z91" s="44" t="s">
+      <c r="W91" s="44"/>
+      <c r="X91" s="44"/>
+      <c r="Y91" s="44"/>
+      <c r="Z91" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="AA91" s="45"/>
-      <c r="AB91" s="45"/>
-      <c r="AC91" s="45"/>
-      <c r="AD91" s="44" t="s">
+      <c r="AA91" s="44"/>
+      <c r="AB91" s="44"/>
+      <c r="AC91" s="44"/>
+      <c r="AD91" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="AE91" s="45"/>
-      <c r="AF91" s="45"/>
-      <c r="AG91" s="45"/>
-      <c r="AH91" s="44" t="s">
+      <c r="AE91" s="44"/>
+      <c r="AF91" s="44"/>
+      <c r="AG91" s="44"/>
+      <c r="AH91" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="AI91" s="45"/>
-      <c r="AJ91" s="45"/>
-      <c r="AK91" s="45"/>
-      <c r="AL91" s="44" t="s">
+      <c r="AI91" s="44"/>
+      <c r="AJ91" s="44"/>
+      <c r="AK91" s="44"/>
+      <c r="AL91" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="AM91" s="45"/>
-      <c r="AN91" s="45"/>
-      <c r="AO91" s="45"/>
-      <c r="AP91" s="44" t="s">
+      <c r="AM91" s="44"/>
+      <c r="AN91" s="44"/>
+      <c r="AO91" s="44"/>
+      <c r="AP91" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="AQ91" s="45"/>
-      <c r="AR91" s="45"/>
-      <c r="AS91" s="45"/>
-      <c r="AT91" s="44" t="s">
+      <c r="AQ91" s="44"/>
+      <c r="AR91" s="44"/>
+      <c r="AS91" s="44"/>
+      <c r="AT91" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="AU91" s="45"/>
-      <c r="AV91" s="45"/>
-      <c r="AW91" s="45"/>
-      <c r="AX91" s="44" t="s">
+      <c r="AU91" s="44"/>
+      <c r="AV91" s="44"/>
+      <c r="AW91" s="44"/>
+      <c r="AX91" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="AY91" s="45"/>
-      <c r="AZ91" s="45"/>
-      <c r="BA91" s="45"/>
-      <c r="BB91" s="44" t="s">
+      <c r="AY91" s="44"/>
+      <c r="AZ91" s="44"/>
+      <c r="BA91" s="44"/>
+      <c r="BB91" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="BC91" s="45"/>
-      <c r="BD91" s="45"/>
-      <c r="BE91" s="45"/>
-      <c r="BF91" s="44" t="s">
+      <c r="BC91" s="44"/>
+      <c r="BD91" s="44"/>
+      <c r="BE91" s="44"/>
+      <c r="BF91" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="BG91" s="45"/>
-      <c r="BH91" s="45"/>
-      <c r="BI91" s="45"/>
-      <c r="BJ91" s="44" t="s">
+      <c r="BG91" s="44"/>
+      <c r="BH91" s="44"/>
+      <c r="BI91" s="44"/>
+      <c r="BJ91" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="BK91" s="45"/>
-      <c r="BL91" s="45"/>
-      <c r="BM91" s="45"/>
-      <c r="BN91" s="44" t="s">
+      <c r="BK91" s="44"/>
+      <c r="BL91" s="44"/>
+      <c r="BM91" s="44"/>
+      <c r="BN91" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="BO91" s="45"/>
-      <c r="BP91" s="45"/>
-      <c r="BQ91" s="45"/>
-      <c r="BR91" s="44" t="s">
+      <c r="BO91" s="44"/>
+      <c r="BP91" s="44"/>
+      <c r="BQ91" s="44"/>
+      <c r="BR91" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="BS91" s="45"/>
-      <c r="BT91" s="45"/>
-      <c r="BU91" s="45"/>
-      <c r="BV91" s="44" t="s">
+      <c r="BS91" s="44"/>
+      <c r="BT91" s="44"/>
+      <c r="BU91" s="44"/>
+      <c r="BV91" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="BW91" s="45"/>
-      <c r="BX91" s="45"/>
-      <c r="BY91" s="45"/>
-      <c r="BZ91" s="44" t="s">
+      <c r="BW91" s="44"/>
+      <c r="BX91" s="44"/>
+      <c r="BY91" s="44"/>
+      <c r="BZ91" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="CA91" s="45"/>
-      <c r="CB91" s="45"/>
-      <c r="CC91" s="45"/>
-      <c r="CD91" s="44" t="s">
+      <c r="CA91" s="44"/>
+      <c r="CB91" s="44"/>
+      <c r="CC91" s="44"/>
+      <c r="CD91" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="CE91" s="44"/>
-      <c r="CF91" s="44"/>
-      <c r="CG91" s="44"/>
+      <c r="CE91" s="45"/>
+      <c r="CF91" s="45"/>
+      <c r="CG91" s="45"/>
       <c r="CH91" s="26" t="s">
         <v>71</v>
       </c>
@@ -21584,12 +21704,13 @@
       <c r="CV91" s="28"/>
       <c r="CW91" s="28"/>
       <c r="CX91" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="CY91" s="42"/>
+        <v>75</v>
+      </c>
+      <c r="CY91" s="28"/>
       <c r="CZ91" s="42"/>
       <c r="DA91" s="42"/>
       <c r="DB91" s="42"/>
+      <c r="DC91" s="42"/>
     </row>
     <row r="92" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
@@ -21898,17 +22019,20 @@
       <c r="CX92" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="CY92" s="43"/>
+      <c r="CY92" s="34" t="s">
+        <v>7</v>
+      </c>
       <c r="CZ92" s="43"/>
       <c r="DA92" s="43"/>
       <c r="DB92" s="43"/>
+      <c r="DC92" s="43"/>
     </row>
     <row r="93" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7"/>
-      <c r="CY93" s="41"/>
       <c r="CZ93" s="41"/>
       <c r="DA93" s="41"/>
       <c r="DB93" s="41"/>
+      <c r="DC93" s="41"/>
     </row>
     <row r="94" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
@@ -22215,13 +22339,15 @@
         <v>-8.6188538314515739</v>
       </c>
       <c r="CX94" s="35">
-        <v>-6.0122133080354132</v>
-      </c>
-      <c r="CY94" s="37"/>
+        <v>-5.2697387648457408</v>
+      </c>
+      <c r="CY94" s="35">
+        <v>-2.1334839886199006</v>
+      </c>
       <c r="CZ94" s="37"/>
       <c r="DA94" s="37"/>
       <c r="DB94" s="37"/>
-      <c r="DC94" s="9"/>
+      <c r="DC94" s="37"/>
       <c r="DD94" s="9"/>
       <c r="DE94" s="9"/>
       <c r="DF94" s="9"/>
@@ -22568,13 +22694,15 @@
         <v>-2.5352571270074833</v>
       </c>
       <c r="CX95" s="35">
-        <v>-45.438739241173266</v>
-      </c>
-      <c r="CY95" s="37"/>
+        <v>-44.792557070493189</v>
+      </c>
+      <c r="CY95" s="35">
+        <v>-3.7747516225321078</v>
+      </c>
       <c r="CZ95" s="37"/>
       <c r="DA95" s="37"/>
       <c r="DB95" s="37"/>
-      <c r="DC95" s="9"/>
+      <c r="DC95" s="37"/>
       <c r="DD95" s="9"/>
       <c r="DE95" s="9"/>
       <c r="DF95" s="9"/>
@@ -22921,13 +23049,15 @@
         <v>4.2120389819592816</v>
       </c>
       <c r="CX96" s="35">
-        <v>-10.056017422967713</v>
-      </c>
-      <c r="CY96" s="37"/>
+        <v>-6.5556182251260253</v>
+      </c>
+      <c r="CY96" s="35">
+        <v>-37.124590368365354</v>
+      </c>
       <c r="CZ96" s="37"/>
       <c r="DA96" s="37"/>
       <c r="DB96" s="37"/>
-      <c r="DC96" s="9"/>
+      <c r="DC96" s="37"/>
       <c r="DD96" s="9"/>
       <c r="DE96" s="9"/>
       <c r="DF96" s="9"/>
@@ -23274,13 +23404,15 @@
         <v>17.491086625573644</v>
       </c>
       <c r="CX97" s="35">
-        <v>10.273904002824878</v>
-      </c>
-      <c r="CY97" s="37"/>
+        <v>10.454332759040639</v>
+      </c>
+      <c r="CY97" s="35">
+        <v>19.032750593583515</v>
+      </c>
       <c r="CZ97" s="37"/>
       <c r="DA97" s="37"/>
       <c r="DB97" s="37"/>
-      <c r="DC97" s="9"/>
+      <c r="DC97" s="37"/>
       <c r="DD97" s="9"/>
       <c r="DE97" s="9"/>
       <c r="DF97" s="9"/>
@@ -23627,13 +23759,15 @@
         <v>-9.6098608166205111</v>
       </c>
       <c r="CX98" s="35">
-        <v>-5.7652789940374873</v>
-      </c>
-      <c r="CY98" s="37"/>
+        <v>-5.0544489593120261</v>
+      </c>
+      <c r="CY98" s="35">
+        <v>-25.506530321315452</v>
+      </c>
       <c r="CZ98" s="37"/>
       <c r="DA98" s="37"/>
       <c r="DB98" s="37"/>
-      <c r="DC98" s="9"/>
+      <c r="DC98" s="37"/>
       <c r="DD98" s="9"/>
       <c r="DE98" s="9"/>
       <c r="DF98" s="9"/>
@@ -23980,13 +24114,15 @@
         <v>-0.80974295827819276</v>
       </c>
       <c r="CX99" s="35">
-        <v>5.1268865092263667</v>
-      </c>
-      <c r="CY99" s="37"/>
+        <v>5.8948572595486866</v>
+      </c>
+      <c r="CY99" s="35">
+        <v>20.852124271172357</v>
+      </c>
       <c r="CZ99" s="37"/>
       <c r="DA99" s="37"/>
       <c r="DB99" s="37"/>
-      <c r="DC99" s="9"/>
+      <c r="DC99" s="37"/>
       <c r="DD99" s="9"/>
       <c r="DE99" s="9"/>
       <c r="DF99" s="9"/>
@@ -24333,13 +24469,15 @@
         <v>-16.262585892117926</v>
       </c>
       <c r="CX100" s="35">
-        <v>-2.549348731064228</v>
-      </c>
-      <c r="CY100" s="37"/>
+        <v>-2.2644455058806585</v>
+      </c>
+      <c r="CY100" s="35">
+        <v>4.894044809636739</v>
+      </c>
       <c r="CZ100" s="37"/>
       <c r="DA100" s="37"/>
       <c r="DB100" s="37"/>
-      <c r="DC100" s="9"/>
+      <c r="DC100" s="37"/>
       <c r="DD100" s="9"/>
       <c r="DE100" s="9"/>
       <c r="DF100" s="9"/>
@@ -24686,13 +24824,15 @@
         <v>-15.881585527664527</v>
       </c>
       <c r="CX101" s="35">
-        <v>-12.45950574111815</v>
-      </c>
-      <c r="CY101" s="37"/>
+        <v>-12.244320939823879</v>
+      </c>
+      <c r="CY101" s="35">
+        <v>5.2972936847271797</v>
+      </c>
       <c r="CZ101" s="37"/>
       <c r="DA101" s="37"/>
       <c r="DB101" s="37"/>
-      <c r="DC101" s="9"/>
+      <c r="DC101" s="37"/>
       <c r="DD101" s="9"/>
       <c r="DE101" s="9"/>
       <c r="DF101" s="9"/>
@@ -25039,13 +25179,15 @@
         <v>-6.6141807037474365</v>
       </c>
       <c r="CX102" s="35">
-        <v>3.3864776426430154</v>
-      </c>
-      <c r="CY102" s="37"/>
+        <v>3.1054872753199021</v>
+      </c>
+      <c r="CY102" s="35">
+        <v>18.687475144776172</v>
+      </c>
       <c r="CZ102" s="37"/>
       <c r="DA102" s="37"/>
       <c r="DB102" s="37"/>
-      <c r="DC102" s="9"/>
+      <c r="DC102" s="37"/>
       <c r="DD102" s="9"/>
       <c r="DE102" s="9"/>
       <c r="DF102" s="9"/>
@@ -25392,13 +25534,15 @@
         <v>11.300172405380977</v>
       </c>
       <c r="CX103" s="35">
-        <v>36.228325049430111</v>
-      </c>
-      <c r="CY103" s="37"/>
+        <v>38.177317655870922</v>
+      </c>
+      <c r="CY103" s="35">
+        <v>17.164915240631217</v>
+      </c>
       <c r="CZ103" s="37"/>
       <c r="DA103" s="37"/>
       <c r="DB103" s="37"/>
-      <c r="DC103" s="9"/>
+      <c r="DC103" s="37"/>
       <c r="DD103" s="9"/>
       <c r="DE103" s="9"/>
       <c r="DF103" s="9"/>
@@ -25745,13 +25889,15 @@
         <v>-14.065456488146097</v>
       </c>
       <c r="CX104" s="35">
-        <v>1.1766397538862208</v>
-      </c>
-      <c r="CY104" s="37"/>
+        <v>1.8346163598701253</v>
+      </c>
+      <c r="CY104" s="35">
+        <v>-5.2227092391413521</v>
+      </c>
       <c r="CZ104" s="37"/>
       <c r="DA104" s="37"/>
       <c r="DB104" s="37"/>
-      <c r="DC104" s="9"/>
+      <c r="DC104" s="37"/>
       <c r="DD104" s="9"/>
       <c r="DE104" s="9"/>
       <c r="DF104" s="9"/>
@@ -26098,13 +26244,15 @@
         <v>11.56369868126292</v>
       </c>
       <c r="CX105" s="35">
-        <v>5.7926982564326011</v>
-      </c>
-      <c r="CY105" s="37"/>
+        <v>7.2255373689841207</v>
+      </c>
+      <c r="CY105" s="35">
+        <v>-1.1683954785240331</v>
+      </c>
       <c r="CZ105" s="37"/>
       <c r="DA105" s="37"/>
       <c r="DB105" s="37"/>
-      <c r="DC105" s="9"/>
+      <c r="DC105" s="37"/>
       <c r="DD105" s="9"/>
       <c r="DE105" s="9"/>
       <c r="DF105" s="9"/>
@@ -26451,13 +26599,15 @@
         <v>22.91512402902876</v>
       </c>
       <c r="CX106" s="35">
-        <v>116.89493707821339</v>
-      </c>
-      <c r="CY106" s="37"/>
+        <v>121.26677943088819</v>
+      </c>
+      <c r="CY106" s="35">
+        <v>38.373907735107991</v>
+      </c>
       <c r="CZ106" s="37"/>
       <c r="DA106" s="37"/>
       <c r="DB106" s="37"/>
-      <c r="DC106" s="9"/>
+      <c r="DC106" s="37"/>
       <c r="DD106" s="9"/>
       <c r="DE106" s="9"/>
       <c r="DF106" s="9"/>
@@ -26804,13 +26954,15 @@
         <v>16.69503261506695</v>
       </c>
       <c r="CX107" s="35">
-        <v>10.094396166108368</v>
-      </c>
-      <c r="CY107" s="37"/>
+        <v>11.259319649436648</v>
+      </c>
+      <c r="CY107" s="35">
+        <v>16.216414783943421</v>
+      </c>
       <c r="CZ107" s="37"/>
       <c r="DA107" s="37"/>
       <c r="DB107" s="37"/>
-      <c r="DC107" s="9"/>
+      <c r="DC107" s="37"/>
       <c r="DD107" s="9"/>
       <c r="DE107" s="9"/>
       <c r="DF107" s="9"/>
@@ -27157,13 +27309,15 @@
         <v>-0.64309506607362721</v>
       </c>
       <c r="CX108" s="35">
-        <v>-0.87242542891191022</v>
-      </c>
-      <c r="CY108" s="37"/>
+        <v>-0.39678746911674523</v>
+      </c>
+      <c r="CY108" s="35">
+        <v>-27.176017044275085</v>
+      </c>
       <c r="CZ108" s="37"/>
       <c r="DA108" s="37"/>
       <c r="DB108" s="37"/>
-      <c r="DC108" s="9"/>
+      <c r="DC108" s="37"/>
       <c r="DD108" s="9"/>
       <c r="DE108" s="9"/>
       <c r="DF108" s="9"/>
@@ -27510,13 +27664,15 @@
         <v>-2.2845016140855421</v>
       </c>
       <c r="CX109" s="35">
-        <v>-4.2654101717939881</v>
-      </c>
-      <c r="CY109" s="37"/>
+        <v>-3.7490023670081314</v>
+      </c>
+      <c r="CY109" s="35">
+        <v>-23.057219512765016</v>
+      </c>
       <c r="CZ109" s="37"/>
       <c r="DA109" s="37"/>
       <c r="DB109" s="37"/>
-      <c r="DC109" s="9"/>
+      <c r="DC109" s="37"/>
       <c r="DD109" s="9"/>
       <c r="DE109" s="9"/>
       <c r="DF109" s="9"/>
@@ -27863,13 +28019,15 @@
         <v>-95.338979391788129</v>
       </c>
       <c r="CX110" s="35">
-        <v>-35.799916910848921</v>
-      </c>
-      <c r="CY110" s="37"/>
+        <v>-34.171924767885358</v>
+      </c>
+      <c r="CY110" s="35">
+        <v>105.77755289126509</v>
+      </c>
       <c r="CZ110" s="37"/>
       <c r="DA110" s="37"/>
       <c r="DB110" s="37"/>
-      <c r="DC110" s="9"/>
+      <c r="DC110" s="37"/>
       <c r="DD110" s="9"/>
       <c r="DE110" s="9"/>
       <c r="DF110" s="9"/>
@@ -28218,11 +28376,13 @@
       <c r="CX111" s="35">
         <v>-23.285139844241769</v>
       </c>
-      <c r="CY111" s="37"/>
+      <c r="CY111" s="35">
+        <v>32.032990076700059</v>
+      </c>
       <c r="CZ111" s="37"/>
       <c r="DA111" s="37"/>
       <c r="DB111" s="37"/>
-      <c r="DC111" s="9"/>
+      <c r="DC111" s="37"/>
       <c r="DD111" s="9"/>
       <c r="DE111" s="9"/>
       <c r="DF111" s="9"/>
@@ -28569,13 +28729,15 @@
         <v>-40.250147148520597</v>
       </c>
       <c r="CX112" s="35">
-        <v>227.33024838218421</v>
-      </c>
-      <c r="CY112" s="37"/>
+        <v>227.13286203798987</v>
+      </c>
+      <c r="CY112" s="35">
+        <v>-79.91823162894498</v>
+      </c>
       <c r="CZ112" s="37"/>
       <c r="DA112" s="37"/>
       <c r="DB112" s="37"/>
-      <c r="DC112" s="9"/>
+      <c r="DC112" s="37"/>
       <c r="DD112" s="9"/>
       <c r="DE112" s="9"/>
       <c r="DF112" s="9"/>
@@ -28922,13 +29084,15 @@
         <v>5.4181405590148444</v>
       </c>
       <c r="CX113" s="35">
-        <v>2.2515013967214799</v>
-      </c>
-      <c r="CY113" s="37"/>
+        <v>1.9317193183797485</v>
+      </c>
+      <c r="CY113" s="35">
+        <v>20.83850816725419</v>
+      </c>
       <c r="CZ113" s="37"/>
       <c r="DA113" s="37"/>
       <c r="DB113" s="37"/>
-      <c r="DC113" s="9"/>
+      <c r="DC113" s="37"/>
       <c r="DD113" s="9"/>
       <c r="DE113" s="9"/>
       <c r="DF113" s="9"/>
@@ -29275,13 +29439,15 @@
         <v>41.841228876531858</v>
       </c>
       <c r="CX114" s="35">
-        <v>43.311590129847843</v>
-      </c>
-      <c r="CY114" s="37"/>
+        <v>46.377201745584159</v>
+      </c>
+      <c r="CY114" s="35">
+        <v>35.868928375830535</v>
+      </c>
       <c r="CZ114" s="37"/>
       <c r="DA114" s="37"/>
       <c r="DB114" s="37"/>
-      <c r="DC114" s="9"/>
+      <c r="DC114" s="37"/>
       <c r="DD114" s="9"/>
       <c r="DE114" s="9"/>
       <c r="DF114" s="9"/>
@@ -29628,13 +29794,15 @@
         <v>-15.135173015990489</v>
       </c>
       <c r="CX115" s="35">
-        <v>-12.057640636296227</v>
-      </c>
-      <c r="CY115" s="37"/>
+        <v>-10.58268039732468</v>
+      </c>
+      <c r="CY115" s="35">
+        <v>47.281873936221615</v>
+      </c>
       <c r="CZ115" s="37"/>
       <c r="DA115" s="37"/>
       <c r="DB115" s="37"/>
-      <c r="DC115" s="9"/>
+      <c r="DC115" s="37"/>
       <c r="DD115" s="9"/>
       <c r="DE115" s="9"/>
       <c r="DF115" s="9"/>
@@ -29981,13 +30149,15 @@
         <v>10.494187956421385</v>
       </c>
       <c r="CX116" s="35">
-        <v>7.0657804886849362</v>
-      </c>
-      <c r="CY116" s="37"/>
+        <v>6.8871416409457993</v>
+      </c>
+      <c r="CY116" s="35">
+        <v>20.198850204637964</v>
+      </c>
       <c r="CZ116" s="37"/>
       <c r="DA116" s="37"/>
       <c r="DB116" s="37"/>
-      <c r="DC116" s="9"/>
+      <c r="DC116" s="37"/>
       <c r="DD116" s="9"/>
       <c r="DE116" s="9"/>
       <c r="DF116" s="9"/>
@@ -30334,13 +30504,15 @@
         <v>-8.1584786434592047</v>
       </c>
       <c r="CX117" s="35">
-        <v>-8.6410182833326985</v>
-      </c>
-      <c r="CY117" s="37"/>
+        <v>-11.519901161745139</v>
+      </c>
+      <c r="CY117" s="35">
+        <v>-0.40956189900954598</v>
+      </c>
       <c r="CZ117" s="37"/>
       <c r="DA117" s="37"/>
       <c r="DB117" s="37"/>
-      <c r="DC117" s="9"/>
+      <c r="DC117" s="37"/>
       <c r="DD117" s="9"/>
       <c r="DE117" s="9"/>
       <c r="DF117" s="9"/>
@@ -30484,11 +30656,11 @@
       <c r="CV118" s="31"/>
       <c r="CW118" s="31"/>
       <c r="CX118" s="31"/>
-      <c r="CY118" s="39"/>
+      <c r="CY118" s="31"/>
       <c r="CZ118" s="39"/>
       <c r="DA118" s="39"/>
       <c r="DB118" s="39"/>
-      <c r="DC118" s="9"/>
+      <c r="DC118" s="39"/>
       <c r="DD118" s="9"/>
       <c r="DE118" s="9"/>
       <c r="DF118" s="9"/>
@@ -30835,13 +31007,15 @@
         <v>1.2035193095950092</v>
       </c>
       <c r="CX119" s="38">
-        <v>4.8313580178237743</v>
-      </c>
-      <c r="CY119" s="40"/>
+        <v>5.4328466261428332</v>
+      </c>
+      <c r="CY119" s="38">
+        <v>-7.9312810986711924</v>
+      </c>
       <c r="CZ119" s="40"/>
       <c r="DA119" s="40"/>
       <c r="DB119" s="40"/>
-      <c r="DC119" s="9"/>
+      <c r="DC119" s="40"/>
       <c r="DD119" s="9"/>
       <c r="DE119" s="9"/>
       <c r="DF119" s="9"/>
@@ -30986,19 +31160,20 @@
       <c r="CV120" s="33"/>
       <c r="CW120" s="33"/>
       <c r="CX120" s="33"/>
-      <c r="CY120" s="43"/>
+      <c r="CY120" s="33"/>
       <c r="CZ120" s="43"/>
       <c r="DA120" s="43"/>
       <c r="DB120" s="43"/>
+      <c r="DC120" s="43"/>
     </row>
     <row r="121" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CY121" s="41"/>
       <c r="CZ121" s="41"/>
       <c r="DA121" s="41"/>
       <c r="DB121" s="41"/>
+      <c r="DC121" s="41"/>
     </row>
     <row r="122" spans="1:147" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
@@ -31105,11 +31280,11 @@
       <c r="CV122" s="31"/>
       <c r="CW122" s="31"/>
       <c r="CX122" s="31"/>
-      <c r="CY122" s="39"/>
+      <c r="CY122" s="31"/>
       <c r="CZ122" s="39"/>
       <c r="DA122" s="39"/>
       <c r="DB122" s="39"/>
-      <c r="DC122" s="9"/>
+      <c r="DC122" s="39"/>
       <c r="DD122" s="9"/>
       <c r="DE122" s="9"/>
       <c r="DF122" s="9"/>
@@ -31253,11 +31428,11 @@
       <c r="CV123" s="31"/>
       <c r="CW123" s="31"/>
       <c r="CX123" s="31"/>
-      <c r="CY123" s="39"/>
+      <c r="CY123" s="31"/>
       <c r="CZ123" s="39"/>
       <c r="DA123" s="39"/>
       <c r="DB123" s="39"/>
-      <c r="DC123" s="9"/>
+      <c r="DC123" s="39"/>
       <c r="DD123" s="9"/>
       <c r="DE123" s="9"/>
       <c r="DF123" s="9"/>
@@ -31303,196 +31478,196 @@
       <c r="A124" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="CY124" s="41"/>
       <c r="CZ124" s="41"/>
       <c r="DA124" s="41"/>
       <c r="DB124" s="41"/>
+      <c r="DC124" s="41"/>
     </row>
     <row r="125" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="CY125" s="41"/>
       <c r="CZ125" s="41"/>
       <c r="DA125" s="41"/>
       <c r="DB125" s="41"/>
+      <c r="DC125" s="41"/>
     </row>
     <row r="126" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="CY126" s="41"/>
+        <v>76</v>
+      </c>
       <c r="CZ126" s="41"/>
       <c r="DA126" s="41"/>
       <c r="DB126" s="41"/>
+      <c r="DC126" s="41"/>
     </row>
     <row r="127" spans="1:147" x14ac:dyDescent="0.2">
-      <c r="CY127" s="41"/>
       <c r="CZ127" s="41"/>
       <c r="DA127" s="41"/>
       <c r="DB127" s="41"/>
+      <c r="DC127" s="41"/>
     </row>
     <row r="128" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CY128" s="41"/>
       <c r="CZ128" s="41"/>
       <c r="DA128" s="41"/>
       <c r="DB128" s="41"/>
+      <c r="DC128" s="41"/>
     </row>
     <row r="129" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CY129" s="41"/>
+        <v>78</v>
+      </c>
       <c r="CZ129" s="41"/>
       <c r="DA129" s="41"/>
       <c r="DB129" s="41"/>
+      <c r="DC129" s="41"/>
     </row>
     <row r="130" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="CY130" s="41"/>
       <c r="CZ130" s="41"/>
       <c r="DA130" s="41"/>
       <c r="DB130" s="41"/>
+      <c r="DC130" s="41"/>
     </row>
     <row r="131" spans="1:147" x14ac:dyDescent="0.2">
-      <c r="CY131" s="41"/>
       <c r="CZ131" s="41"/>
       <c r="DA131" s="41"/>
       <c r="DB131" s="41"/>
+      <c r="DC131" s="41"/>
     </row>
     <row r="132" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
-      <c r="B132" s="44" t="s">
+      <c r="B132" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C132" s="45"/>
-      <c r="D132" s="45"/>
-      <c r="E132" s="45"/>
-      <c r="F132" s="44" t="s">
+      <c r="C132" s="44"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="44"/>
+      <c r="F132" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G132" s="45"/>
-      <c r="H132" s="45"/>
-      <c r="I132" s="45"/>
-      <c r="J132" s="44" t="s">
+      <c r="G132" s="44"/>
+      <c r="H132" s="44"/>
+      <c r="I132" s="44"/>
+      <c r="J132" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K132" s="45"/>
-      <c r="L132" s="45"/>
-      <c r="M132" s="45"/>
-      <c r="N132" s="44" t="s">
+      <c r="K132" s="44"/>
+      <c r="L132" s="44"/>
+      <c r="M132" s="44"/>
+      <c r="N132" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="O132" s="45"/>
-      <c r="P132" s="45"/>
-      <c r="Q132" s="45"/>
-      <c r="R132" s="44" t="s">
+      <c r="O132" s="44"/>
+      <c r="P132" s="44"/>
+      <c r="Q132" s="44"/>
+      <c r="R132" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="S132" s="45"/>
-      <c r="T132" s="45"/>
-      <c r="U132" s="45"/>
-      <c r="V132" s="44" t="s">
+      <c r="S132" s="44"/>
+      <c r="T132" s="44"/>
+      <c r="U132" s="44"/>
+      <c r="V132" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="W132" s="45"/>
-      <c r="X132" s="45"/>
-      <c r="Y132" s="45"/>
-      <c r="Z132" s="44" t="s">
+      <c r="W132" s="44"/>
+      <c r="X132" s="44"/>
+      <c r="Y132" s="44"/>
+      <c r="Z132" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="AA132" s="45"/>
-      <c r="AB132" s="45"/>
-      <c r="AC132" s="45"/>
-      <c r="AD132" s="44" t="s">
+      <c r="AA132" s="44"/>
+      <c r="AB132" s="44"/>
+      <c r="AC132" s="44"/>
+      <c r="AD132" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="AE132" s="45"/>
-      <c r="AF132" s="45"/>
-      <c r="AG132" s="45"/>
-      <c r="AH132" s="44" t="s">
+      <c r="AE132" s="44"/>
+      <c r="AF132" s="44"/>
+      <c r="AG132" s="44"/>
+      <c r="AH132" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="AI132" s="45"/>
-      <c r="AJ132" s="45"/>
-      <c r="AK132" s="45"/>
-      <c r="AL132" s="44" t="s">
+      <c r="AI132" s="44"/>
+      <c r="AJ132" s="44"/>
+      <c r="AK132" s="44"/>
+      <c r="AL132" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="AM132" s="45"/>
-      <c r="AN132" s="45"/>
-      <c r="AO132" s="45"/>
-      <c r="AP132" s="44" t="s">
+      <c r="AM132" s="44"/>
+      <c r="AN132" s="44"/>
+      <c r="AO132" s="44"/>
+      <c r="AP132" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="AQ132" s="45"/>
-      <c r="AR132" s="45"/>
-      <c r="AS132" s="45"/>
-      <c r="AT132" s="44" t="s">
+      <c r="AQ132" s="44"/>
+      <c r="AR132" s="44"/>
+      <c r="AS132" s="44"/>
+      <c r="AT132" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="AU132" s="45"/>
-      <c r="AV132" s="45"/>
-      <c r="AW132" s="45"/>
-      <c r="AX132" s="44" t="s">
+      <c r="AU132" s="44"/>
+      <c r="AV132" s="44"/>
+      <c r="AW132" s="44"/>
+      <c r="AX132" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="AY132" s="45"/>
-      <c r="AZ132" s="45"/>
-      <c r="BA132" s="45"/>
-      <c r="BB132" s="44" t="s">
+      <c r="AY132" s="44"/>
+      <c r="AZ132" s="44"/>
+      <c r="BA132" s="44"/>
+      <c r="BB132" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="BC132" s="45"/>
-      <c r="BD132" s="45"/>
-      <c r="BE132" s="45"/>
-      <c r="BF132" s="44" t="s">
+      <c r="BC132" s="44"/>
+      <c r="BD132" s="44"/>
+      <c r="BE132" s="44"/>
+      <c r="BF132" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="BG132" s="45"/>
-      <c r="BH132" s="45"/>
-      <c r="BI132" s="45"/>
-      <c r="BJ132" s="44" t="s">
+      <c r="BG132" s="44"/>
+      <c r="BH132" s="44"/>
+      <c r="BI132" s="44"/>
+      <c r="BJ132" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="BK132" s="45"/>
-      <c r="BL132" s="45"/>
-      <c r="BM132" s="45"/>
-      <c r="BN132" s="44" t="s">
+      <c r="BK132" s="44"/>
+      <c r="BL132" s="44"/>
+      <c r="BM132" s="44"/>
+      <c r="BN132" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="BO132" s="45"/>
-      <c r="BP132" s="45"/>
-      <c r="BQ132" s="45"/>
-      <c r="BR132" s="44" t="s">
+      <c r="BO132" s="44"/>
+      <c r="BP132" s="44"/>
+      <c r="BQ132" s="44"/>
+      <c r="BR132" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="BS132" s="45"/>
-      <c r="BT132" s="45"/>
-      <c r="BU132" s="45"/>
-      <c r="BV132" s="44" t="s">
+      <c r="BS132" s="44"/>
+      <c r="BT132" s="44"/>
+      <c r="BU132" s="44"/>
+      <c r="BV132" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="BW132" s="45"/>
-      <c r="BX132" s="45"/>
-      <c r="BY132" s="45"/>
-      <c r="BZ132" s="44" t="s">
+      <c r="BW132" s="44"/>
+      <c r="BX132" s="44"/>
+      <c r="BY132" s="44"/>
+      <c r="BZ132" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="CA132" s="45"/>
-      <c r="CB132" s="45"/>
-      <c r="CC132" s="45"/>
-      <c r="CD132" s="44" t="s">
+      <c r="CA132" s="44"/>
+      <c r="CB132" s="44"/>
+      <c r="CC132" s="44"/>
+      <c r="CD132" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="CE132" s="44"/>
-      <c r="CF132" s="44"/>
-      <c r="CG132" s="44"/>
+      <c r="CE132" s="45"/>
+      <c r="CF132" s="45"/>
+      <c r="CG132" s="45"/>
       <c r="CH132" s="26" t="s">
         <v>71</v>
       </c>
@@ -31518,12 +31693,13 @@
       <c r="CV132" s="28"/>
       <c r="CW132" s="28"/>
       <c r="CX132" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="CY132" s="42"/>
+        <v>75</v>
+      </c>
+      <c r="CY132" s="28"/>
       <c r="CZ132" s="42"/>
       <c r="DA132" s="42"/>
       <c r="DB132" s="42"/>
+      <c r="DC132" s="42"/>
     </row>
     <row r="133" spans="1:147" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
@@ -31832,17 +32008,20 @@
       <c r="CX133" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="CY133" s="43"/>
+      <c r="CY133" s="34" t="s">
+        <v>7</v>
+      </c>
       <c r="CZ133" s="43"/>
       <c r="DA133" s="43"/>
       <c r="DB133" s="43"/>
+      <c r="DC133" s="43"/>
     </row>
     <row r="134" spans="1:147" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
-      <c r="CY134" s="41"/>
       <c r="CZ134" s="41"/>
       <c r="DA134" s="41"/>
       <c r="DB134" s="41"/>
+      <c r="DC134" s="41"/>
     </row>
     <row r="135" spans="1:147" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
@@ -32149,13 +32328,15 @@
         <v>-9.2074653161846953</v>
       </c>
       <c r="CX135" s="35">
-        <v>-8.293875519041265</v>
-      </c>
-      <c r="CY135" s="37"/>
+        <v>-7.7549660140257117</v>
+      </c>
+      <c r="CY135" s="35">
+        <v>-2.3611502537768132</v>
+      </c>
       <c r="CZ135" s="37"/>
       <c r="DA135" s="37"/>
       <c r="DB135" s="37"/>
-      <c r="DC135" s="9"/>
+      <c r="DC135" s="37"/>
       <c r="DD135" s="9"/>
       <c r="DE135" s="9"/>
       <c r="DF135" s="9"/>
@@ -32502,13 +32683,15 @@
         <v>-7.0178251160777307</v>
       </c>
       <c r="CX136" s="35">
-        <v>-47.727151911273026</v>
-      </c>
-      <c r="CY136" s="37"/>
+        <v>-47.11662336626862</v>
+      </c>
+      <c r="CY136" s="35">
+        <v>-14.20276552018646</v>
+      </c>
       <c r="CZ136" s="37"/>
       <c r="DA136" s="37"/>
       <c r="DB136" s="37"/>
-      <c r="DC136" s="9"/>
+      <c r="DC136" s="37"/>
       <c r="DD136" s="9"/>
       <c r="DE136" s="9"/>
       <c r="DF136" s="9"/>
@@ -32855,13 +33038,15 @@
         <v>-0.5111894945355715</v>
       </c>
       <c r="CX137" s="35">
-        <v>-14.027891599757197</v>
-      </c>
-      <c r="CY137" s="37"/>
+        <v>-10.735210219269973</v>
+      </c>
+      <c r="CY137" s="35">
+        <v>-42.746925595161521</v>
+      </c>
       <c r="CZ137" s="37"/>
       <c r="DA137" s="37"/>
       <c r="DB137" s="37"/>
-      <c r="DC137" s="9"/>
+      <c r="DC137" s="37"/>
       <c r="DD137" s="9"/>
       <c r="DE137" s="9"/>
       <c r="DF137" s="9"/>
@@ -33208,13 +33393,15 @@
         <v>15.078692809835132</v>
       </c>
       <c r="CX138" s="35">
-        <v>2.6231952990704315</v>
-      </c>
-      <c r="CY138" s="37"/>
+        <v>2.5727450005502277</v>
+      </c>
+      <c r="CY138" s="35">
+        <v>2.9439860646244682</v>
+      </c>
       <c r="CZ138" s="37"/>
       <c r="DA138" s="37"/>
       <c r="DB138" s="37"/>
-      <c r="DC138" s="9"/>
+      <c r="DC138" s="37"/>
       <c r="DD138" s="9"/>
       <c r="DE138" s="9"/>
       <c r="DF138" s="9"/>
@@ -33561,13 +33748,15 @@
         <v>-12.765076251092168</v>
       </c>
       <c r="CX139" s="35">
-        <v>-10.044882586604373</v>
-      </c>
-      <c r="CY139" s="37"/>
+        <v>-9.4523796865207004</v>
+      </c>
+      <c r="CY139" s="35">
+        <v>-31.189354667544492</v>
+      </c>
       <c r="CZ139" s="37"/>
       <c r="DA139" s="37"/>
       <c r="DB139" s="37"/>
-      <c r="DC139" s="9"/>
+      <c r="DC139" s="37"/>
       <c r="DD139" s="9"/>
       <c r="DE139" s="9"/>
       <c r="DF139" s="9"/>
@@ -33914,13 +34103,15 @@
         <v>-4.9595381667371754</v>
       </c>
       <c r="CX140" s="35">
-        <v>0.46928561914332079</v>
-      </c>
-      <c r="CY140" s="37"/>
+        <v>1.1749480218201001</v>
+      </c>
+      <c r="CY140" s="35">
+        <v>6.5756420010293368</v>
+      </c>
       <c r="CZ140" s="37"/>
       <c r="DA140" s="37"/>
       <c r="DB140" s="37"/>
-      <c r="DC140" s="9"/>
+      <c r="DC140" s="37"/>
       <c r="DD140" s="9"/>
       <c r="DE140" s="9"/>
       <c r="DF140" s="9"/>
@@ -34267,13 +34458,15 @@
         <v>-14.858434191282882</v>
       </c>
       <c r="CX141" s="35">
-        <v>-3.3117867762819486</v>
-      </c>
-      <c r="CY141" s="37"/>
+        <v>-3.2557239754609952</v>
+      </c>
+      <c r="CY141" s="35">
+        <v>3.3447920545249303</v>
+      </c>
       <c r="CZ141" s="37"/>
       <c r="DA141" s="37"/>
       <c r="DB141" s="37"/>
-      <c r="DC141" s="9"/>
+      <c r="DC141" s="37"/>
       <c r="DD141" s="9"/>
       <c r="DE141" s="9"/>
       <c r="DF141" s="9"/>
@@ -34620,13 +34813,15 @@
         <v>-19.577366501743072</v>
       </c>
       <c r="CX142" s="35">
-        <v>-16.052589939628263</v>
-      </c>
-      <c r="CY142" s="37"/>
+        <v>-15.874166206633973</v>
+      </c>
+      <c r="CY142" s="35">
+        <v>-6.2056596404736837</v>
+      </c>
       <c r="CZ142" s="37"/>
       <c r="DA142" s="37"/>
       <c r="DB142" s="37"/>
-      <c r="DC142" s="9"/>
+      <c r="DC142" s="37"/>
       <c r="DD142" s="9"/>
       <c r="DE142" s="9"/>
       <c r="DF142" s="9"/>
@@ -34973,13 +35168,15 @@
         <v>-9.0759610173663674</v>
       </c>
       <c r="CX143" s="35">
-        <v>-2.1977582086133651</v>
-      </c>
-      <c r="CY143" s="37"/>
+        <v>-2.5530233862163811</v>
+      </c>
+      <c r="CY143" s="35">
+        <v>1.9529132733671304</v>
+      </c>
       <c r="CZ143" s="37"/>
       <c r="DA143" s="37"/>
       <c r="DB143" s="37"/>
-      <c r="DC143" s="9"/>
+      <c r="DC143" s="37"/>
       <c r="DD143" s="9"/>
       <c r="DE143" s="9"/>
       <c r="DF143" s="9"/>
@@ -35326,13 +35523,15 @@
         <v>5.0127994168731789</v>
       </c>
       <c r="CX144" s="35">
-        <v>26.162605397625654</v>
-      </c>
-      <c r="CY144" s="37"/>
+        <v>27.62394904200778</v>
+      </c>
+      <c r="CY144" s="35">
+        <v>4.1088010262646719</v>
+      </c>
       <c r="CZ144" s="37"/>
       <c r="DA144" s="37"/>
       <c r="DB144" s="37"/>
-      <c r="DC144" s="9"/>
+      <c r="DC144" s="37"/>
       <c r="DD144" s="9"/>
       <c r="DE144" s="9"/>
       <c r="DF144" s="9"/>
@@ -35679,13 +35878,15 @@
         <v>-16.423444567517578</v>
       </c>
       <c r="CX145" s="35">
-        <v>-2.7955741019194704</v>
-      </c>
-      <c r="CY145" s="37"/>
+        <v>-2.2282660325823826</v>
+      </c>
+      <c r="CY145" s="35">
+        <v>-15.567382608321552</v>
+      </c>
       <c r="CZ145" s="37"/>
       <c r="DA145" s="37"/>
       <c r="DB145" s="37"/>
-      <c r="DC145" s="9"/>
+      <c r="DC145" s="37"/>
       <c r="DD145" s="9"/>
       <c r="DE145" s="9"/>
       <c r="DF145" s="9"/>
@@ -36032,13 +36233,15 @@
         <v>6.567033343925516</v>
       </c>
       <c r="CX146" s="35">
-        <v>0.92667818402595969</v>
-      </c>
-      <c r="CY146" s="37"/>
+        <v>2.2380142407550636</v>
+      </c>
+      <c r="CY146" s="35">
+        <v>-12.11709213273727</v>
+      </c>
       <c r="CZ146" s="37"/>
       <c r="DA146" s="37"/>
       <c r="DB146" s="37"/>
-      <c r="DC146" s="9"/>
+      <c r="DC146" s="37"/>
       <c r="DD146" s="9"/>
       <c r="DE146" s="9"/>
       <c r="DF146" s="9"/>
@@ -36385,13 +36588,15 @@
         <v>16.268772853001948</v>
       </c>
       <c r="CX147" s="35">
-        <v>100.5171177051925</v>
-      </c>
-      <c r="CY147" s="37"/>
+        <v>103.88756581743596</v>
+      </c>
+      <c r="CY147" s="35">
+        <v>23.305812797290244</v>
+      </c>
       <c r="CZ147" s="37"/>
       <c r="DA147" s="37"/>
       <c r="DB147" s="37"/>
-      <c r="DC147" s="9"/>
+      <c r="DC147" s="37"/>
       <c r="DD147" s="9"/>
       <c r="DE147" s="9"/>
       <c r="DF147" s="9"/>
@@ -36738,13 +36943,15 @@
         <v>7.9087537470289533</v>
       </c>
       <c r="CX148" s="35">
-        <v>3.3709120089652487</v>
-      </c>
-      <c r="CY148" s="37"/>
+        <v>4.1920646241845105</v>
+      </c>
+      <c r="CY148" s="35">
+        <v>0.21260271197631653</v>
+      </c>
       <c r="CZ148" s="37"/>
       <c r="DA148" s="37"/>
       <c r="DB148" s="37"/>
-      <c r="DC148" s="9"/>
+      <c r="DC148" s="37"/>
       <c r="DD148" s="9"/>
       <c r="DE148" s="9"/>
       <c r="DF148" s="9"/>
@@ -37091,13 +37298,15 @@
         <v>-1.9792049678420085</v>
       </c>
       <c r="CX149" s="35">
-        <v>-5.6752651444801216</v>
-      </c>
-      <c r="CY149" s="37"/>
+        <v>-5.3072310174428452</v>
+      </c>
+      <c r="CY149" s="35">
+        <v>-32.158555127289588</v>
+      </c>
       <c r="CZ149" s="37"/>
       <c r="DA149" s="37"/>
       <c r="DB149" s="37"/>
-      <c r="DC149" s="9"/>
+      <c r="DC149" s="37"/>
       <c r="DD149" s="9"/>
       <c r="DE149" s="9"/>
       <c r="DF149" s="9"/>
@@ -37444,13 +37653,15 @@
         <v>-2.9913762069901821</v>
       </c>
       <c r="CX150" s="35">
-        <v>-7.9121091487441078</v>
-      </c>
-      <c r="CY150" s="37"/>
+        <v>-7.5171272183141866</v>
+      </c>
+      <c r="CY150" s="35">
+        <v>-28.444758375132054</v>
+      </c>
       <c r="CZ150" s="37"/>
       <c r="DA150" s="37"/>
       <c r="DB150" s="37"/>
-      <c r="DC150" s="9"/>
+      <c r="DC150" s="37"/>
       <c r="DD150" s="9"/>
       <c r="DE150" s="9"/>
       <c r="DF150" s="9"/>
@@ -37797,13 +38008,15 @@
         <v>-95.498890794272413</v>
       </c>
       <c r="CX151" s="35">
-        <v>-38.590922220739657</v>
-      </c>
-      <c r="CY151" s="37"/>
+        <v>-37.033704670219556</v>
+      </c>
+      <c r="CY151" s="35">
+        <v>84.855061359765557</v>
+      </c>
       <c r="CZ151" s="37"/>
       <c r="DA151" s="37"/>
       <c r="DB151" s="37"/>
-      <c r="DC151" s="9"/>
+      <c r="DC151" s="37"/>
       <c r="DD151" s="9"/>
       <c r="DE151" s="9"/>
       <c r="DF151" s="9"/>
@@ -38152,11 +38365,13 @@
       <c r="CX152" s="35">
         <v>-26.062410191848969</v>
       </c>
-      <c r="CY152" s="37"/>
+      <c r="CY152" s="35">
+        <v>18.551917287546786</v>
+      </c>
       <c r="CZ152" s="37"/>
       <c r="DA152" s="37"/>
       <c r="DB152" s="37"/>
-      <c r="DC152" s="9"/>
+      <c r="DC152" s="37"/>
       <c r="DD152" s="9"/>
       <c r="DE152" s="9"/>
       <c r="DF152" s="9"/>
@@ -38503,13 +38718,15 @@
         <v>-42.06050609640851</v>
       </c>
       <c r="CX153" s="35">
-        <v>179.73334310635613</v>
-      </c>
-      <c r="CY153" s="37"/>
+        <v>179.41885663135986</v>
+      </c>
+      <c r="CY153" s="35">
+        <v>-81.947723541494071</v>
+      </c>
       <c r="CZ153" s="37"/>
       <c r="DA153" s="37"/>
       <c r="DB153" s="37"/>
-      <c r="DC153" s="9"/>
+      <c r="DC153" s="37"/>
       <c r="DD153" s="9"/>
       <c r="DE153" s="9"/>
       <c r="DF153" s="9"/>
@@ -38856,13 +39073,15 @@
         <v>0.94483933697429734</v>
       </c>
       <c r="CX154" s="35">
-        <v>-1.8420985574280735E-2</v>
-      </c>
-      <c r="CY154" s="37"/>
+        <v>-0.50725748353418965</v>
+      </c>
+      <c r="CY154" s="35">
+        <v>14.847305710779324</v>
+      </c>
       <c r="CZ154" s="37"/>
       <c r="DA154" s="37"/>
       <c r="DB154" s="37"/>
-      <c r="DC154" s="9"/>
+      <c r="DC154" s="37"/>
       <c r="DD154" s="9"/>
       <c r="DE154" s="9"/>
       <c r="DF154" s="9"/>
@@ -39209,13 +39428,15 @@
         <v>37.301213730238345</v>
       </c>
       <c r="CX155" s="35">
-        <v>39.531958982577578</v>
-      </c>
-      <c r="CY155" s="37"/>
+        <v>42.490929489682969</v>
+      </c>
+      <c r="CY155" s="35">
+        <v>23.006730468444061</v>
+      </c>
       <c r="CZ155" s="37"/>
       <c r="DA155" s="37"/>
       <c r="DB155" s="37"/>
-      <c r="DC155" s="9"/>
+      <c r="DC155" s="37"/>
       <c r="DD155" s="9"/>
       <c r="DE155" s="9"/>
       <c r="DF155" s="9"/>
@@ -39562,13 +39783,15 @@
         <v>-10.764893822149276</v>
       </c>
       <c r="CX156" s="35">
-        <v>-13.277401770876835</v>
-      </c>
-      <c r="CY156" s="37"/>
+        <v>-11.80350567203358</v>
+      </c>
+      <c r="CY156" s="35">
+        <v>38.679309503554805</v>
+      </c>
       <c r="CZ156" s="37"/>
       <c r="DA156" s="37"/>
       <c r="DB156" s="37"/>
-      <c r="DC156" s="9"/>
+      <c r="DC156" s="37"/>
       <c r="DD156" s="9"/>
       <c r="DE156" s="9"/>
       <c r="DF156" s="9"/>
@@ -39915,13 +40138,15 @@
         <v>5.5642397899447076</v>
       </c>
       <c r="CX157" s="35">
-        <v>4.4603768142738858</v>
-      </c>
-      <c r="CY157" s="37"/>
+        <v>3.8822718534412957</v>
+      </c>
+      <c r="CY157" s="35">
+        <v>10.614288758698407</v>
+      </c>
       <c r="CZ157" s="37"/>
       <c r="DA157" s="37"/>
       <c r="DB157" s="37"/>
-      <c r="DC157" s="9"/>
+      <c r="DC157" s="37"/>
       <c r="DD157" s="9"/>
       <c r="DE157" s="9"/>
       <c r="DF157" s="9"/>
@@ -40268,13 +40493,15 @@
         <v>-11.239564138509579</v>
       </c>
       <c r="CX158" s="35">
-        <v>-8.7504163830281101</v>
-      </c>
-      <c r="CY158" s="37"/>
+        <v>-11.796100103530904</v>
+      </c>
+      <c r="CY158" s="35">
+        <v>-3.0711210990180717</v>
+      </c>
       <c r="CZ158" s="37"/>
       <c r="DA158" s="37"/>
       <c r="DB158" s="37"/>
-      <c r="DC158" s="9"/>
+      <c r="DC158" s="37"/>
       <c r="DD158" s="9"/>
       <c r="DE158" s="9"/>
       <c r="DF158" s="9"/>
@@ -40418,11 +40645,11 @@
       <c r="CV159" s="31"/>
       <c r="CW159" s="31"/>
       <c r="CX159" s="31"/>
-      <c r="CY159" s="39"/>
+      <c r="CY159" s="31"/>
       <c r="CZ159" s="39"/>
       <c r="DA159" s="39"/>
       <c r="DB159" s="39"/>
-      <c r="DC159" s="9"/>
+      <c r="DC159" s="39"/>
       <c r="DD159" s="9"/>
       <c r="DE159" s="9"/>
       <c r="DF159" s="9"/>
@@ -40769,13 +40996,15 @@
         <v>-1.6819530960023883</v>
       </c>
       <c r="CX160" s="38">
-        <v>-0.11522949363182988</v>
-      </c>
-      <c r="CY160" s="40"/>
+        <v>0.28621894574460782</v>
+      </c>
+      <c r="CY160" s="38">
+        <v>-13.606080707756931</v>
+      </c>
       <c r="CZ160" s="40"/>
       <c r="DA160" s="40"/>
       <c r="DB160" s="40"/>
-      <c r="DC160" s="9"/>
+      <c r="DC160" s="40"/>
       <c r="DD160" s="9"/>
       <c r="DE160" s="9"/>
       <c r="DF160" s="9"/>
@@ -40920,19 +41149,20 @@
       <c r="CV161" s="33"/>
       <c r="CW161" s="33"/>
       <c r="CX161" s="33"/>
-      <c r="CY161" s="43"/>
+      <c r="CY161" s="33"/>
       <c r="CZ161" s="43"/>
       <c r="DA161" s="43"/>
       <c r="DB161" s="43"/>
+      <c r="DC161" s="43"/>
     </row>
     <row r="162" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="CY162" s="41"/>
       <c r="CZ162" s="41"/>
       <c r="DA162" s="41"/>
       <c r="DB162" s="41"/>
+      <c r="DC162" s="41"/>
     </row>
     <row r="163" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
@@ -41039,11 +41269,11 @@
       <c r="CV163" s="31"/>
       <c r="CW163" s="31"/>
       <c r="CX163" s="39"/>
-      <c r="CY163" s="39"/>
+      <c r="CY163" s="31"/>
       <c r="CZ163" s="39"/>
       <c r="DA163" s="39"/>
       <c r="DB163" s="39"/>
-      <c r="DC163" s="9"/>
+      <c r="DC163" s="39"/>
       <c r="DD163" s="9"/>
       <c r="DE163" s="9"/>
       <c r="DF163" s="9"/>
@@ -41191,7 +41421,7 @@
       <c r="CZ164" s="31"/>
       <c r="DA164" s="31"/>
       <c r="DB164" s="31"/>
-      <c r="DC164" s="9"/>
+      <c r="DC164" s="31"/>
       <c r="DD164" s="9"/>
       <c r="DE164" s="9"/>
       <c r="DF164" s="9"/>
@@ -41245,7 +41475,7 @@
     </row>
     <row r="166" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="168" spans="1:152" x14ac:dyDescent="0.2">
@@ -41255,7 +41485,7 @@
     </row>
     <row r="169" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="170" spans="1:152" x14ac:dyDescent="0.2">
@@ -41265,132 +41495,132 @@
     </row>
     <row r="172" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
-      <c r="B172" s="45">
+      <c r="B172" s="44">
         <v>2000</v>
       </c>
-      <c r="C172" s="45"/>
-      <c r="D172" s="45"/>
-      <c r="E172" s="45"/>
-      <c r="F172" s="45">
+      <c r="C172" s="44"/>
+      <c r="D172" s="44"/>
+      <c r="E172" s="44"/>
+      <c r="F172" s="44">
         <v>2001</v>
       </c>
-      <c r="G172" s="45"/>
-      <c r="H172" s="45"/>
-      <c r="I172" s="45"/>
-      <c r="J172" s="45">
+      <c r="G172" s="44"/>
+      <c r="H172" s="44"/>
+      <c r="I172" s="44"/>
+      <c r="J172" s="44">
         <v>2002</v>
       </c>
-      <c r="K172" s="45"/>
-      <c r="L172" s="45"/>
-      <c r="M172" s="45"/>
-      <c r="N172" s="45">
+      <c r="K172" s="44"/>
+      <c r="L172" s="44"/>
+      <c r="M172" s="44"/>
+      <c r="N172" s="44">
         <v>2003</v>
       </c>
-      <c r="O172" s="45"/>
-      <c r="P172" s="45"/>
-      <c r="Q172" s="45"/>
-      <c r="R172" s="45">
+      <c r="O172" s="44"/>
+      <c r="P172" s="44"/>
+      <c r="Q172" s="44"/>
+      <c r="R172" s="44">
         <v>2004</v>
       </c>
-      <c r="S172" s="45"/>
-      <c r="T172" s="45"/>
-      <c r="U172" s="45"/>
-      <c r="V172" s="45">
+      <c r="S172" s="44"/>
+      <c r="T172" s="44"/>
+      <c r="U172" s="44"/>
+      <c r="V172" s="44">
         <v>2005</v>
       </c>
-      <c r="W172" s="45"/>
-      <c r="X172" s="45"/>
-      <c r="Y172" s="45"/>
-      <c r="Z172" s="45">
+      <c r="W172" s="44"/>
+      <c r="X172" s="44"/>
+      <c r="Y172" s="44"/>
+      <c r="Z172" s="44">
         <v>2006</v>
       </c>
-      <c r="AA172" s="45"/>
-      <c r="AB172" s="45"/>
-      <c r="AC172" s="45"/>
-      <c r="AD172" s="45">
+      <c r="AA172" s="44"/>
+      <c r="AB172" s="44"/>
+      <c r="AC172" s="44"/>
+      <c r="AD172" s="44">
         <v>2007</v>
       </c>
-      <c r="AE172" s="45"/>
-      <c r="AF172" s="45"/>
-      <c r="AG172" s="45"/>
-      <c r="AH172" s="45">
+      <c r="AE172" s="44"/>
+      <c r="AF172" s="44"/>
+      <c r="AG172" s="44"/>
+      <c r="AH172" s="44">
         <v>2008</v>
       </c>
-      <c r="AI172" s="45"/>
-      <c r="AJ172" s="45"/>
-      <c r="AK172" s="45"/>
-      <c r="AL172" s="45">
+      <c r="AI172" s="44"/>
+      <c r="AJ172" s="44"/>
+      <c r="AK172" s="44"/>
+      <c r="AL172" s="44">
         <v>2009</v>
       </c>
-      <c r="AM172" s="45"/>
-      <c r="AN172" s="45"/>
-      <c r="AO172" s="45"/>
-      <c r="AP172" s="45">
+      <c r="AM172" s="44"/>
+      <c r="AN172" s="44"/>
+      <c r="AO172" s="44"/>
+      <c r="AP172" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ172" s="45"/>
-      <c r="AR172" s="45"/>
-      <c r="AS172" s="45"/>
-      <c r="AT172" s="45">
+      <c r="AQ172" s="44"/>
+      <c r="AR172" s="44"/>
+      <c r="AS172" s="44"/>
+      <c r="AT172" s="44">
         <v>2011</v>
       </c>
-      <c r="AU172" s="45"/>
-      <c r="AV172" s="45"/>
-      <c r="AW172" s="45"/>
-      <c r="AX172" s="45">
+      <c r="AU172" s="44"/>
+      <c r="AV172" s="44"/>
+      <c r="AW172" s="44"/>
+      <c r="AX172" s="44">
         <v>2012</v>
       </c>
-      <c r="AY172" s="45"/>
-      <c r="AZ172" s="45"/>
-      <c r="BA172" s="45"/>
-      <c r="BB172" s="45">
+      <c r="AY172" s="44"/>
+      <c r="AZ172" s="44"/>
+      <c r="BA172" s="44"/>
+      <c r="BB172" s="44">
         <v>2013</v>
       </c>
-      <c r="BC172" s="45"/>
-      <c r="BD172" s="45"/>
-      <c r="BE172" s="45"/>
-      <c r="BF172" s="45">
+      <c r="BC172" s="44"/>
+      <c r="BD172" s="44"/>
+      <c r="BE172" s="44"/>
+      <c r="BF172" s="44">
         <v>2014</v>
       </c>
-      <c r="BG172" s="45"/>
-      <c r="BH172" s="45"/>
-      <c r="BI172" s="45"/>
-      <c r="BJ172" s="45">
+      <c r="BG172" s="44"/>
+      <c r="BH172" s="44"/>
+      <c r="BI172" s="44"/>
+      <c r="BJ172" s="44">
         <v>2015</v>
       </c>
-      <c r="BK172" s="45"/>
-      <c r="BL172" s="45"/>
-      <c r="BM172" s="45"/>
-      <c r="BN172" s="45">
+      <c r="BK172" s="44"/>
+      <c r="BL172" s="44"/>
+      <c r="BM172" s="44"/>
+      <c r="BN172" s="44">
         <v>2016</v>
       </c>
-      <c r="BO172" s="45"/>
-      <c r="BP172" s="45"/>
-      <c r="BQ172" s="45"/>
-      <c r="BR172" s="45">
+      <c r="BO172" s="44"/>
+      <c r="BP172" s="44"/>
+      <c r="BQ172" s="44"/>
+      <c r="BR172" s="44">
         <v>2017</v>
       </c>
-      <c r="BS172" s="45"/>
-      <c r="BT172" s="45"/>
-      <c r="BU172" s="45"/>
-      <c r="BV172" s="45">
+      <c r="BS172" s="44"/>
+      <c r="BT172" s="44"/>
+      <c r="BU172" s="44"/>
+      <c r="BV172" s="44">
         <v>2018</v>
       </c>
-      <c r="BW172" s="45"/>
-      <c r="BX172" s="45"/>
-      <c r="BY172" s="45"/>
-      <c r="BZ172" s="45">
+      <c r="BW172" s="44"/>
+      <c r="BX172" s="44"/>
+      <c r="BY172" s="44"/>
+      <c r="BZ172" s="44">
         <v>2019</v>
       </c>
-      <c r="CA172" s="45"/>
-      <c r="CB172" s="45"/>
-      <c r="CC172" s="45"/>
-      <c r="CD172" s="44">
+      <c r="CA172" s="44"/>
+      <c r="CB172" s="44"/>
+      <c r="CC172" s="44"/>
+      <c r="CD172" s="45">
         <v>2020</v>
       </c>
-      <c r="CE172" s="44"/>
-      <c r="CF172" s="44"/>
-      <c r="CG172" s="44"/>
+      <c r="CE172" s="45"/>
+      <c r="CF172" s="45"/>
+      <c r="CG172" s="45"/>
       <c r="CH172" s="26">
         <v>2021</v>
       </c>
@@ -41424,6 +41654,7 @@
       <c r="DB172" s="28">
         <v>2026</v>
       </c>
+      <c r="DC172" s="28"/>
     </row>
     <row r="173" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
@@ -41743,6 +41974,9 @@
       </c>
       <c r="DB173" s="34" t="s">
         <v>6</v>
+      </c>
+      <c r="DC173" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -42065,9 +42299,11 @@
         <v>102.87606721083147</v>
       </c>
       <c r="DB175" s="38">
-        <v>127.63754641377201</v>
-      </c>
-      <c r="DC175" s="9"/>
+        <v>127.89427511992335</v>
+      </c>
+      <c r="DC175" s="38">
+        <v>171.9442707097198</v>
+      </c>
       <c r="DD175" s="9"/>
       <c r="DE175" s="9"/>
       <c r="DF175" s="9"/>
@@ -42431,9 +42667,11 @@
         <v>92.830750395851794</v>
       </c>
       <c r="DB176" s="38">
-        <v>136.01553631776736</v>
-      </c>
-      <c r="DC176" s="9"/>
+        <v>136.03753044275493</v>
+      </c>
+      <c r="DC176" s="38">
+        <v>423.41120362035457</v>
+      </c>
       <c r="DD176" s="9"/>
       <c r="DE176" s="9"/>
       <c r="DF176" s="9"/>
@@ -42797,9 +43035,11 @@
         <v>91.87344208532042</v>
       </c>
       <c r="DB177" s="38">
-        <v>138.03120793351826</v>
-      </c>
-      <c r="DC177" s="9"/>
+        <v>138.11338237547068</v>
+      </c>
+      <c r="DC177" s="38">
+        <v>400.49135335716704</v>
+      </c>
       <c r="DD177" s="9"/>
       <c r="DE177" s="9"/>
       <c r="DF177" s="9"/>
@@ -43163,9 +43403,11 @@
         <v>96.247691803965779</v>
       </c>
       <c r="DB178" s="38">
-        <v>122.6075133252448</v>
-      </c>
-      <c r="DC178" s="9"/>
+        <v>122.86852522368493</v>
+      </c>
+      <c r="DC178" s="38">
+        <v>336.23052986950228</v>
+      </c>
       <c r="DD178" s="9"/>
       <c r="DE178" s="9"/>
       <c r="DF178" s="9"/>
@@ -43529,9 +43771,11 @@
         <v>95.68054786421844</v>
       </c>
       <c r="DB179" s="38">
-        <v>164.20850320952306</v>
-      </c>
-      <c r="DC179" s="9"/>
+        <v>164.3645467143017</v>
+      </c>
+      <c r="DC179" s="38">
+        <v>379.07780458622091</v>
+      </c>
       <c r="DD179" s="9"/>
       <c r="DE179" s="9"/>
       <c r="DF179" s="9"/>
@@ -43895,9 +44139,11 @@
         <v>94.138266781181585</v>
       </c>
       <c r="DB180" s="38">
-        <v>142.96542137246601</v>
-      </c>
-      <c r="DC180" s="9"/>
+        <v>143.00538775383029</v>
+      </c>
+      <c r="DC180" s="38">
+        <v>403.7217202231422</v>
+      </c>
       <c r="DD180" s="9"/>
       <c r="DE180" s="9"/>
       <c r="DF180" s="9"/>
@@ -44261,9 +44507,11 @@
         <v>117.96435007487089</v>
       </c>
       <c r="DB181" s="38">
-        <v>120.2484084048027</v>
-      </c>
-      <c r="DC181" s="9"/>
+        <v>120.53007528823304</v>
+      </c>
+      <c r="DC181" s="38">
+        <v>109.01246674068719</v>
+      </c>
       <c r="DD181" s="9"/>
       <c r="DE181" s="9"/>
       <c r="DF181" s="9"/>
@@ -44627,9 +44875,11 @@
         <v>89.898087335898964</v>
       </c>
       <c r="DB182" s="38">
-        <v>133.32105999653814</v>
-      </c>
-      <c r="DC182" s="9"/>
+        <v>133.36532111324391</v>
+      </c>
+      <c r="DC182" s="38">
+        <v>402.27704268424674</v>
+      </c>
       <c r="DD182" s="9"/>
       <c r="DE182" s="9"/>
       <c r="DF182" s="9"/>
@@ -44993,9 +45243,11 @@
         <v>95.90495594923199</v>
       </c>
       <c r="DB183" s="38">
-        <v>134.29660612247594</v>
-      </c>
-      <c r="DC183" s="9"/>
+        <v>134.41988445100509</v>
+      </c>
+      <c r="DC183" s="38">
+        <v>300.90236127997559</v>
+      </c>
       <c r="DD183" s="9"/>
       <c r="DE183" s="9"/>
       <c r="DF183" s="9"/>
@@ -45359,9 +45611,11 @@
         <v>121.97647885555291</v>
       </c>
       <c r="DB184" s="38">
-        <v>131.2266778652469</v>
-      </c>
-      <c r="DC184" s="9"/>
+        <v>131.58001921894456</v>
+      </c>
+      <c r="DC184" s="38">
+        <v>156.50654300430037</v>
+      </c>
       <c r="DD184" s="9"/>
       <c r="DE184" s="9"/>
       <c r="DF184" s="9"/>
@@ -45725,9 +45979,11 @@
         <v>126.46627635239179</v>
       </c>
       <c r="DB185" s="38">
-        <v>131.52155537822415</v>
-      </c>
-      <c r="DC185" s="9"/>
+        <v>131.60877245332912</v>
+      </c>
+      <c r="DC185" s="38">
+        <v>171.95021763382556</v>
+      </c>
       <c r="DD185" s="9"/>
       <c r="DE185" s="9"/>
       <c r="DF185" s="9"/>
@@ -46091,9 +46347,11 @@
         <v>135.5228640078017</v>
       </c>
       <c r="DB186" s="38">
-        <v>138.59534157946945</v>
-      </c>
-      <c r="DC186" s="9"/>
+        <v>138.67071167641646</v>
+      </c>
+      <c r="DC186" s="38">
+        <v>170.34552028392545</v>
+      </c>
       <c r="DD186" s="9"/>
       <c r="DE186" s="9"/>
       <c r="DF186" s="9"/>
@@ -46457,9 +46715,11 @@
         <v>140.07964928086204</v>
       </c>
       <c r="DB187" s="38">
-        <v>140.15843348031652</v>
-      </c>
-      <c r="DC187" s="9"/>
+        <v>140.61988790071246</v>
+      </c>
+      <c r="DC187" s="38">
+        <v>147.98078626058896</v>
+      </c>
       <c r="DD187" s="9"/>
       <c r="DE187" s="9"/>
       <c r="DF187" s="9"/>
@@ -46823,9 +47083,11 @@
         <v>105.48459402210111</v>
       </c>
       <c r="DB188" s="38">
-        <v>119.90134007065612</v>
-      </c>
-      <c r="DC188" s="9"/>
+        <v>120.21507372098125</v>
+      </c>
+      <c r="DC188" s="38">
+        <v>156.33871299367752</v>
+      </c>
       <c r="DD188" s="9"/>
       <c r="DE188" s="9"/>
       <c r="DF188" s="9"/>
@@ -47189,9 +47451,11 @@
         <v>119.0147000058938</v>
       </c>
       <c r="DB189" s="38">
-        <v>117.47694631545072</v>
-      </c>
-      <c r="DC189" s="9"/>
+        <v>117.58185075870485</v>
+      </c>
+      <c r="DC189" s="38">
+        <v>120.09329493493395</v>
+      </c>
       <c r="DD189" s="9"/>
       <c r="DE189" s="9"/>
       <c r="DF189" s="9"/>
@@ -47555,9 +47819,11 @@
         <v>115.09390978811074</v>
       </c>
       <c r="DB190" s="38">
-        <v>114.27546949848887</v>
-      </c>
-      <c r="DC190" s="9"/>
+        <v>114.40120196314116</v>
+      </c>
+      <c r="DC190" s="38">
+        <v>119.61379572641484</v>
+      </c>
       <c r="DD190" s="9"/>
       <c r="DE190" s="9"/>
       <c r="DF190" s="9"/>
@@ -47923,7 +48189,9 @@
       <c r="DB191" s="38">
         <v>129.59954707186091</v>
       </c>
-      <c r="DC191" s="9"/>
+      <c r="DC191" s="38">
+        <v>112.28601657119484</v>
+      </c>
       <c r="DD191" s="9"/>
       <c r="DE191" s="9"/>
       <c r="DF191" s="9"/>
@@ -48289,7 +48557,9 @@
       <c r="DB192" s="38">
         <v>149.21992757273628</v>
       </c>
-      <c r="DC192" s="9"/>
+      <c r="DC192" s="38">
+        <v>130.91986860104055</v>
+      </c>
       <c r="DD192" s="9"/>
       <c r="DE192" s="9"/>
       <c r="DF192" s="9"/>
@@ -48653,9 +48923,11 @@
         <v>134.65023025636614</v>
       </c>
       <c r="DB193" s="38">
-        <v>155.59598749648018</v>
-      </c>
-      <c r="DC193" s="9"/>
+        <v>155.67717815514473</v>
+      </c>
+      <c r="DC193" s="38">
+        <v>131.62933080828967</v>
+      </c>
       <c r="DD193" s="9"/>
       <c r="DE193" s="9"/>
       <c r="DF193" s="9"/>
@@ -49019,9 +49291,11 @@
         <v>176.95453183302971</v>
       </c>
       <c r="DB194" s="38">
-        <v>122.78371712532226</v>
-      </c>
-      <c r="DC194" s="9"/>
+        <v>123.00110753593989</v>
+      </c>
+      <c r="DC194" s="38">
+        <v>95.679750764880353</v>
+      </c>
       <c r="DD194" s="9"/>
       <c r="DE194" s="9"/>
       <c r="DF194" s="9"/>
@@ -49385,9 +49659,11 @@
         <v>223.76129586262556</v>
       </c>
       <c r="DB195" s="38">
-        <v>109.86565705816514</v>
-      </c>
-      <c r="DC195" s="9"/>
+        <v>109.88554218685161</v>
+      </c>
+      <c r="DC195" s="38">
+        <v>77.029668350296561</v>
+      </c>
       <c r="DD195" s="9"/>
       <c r="DE195" s="9"/>
       <c r="DF195" s="9"/>
@@ -49751,9 +50027,11 @@
         <v>144.50254034872353</v>
       </c>
       <c r="DB196" s="38">
-        <v>101.78801593725855</v>
-      </c>
-      <c r="DC196" s="9"/>
+        <v>101.76563372255862</v>
+      </c>
+      <c r="DC196" s="38">
+        <v>78.942267391098767</v>
+      </c>
       <c r="DD196" s="9"/>
       <c r="DE196" s="9"/>
       <c r="DF196" s="9"/>
@@ -50117,9 +50395,11 @@
         <v>190.40139219098597</v>
       </c>
       <c r="DB197" s="38">
-        <v>137.37387353401033</v>
-      </c>
-      <c r="DC197" s="9"/>
+        <v>137.90787596886983</v>
+      </c>
+      <c r="DC197" s="38">
+        <v>99.329392407258936</v>
+      </c>
       <c r="DD197" s="9"/>
       <c r="DE197" s="9"/>
       <c r="DF197" s="9"/>
@@ -50483,9 +50763,11 @@
         <v>146.35821735713688</v>
       </c>
       <c r="DB198" s="38">
-        <v>116.08168278339809</v>
-      </c>
-      <c r="DC198" s="9"/>
+        <v>116.30573970176994</v>
+      </c>
+      <c r="DC198" s="38">
+        <v>124.31834107673969</v>
+      </c>
       <c r="DD198" s="9"/>
       <c r="DE198" s="9"/>
       <c r="DF198" s="9"/>
@@ -50638,7 +50920,7 @@
       <c r="CZ199" s="31"/>
       <c r="DA199" s="31"/>
       <c r="DB199" s="31"/>
-      <c r="DC199" s="9"/>
+      <c r="DC199" s="31"/>
       <c r="DD199" s="9"/>
       <c r="DE199" s="9"/>
       <c r="DF199" s="9"/>
@@ -51002,9 +51284,11 @@
         <v>124.50184977918649</v>
       </c>
       <c r="DB200" s="38">
-        <v>122.57502288121853</v>
-      </c>
-      <c r="DC200" s="9"/>
+        <v>122.78483249466899</v>
+      </c>
+      <c r="DC200" s="38">
+        <v>124.16955206707544</v>
+      </c>
       <c r="DD200" s="9"/>
       <c r="DE200" s="9"/>
       <c r="DF200" s="9"/>
@@ -51158,6 +51442,7 @@
       <c r="CZ201" s="33"/>
       <c r="DA201" s="33"/>
       <c r="DB201" s="33"/>
+      <c r="DC201" s="33"/>
     </row>
     <row r="202" spans="1:152" ht="15" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
@@ -51171,11 +51456,6 @@
       <c r="CU202"/>
       <c r="CV202"/>
       <c r="CW202"/>
-      <c r="CX202"/>
-      <c r="CY202"/>
-      <c r="CZ202"/>
-      <c r="DA202"/>
-      <c r="DB202"/>
     </row>
     <row r="203" spans="1:152" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B203" s="9"/>
@@ -51283,7 +51563,7 @@
       <c r="CZ203" s="31"/>
       <c r="DA203" s="31"/>
       <c r="DB203" s="31"/>
-      <c r="DC203" s="9"/>
+      <c r="DC203" s="31"/>
       <c r="DD203" s="9"/>
       <c r="DE203" s="9"/>
       <c r="DF203" s="9"/>
@@ -51436,7 +51716,7 @@
       <c r="CZ204" s="31"/>
       <c r="DA204" s="31"/>
       <c r="DB204" s="31"/>
-      <c r="DC204" s="9"/>
+      <c r="DC204" s="31"/>
       <c r="DD204" s="9"/>
       <c r="DE204" s="9"/>
       <c r="DF204" s="9"/>
@@ -51495,7 +51775,7 @@
     </row>
     <row r="207" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="209" spans="1:152" x14ac:dyDescent="0.2">
@@ -51505,7 +51785,7 @@
     </row>
     <row r="210" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="211" spans="1:152" x14ac:dyDescent="0.2">
@@ -51515,132 +51795,132 @@
     </row>
     <row r="213" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
-      <c r="B213" s="45">
+      <c r="B213" s="44">
         <v>2000</v>
       </c>
-      <c r="C213" s="45"/>
-      <c r="D213" s="45"/>
-      <c r="E213" s="45"/>
-      <c r="F213" s="45">
+      <c r="C213" s="44"/>
+      <c r="D213" s="44"/>
+      <c r="E213" s="44"/>
+      <c r="F213" s="44">
         <v>2001</v>
       </c>
-      <c r="G213" s="45"/>
-      <c r="H213" s="45"/>
-      <c r="I213" s="45"/>
-      <c r="J213" s="45">
+      <c r="G213" s="44"/>
+      <c r="H213" s="44"/>
+      <c r="I213" s="44"/>
+      <c r="J213" s="44">
         <v>2002</v>
       </c>
-      <c r="K213" s="45"/>
-      <c r="L213" s="45"/>
-      <c r="M213" s="45"/>
-      <c r="N213" s="45">
+      <c r="K213" s="44"/>
+      <c r="L213" s="44"/>
+      <c r="M213" s="44"/>
+      <c r="N213" s="44">
         <v>2003</v>
       </c>
-      <c r="O213" s="45"/>
-      <c r="P213" s="45"/>
-      <c r="Q213" s="45"/>
-      <c r="R213" s="45">
+      <c r="O213" s="44"/>
+      <c r="P213" s="44"/>
+      <c r="Q213" s="44"/>
+      <c r="R213" s="44">
         <v>2004</v>
       </c>
-      <c r="S213" s="45"/>
-      <c r="T213" s="45"/>
-      <c r="U213" s="45"/>
-      <c r="V213" s="45">
+      <c r="S213" s="44"/>
+      <c r="T213" s="44"/>
+      <c r="U213" s="44"/>
+      <c r="V213" s="44">
         <v>2005</v>
       </c>
-      <c r="W213" s="45"/>
-      <c r="X213" s="45"/>
-      <c r="Y213" s="45"/>
-      <c r="Z213" s="45">
+      <c r="W213" s="44"/>
+      <c r="X213" s="44"/>
+      <c r="Y213" s="44"/>
+      <c r="Z213" s="44">
         <v>2006</v>
       </c>
-      <c r="AA213" s="45"/>
-      <c r="AB213" s="45"/>
-      <c r="AC213" s="45"/>
-      <c r="AD213" s="45">
+      <c r="AA213" s="44"/>
+      <c r="AB213" s="44"/>
+      <c r="AC213" s="44"/>
+      <c r="AD213" s="44">
         <v>2007</v>
       </c>
-      <c r="AE213" s="45"/>
-      <c r="AF213" s="45"/>
-      <c r="AG213" s="45"/>
-      <c r="AH213" s="45">
+      <c r="AE213" s="44"/>
+      <c r="AF213" s="44"/>
+      <c r="AG213" s="44"/>
+      <c r="AH213" s="44">
         <v>2008</v>
       </c>
-      <c r="AI213" s="45"/>
-      <c r="AJ213" s="45"/>
-      <c r="AK213" s="45"/>
-      <c r="AL213" s="45">
+      <c r="AI213" s="44"/>
+      <c r="AJ213" s="44"/>
+      <c r="AK213" s="44"/>
+      <c r="AL213" s="44">
         <v>2009</v>
       </c>
-      <c r="AM213" s="45"/>
-      <c r="AN213" s="45"/>
-      <c r="AO213" s="45"/>
-      <c r="AP213" s="45">
+      <c r="AM213" s="44"/>
+      <c r="AN213" s="44"/>
+      <c r="AO213" s="44"/>
+      <c r="AP213" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ213" s="45"/>
-      <c r="AR213" s="45"/>
-      <c r="AS213" s="45"/>
-      <c r="AT213" s="45">
+      <c r="AQ213" s="44"/>
+      <c r="AR213" s="44"/>
+      <c r="AS213" s="44"/>
+      <c r="AT213" s="44">
         <v>2011</v>
       </c>
-      <c r="AU213" s="45"/>
-      <c r="AV213" s="45"/>
-      <c r="AW213" s="45"/>
-      <c r="AX213" s="45">
+      <c r="AU213" s="44"/>
+      <c r="AV213" s="44"/>
+      <c r="AW213" s="44"/>
+      <c r="AX213" s="44">
         <v>2012</v>
       </c>
-      <c r="AY213" s="45"/>
-      <c r="AZ213" s="45"/>
-      <c r="BA213" s="45"/>
-      <c r="BB213" s="45">
+      <c r="AY213" s="44"/>
+      <c r="AZ213" s="44"/>
+      <c r="BA213" s="44"/>
+      <c r="BB213" s="44">
         <v>2013</v>
       </c>
-      <c r="BC213" s="45"/>
-      <c r="BD213" s="45"/>
-      <c r="BE213" s="45"/>
-      <c r="BF213" s="45">
+      <c r="BC213" s="44"/>
+      <c r="BD213" s="44"/>
+      <c r="BE213" s="44"/>
+      <c r="BF213" s="44">
         <v>2014</v>
       </c>
-      <c r="BG213" s="45"/>
-      <c r="BH213" s="45"/>
-      <c r="BI213" s="45"/>
-      <c r="BJ213" s="45">
+      <c r="BG213" s="44"/>
+      <c r="BH213" s="44"/>
+      <c r="BI213" s="44"/>
+      <c r="BJ213" s="44">
         <v>2015</v>
       </c>
-      <c r="BK213" s="45"/>
-      <c r="BL213" s="45"/>
-      <c r="BM213" s="45"/>
-      <c r="BN213" s="45">
+      <c r="BK213" s="44"/>
+      <c r="BL213" s="44"/>
+      <c r="BM213" s="44"/>
+      <c r="BN213" s="44">
         <v>2016</v>
       </c>
-      <c r="BO213" s="45"/>
-      <c r="BP213" s="45"/>
-      <c r="BQ213" s="45"/>
-      <c r="BR213" s="45">
+      <c r="BO213" s="44"/>
+      <c r="BP213" s="44"/>
+      <c r="BQ213" s="44"/>
+      <c r="BR213" s="44">
         <v>2017</v>
       </c>
-      <c r="BS213" s="45"/>
-      <c r="BT213" s="45"/>
-      <c r="BU213" s="45"/>
-      <c r="BV213" s="45">
+      <c r="BS213" s="44"/>
+      <c r="BT213" s="44"/>
+      <c r="BU213" s="44"/>
+      <c r="BV213" s="44">
         <v>2018</v>
       </c>
-      <c r="BW213" s="45"/>
-      <c r="BX213" s="45"/>
-      <c r="BY213" s="45"/>
-      <c r="BZ213" s="45">
+      <c r="BW213" s="44"/>
+      <c r="BX213" s="44"/>
+      <c r="BY213" s="44"/>
+      <c r="BZ213" s="44">
         <v>2019</v>
       </c>
-      <c r="CA213" s="45"/>
-      <c r="CB213" s="45"/>
-      <c r="CC213" s="45"/>
-      <c r="CD213" s="44">
+      <c r="CA213" s="44"/>
+      <c r="CB213" s="44"/>
+      <c r="CC213" s="44"/>
+      <c r="CD213" s="45">
         <v>2020</v>
       </c>
-      <c r="CE213" s="44"/>
-      <c r="CF213" s="44"/>
-      <c r="CG213" s="44"/>
+      <c r="CE213" s="45"/>
+      <c r="CF213" s="45"/>
+      <c r="CG213" s="45"/>
       <c r="CH213" s="26">
         <v>2021</v>
       </c>
@@ -51674,6 +51954,7 @@
       <c r="DB213" s="28">
         <v>2026</v>
       </c>
+      <c r="DC213" s="28"/>
     </row>
     <row r="214" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A214" s="5" t="s">
@@ -51993,6 +52274,9 @@
       </c>
       <c r="DB214" s="34" t="s">
         <v>6</v>
+      </c>
+      <c r="DC214" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -52315,9 +52599,11 @@
         <v>13.514738944898836</v>
       </c>
       <c r="DB216" s="38">
-        <v>14.637734697353128</v>
-      </c>
-      <c r="DC216" s="9"/>
+        <v>14.66920113233777</v>
+      </c>
+      <c r="DC216" s="38">
+        <v>15.446138262711187</v>
+      </c>
       <c r="DD216" s="9"/>
       <c r="DE216" s="9"/>
       <c r="DF216" s="9"/>
@@ -52681,9 +52967,11 @@
         <v>0.82257618657706022</v>
       </c>
       <c r="DB217" s="38">
-        <v>0.71149732891045925</v>
-      </c>
-      <c r="DC217" s="9"/>
+        <v>0.71581663779005134</v>
+      </c>
+      <c r="DC217" s="38">
+        <v>1.2577682056681723</v>
+      </c>
       <c r="DD217" s="9"/>
       <c r="DE217" s="9"/>
       <c r="DF217" s="9"/>
@@ -53047,9 +53335,11 @@
         <v>2.7498058058193902</v>
       </c>
       <c r="DB218" s="38">
-        <v>2.1419409361185004</v>
-      </c>
-      <c r="DC218" s="9"/>
+        <v>2.2126048092446218</v>
+      </c>
+      <c r="DC218" s="38">
+        <v>2.0833881239180991</v>
+      </c>
       <c r="DD218" s="9"/>
       <c r="DE218" s="9"/>
       <c r="DF218" s="9"/>
@@ -53413,9 +53703,11 @@
         <v>0.35992455386890493</v>
       </c>
       <c r="DB219" s="38">
-        <v>0.20082544266650637</v>
-      </c>
-      <c r="DC219" s="9"/>
+        <v>0.20000645798182504</v>
+      </c>
+      <c r="DC219" s="38">
+        <v>0.44906950248768829</v>
+      </c>
       <c r="DD219" s="9"/>
       <c r="DE219" s="9"/>
       <c r="DF219" s="9"/>
@@ -53779,9 +54071,11 @@
         <v>0.17013438036861073</v>
       </c>
       <c r="DB220" s="38">
-        <v>0.18919949855583618</v>
-      </c>
-      <c r="DC220" s="9"/>
+        <v>0.18953915090402507</v>
+      </c>
+      <c r="DC220" s="38">
+        <v>0.20626928088601981</v>
+      </c>
       <c r="DD220" s="9"/>
       <c r="DE220" s="9"/>
       <c r="DF220" s="9"/>
@@ -54145,9 +54439,11 @@
         <v>0.64927553639501856</v>
       </c>
       <c r="DB221" s="38">
-        <v>0.84334208592838655</v>
-      </c>
-      <c r="DC221" s="9"/>
+        <v>0.84465648385770986</v>
+      </c>
+      <c r="DC221" s="38">
+        <v>1.0566853916021168</v>
+      </c>
       <c r="DD221" s="9"/>
       <c r="DE221" s="9"/>
       <c r="DF221" s="9"/>
@@ -54511,9 +54807,11 @@
         <v>5.8912399625528575</v>
       </c>
       <c r="DB222" s="38">
-        <v>7.6619478489720212</v>
-      </c>
-      <c r="DC222" s="9"/>
+        <v>7.6405092604054747</v>
+      </c>
+      <c r="DC222" s="38">
+        <v>7.367441445344161</v>
+      </c>
       <c r="DD222" s="9"/>
       <c r="DE222" s="9"/>
       <c r="DF222" s="9"/>
@@ -54877,9 +55175,11 @@
         <v>0.39911790432086086</v>
       </c>
       <c r="DB223" s="38">
-        <v>0.26723677398988749</v>
-      </c>
-      <c r="DC223" s="9"/>
+        <v>0.2663653546051834</v>
+      </c>
+      <c r="DC223" s="38">
+        <v>0.56811090676883447</v>
+      </c>
       <c r="DD223" s="9"/>
       <c r="DE223" s="9"/>
       <c r="DF223" s="9"/>
@@ -55243,9 +55543,11 @@
         <v>2.4726646149961335</v>
       </c>
       <c r="DB224" s="38">
-        <v>2.6217447822115316</v>
-      </c>
-      <c r="DC224" s="9"/>
+        <v>2.5997029775488758</v>
+      </c>
+      <c r="DC224" s="38">
+        <v>2.4574054060360973</v>
+      </c>
       <c r="DD224" s="9"/>
       <c r="DE224" s="9"/>
       <c r="DF224" s="9"/>
@@ -55609,9 +55911,11 @@
         <v>18.031278222984266</v>
       </c>
       <c r="DB225" s="38">
-        <v>20.804567004595224</v>
-      </c>
-      <c r="DC225" s="9"/>
+        <v>20.981826994444884</v>
+      </c>
+      <c r="DC225" s="38">
+        <v>19.991354440577933</v>
+      </c>
       <c r="DD225" s="9"/>
       <c r="DE225" s="9"/>
       <c r="DF225" s="9"/>
@@ -55975,9 +56279,11 @@
         <v>3.0206415351181293</v>
       </c>
       <c r="DB226" s="38">
-        <v>3.0382936366875062</v>
-      </c>
-      <c r="DC226" s="9"/>
+        <v>3.040606387180159</v>
+      </c>
+      <c r="DC226" s="38">
+        <v>3.3077456908763918</v>
+      </c>
       <c r="DD226" s="9"/>
       <c r="DE226" s="9"/>
       <c r="DF226" s="9"/>
@@ -56341,9 +56647,11 @@
         <v>2.0742348965887216</v>
       </c>
       <c r="DB227" s="38">
-        <v>1.8867076629707589</v>
-      </c>
-      <c r="DC227" s="9"/>
+        <v>1.9013515812314661</v>
+      </c>
+      <c r="DC227" s="38">
+        <v>2.0871174961813193</v>
+      </c>
       <c r="DD227" s="9"/>
       <c r="DE227" s="9"/>
       <c r="DF227" s="9"/>
@@ -56707,9 +57015,11 @@
         <v>5.980685187044581</v>
       </c>
       <c r="DB228" s="38">
-        <v>8.8050044199879096</v>
-      </c>
-      <c r="DC228" s="9"/>
+        <v>8.9312379035183351</v>
+      </c>
+      <c r="DC228" s="38">
+        <v>7.9761296170832319</v>
+      </c>
       <c r="DD228" s="9"/>
       <c r="DE228" s="9"/>
       <c r="DF228" s="9"/>
@@ -57073,9 +57383,11 @@
         <v>6.9557166042328342</v>
       </c>
       <c r="DB229" s="38">
-        <v>7.0745612849490476</v>
-      </c>
-      <c r="DC229" s="9"/>
+        <v>7.1086311225149217</v>
+      </c>
+      <c r="DC229" s="38">
+        <v>6.6203616364369946</v>
+      </c>
       <c r="DD229" s="9"/>
       <c r="DE229" s="9"/>
       <c r="DF229" s="9"/>
@@ -57439,9 +57751,11 @@
         <v>49.85576233878745</v>
       </c>
       <c r="DB230" s="38">
-        <v>45.723137172633457</v>
-      </c>
-      <c r="DC230" s="9"/>
+        <v>45.680428187302617</v>
+      </c>
+      <c r="DC230" s="38">
+        <v>40.94460933554069</v>
+      </c>
       <c r="DD230" s="9"/>
       <c r="DE230" s="9"/>
       <c r="DF230" s="9"/>
@@ -57805,9 +58119,11 @@
         <v>42.316991967772751</v>
       </c>
       <c r="DB231" s="38">
-        <v>40.771556418811706</v>
-      </c>
-      <c r="DC231" s="9"/>
+        <v>40.757630591604482</v>
+      </c>
+      <c r="DC231" s="38">
+        <v>39.059330186835993</v>
+      </c>
       <c r="DD231" s="9"/>
       <c r="DE231" s="9"/>
       <c r="DF231" s="9"/>
@@ -58171,9 +58487,11 @@
         <v>4.1377283835592943E-2</v>
       </c>
       <c r="DB232" s="38">
-        <v>4.8594800268839645E-2</v>
-      </c>
-      <c r="DC232" s="9"/>
+        <v>4.954281137178098E-2</v>
+      </c>
+      <c r="DC232" s="38">
+        <v>2.6651347146781697E-2</v>
+      </c>
       <c r="DD232" s="9"/>
       <c r="DE232" s="9"/>
       <c r="DF232" s="9"/>
@@ -58537,9 +58855,11 @@
         <v>7.1694819976990845</v>
       </c>
       <c r="DB233" s="38">
-        <v>1.9677531976381664</v>
-      </c>
-      <c r="DC233" s="9"/>
+        <v>1.9565272735524812</v>
+      </c>
+      <c r="DC233" s="38">
+        <v>0.90195985270845203</v>
+      </c>
       <c r="DD233" s="9"/>
       <c r="DE233" s="9"/>
       <c r="DF233" s="9"/>
@@ -58903,9 +59223,11 @@
         <v>0.32791108948002207</v>
       </c>
       <c r="DB234" s="38">
-        <v>2.9352327559147424</v>
-      </c>
-      <c r="DC234" s="9"/>
+        <v>2.9167275107738764</v>
+      </c>
+      <c r="DC234" s="38">
+        <v>0.95666794884945883</v>
+      </c>
       <c r="DD234" s="9"/>
       <c r="DE234" s="9"/>
       <c r="DF234" s="9"/>
@@ -59269,9 +59591,11 @@
         <v>18.598220493329435</v>
       </c>
       <c r="DB235" s="38">
-        <v>18.834561125418194</v>
-      </c>
-      <c r="DC235" s="9"/>
+        <v>18.668543685914734</v>
+      </c>
+      <c r="DC235" s="38">
+        <v>23.61789796117019</v>
+      </c>
       <c r="DD235" s="9"/>
       <c r="DE235" s="9"/>
       <c r="DF235" s="9"/>
@@ -59635,9 +59959,11 @@
         <v>2.5203907587657581</v>
       </c>
       <c r="DB236" s="38">
-        <v>1.8219478864248981</v>
-      </c>
-      <c r="DC236" s="9"/>
+        <v>1.8503051425039287</v>
+      </c>
+      <c r="DC236" s="38">
+        <v>2.4388656016695491</v>
+      </c>
       <c r="DD236" s="9"/>
       <c r="DE236" s="9"/>
       <c r="DF236" s="9"/>
@@ -60001,9 +60327,11 @@
         <v>2.7971051236639779</v>
       </c>
       <c r="DB237" s="38">
-        <v>2.9264320845045511</v>
-      </c>
-      <c r="DC237" s="9"/>
+        <v>2.9585387598773676</v>
+      </c>
+      <c r="DC237" s="38">
+        <v>4.3529531955651306</v>
+      </c>
       <c r="DD237" s="9"/>
       <c r="DE237" s="9"/>
       <c r="DF237" s="9"/>
@@ -60367,9 +60695,11 @@
         <v>10.288004794855087</v>
       </c>
       <c r="DB238" s="38">
-        <v>9.9493646384223453</v>
-      </c>
-      <c r="DC238" s="9"/>
+        <v>9.8760982864936047</v>
+      </c>
+      <c r="DC238" s="38">
+        <v>12.202791584762794</v>
+      </c>
       <c r="DD238" s="9"/>
       <c r="DE238" s="9"/>
       <c r="DF238" s="9"/>
@@ -60733,9 +61063,11 @@
         <v>2.9927198160446111</v>
       </c>
       <c r="DB239" s="38">
-        <v>4.1368165160664017</v>
-      </c>
-      <c r="DC239" s="9"/>
+        <v>3.9836014970398312</v>
+      </c>
+      <c r="DC239" s="38">
+        <v>4.6232875791727155</v>
+      </c>
       <c r="DD239" s="9"/>
       <c r="DE239" s="9"/>
       <c r="DF239" s="9"/>
@@ -60888,7 +61220,7 @@
       <c r="CZ240" s="31"/>
       <c r="DA240" s="31"/>
       <c r="DB240" s="31"/>
-      <c r="DC240" s="9"/>
+      <c r="DC240" s="31"/>
       <c r="DD240" s="9"/>
       <c r="DE240" s="9"/>
       <c r="DF240" s="9"/>
@@ -61254,7 +61586,9 @@
       <c r="DB241" s="38">
         <v>100</v>
       </c>
-      <c r="DC241" s="9"/>
+      <c r="DC241" s="38">
+        <v>100</v>
+      </c>
       <c r="DD241" s="9"/>
       <c r="DE241" s="9"/>
       <c r="DF241" s="9"/>
@@ -61408,6 +61742,7 @@
       <c r="CZ242" s="33"/>
       <c r="DA242" s="33"/>
       <c r="DB242" s="33"/>
+      <c r="DC242" s="33"/>
     </row>
     <row r="243" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
@@ -61520,7 +61855,7 @@
       <c r="CZ244" s="31"/>
       <c r="DA244" s="31"/>
       <c r="DB244" s="31"/>
-      <c r="DC244" s="9"/>
+      <c r="DC244" s="31"/>
       <c r="DD244" s="9"/>
       <c r="DE244" s="9"/>
       <c r="DF244" s="9"/>
@@ -61673,7 +62008,7 @@
       <c r="CZ245" s="31"/>
       <c r="DA245" s="31"/>
       <c r="DB245" s="31"/>
-      <c r="DC245" s="9"/>
+      <c r="DC245" s="31"/>
       <c r="DD245" s="9"/>
       <c r="DE245" s="9"/>
       <c r="DF245" s="9"/>
@@ -61732,7 +62067,7 @@
     </row>
     <row r="248" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="250" spans="1:152" x14ac:dyDescent="0.2">
@@ -61742,7 +62077,7 @@
     </row>
     <row r="251" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="252" spans="1:152" x14ac:dyDescent="0.2">
@@ -61752,132 +62087,132 @@
     </row>
     <row r="254" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
-      <c r="B254" s="45">
+      <c r="B254" s="44">
         <v>2000</v>
       </c>
-      <c r="C254" s="45"/>
-      <c r="D254" s="45"/>
-      <c r="E254" s="45"/>
-      <c r="F254" s="45">
+      <c r="C254" s="44"/>
+      <c r="D254" s="44"/>
+      <c r="E254" s="44"/>
+      <c r="F254" s="44">
         <v>2001</v>
       </c>
-      <c r="G254" s="45"/>
-      <c r="H254" s="45"/>
-      <c r="I254" s="45"/>
-      <c r="J254" s="45">
+      <c r="G254" s="44"/>
+      <c r="H254" s="44"/>
+      <c r="I254" s="44"/>
+      <c r="J254" s="44">
         <v>2002</v>
       </c>
-      <c r="K254" s="45"/>
-      <c r="L254" s="45"/>
-      <c r="M254" s="45"/>
-      <c r="N254" s="45">
+      <c r="K254" s="44"/>
+      <c r="L254" s="44"/>
+      <c r="M254" s="44"/>
+      <c r="N254" s="44">
         <v>2003</v>
       </c>
-      <c r="O254" s="45"/>
-      <c r="P254" s="45"/>
-      <c r="Q254" s="45"/>
-      <c r="R254" s="45">
+      <c r="O254" s="44"/>
+      <c r="P254" s="44"/>
+      <c r="Q254" s="44"/>
+      <c r="R254" s="44">
         <v>2004</v>
       </c>
-      <c r="S254" s="45"/>
-      <c r="T254" s="45"/>
-      <c r="U254" s="45"/>
-      <c r="V254" s="45">
+      <c r="S254" s="44"/>
+      <c r="T254" s="44"/>
+      <c r="U254" s="44"/>
+      <c r="V254" s="44">
         <v>2005</v>
       </c>
-      <c r="W254" s="45"/>
-      <c r="X254" s="45"/>
-      <c r="Y254" s="45"/>
-      <c r="Z254" s="45">
+      <c r="W254" s="44"/>
+      <c r="X254" s="44"/>
+      <c r="Y254" s="44"/>
+      <c r="Z254" s="44">
         <v>2006</v>
       </c>
-      <c r="AA254" s="45"/>
-      <c r="AB254" s="45"/>
-      <c r="AC254" s="45"/>
-      <c r="AD254" s="45">
+      <c r="AA254" s="44"/>
+      <c r="AB254" s="44"/>
+      <c r="AC254" s="44"/>
+      <c r="AD254" s="44">
         <v>2007</v>
       </c>
-      <c r="AE254" s="45"/>
-      <c r="AF254" s="45"/>
-      <c r="AG254" s="45"/>
-      <c r="AH254" s="45">
+      <c r="AE254" s="44"/>
+      <c r="AF254" s="44"/>
+      <c r="AG254" s="44"/>
+      <c r="AH254" s="44">
         <v>2008</v>
       </c>
-      <c r="AI254" s="45"/>
-      <c r="AJ254" s="45"/>
-      <c r="AK254" s="45"/>
-      <c r="AL254" s="45">
+      <c r="AI254" s="44"/>
+      <c r="AJ254" s="44"/>
+      <c r="AK254" s="44"/>
+      <c r="AL254" s="44">
         <v>2009</v>
       </c>
-      <c r="AM254" s="45"/>
-      <c r="AN254" s="45"/>
-      <c r="AO254" s="45"/>
-      <c r="AP254" s="45">
+      <c r="AM254" s="44"/>
+      <c r="AN254" s="44"/>
+      <c r="AO254" s="44"/>
+      <c r="AP254" s="44">
         <v>2010</v>
       </c>
-      <c r="AQ254" s="45"/>
-      <c r="AR254" s="45"/>
-      <c r="AS254" s="45"/>
-      <c r="AT254" s="45">
+      <c r="AQ254" s="44"/>
+      <c r="AR254" s="44"/>
+      <c r="AS254" s="44"/>
+      <c r="AT254" s="44">
         <v>2011</v>
       </c>
-      <c r="AU254" s="45"/>
-      <c r="AV254" s="45"/>
-      <c r="AW254" s="45"/>
-      <c r="AX254" s="45">
+      <c r="AU254" s="44"/>
+      <c r="AV254" s="44"/>
+      <c r="AW254" s="44"/>
+      <c r="AX254" s="44">
         <v>2012</v>
       </c>
-      <c r="AY254" s="45"/>
-      <c r="AZ254" s="45"/>
-      <c r="BA254" s="45"/>
-      <c r="BB254" s="45">
+      <c r="AY254" s="44"/>
+      <c r="AZ254" s="44"/>
+      <c r="BA254" s="44"/>
+      <c r="BB254" s="44">
         <v>2013</v>
       </c>
-      <c r="BC254" s="45"/>
-      <c r="BD254" s="45"/>
-      <c r="BE254" s="45"/>
-      <c r="BF254" s="45">
+      <c r="BC254" s="44"/>
+      <c r="BD254" s="44"/>
+      <c r="BE254" s="44"/>
+      <c r="BF254" s="44">
         <v>2014</v>
       </c>
-      <c r="BG254" s="45"/>
-      <c r="BH254" s="45"/>
-      <c r="BI254" s="45"/>
-      <c r="BJ254" s="45">
+      <c r="BG254" s="44"/>
+      <c r="BH254" s="44"/>
+      <c r="BI254" s="44"/>
+      <c r="BJ254" s="44">
         <v>2015</v>
       </c>
-      <c r="BK254" s="45"/>
-      <c r="BL254" s="45"/>
-      <c r="BM254" s="45"/>
-      <c r="BN254" s="45">
+      <c r="BK254" s="44"/>
+      <c r="BL254" s="44"/>
+      <c r="BM254" s="44"/>
+      <c r="BN254" s="44">
         <v>2016</v>
       </c>
-      <c r="BO254" s="45"/>
-      <c r="BP254" s="45"/>
-      <c r="BQ254" s="45"/>
-      <c r="BR254" s="45">
+      <c r="BO254" s="44"/>
+      <c r="BP254" s="44"/>
+      <c r="BQ254" s="44"/>
+      <c r="BR254" s="44">
         <v>2017</v>
       </c>
-      <c r="BS254" s="45"/>
-      <c r="BT254" s="45"/>
-      <c r="BU254" s="45"/>
-      <c r="BV254" s="45">
+      <c r="BS254" s="44"/>
+      <c r="BT254" s="44"/>
+      <c r="BU254" s="44"/>
+      <c r="BV254" s="44">
         <v>2018</v>
       </c>
-      <c r="BW254" s="45"/>
-      <c r="BX254" s="45"/>
-      <c r="BY254" s="45"/>
-      <c r="BZ254" s="45">
+      <c r="BW254" s="44"/>
+      <c r="BX254" s="44"/>
+      <c r="BY254" s="44"/>
+      <c r="BZ254" s="44">
         <v>2019</v>
       </c>
-      <c r="CA254" s="45"/>
-      <c r="CB254" s="45"/>
-      <c r="CC254" s="45"/>
-      <c r="CD254" s="44">
+      <c r="CA254" s="44"/>
+      <c r="CB254" s="44"/>
+      <c r="CC254" s="44"/>
+      <c r="CD254" s="45">
         <v>2020</v>
       </c>
-      <c r="CE254" s="44"/>
-      <c r="CF254" s="44"/>
-      <c r="CG254" s="44"/>
+      <c r="CE254" s="45"/>
+      <c r="CF254" s="45"/>
+      <c r="CG254" s="45"/>
       <c r="CH254" s="26">
         <v>2021</v>
       </c>
@@ -61911,6 +62246,7 @@
       <c r="DB254" s="28">
         <v>2026</v>
       </c>
+      <c r="DC254" s="28"/>
     </row>
     <row r="255" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
@@ -62230,6 +62566,9 @@
       </c>
       <c r="DB255" s="34" t="s">
         <v>6</v>
+      </c>
+      <c r="DC255" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="256" spans="1:152" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -62552,9 +62891,11 @@
         <v>16.355699080860276</v>
       </c>
       <c r="DB257" s="38">
-        <v>14.057154151497157</v>
-      </c>
-      <c r="DC257" s="9"/>
+        <v>14.083158938707788</v>
+      </c>
+      <c r="DC257" s="38">
+        <v>11.154428474589146</v>
+      </c>
       <c r="DD257" s="9"/>
       <c r="DE257" s="9"/>
       <c r="DF257" s="9"/>
@@ -62918,9 +63259,11 @@
         <v>1.1032147901039653</v>
       </c>
       <c r="DB258" s="38">
-        <v>0.64118999734983328</v>
-      </c>
-      <c r="DC258" s="9"/>
+        <v>0.64608219277351264</v>
+      </c>
+      <c r="DC258" s="38">
+        <v>0.36885305198976165</v>
+      </c>
       <c r="DD258" s="9"/>
       <c r="DE258" s="9"/>
       <c r="DF258" s="9"/>
@@ -63284,9 +63627,11 @@
         <v>3.7263860108792235</v>
       </c>
       <c r="DB259" s="38">
-        <v>1.9020949188635543</v>
-      </c>
-      <c r="DC259" s="9"/>
+        <v>1.967038285554652</v>
+      </c>
+      <c r="DC259" s="38">
+        <v>0.64593996339807758</v>
+      </c>
       <c r="DD259" s="9"/>
       <c r="DE259" s="9"/>
       <c r="DF259" s="9"/>
@@ -63650,9 +63995,11 @@
         <v>0.46558283006825013</v>
       </c>
       <c r="DB260" s="38">
-        <v>0.20077222482016854</v>
-      </c>
-      <c r="DC260" s="9"/>
+        <v>0.19987022222690864</v>
+      </c>
+      <c r="DC260" s="38">
+        <v>0.16584085624979542</v>
+      </c>
       <c r="DD260" s="9"/>
       <c r="DE260" s="9"/>
       <c r="DF260" s="9"/>
@@ -64016,9 +64363,11 @@
         <v>0.22138298264123102</v>
       </c>
       <c r="DB261" s="38">
-        <v>0.14122979268013783</v>
-      </c>
-      <c r="DC261" s="9"/>
+        <v>0.14159095352469653</v>
+      </c>
+      <c r="DC261" s="38">
+        <v>6.7564927049136525E-2</v>
+      </c>
       <c r="DD261" s="9"/>
       <c r="DE261" s="9"/>
       <c r="DF261" s="9"/>
@@ -64382,9 +64731,11 @@
         <v>0.85869442960376019</v>
       </c>
       <c r="DB262" s="38">
-        <v>0.72306068479349994</v>
-      </c>
-      <c r="DC262" s="9"/>
+        <v>0.72522445842763106</v>
+      </c>
+      <c r="DC262" s="38">
+        <v>0.32499651412992253</v>
+      </c>
       <c r="DD262" s="9"/>
       <c r="DE262" s="9"/>
       <c r="DF262" s="9"/>
@@ -64748,9 +65099,11 @@
         <v>6.2177282574385329</v>
       </c>
       <c r="DB263" s="38">
-        <v>7.8101942916438505</v>
-      </c>
-      <c r="DC263" s="9"/>
+        <v>7.7834403361103757</v>
+      </c>
+      <c r="DC263" s="38">
+        <v>8.3918099599094038</v>
+      </c>
       <c r="DD263" s="9"/>
       <c r="DE263" s="9"/>
       <c r="DF263" s="9"/>
@@ -65114,9 +65467,11 @@
         <v>0.55274721454609288</v>
       </c>
       <c r="DB264" s="38">
-        <v>0.24569676904282076</v>
-      </c>
-      <c r="DC264" s="9"/>
+        <v>0.24523335732689736</v>
+      </c>
+      <c r="DC264" s="38">
+        <v>0.17535695387239825</v>
+      </c>
       <c r="DD264" s="9"/>
       <c r="DE264" s="9"/>
       <c r="DF264" s="9"/>
@@ -65480,9 +65835,11 @@
         <v>3.2099625655792186</v>
       </c>
       <c r="DB265" s="38">
-        <v>2.3929154723032924</v>
-      </c>
-      <c r="DC265" s="9"/>
+        <v>2.3746791327631147</v>
+      </c>
+      <c r="DC265" s="38">
+        <v>1.0140662479906499</v>
+      </c>
       <c r="DD265" s="9"/>
       <c r="DE265" s="9"/>
       <c r="DF265" s="9"/>
@@ -65846,9 +66203,11 @@
         <v>18.404593358553939</v>
       </c>
       <c r="DB266" s="38">
-        <v>19.432940908865749</v>
-      </c>
-      <c r="DC266" s="9"/>
+        <v>19.579341363814883</v>
+      </c>
+      <c r="DC266" s="38">
+        <v>15.860790727659833</v>
+      </c>
       <c r="DD266" s="9"/>
       <c r="DE266" s="9"/>
       <c r="DF266" s="9"/>
@@ -66212,9 +66571,11 @@
         <v>2.9737212914700968</v>
       </c>
       <c r="DB267" s="38">
-        <v>2.8316188245025313</v>
-      </c>
-      <c r="DC267" s="9"/>
+        <v>2.8367436225767531</v>
+      </c>
+      <c r="DC267" s="38">
+        <v>2.3886058793049449</v>
+      </c>
       <c r="DD267" s="9"/>
       <c r="DE267" s="9"/>
       <c r="DF267" s="9"/>
@@ -66578,9 +66939,11 @@
         <v>1.9055536008076757</v>
       </c>
       <c r="DB268" s="38">
-        <v>1.6686219920761667</v>
-      </c>
-      <c r="DC268" s="9"/>
+        <v>1.6835360011690437</v>
+      </c>
+      <c r="DC268" s="38">
+        <v>1.5213575571593447</v>
+      </c>
       <c r="DD268" s="9"/>
       <c r="DE268" s="9"/>
       <c r="DF268" s="9"/>
@@ -66944,9 +67307,11 @@
         <v>5.3155927542414254</v>
       </c>
       <c r="DB269" s="38">
-        <v>7.7003829983646233</v>
-      </c>
-      <c r="DC269" s="9"/>
+        <v>7.7984740730829536</v>
+      </c>
+      <c r="DC269" s="38">
+        <v>6.6927096875814165</v>
+      </c>
       <c r="DD269" s="9"/>
       <c r="DE269" s="9"/>
       <c r="DF269" s="9"/>
@@ -67310,9 +67675,11 @@
         <v>8.2097257120347411</v>
       </c>
       <c r="DB270" s="38">
-        <v>7.2323170939224273</v>
-      </c>
-      <c r="DC270" s="9"/>
+        <v>7.2605876669861331</v>
+      </c>
+      <c r="DC270" s="38">
+        <v>5.2581176036141253</v>
+      </c>
       <c r="DD270" s="9"/>
       <c r="DE270" s="9"/>
       <c r="DF270" s="9"/>
@@ -67676,9 +68043,11 @@
         <v>52.154352638986204</v>
       </c>
       <c r="DB271" s="38">
-        <v>47.707356727568659</v>
-      </c>
-      <c r="DC271" s="9"/>
+        <v>47.701781244904168</v>
+      </c>
+      <c r="DC271" s="38">
+        <v>42.334368488349114</v>
+      </c>
       <c r="DD271" s="9"/>
       <c r="DE271" s="9"/>
       <c r="DF271" s="9"/>
@@ -68042,9 +68411,11 @@
         <v>45.77604311799066</v>
       </c>
       <c r="DB272" s="38">
-        <v>43.732696814733465</v>
-      </c>
-      <c r="DC272" s="9"/>
+        <v>43.744460365740935</v>
+      </c>
+      <c r="DC272" s="38">
+        <v>40.5469912888015</v>
+      </c>
       <c r="DD272" s="9"/>
       <c r="DE272" s="9"/>
       <c r="DF272" s="9"/>
@@ -68408,9 +68779,11 @@
         <v>3.3839201566735908E-2</v>
       </c>
       <c r="DB273" s="38">
-        <v>4.5960876325890805E-2</v>
-      </c>
-      <c r="DC273" s="9"/>
+        <v>4.6937708757779244E-2</v>
+      </c>
+      <c r="DC273" s="38">
+        <v>2.9471931931094583E-2</v>
+      </c>
       <c r="DD273" s="9"/>
       <c r="DE273" s="9"/>
       <c r="DF273" s="9"/>
@@ -68774,9 +69147,11 @@
         <v>6.0412733837411263</v>
       </c>
       <c r="DB274" s="38">
-        <v>1.6163886228099063</v>
-      </c>
-      <c r="DC274" s="9"/>
+        <v>1.6099181755552947</v>
+      </c>
+      <c r="DC274" s="38">
+        <v>0.85545419568503689</v>
+      </c>
       <c r="DD274" s="9"/>
       <c r="DE274" s="9"/>
       <c r="DF274" s="9"/>
@@ -69140,9 +69515,11 @@
         <v>0.30319693568768252</v>
       </c>
       <c r="DB275" s="38">
-        <v>2.3123104136993931</v>
-      </c>
-      <c r="DC275" s="9"/>
+        <v>2.3004649948501648</v>
+      </c>
+      <c r="DC275" s="38">
+        <v>0.90245107193148577</v>
+      </c>
       <c r="DD275" s="9"/>
       <c r="DE275" s="9"/>
       <c r="DF275" s="9"/>
@@ -69506,9 +69883,11 @@
         <v>13.085354921599604</v>
       </c>
       <c r="DB276" s="38">
-        <v>18.802548212068434</v>
-      </c>
-      <c r="DC276" s="9"/>
+        <v>18.635718452573162</v>
+      </c>
+      <c r="DC276" s="38">
+        <v>30.650412309401919</v>
+      </c>
       <c r="DD276" s="9"/>
       <c r="DE276" s="9"/>
       <c r="DF276" s="9"/>
@@ -69872,9 +70251,11 @@
         <v>1.4023574113789203</v>
       </c>
       <c r="DB277" s="38">
-        <v>2.0327125859602022</v>
-      </c>
-      <c r="DC277" s="9"/>
+        <v>2.0675095418836085</v>
+      </c>
+      <c r="DC277" s="38">
+        <v>3.9313793736454596</v>
+      </c>
       <c r="DD277" s="9"/>
       <c r="DE277" s="9"/>
       <c r="DF277" s="9"/>
@@ -70238,9 +70619,11 @@
         <v>2.4099559847363037</v>
       </c>
       <c r="DB278" s="38">
-        <v>3.524063971731036</v>
-      </c>
-      <c r="DC278" s="9"/>
+        <v>3.5696106118779345</v>
+      </c>
+      <c r="DC278" s="38">
+        <v>6.8468295417014104</v>
+      </c>
       <c r="DD278" s="9"/>
       <c r="DE278" s="9"/>
       <c r="DF278" s="9"/>
@@ -70604,9 +70987,11 @@
         <v>6.727238770459147</v>
       </c>
       <c r="DB279" s="38">
-        <v>8.8775512172354745</v>
-      </c>
-      <c r="DC279" s="9"/>
+        <v>8.7930806365383702</v>
+      </c>
+      <c r="DC279" s="38">
+        <v>15.254449144673742</v>
+      </c>
       <c r="DD279" s="9"/>
       <c r="DE279" s="9"/>
       <c r="DF279" s="9"/>
@@ -70970,9 +71355,11 @@
         <v>2.5458027550252322</v>
       </c>
       <c r="DB280" s="38">
-        <v>4.3682204371417219</v>
-      </c>
-      <c r="DC280" s="9"/>
+        <v>4.2055176622732473</v>
+      </c>
+      <c r="DC280" s="38">
+        <v>4.6177542493813091</v>
+      </c>
       <c r="DD280" s="9"/>
       <c r="DE280" s="9"/>
       <c r="DF280" s="9"/>
@@ -71125,7 +71512,7 @@
       <c r="CZ281" s="31"/>
       <c r="DA281" s="31"/>
       <c r="DB281" s="31"/>
-      <c r="DC281" s="9"/>
+      <c r="DC281" s="31"/>
       <c r="DD281" s="9"/>
       <c r="DE281" s="9"/>
       <c r="DF281" s="9"/>
@@ -71491,7 +71878,9 @@
       <c r="DB282" s="38">
         <v>100</v>
       </c>
-      <c r="DC282" s="9"/>
+      <c r="DC282" s="38">
+        <v>100</v>
+      </c>
       <c r="DD282" s="9"/>
       <c r="DE282" s="9"/>
       <c r="DF282" s="9"/>
@@ -71645,6 +72034,7 @@
       <c r="CZ283" s="33"/>
       <c r="DA283" s="33"/>
       <c r="DB283" s="33"/>
+      <c r="DC283" s="33"/>
     </row>
     <row r="284" spans="1:152" x14ac:dyDescent="0.2">
       <c r="A284" s="15" t="s">
@@ -71663,6 +72053,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="CD132:CG132"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="CD254:CG254"/>
+    <mergeCell ref="CD213:CG213"/>
+    <mergeCell ref="CD172:CG172"/>
+    <mergeCell ref="CD50:CG50"/>
+    <mergeCell ref="CD91:CG91"/>
+    <mergeCell ref="BJ9:BM9"/>
+    <mergeCell ref="BN9:BQ9"/>
+    <mergeCell ref="BZ50:CC50"/>
+    <mergeCell ref="BV254:BY254"/>
+    <mergeCell ref="BN132:BQ132"/>
+    <mergeCell ref="BJ91:BM91"/>
+    <mergeCell ref="BN91:BQ91"/>
+    <mergeCell ref="BJ132:BM132"/>
+    <mergeCell ref="BJ172:BM172"/>
+    <mergeCell ref="BR132:BU132"/>
+    <mergeCell ref="BV132:BY132"/>
+    <mergeCell ref="BR50:BU50"/>
+    <mergeCell ref="BV50:BY50"/>
+    <mergeCell ref="BF254:BI254"/>
+    <mergeCell ref="BJ254:BM254"/>
+    <mergeCell ref="BN254:BQ254"/>
+    <mergeCell ref="BV9:BY9"/>
+    <mergeCell ref="BZ9:CC9"/>
+    <mergeCell ref="BR9:BU9"/>
+    <mergeCell ref="BR91:BU91"/>
+    <mergeCell ref="BV91:BY91"/>
+    <mergeCell ref="BR213:BU213"/>
+    <mergeCell ref="BV213:BY213"/>
+    <mergeCell ref="BZ213:CC213"/>
+    <mergeCell ref="BZ172:CC172"/>
+    <mergeCell ref="BR172:BU172"/>
+    <mergeCell ref="BV172:BY172"/>
+    <mergeCell ref="BZ91:CC91"/>
+    <mergeCell ref="BZ132:CC132"/>
+    <mergeCell ref="BF213:BI213"/>
+    <mergeCell ref="BJ213:BM213"/>
+    <mergeCell ref="BN213:BQ213"/>
+    <mergeCell ref="BJ50:BM50"/>
+    <mergeCell ref="BN50:BQ50"/>
+    <mergeCell ref="BN172:BQ172"/>
+    <mergeCell ref="BZ254:CC254"/>
+    <mergeCell ref="BR254:BU254"/>
+    <mergeCell ref="AX254:BA254"/>
+    <mergeCell ref="BB254:BE254"/>
+    <mergeCell ref="N213:Q213"/>
+    <mergeCell ref="R213:U213"/>
+    <mergeCell ref="V213:Y213"/>
+    <mergeCell ref="Z213:AC213"/>
+    <mergeCell ref="AD213:AG213"/>
+    <mergeCell ref="AH213:AK213"/>
+    <mergeCell ref="AL213:AO213"/>
+    <mergeCell ref="AL254:AO254"/>
+    <mergeCell ref="AP254:AS254"/>
+    <mergeCell ref="AT254:AW254"/>
+    <mergeCell ref="AL91:AO91"/>
+    <mergeCell ref="Z172:AC172"/>
+    <mergeCell ref="AD172:AG172"/>
+    <mergeCell ref="AH172:AK172"/>
+    <mergeCell ref="AP91:AS91"/>
+    <mergeCell ref="Z132:AC132"/>
+    <mergeCell ref="AD132:AG132"/>
+    <mergeCell ref="AH132:AK132"/>
+    <mergeCell ref="AL132:AO132"/>
+    <mergeCell ref="AL172:AO172"/>
+    <mergeCell ref="AP172:AS172"/>
+    <mergeCell ref="AD91:AG91"/>
+    <mergeCell ref="AH91:AK91"/>
+    <mergeCell ref="AT172:AW172"/>
+    <mergeCell ref="AX172:BA172"/>
+    <mergeCell ref="BB172:BE172"/>
+    <mergeCell ref="B132:E132"/>
+    <mergeCell ref="F132:I132"/>
+    <mergeCell ref="J132:M132"/>
+    <mergeCell ref="N132:Q132"/>
+    <mergeCell ref="R132:U132"/>
+    <mergeCell ref="V132:Y132"/>
+    <mergeCell ref="AX132:BA132"/>
+    <mergeCell ref="BB132:BE132"/>
+    <mergeCell ref="F254:I254"/>
+    <mergeCell ref="J254:M254"/>
+    <mergeCell ref="N254:Q254"/>
+    <mergeCell ref="R254:U254"/>
+    <mergeCell ref="V254:Y254"/>
+    <mergeCell ref="Z254:AC254"/>
+    <mergeCell ref="AD254:AG254"/>
+    <mergeCell ref="AH254:AK254"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="F213:I213"/>
+    <mergeCell ref="J213:M213"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="F172:I172"/>
+    <mergeCell ref="J172:M172"/>
+    <mergeCell ref="N172:Q172"/>
+    <mergeCell ref="R172:U172"/>
+    <mergeCell ref="V172:Y172"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="N91:Q91"/>
+    <mergeCell ref="R91:U91"/>
+    <mergeCell ref="V91:Y91"/>
+    <mergeCell ref="Z91:AC91"/>
+    <mergeCell ref="V50:Y50"/>
+    <mergeCell ref="Z50:AC50"/>
+    <mergeCell ref="AD50:AG50"/>
+    <mergeCell ref="AH50:AK50"/>
+    <mergeCell ref="AL50:AO50"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AH9:AK9"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="N50:Q50"/>
+    <mergeCell ref="R50:U50"/>
     <mergeCell ref="B254:E254"/>
     <mergeCell ref="AT50:AW50"/>
     <mergeCell ref="AX50:BA50"/>
@@ -71687,141 +72200,18 @@
     <mergeCell ref="BF91:BI91"/>
     <mergeCell ref="AX213:BA213"/>
     <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="N50:Q50"/>
-    <mergeCell ref="R50:U50"/>
-    <mergeCell ref="V50:Y50"/>
-    <mergeCell ref="Z50:AC50"/>
-    <mergeCell ref="AD50:AG50"/>
-    <mergeCell ref="AH50:AK50"/>
-    <mergeCell ref="AL50:AO50"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AH9:AK9"/>
-    <mergeCell ref="F254:I254"/>
-    <mergeCell ref="J254:M254"/>
-    <mergeCell ref="N254:Q254"/>
-    <mergeCell ref="R254:U254"/>
-    <mergeCell ref="V254:Y254"/>
-    <mergeCell ref="Z254:AC254"/>
-    <mergeCell ref="AD254:AG254"/>
-    <mergeCell ref="AH254:AK254"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B213:E213"/>
-    <mergeCell ref="F213:I213"/>
-    <mergeCell ref="J213:M213"/>
-    <mergeCell ref="B172:E172"/>
-    <mergeCell ref="F172:I172"/>
-    <mergeCell ref="J172:M172"/>
-    <mergeCell ref="N172:Q172"/>
-    <mergeCell ref="R172:U172"/>
-    <mergeCell ref="V172:Y172"/>
-    <mergeCell ref="F91:I91"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="N91:Q91"/>
-    <mergeCell ref="R91:U91"/>
-    <mergeCell ref="V91:Y91"/>
-    <mergeCell ref="Z91:AC91"/>
-    <mergeCell ref="AT172:AW172"/>
-    <mergeCell ref="AX172:BA172"/>
-    <mergeCell ref="BB172:BE172"/>
-    <mergeCell ref="B132:E132"/>
-    <mergeCell ref="F132:I132"/>
-    <mergeCell ref="J132:M132"/>
-    <mergeCell ref="N132:Q132"/>
-    <mergeCell ref="R132:U132"/>
-    <mergeCell ref="V132:Y132"/>
-    <mergeCell ref="AX132:BA132"/>
-    <mergeCell ref="BB132:BE132"/>
-    <mergeCell ref="AL91:AO91"/>
-    <mergeCell ref="Z172:AC172"/>
-    <mergeCell ref="AD172:AG172"/>
-    <mergeCell ref="AH172:AK172"/>
-    <mergeCell ref="AP91:AS91"/>
-    <mergeCell ref="Z132:AC132"/>
-    <mergeCell ref="AD132:AG132"/>
-    <mergeCell ref="AH132:AK132"/>
-    <mergeCell ref="AL132:AO132"/>
-    <mergeCell ref="AL172:AO172"/>
-    <mergeCell ref="AP172:AS172"/>
-    <mergeCell ref="AD91:AG91"/>
-    <mergeCell ref="AH91:AK91"/>
-    <mergeCell ref="AX254:BA254"/>
-    <mergeCell ref="BB254:BE254"/>
-    <mergeCell ref="N213:Q213"/>
-    <mergeCell ref="R213:U213"/>
-    <mergeCell ref="V213:Y213"/>
-    <mergeCell ref="Z213:AC213"/>
-    <mergeCell ref="AD213:AG213"/>
-    <mergeCell ref="AH213:AK213"/>
-    <mergeCell ref="AL213:AO213"/>
-    <mergeCell ref="AL254:AO254"/>
-    <mergeCell ref="AP254:AS254"/>
-    <mergeCell ref="AT254:AW254"/>
-    <mergeCell ref="BF254:BI254"/>
-    <mergeCell ref="BJ254:BM254"/>
-    <mergeCell ref="BN254:BQ254"/>
-    <mergeCell ref="BV9:BY9"/>
-    <mergeCell ref="BZ9:CC9"/>
-    <mergeCell ref="BR9:BU9"/>
-    <mergeCell ref="BR91:BU91"/>
-    <mergeCell ref="BV91:BY91"/>
-    <mergeCell ref="BR213:BU213"/>
-    <mergeCell ref="BV213:BY213"/>
-    <mergeCell ref="BZ213:CC213"/>
-    <mergeCell ref="BZ172:CC172"/>
-    <mergeCell ref="BR172:BU172"/>
-    <mergeCell ref="BV172:BY172"/>
-    <mergeCell ref="BZ91:CC91"/>
-    <mergeCell ref="BZ132:CC132"/>
-    <mergeCell ref="BF213:BI213"/>
-    <mergeCell ref="BJ213:BM213"/>
-    <mergeCell ref="BN213:BQ213"/>
-    <mergeCell ref="BJ50:BM50"/>
-    <mergeCell ref="BN50:BQ50"/>
-    <mergeCell ref="BN172:BQ172"/>
-    <mergeCell ref="BZ254:CC254"/>
-    <mergeCell ref="BR254:BU254"/>
-    <mergeCell ref="CD132:CG132"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="CD254:CG254"/>
-    <mergeCell ref="CD213:CG213"/>
-    <mergeCell ref="CD172:CG172"/>
-    <mergeCell ref="CD50:CG50"/>
-    <mergeCell ref="CD91:CG91"/>
-    <mergeCell ref="BJ9:BM9"/>
-    <mergeCell ref="BN9:BQ9"/>
-    <mergeCell ref="BZ50:CC50"/>
-    <mergeCell ref="BV254:BY254"/>
-    <mergeCell ref="BN132:BQ132"/>
-    <mergeCell ref="BJ91:BM91"/>
-    <mergeCell ref="BN91:BQ91"/>
-    <mergeCell ref="BJ132:BM132"/>
-    <mergeCell ref="BJ172:BM172"/>
-    <mergeCell ref="BR132:BU132"/>
-    <mergeCell ref="BV132:BY132"/>
-    <mergeCell ref="BR50:BU50"/>
-    <mergeCell ref="BV50:BY50"/>
   </mergeCells>
-  <conditionalFormatting sqref="CP94:CW109 CS110:CW110 CP111:CW111 CP112:CT112 CV112:CW112 CP113:CW119 CP135:CW150 CS151:CW151 CP152:CW152 CP153:CT153 CV153:CW153 CP154:CW160 CP175:DA200 CY135:DA160 CY94:DA119">
+  <conditionalFormatting sqref="CP94:CW109 CS110:CW110 CP111:CW111 CP112:CT112 CV112:CW112 CP113:CW119 CP135:CW150 CS151:CW151 CP152:CW152 CP153:CT153 CV153:CW153 CP154:CW160">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CP175:CW200">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DB94:DB119 DB135:DB160 DB175:DB200">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CX94:CX119 CX135:CX160">
+  <conditionalFormatting sqref="CX94:DC119 CX135:DC160 CX175:DC200">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
@@ -71830,12 +72220,12 @@
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="6" manualBreakCount="6">
-    <brk id="41" max="105" man="1"/>
-    <brk id="82" max="105" man="1"/>
-    <brk id="123" max="105" man="1"/>
-    <brk id="164" max="105" man="1"/>
-    <brk id="204" max="105" man="1"/>
-    <brk id="245" max="105" man="1"/>
+    <brk id="41" max="106" man="1"/>
+    <brk id="82" max="106" man="1"/>
+    <brk id="123" max="106" man="1"/>
+    <brk id="164" max="106" man="1"/>
+    <brk id="204" max="106" man="1"/>
+    <brk id="245" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>